--- a/src/utils/sxsyzlzq/zzz_cardList.xlsx
+++ b/src/utils/sxsyzlzq/zzz_cardList.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="2"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="伊萝莲" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="59">
   <si>
     <t>名称</t>
   </si>
@@ -158,9 +158,6 @@
     <t>方尖魔碑</t>
   </si>
   <si>
-    <t>精英射手</t>
-  </si>
-  <si>
     <t>观星台大预言家</t>
   </si>
   <si>
@@ -171,9 +168,6 @@
   </si>
   <si>
     <t>重装固守</t>
-  </si>
-  <si>
-    <t>苦行武僧</t>
   </si>
   <si>
     <t>执剑道人</t>
@@ -1302,7 +1296,7 @@
         <v>5</v>
       </c>
       <c r="D8" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1341,7 +1335,7 @@
       <c r="C12" s="1"/>
       <c r="D12" s="1">
         <f>AVERAGE(D2:D9)</f>
-        <v>15.5</v>
+        <v>15.625</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1591,7 +1585,7 @@
         <v>4</v>
       </c>
       <c r="D35" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -1700,7 +1694,7 @@
       <c r="C44" s="3"/>
       <c r="D44" s="3">
         <f>AVERAGE(D33:D41)</f>
-        <v>12.6666666666667</v>
+        <v>12.7777777777778</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1711,7 +1705,7 @@
       <c r="C47" s="5"/>
       <c r="D47" s="5">
         <f>AVERAGE(D12,D30,D44)</f>
-        <v>14.2094017094017</v>
+        <v>14.2881054131054</v>
       </c>
     </row>
   </sheetData>
@@ -1784,7 +1778,7 @@
         <v>2</v>
       </c>
       <c r="D4" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1845,7 +1839,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>5</v>
@@ -1854,7 +1848,7 @@
         <v>3</v>
       </c>
       <c r="D9" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1868,7 +1862,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1907,7 +1901,7 @@
       <c r="C14" s="1"/>
       <c r="D14" s="1">
         <f>AVERAGE(D2:D11)</f>
-        <v>15.4</v>
+        <v>15.7</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2038,7 +2032,7 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>15</v>
@@ -2246,7 +2240,7 @@
       </c>
       <c r="D47">
         <f>AVERAGE(D14,D32,D44)</f>
-        <v>13.9648351648352</v>
+        <v>14.0648351648352</v>
       </c>
     </row>
   </sheetData>
@@ -2282,7 +2276,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
@@ -2296,7 +2290,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>5</v>
@@ -2310,7 +2304,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>5</v>
@@ -2324,21 +2318,21 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" s="1">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>5</v>
@@ -2347,12 +2341,12 @@
         <v>3</v>
       </c>
       <c r="D6" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>5</v>
@@ -2361,12 +2355,12 @@
         <v>3</v>
       </c>
       <c r="D7" s="1">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>5</v>
@@ -2375,12 +2369,12 @@
         <v>3</v>
       </c>
       <c r="D8" s="1">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>5</v>
@@ -2389,12 +2383,12 @@
         <v>3</v>
       </c>
       <c r="D9" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>5</v>
@@ -2403,12 +2397,12 @@
         <v>3</v>
       </c>
       <c r="D10" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>5</v>
@@ -2422,21 +2416,21 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C12" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>5</v>
@@ -2445,21 +2439,21 @@
         <v>4</v>
       </c>
       <c r="D13" s="1">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D14" s="1">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2477,18 +2471,10 @@
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C16" s="1">
-        <v>5</v>
-      </c>
-      <c r="D16" s="1">
-        <v>15</v>
-      </c>
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="1"/>
@@ -2497,41 +2483,49 @@
       <c r="D17" s="1"/>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
+      <c r="A18" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1">
-        <f>AVERAGE(D2:D16)</f>
+      <c r="D18" s="1">
+        <f>AVERAGE(D2:D15)</f>
+        <v>14.1428571428571</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="2">
+        <v>2</v>
+      </c>
+      <c r="D21" s="2">
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="2">
+        <v>3</v>
+      </c>
+      <c r="D22" s="2">
         <v>14</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C22" s="2">
-        <v>2</v>
-      </c>
-      <c r="D22" s="2">
-        <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>15</v>
@@ -2545,7 +2539,7 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>15</v>
@@ -2559,21 +2553,21 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C25" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D25" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>15</v>
@@ -2582,26 +2576,26 @@
         <v>4</v>
       </c>
       <c r="D26" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C27" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D27" s="2">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>15</v>
@@ -2610,36 +2604,28 @@
         <v>5</v>
       </c>
       <c r="D28" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C29" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D29" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C30" s="2">
-        <v>6</v>
-      </c>
-      <c r="D30" s="2">
-        <v>15</v>
-      </c>
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2"/>
@@ -2648,41 +2634,49 @@
       <c r="D31" s="2"/>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="2"/>
-      <c r="B32" s="2"/>
+      <c r="A32" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2">
-        <f>AVERAGE(D22:D30)</f>
+      <c r="D32" s="2">
+        <f>AVERAGE(D21:D29)</f>
         <v>14</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C35" s="3">
+        <v>3</v>
+      </c>
+      <c r="D35" s="3">
+        <v>13</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C36" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D36" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="3" t="s">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>29</v>
@@ -2691,12 +2685,12 @@
         <v>4</v>
       </c>
       <c r="D37" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="3" t="s">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>29</v>
@@ -2705,32 +2699,32 @@
         <v>4</v>
       </c>
       <c r="D38" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C39" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D39" s="3">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C40" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D40" s="3">
         <v>13</v>
@@ -2771,8 +2765,8 @@
       </c>
       <c r="C44" s="3"/>
       <c r="D44" s="3">
-        <f>AVERAGE(D36:D41)</f>
-        <v>12.6666666666667</v>
+        <f>AVERAGE(D35:D41)</f>
+        <v>12.7142857142857</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2780,8 +2774,8 @@
         <v>39</v>
       </c>
       <c r="D47">
-        <f>AVERAGE(D19,D33,D44)</f>
-        <v>13.5555555555556</v>
+        <f>AVERAGE(D18,D32,D44)</f>
+        <v>13.6190476190476</v>
       </c>
     </row>
   </sheetData>
@@ -2831,7 +2825,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>5</v>
@@ -2845,7 +2839,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>5</v>
@@ -2859,13 +2853,13 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" s="1">
         <v>13</v>
@@ -2873,7 +2867,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>5</v>
@@ -2910,12 +2904,12 @@
         <v>3</v>
       </c>
       <c r="D8" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>5</v>
@@ -2929,7 +2923,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>5</v>
@@ -2938,12 +2932,12 @@
         <v>3</v>
       </c>
       <c r="D10" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>5</v>
@@ -2952,32 +2946,32 @@
         <v>3</v>
       </c>
       <c r="D11" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C12" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D12" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D13" s="1">
         <v>14</v>
@@ -2994,7 +2988,7 @@
         <v>5</v>
       </c>
       <c r="D14" s="1">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -3019,7 +3013,7 @@
       <c r="C17" s="1"/>
       <c r="D17" s="1">
         <f>AVERAGE(D2:D14)</f>
-        <v>14.3846153846154</v>
+        <v>14.5384615384615</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -3052,7 +3046,7 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>15</v>
@@ -3066,7 +3060,7 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>15</v>
@@ -3094,7 +3088,7 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>15</v>
@@ -3136,7 +3130,7 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>15</v>
@@ -3217,7 +3211,7 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>29</v>
@@ -3316,7 +3310,7 @@
       </c>
       <c r="D47">
         <f>AVERAGE(D17,D32,D44)</f>
-        <v>13.7996336996337</v>
+        <v>13.8509157509157</v>
       </c>
     </row>
   </sheetData>

--- a/src/utils/sxsyzlzq/zzz_cardList.xlsx
+++ b/src/utils/sxsyzlzq/zzz_cardList.xlsx
@@ -1240,7 +1240,7 @@
         <v>2</v>
       </c>
       <c r="D4" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1335,7 +1335,7 @@
       <c r="C12" s="1"/>
       <c r="D12" s="1">
         <f>AVERAGE(D2:D9)</f>
-        <v>15.625</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1419,7 +1419,7 @@
         <v>3</v>
       </c>
       <c r="D20" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1543,7 +1543,7 @@
       <c r="C30" s="2"/>
       <c r="D30" s="2">
         <f>AVERAGE(D15:D27)</f>
-        <v>14.4615384615385</v>
+        <v>14.5384615384615</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -1599,7 +1599,7 @@
         <v>4</v>
       </c>
       <c r="D36" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1694,7 +1694,7 @@
       <c r="C44" s="3"/>
       <c r="D44" s="3">
         <f>AVERAGE(D33:D41)</f>
-        <v>12.7777777777778</v>
+        <v>12.8888888888889</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1705,7 +1705,7 @@
       <c r="C47" s="5"/>
       <c r="D47" s="5">
         <f>AVERAGE(D12,D30,D44)</f>
-        <v>14.2881054131054</v>
+        <v>14.3924501424501</v>
       </c>
     </row>
   </sheetData>
@@ -1806,7 +1806,7 @@
         <v>2</v>
       </c>
       <c r="D6" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1901,7 +1901,7 @@
       <c r="C14" s="1"/>
       <c r="D14" s="1">
         <f>AVERAGE(D2:D11)</f>
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1985,7 +1985,7 @@
         <v>3</v>
       </c>
       <c r="D22" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2108,7 +2108,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2">
         <f>AVERAGE(D17:D29)</f>
-        <v>13.9230769230769</v>
+        <v>14</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2164,7 +2164,7 @@
         <v>4</v>
       </c>
       <c r="D38" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2231,7 +2231,7 @@
       <c r="C44" s="3"/>
       <c r="D44" s="3">
         <f>AVERAGE(D35:D41)</f>
-        <v>12.5714285714286</v>
+        <v>12.7142857142857</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2240,7 +2240,7 @@
       </c>
       <c r="D47">
         <f>AVERAGE(D14,D32,D44)</f>
-        <v>14.0648351648352</v>
+        <v>14.1714285714286</v>
       </c>
     </row>
   </sheetData>
@@ -2548,7 +2548,7 @@
         <v>3</v>
       </c>
       <c r="D24" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2643,7 +2643,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2">
         <f>AVERAGE(D21:D29)</f>
-        <v>14</v>
+        <v>14.1111111111111</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2699,7 +2699,7 @@
         <v>4</v>
       </c>
       <c r="D38" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2766,7 +2766,7 @@
       <c r="C44" s="3"/>
       <c r="D44" s="3">
         <f>AVERAGE(D35:D41)</f>
-        <v>12.7142857142857</v>
+        <v>12.8571428571429</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="D47">
         <f>AVERAGE(D18,D32,D44)</f>
-        <v>13.6190476190476</v>
+        <v>13.7037037037037</v>
       </c>
     </row>
   </sheetData>
@@ -3083,7 +3083,7 @@
         <v>3</v>
       </c>
       <c r="D24" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -3178,7 +3178,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2">
         <f>AVERAGE(D20:D29)</f>
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -3234,7 +3234,7 @@
         <v>4</v>
       </c>
       <c r="D38" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -3301,7 +3301,7 @@
       <c r="C44" s="3"/>
       <c r="D44" s="3">
         <f>AVERAGE(D35:D41)</f>
-        <v>12.7142857142857</v>
+        <v>12.8571428571429</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="D47">
         <f>AVERAGE(D17,D32,D44)</f>
-        <v>13.8509157509157</v>
+        <v>13.9318681318681</v>
       </c>
     </row>
   </sheetData>

--- a/src/utils/sxsyzlzq/zzz_cardList.xlsx
+++ b/src/utils/sxsyzlzq/zzz_cardList.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="1"/>
+    <workbookView windowWidth="24345" windowHeight="12345" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="伊萝莲" sheetId="1" r:id="rId1"/>
@@ -12,25 +12,12 @@
     <sheet name="梅" sheetId="3" r:id="rId3"/>
     <sheet name="白处尊" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="57">
   <si>
     <t>名称</t>
   </si>
@@ -101,123 +88,117 @@
     <t>召集护卫</t>
   </si>
   <si>
+    <t>观星台大预言家</t>
+  </si>
+  <si>
+    <t>惩戒天使</t>
+  </si>
+  <si>
+    <t>禁卫指挥官</t>
+  </si>
+  <si>
+    <t>米拉方舟</t>
+  </si>
+  <si>
+    <t>紫色卡等：</t>
+  </si>
+  <si>
+    <t>花光春影·安娜贝尔</t>
+  </si>
+  <si>
+    <t>橙色</t>
+  </si>
+  <si>
+    <t>百花长枪·卡罗琳</t>
+  </si>
+  <si>
+    <t>明日香·露娜</t>
+  </si>
+  <si>
+    <t>永恒之王·莱哈特</t>
+  </si>
+  <si>
+    <t>月之神·米拉</t>
+  </si>
+  <si>
+    <t>白袍·伊恩</t>
+  </si>
+  <si>
+    <t>火蛇巫女·沃凡瑞拉</t>
+  </si>
+  <si>
+    <t>武圣·云长</t>
+  </si>
+  <si>
+    <t>橙色卡等：</t>
+  </si>
+  <si>
+    <t>总计：</t>
+  </si>
+  <si>
+    <t>学仆-观测型</t>
+  </si>
+  <si>
+    <t>卜命道长</t>
+  </si>
+  <si>
+    <t>旅行背包</t>
+  </si>
+  <si>
+    <t>重装固守</t>
+  </si>
+  <si>
+    <t>执剑道人</t>
+  </si>
+  <si>
+    <t>连击</t>
+  </si>
+  <si>
+    <t>龟族僧人</t>
+  </si>
+  <si>
+    <t>深山采药人</t>
+  </si>
+  <si>
+    <t>叶幻师</t>
+  </si>
+  <si>
+    <t>风卷残云</t>
+  </si>
+  <si>
+    <t>祥云师太</t>
+  </si>
+  <si>
+    <t>驱魔道人</t>
+  </si>
+  <si>
+    <t>扫叶僧</t>
+  </si>
+  <si>
+    <t>御风武者</t>
+  </si>
+  <si>
+    <t>蟠桃会</t>
+  </si>
+  <si>
+    <t>万物之灵</t>
+  </si>
+  <si>
+    <t>上宝沁金耙</t>
+  </si>
+  <si>
     <t>禁卫百夫长</t>
-  </si>
-  <si>
-    <t>惩戒天使</t>
-  </si>
-  <si>
-    <t>禁卫指挥官</t>
-  </si>
-  <si>
-    <t>米拉方舟</t>
-  </si>
-  <si>
-    <t>紫色卡等：</t>
-  </si>
-  <si>
-    <t>花光春影·安娜贝尔</t>
-  </si>
-  <si>
-    <t>橙色</t>
-  </si>
-  <si>
-    <t>百花长枪·卡罗琳</t>
-  </si>
-  <si>
-    <t>流星-7号</t>
-  </si>
-  <si>
-    <t>明日香·露娜</t>
-  </si>
-  <si>
-    <t>永恒之王·莱哈特</t>
-  </si>
-  <si>
-    <t>月之神·米拉</t>
-  </si>
-  <si>
-    <t>白袍·伊恩</t>
-  </si>
-  <si>
-    <t>火蛇巫女·沃凡瑞拉</t>
-  </si>
-  <si>
-    <t>武圣·云长</t>
-  </si>
-  <si>
-    <t>橙色卡等：</t>
-  </si>
-  <si>
-    <t>总计：</t>
-  </si>
-  <si>
-    <t>学仆-观测型</t>
-  </si>
-  <si>
-    <t>方尖魔碑</t>
-  </si>
-  <si>
-    <t>观星台大预言家</t>
-  </si>
-  <si>
-    <t>卜命道长</t>
-  </si>
-  <si>
-    <t>旅行背包</t>
-  </si>
-  <si>
-    <t>重装固守</t>
-  </si>
-  <si>
-    <t>执剑道人</t>
-  </si>
-  <si>
-    <t>连击</t>
-  </si>
-  <si>
-    <t>龟族僧人</t>
-  </si>
-  <si>
-    <t>深山采药人</t>
-  </si>
-  <si>
-    <t>叶幻师</t>
-  </si>
-  <si>
-    <t>风卷残云</t>
-  </si>
-  <si>
-    <t>祥云师太</t>
-  </si>
-  <si>
-    <t>驱魔道人</t>
-  </si>
-  <si>
-    <t>扫叶僧</t>
-  </si>
-  <si>
-    <t>御风武者</t>
-  </si>
-  <si>
-    <t>泰山之力</t>
-  </si>
-  <si>
-    <t>万物之灵</t>
-  </si>
-  <si>
-    <t>上宝沁金耙</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -264,11 +245,124 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -286,119 +380,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -409,7 +390,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -421,7 +480,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -433,13 +492,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -451,31 +546,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -487,109 +570,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -600,6 +581,30 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -618,39 +623,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -662,6 +634,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -683,15 +664,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -700,153 +672,162 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -872,52 +853,52 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -1231,7 +1212,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>5</v>
@@ -1245,7 +1226,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>5</v>
@@ -1254,26 +1235,26 @@
         <v>2</v>
       </c>
       <c r="D5" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" s="1">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>5</v>
@@ -1282,18 +1263,18 @@
         <v>3</v>
       </c>
       <c r="D7" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D8" s="1">
         <v>16</v>
@@ -1310,14 +1291,22 @@
         <v>5</v>
       </c>
       <c r="D9" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
+      <c r="A10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="1">
+        <v>5</v>
+      </c>
+      <c r="D10" s="1">
+        <v>15</v>
+      </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1"/>
@@ -1326,35 +1315,27 @@
       <c r="D11" s="1"/>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1">
-        <f>AVERAGE(D2:D9)</f>
-        <v>15.75</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="2">
-        <v>2</v>
-      </c>
-      <c r="D15" s="2">
-        <v>17</v>
+      <c r="B13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1">
+        <f>AVERAGE(D2:D10)</f>
+        <v>15.5555555555556</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>15</v>
@@ -1363,12 +1344,12 @@
         <v>2</v>
       </c>
       <c r="D16" s="2">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>15</v>
@@ -1377,26 +1358,26 @@
         <v>2</v>
       </c>
       <c r="D17" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C18" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D18" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>15</v>
@@ -1405,12 +1386,12 @@
         <v>3</v>
       </c>
       <c r="D19" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>15</v>
@@ -1433,18 +1414,18 @@
         <v>3</v>
       </c>
       <c r="D21" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C22" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D22" s="2">
         <v>14</v>
@@ -1452,7 +1433,7 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>15</v>
@@ -1461,40 +1442,40 @@
         <v>4</v>
       </c>
       <c r="D23" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C24" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D24" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C25" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D25" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>15</v>
@@ -1503,29 +1484,37 @@
         <v>6</v>
       </c>
       <c r="D26" s="2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
       <c r="A27" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" s="2">
+        <v>6</v>
+      </c>
+      <c r="D27" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C27" s="2">
+      <c r="B28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C28" s="2">
         <v>7</v>
       </c>
-      <c r="D27" s="2">
+      <c r="D28" s="2">
         <v>14</v>
       </c>
-      <c r="F27" s="4"/>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
+      <c r="F28" s="4"/>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2"/>
@@ -1534,49 +1523,41 @@
       <c r="D29" s="2"/>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B31" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2">
-        <f>AVERAGE(D15:D27)</f>
-        <v>14.5384615384615</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C33" s="3">
-        <v>3</v>
-      </c>
-      <c r="D33" s="3">
-        <v>13</v>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2">
+        <f>AVERAGE(D16:D28)</f>
+        <v>14.4615384615385</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C34" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D34" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>29</v>
@@ -1590,7 +1571,7 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>29</v>
@@ -1604,7 +1585,7 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>29</v>
@@ -1613,12 +1594,12 @@
         <v>5</v>
       </c>
       <c r="D37" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>29</v>
@@ -1632,7 +1613,7 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>29</v>
@@ -1646,7 +1627,7 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>29</v>
@@ -1660,7 +1641,7 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>29</v>
@@ -1689,23 +1670,23 @@
         <v>12</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C44" s="3"/>
       <c r="D44" s="3">
-        <f>AVERAGE(D33:D41)</f>
-        <v>12.8888888888889</v>
+        <f>AVERAGE(D34:D41)</f>
+        <v>12.875</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
       <c r="D47" s="5">
-        <f>AVERAGE(D12,D30,D44)</f>
-        <v>14.3924501424501</v>
+        <f>AVERAGE(D13,D31,D44)</f>
+        <v>14.2973646723647</v>
       </c>
     </row>
   </sheetData>
@@ -1755,7 +1736,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>5</v>
@@ -1769,7 +1750,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>5</v>
@@ -1783,7 +1764,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>5</v>
@@ -1797,7 +1778,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>5</v>
@@ -1806,7 +1787,7 @@
         <v>2</v>
       </c>
       <c r="D6" s="1">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1820,7 +1801,7 @@
         <v>2</v>
       </c>
       <c r="D7" s="1">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1901,7 +1882,7 @@
       <c r="C14" s="1"/>
       <c r="D14" s="1">
         <f>AVERAGE(D2:D11)</f>
-        <v>15.8</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1929,7 +1910,7 @@
         <v>2</v>
       </c>
       <c r="D18" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1985,7 +1966,7 @@
         <v>3</v>
       </c>
       <c r="D22" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2013,7 +1994,7 @@
         <v>4</v>
       </c>
       <c r="D24" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2032,7 +2013,7 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>15</v>
@@ -2046,21 +2027,21 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C27" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D27" s="2">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>15</v>
@@ -2069,28 +2050,36 @@
         <v>6</v>
       </c>
       <c r="D28" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C29" s="2">
+        <v>6</v>
+      </c>
+      <c r="D29" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C29" s="2">
+      <c r="B30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="2">
         <v>7</v>
       </c>
-      <c r="D29" s="2">
+      <c r="D30" s="2">
         <v>14</v>
       </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2"/>
@@ -2099,49 +2088,41 @@
       <c r="D31" s="2"/>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B33" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2">
-        <f>AVERAGE(D17:D29)</f>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C35" s="3">
-        <v>3</v>
-      </c>
-      <c r="D35" s="3">
-        <v>13</v>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2">
+        <f>AVERAGE(D17:D30)</f>
+        <v>13.9285714285714</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C36" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D36" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>29</v>
@@ -2150,12 +2131,12 @@
         <v>4</v>
       </c>
       <c r="D37" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>29</v>
@@ -2169,7 +2150,7 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>29</v>
@@ -2183,7 +2164,7 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>29</v>
@@ -2197,7 +2178,7 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>29</v>
@@ -2226,21 +2207,21 @@
         <v>12</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C44" s="3"/>
       <c r="D44" s="3">
-        <f>AVERAGE(D35:D41)</f>
-        <v>12.7142857142857</v>
+        <f>AVERAGE(D36:D41)</f>
+        <v>12.6666666666667</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D47">
-        <f>AVERAGE(D14,D32,D44)</f>
-        <v>14.1714285714286</v>
+        <f>AVERAGE(D14,D33,D44)</f>
+        <v>13.9650793650794</v>
       </c>
     </row>
   </sheetData>
@@ -2276,7 +2257,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
@@ -2285,12 +2266,12 @@
         <v>1</v>
       </c>
       <c r="D2" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>5</v>
@@ -2299,12 +2280,12 @@
         <v>1</v>
       </c>
       <c r="D3" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>5</v>
@@ -2318,21 +2299,21 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D5" s="1">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>5</v>
@@ -2341,12 +2322,12 @@
         <v>3</v>
       </c>
       <c r="D6" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>5</v>
@@ -2355,12 +2336,12 @@
         <v>3</v>
       </c>
       <c r="D7" s="1">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>5</v>
@@ -2369,12 +2350,12 @@
         <v>3</v>
       </c>
       <c r="D8" s="1">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>5</v>
@@ -2383,12 +2364,12 @@
         <v>3</v>
       </c>
       <c r="D9" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>5</v>
@@ -2397,12 +2378,12 @@
         <v>3</v>
       </c>
       <c r="D10" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>5</v>
@@ -2416,21 +2397,21 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C12" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D12" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>5</v>
@@ -2439,21 +2420,21 @@
         <v>4</v>
       </c>
       <c r="D13" s="1">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D14" s="1">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2467,14 +2448,22 @@
         <v>5</v>
       </c>
       <c r="D15" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
+      <c r="A16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="1">
+        <v>5</v>
+      </c>
+      <c r="D16" s="1">
+        <v>15</v>
+      </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="1"/>
@@ -2483,49 +2472,41 @@
       <c r="D17" s="1"/>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1">
-        <f>AVERAGE(D2:D15)</f>
-        <v>14.1428571428571</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C21" s="2">
-        <v>2</v>
-      </c>
-      <c r="D21" s="2">
-        <v>17</v>
+      <c r="B19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1">
+        <f>AVERAGE(D2:D16)</f>
+        <v>14.2</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C22" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D22" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>15</v>
@@ -2539,7 +2520,7 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>15</v>
@@ -2548,26 +2529,26 @@
         <v>3</v>
       </c>
       <c r="D24" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C25" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D25" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>15</v>
@@ -2576,26 +2557,26 @@
         <v>4</v>
       </c>
       <c r="D26" s="2">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C27" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D27" s="2">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>15</v>
@@ -2604,7 +2585,7 @@
         <v>5</v>
       </c>
       <c r="D28" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2642,8 +2623,8 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2">
-        <f>AVERAGE(D21:D29)</f>
-        <v>14.1111111111111</v>
+        <f>AVERAGE(D22:D29)</f>
+        <v>14</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2676,7 +2657,7 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>29</v>
@@ -2690,7 +2671,7 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>29</v>
@@ -2704,7 +2685,7 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>29</v>
@@ -2713,12 +2694,12 @@
         <v>5</v>
       </c>
       <c r="D39" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>29</v>
@@ -2732,7 +2713,7 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>29</v>
@@ -2761,21 +2742,21 @@
         <v>12</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C44" s="3"/>
       <c r="D44" s="3">
         <f>AVERAGE(D35:D41)</f>
-        <v>12.8571428571429</v>
+        <v>13</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D47">
-        <f>AVERAGE(D18,D32,D44)</f>
-        <v>13.7037037037037</v>
+        <f>AVERAGE(D19,D32,D44)</f>
+        <v>13.7333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -2825,7 +2806,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>5</v>
@@ -2839,7 +2820,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>5</v>
@@ -2853,7 +2834,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>5</v>
@@ -2867,7 +2848,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>5</v>
@@ -2909,7 +2890,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>5</v>
@@ -2923,7 +2904,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>5</v>
@@ -2937,7 +2918,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>5</v>
@@ -2951,7 +2932,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>5</v>
@@ -2965,7 +2946,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>5</v>
@@ -3046,7 +3027,7 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>15</v>
@@ -3060,7 +3041,7 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>15</v>
@@ -3088,7 +3069,7 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>15</v>
@@ -3116,7 +3097,7 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>15</v>
@@ -3130,7 +3111,7 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>15</v>
@@ -3211,7 +3192,7 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>29</v>
@@ -3225,7 +3206,7 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>29</v>
@@ -3239,7 +3220,7 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>29</v>
@@ -3253,7 +3234,7 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>29</v>
@@ -3267,7 +3248,7 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>29</v>
@@ -3296,7 +3277,7 @@
         <v>12</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C44" s="3"/>
       <c r="D44" s="3">
@@ -3306,7 +3287,7 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D47">
         <f>AVERAGE(D17,D32,D44)</f>

--- a/src/utils/sxsyzlzq/zzz_cardList.xlsx
+++ b/src/utils/sxsyzlzq/zzz_cardList.xlsx
@@ -4,20 +4,24 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24345" windowHeight="12345" activeTab="2"/>
+    <workbookView windowWidth="28245" windowHeight="12345" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="伊萝莲" sheetId="1" r:id="rId1"/>
     <sheet name="阿斯塔拉" sheetId="2" r:id="rId2"/>
     <sheet name="梅" sheetId="3" r:id="rId3"/>
     <sheet name="白处尊" sheetId="4" r:id="rId4"/>
+    <sheet name="帝国" sheetId="5" r:id="rId5"/>
+    <sheet name="隐秘" sheetId="6" r:id="rId6"/>
+    <sheet name="禅意" sheetId="7" r:id="rId7"/>
+    <sheet name="炼狱" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="82">
   <si>
     <t>名称</t>
   </si>
@@ -188,6 +192,81 @@
   </si>
   <si>
     <t>禁卫百夫长</t>
+  </si>
+  <si>
+    <t>曙光·安娜贝尔</t>
+  </si>
+  <si>
+    <t>圣枪·卡罗琳</t>
+  </si>
+  <si>
+    <t>明日之音·露娜</t>
+  </si>
+  <si>
+    <t>帝国军魂·莱哈特</t>
+  </si>
+  <si>
+    <t>正阳大主教·伊恩</t>
+  </si>
+  <si>
+    <t>钢铁统帅·雷蒙德</t>
+  </si>
+  <si>
+    <t>帝国卡等：</t>
+  </si>
+  <si>
+    <t>No.2时光·米拉</t>
+  </si>
+  <si>
+    <t>No.6沃凡瑞拉</t>
+  </si>
+  <si>
+    <t>执剑道者</t>
+  </si>
+  <si>
+    <t>悟能禅杖</t>
+  </si>
+  <si>
+    <t>冥河守卫</t>
+  </si>
+  <si>
+    <t>落雷击</t>
+  </si>
+  <si>
+    <t>邪眼魔</t>
+  </si>
+  <si>
+    <t>残暴爪钩</t>
+  </si>
+  <si>
+    <t>狂暴炎球</t>
+  </si>
+  <si>
+    <t>烈焰风暴</t>
+  </si>
+  <si>
+    <t>碎颅魔</t>
+  </si>
+  <si>
+    <t>觅食大嘴兽</t>
+  </si>
+  <si>
+    <t>绝望镰魔</t>
+  </si>
+  <si>
+    <t>岩浆球</t>
+  </si>
+  <si>
+    <t>灼神双炎</t>
+  </si>
+  <si>
+    <t>雷光炼狱</t>
+  </si>
+  <si>
+    <t>地狱屠夫</t>
+  </si>
+  <si>
+    <t>痛苦之心</t>
   </si>
 </sst>
 </file>
@@ -195,10 +274,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -237,9 +316,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -252,23 +337,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -284,9 +354,25 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -304,8 +390,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -313,7 +422,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -336,48 +445,18 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -390,7 +469,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -402,43 +577,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -450,37 +595,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -492,49 +607,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -552,25 +631,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -581,6 +660,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -595,6 +683,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -623,26 +726,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -672,15 +760,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -689,10 +768,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -701,153 +780,162 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1334,359 +1422,359 @@
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" s="2">
+      <c r="B16" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="3">
         <v>2</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="3">
         <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" s="2">
+      <c r="B17" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="3">
         <v>2</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="3">
         <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18" s="2">
+      <c r="B18" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="3">
         <v>2</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18" s="3">
         <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="2">
-        <v>3</v>
-      </c>
-      <c r="D19" s="2">
+      <c r="B19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="3">
+        <v>3</v>
+      </c>
+      <c r="D19" s="3">
         <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="2">
-        <v>3</v>
-      </c>
-      <c r="D20" s="2">
+      <c r="B20" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="3">
+        <v>3</v>
+      </c>
+      <c r="D20" s="3">
         <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C21" s="2">
-        <v>3</v>
-      </c>
-      <c r="D21" s="2">
+      <c r="B21" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="3">
+        <v>3</v>
+      </c>
+      <c r="D21" s="3">
         <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C22" s="2">
-        <v>3</v>
-      </c>
-      <c r="D22" s="2">
+      <c r="B22" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="3">
+        <v>3</v>
+      </c>
+      <c r="D22" s="3">
         <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C23" s="2">
+      <c r="B23" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="3">
         <v>4</v>
       </c>
-      <c r="D23" s="2">
+      <c r="D23" s="3">
         <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C24" s="2">
+      <c r="B24" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" s="3">
         <v>4</v>
       </c>
-      <c r="D24" s="2">
+      <c r="D24" s="3">
         <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C25" s="2">
-        <v>5</v>
-      </c>
-      <c r="D25" s="2">
+      <c r="B25" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" s="3">
+        <v>5</v>
+      </c>
+      <c r="D25" s="3">
         <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C26" s="2">
+      <c r="B26" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="3">
         <v>6</v>
       </c>
-      <c r="D26" s="2">
+      <c r="D26" s="3">
         <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C27" s="2">
+      <c r="B27" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" s="3">
         <v>6</v>
       </c>
-      <c r="D27" s="2">
+      <c r="D27" s="3">
         <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:6">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C28" s="2">
+      <c r="B28" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C28" s="3">
         <v>7</v>
       </c>
-      <c r="D28" s="2">
+      <c r="D28" s="3">
         <v>14</v>
       </c>
-      <c r="F28" s="4"/>
+      <c r="F28" s="8"/>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B31" s="2" t="s">
+      <c r="A31" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2">
+      <c r="C31" s="3"/>
+      <c r="D31" s="3">
         <f>AVERAGE(D16:D28)</f>
         <v>14.4615384615385</v>
       </c>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="3" t="s">
+      <c r="A34" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C34" s="3">
-        <v>3</v>
-      </c>
-      <c r="D34" s="3">
+      <c r="C34" s="5">
+        <v>3</v>
+      </c>
+      <c r="D34" s="5">
         <v>13</v>
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="3" t="s">
+      <c r="A35" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C35" s="3">
+      <c r="C35" s="5">
         <v>4</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="5">
         <v>14</v>
       </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="3" t="s">
+      <c r="A36" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C36" s="3">
+      <c r="C36" s="5">
         <v>4</v>
       </c>
-      <c r="D36" s="3">
+      <c r="D36" s="5">
         <v>12</v>
       </c>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="3" t="s">
+      <c r="A37" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C37" s="3">
-        <v>5</v>
-      </c>
-      <c r="D37" s="3">
+      <c r="C37" s="5">
+        <v>5</v>
+      </c>
+      <c r="D37" s="5">
         <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="3" t="s">
+      <c r="A38" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C38" s="3">
-        <v>5</v>
-      </c>
-      <c r="D38" s="3">
+      <c r="C38" s="5">
+        <v>5</v>
+      </c>
+      <c r="D38" s="5">
         <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="3" t="s">
+      <c r="A39" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C39" s="3">
+      <c r="C39" s="5">
         <v>6</v>
       </c>
-      <c r="D39" s="3">
+      <c r="D39" s="5">
         <v>13</v>
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="3" t="s">
+      <c r="A40" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B40" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C40" s="3">
+      <c r="C40" s="5">
         <v>7</v>
       </c>
-      <c r="D40" s="3">
+      <c r="D40" s="5">
         <v>12</v>
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="3" t="s">
+      <c r="A41" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B41" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C41" s="3">
+      <c r="C41" s="5">
         <v>8</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="5">
         <v>13</v>
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="3"/>
-      <c r="B42" s="3"/>
-      <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
+      <c r="A42" s="5"/>
+      <c r="B42" s="5"/>
+      <c r="C42" s="5"/>
+      <c r="D42" s="5"/>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="3"/>
-      <c r="B43" s="3"/>
-      <c r="C43" s="3"/>
-      <c r="D43" s="3"/>
+      <c r="A43" s="5"/>
+      <c r="B43" s="5"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="5"/>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B44" s="3" t="s">
+      <c r="A44" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B44" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C44" s="3"/>
-      <c r="D44" s="3">
+      <c r="C44" s="5"/>
+      <c r="D44" s="5">
         <f>AVERAGE(D34:D41)</f>
         <v>12.875</v>
       </c>
     </row>
     <row r="47" spans="1:4">
-      <c r="A47" s="5" t="s">
+      <c r="A47" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B47" s="5"/>
-      <c r="C47" s="5"/>
-      <c r="D47" s="5">
-        <f>AVERAGE(D13,D31,D44)</f>
-        <v>14.2973646723647</v>
+      <c r="B47" s="7"/>
+      <c r="C47" s="7"/>
+      <c r="D47" s="7">
+        <f>AVERAGE(D2:D10,D16:D28,D34:D41)</f>
+        <v>14.3666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -1886,331 +1974,331 @@
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" s="2">
+      <c r="B17" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="3">
         <v>2</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="3">
         <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18" s="2">
+      <c r="B18" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="3">
         <v>2</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18" s="3">
         <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="2">
+      <c r="B19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="3">
         <v>2</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19" s="3">
         <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="2">
+      <c r="B20" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="3">
         <v>2</v>
       </c>
-      <c r="D20" s="2">
+      <c r="D20" s="3">
         <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C21" s="2">
-        <v>3</v>
-      </c>
-      <c r="D21" s="2">
+      <c r="B21" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="3">
+        <v>3</v>
+      </c>
+      <c r="D21" s="3">
         <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C22" s="2">
-        <v>3</v>
-      </c>
-      <c r="D22" s="2">
+      <c r="B22" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="3">
+        <v>3</v>
+      </c>
+      <c r="D22" s="3">
         <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C23" s="2">
-        <v>3</v>
-      </c>
-      <c r="D23" s="2">
+      <c r="B23" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="3">
+        <v>3</v>
+      </c>
+      <c r="D23" s="3">
         <v>14</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C24" s="2">
+      <c r="B24" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" s="3">
         <v>4</v>
       </c>
-      <c r="D24" s="2">
+      <c r="D24" s="3">
         <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C25" s="2">
+      <c r="B25" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" s="3">
         <v>4</v>
       </c>
-      <c r="D25" s="2">
+      <c r="D25" s="3">
         <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C26" s="2">
-        <v>5</v>
-      </c>
-      <c r="D26" s="2">
+      <c r="B26" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="3">
+        <v>5</v>
+      </c>
+      <c r="D26" s="3">
         <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C27" s="2">
-        <v>5</v>
-      </c>
-      <c r="D27" s="2">
-        <v>10</v>
+      <c r="B27" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" s="3">
+        <v>5</v>
+      </c>
+      <c r="D27" s="3">
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C28" s="2">
+      <c r="B28" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C28" s="3">
         <v>6</v>
       </c>
-      <c r="D28" s="2">
+      <c r="D28" s="3">
         <v>14</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C29" s="2">
+      <c r="B29" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C29" s="3">
         <v>6</v>
       </c>
-      <c r="D29" s="2">
+      <c r="D29" s="3">
         <v>15</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C30" s="2">
+      <c r="B30" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="3">
         <v>7</v>
       </c>
-      <c r="D30" s="2">
+      <c r="D30" s="3">
         <v>14</v>
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="2"/>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
+      <c r="A32" s="3"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B33" s="2" t="s">
+      <c r="A33" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2">
+      <c r="C33" s="3"/>
+      <c r="D33" s="3">
         <f>AVERAGE(D17:D30)</f>
-        <v>13.9285714285714</v>
+        <v>14</v>
       </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="3" t="s">
+      <c r="A36" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C36" s="3">
-        <v>3</v>
-      </c>
-      <c r="D36" s="3">
+      <c r="C36" s="5">
+        <v>3</v>
+      </c>
+      <c r="D36" s="5">
         <v>13</v>
       </c>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="3" t="s">
+      <c r="A37" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C37" s="3">
+      <c r="C37" s="5">
         <v>4</v>
       </c>
-      <c r="D37" s="3">
+      <c r="D37" s="5">
         <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="3" t="s">
+      <c r="A38" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C38" s="3">
+      <c r="C38" s="5">
         <v>4</v>
       </c>
-      <c r="D38" s="3">
+      <c r="D38" s="5">
         <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="3" t="s">
+      <c r="A39" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C39" s="3">
-        <v>5</v>
-      </c>
-      <c r="D39" s="3">
+      <c r="C39" s="5">
+        <v>5</v>
+      </c>
+      <c r="D39" s="5">
         <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="3" t="s">
+      <c r="A40" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B40" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C40" s="3">
+      <c r="C40" s="5">
         <v>6</v>
       </c>
-      <c r="D40" s="3">
+      <c r="D40" s="5">
         <v>13</v>
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="3" t="s">
+      <c r="A41" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B41" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C41" s="3">
+      <c r="C41" s="5">
         <v>7</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="5">
         <v>12</v>
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="3"/>
-      <c r="B42" s="3"/>
-      <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
+      <c r="A42" s="5"/>
+      <c r="B42" s="5"/>
+      <c r="C42" s="5"/>
+      <c r="D42" s="5"/>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="3"/>
-      <c r="B43" s="3"/>
-      <c r="C43" s="3"/>
-      <c r="D43" s="3"/>
+      <c r="A43" s="5"/>
+      <c r="B43" s="5"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="5"/>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B44" s="3" t="s">
+      <c r="A44" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B44" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C44" s="3"/>
-      <c r="D44" s="3">
+      <c r="C44" s="5"/>
+      <c r="D44" s="5">
         <f>AVERAGE(D36:D41)</f>
         <v>12.6666666666667</v>
       </c>
@@ -2220,8 +2308,8 @@
         <v>38</v>
       </c>
       <c r="D47">
-        <f>AVERAGE(D14,D33,D44)</f>
-        <v>13.9650793650794</v>
+        <f>AVERAGE(D2:D11,D17:D30,D36:D41)</f>
+        <v>14.1666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -2491,261 +2579,261 @@
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C22" s="2">
+      <c r="B22" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="3">
         <v>2</v>
       </c>
-      <c r="D22" s="2">
+      <c r="D22" s="3">
         <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C23" s="2">
-        <v>3</v>
-      </c>
-      <c r="D23" s="2">
+      <c r="B23" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="3">
+        <v>3</v>
+      </c>
+      <c r="D23" s="3">
         <v>14</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C24" s="2">
-        <v>3</v>
-      </c>
-      <c r="D24" s="2">
+      <c r="B24" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" s="3">
+        <v>3</v>
+      </c>
+      <c r="D24" s="3">
         <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C25" s="2">
-        <v>3</v>
-      </c>
-      <c r="D25" s="2">
+      <c r="B25" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" s="3">
+        <v>3</v>
+      </c>
+      <c r="D25" s="3">
         <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C26" s="2">
+      <c r="B26" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="3">
         <v>4</v>
       </c>
-      <c r="D26" s="2">
+      <c r="D26" s="3">
         <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C27" s="2">
+      <c r="B27" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" s="3">
         <v>4</v>
       </c>
-      <c r="D27" s="2">
+      <c r="D27" s="3">
         <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C28" s="2">
-        <v>5</v>
-      </c>
-      <c r="D28" s="2">
+      <c r="B28" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C28" s="3">
+        <v>5</v>
+      </c>
+      <c r="D28" s="3">
         <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C29" s="2">
+      <c r="B29" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C29" s="3">
         <v>6</v>
       </c>
-      <c r="D29" s="2">
+      <c r="D29" s="3">
         <v>15</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B32" s="2" t="s">
+      <c r="A32" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2">
+      <c r="C32" s="3"/>
+      <c r="D32" s="3">
         <f>AVERAGE(D22:D29)</f>
         <v>14</v>
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="3" t="s">
+      <c r="A35" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C35" s="3">
-        <v>3</v>
-      </c>
-      <c r="D35" s="3">
+      <c r="C35" s="5">
+        <v>3</v>
+      </c>
+      <c r="D35" s="5">
         <v>13</v>
       </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="3" t="s">
+      <c r="A36" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C36" s="3">
+      <c r="C36" s="5">
         <v>4</v>
       </c>
-      <c r="D36" s="3">
+      <c r="D36" s="5">
         <v>14</v>
       </c>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="3" t="s">
+      <c r="A37" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C37" s="3">
+      <c r="C37" s="5">
         <v>4</v>
       </c>
-      <c r="D37" s="3">
+      <c r="D37" s="5">
         <v>12</v>
       </c>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="3" t="s">
+      <c r="A38" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C38" s="3">
+      <c r="C38" s="5">
         <v>4</v>
       </c>
-      <c r="D38" s="3">
+      <c r="D38" s="5">
         <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="3" t="s">
+      <c r="A39" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C39" s="3">
-        <v>5</v>
-      </c>
-      <c r="D39" s="3">
+      <c r="C39" s="5">
+        <v>5</v>
+      </c>
+      <c r="D39" s="5">
         <v>14</v>
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="3" t="s">
+      <c r="A40" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B40" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C40" s="3">
+      <c r="C40" s="5">
         <v>6</v>
       </c>
-      <c r="D40" s="3">
+      <c r="D40" s="5">
         <v>13</v>
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="3" t="s">
+      <c r="A41" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B41" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C41" s="3">
+      <c r="C41" s="5">
         <v>8</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="5">
         <v>13</v>
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="3"/>
-      <c r="B42" s="3"/>
-      <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
+      <c r="A42" s="5"/>
+      <c r="B42" s="5"/>
+      <c r="C42" s="5"/>
+      <c r="D42" s="5"/>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="3"/>
-      <c r="B43" s="3"/>
-      <c r="C43" s="3"/>
-      <c r="D43" s="3"/>
+      <c r="A43" s="5"/>
+      <c r="B43" s="5"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="5"/>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B44" s="3" t="s">
+      <c r="A44" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B44" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C44" s="3"/>
-      <c r="D44" s="3">
+      <c r="C44" s="5"/>
+      <c r="D44" s="5">
         <f>AVERAGE(D35:D41)</f>
         <v>13</v>
       </c>
@@ -2755,8 +2843,8 @@
         <v>38</v>
       </c>
       <c r="D47">
-        <f>AVERAGE(D19,D32,D44)</f>
-        <v>13.7333333333333</v>
+        <f>AVERAGE(D2:D16,D22:D29,D35:D41)</f>
+        <v>13.8666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -2998,289 +3086,289 @@
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="2">
+      <c r="B20" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="3">
         <v>2</v>
       </c>
-      <c r="D20" s="2">
+      <c r="D20" s="3">
         <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C21" s="2">
-        <v>3</v>
-      </c>
-      <c r="D21" s="2">
+      <c r="B21" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="3">
+        <v>3</v>
+      </c>
+      <c r="D21" s="3">
         <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C22" s="2">
-        <v>3</v>
-      </c>
-      <c r="D22" s="2">
+      <c r="B22" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="3">
+        <v>3</v>
+      </c>
+      <c r="D22" s="3">
         <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C23" s="2">
-        <v>3</v>
-      </c>
-      <c r="D23" s="2">
+      <c r="B23" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="3">
+        <v>3</v>
+      </c>
+      <c r="D23" s="3">
         <v>14</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C24" s="2">
-        <v>3</v>
-      </c>
-      <c r="D24" s="2">
+      <c r="B24" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" s="3">
+        <v>3</v>
+      </c>
+      <c r="D24" s="3">
         <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C25" s="2">
+      <c r="B25" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" s="3">
         <v>4</v>
       </c>
-      <c r="D25" s="2">
+      <c r="D25" s="3">
         <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C26" s="2">
+      <c r="B26" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="3">
         <v>4</v>
       </c>
-      <c r="D26" s="2">
+      <c r="D26" s="3">
         <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C27" s="2">
-        <v>5</v>
-      </c>
-      <c r="D27" s="2">
+      <c r="B27" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" s="3">
+        <v>5</v>
+      </c>
+      <c r="D27" s="3">
         <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C28" s="2">
-        <v>5</v>
-      </c>
-      <c r="D28" s="2">
+      <c r="B28" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C28" s="3">
+        <v>5</v>
+      </c>
+      <c r="D28" s="3">
         <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C29" s="2">
+      <c r="B29" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C29" s="3">
         <v>6</v>
       </c>
-      <c r="D29" s="2">
+      <c r="D29" s="3">
         <v>15</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B32" s="2" t="s">
+      <c r="A32" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2">
+      <c r="C32" s="3"/>
+      <c r="D32" s="3">
         <f>AVERAGE(D20:D29)</f>
         <v>14.4</v>
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="3" t="s">
+      <c r="A35" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C35" s="3">
-        <v>3</v>
-      </c>
-      <c r="D35" s="3">
+      <c r="C35" s="5">
+        <v>3</v>
+      </c>
+      <c r="D35" s="5">
         <v>13</v>
       </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="3" t="s">
+      <c r="A36" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C36" s="3">
+      <c r="C36" s="5">
         <v>4</v>
       </c>
-      <c r="D36" s="3">
+      <c r="D36" s="5">
         <v>14</v>
       </c>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="3" t="s">
+      <c r="A37" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C37" s="3">
+      <c r="C37" s="5">
         <v>4</v>
       </c>
-      <c r="D37" s="3">
+      <c r="D37" s="5">
         <v>12</v>
       </c>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="3" t="s">
+      <c r="A38" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C38" s="3">
+      <c r="C38" s="5">
         <v>4</v>
       </c>
-      <c r="D38" s="3">
+      <c r="D38" s="5">
         <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="3" t="s">
+      <c r="A39" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C39" s="3">
-        <v>5</v>
-      </c>
-      <c r="D39" s="3">
+      <c r="C39" s="5">
+        <v>5</v>
+      </c>
+      <c r="D39" s="5">
         <v>13</v>
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="3" t="s">
+      <c r="A40" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B40" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C40" s="3">
+      <c r="C40" s="5">
         <v>6</v>
       </c>
-      <c r="D40" s="3">
+      <c r="D40" s="5">
         <v>13</v>
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="3" t="s">
+      <c r="A41" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B41" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C41" s="3">
+      <c r="C41" s="5">
         <v>8</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="5">
         <v>13</v>
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="3"/>
-      <c r="B42" s="3"/>
-      <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
+      <c r="A42" s="5"/>
+      <c r="B42" s="5"/>
+      <c r="C42" s="5"/>
+      <c r="D42" s="5"/>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="3"/>
-      <c r="B43" s="3"/>
-      <c r="C43" s="3"/>
-      <c r="D43" s="3"/>
+      <c r="A43" s="5"/>
+      <c r="B43" s="5"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="5"/>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B44" s="3" t="s">
+      <c r="A44" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B44" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C44" s="3"/>
-      <c r="D44" s="3">
+      <c r="C44" s="5"/>
+      <c r="D44" s="5">
         <f>AVERAGE(D35:D41)</f>
         <v>12.8571428571429</v>
       </c>
@@ -3290,8 +3378,1148 @@
         <v>38</v>
       </c>
       <c r="D47">
-        <f>AVERAGE(D17,D32,D44)</f>
-        <v>13.9318681318681</v>
+        <f>AVERAGE(D2:D14,D20:D29,D35:D41)</f>
+        <v>14.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D37"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="16.375" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="11.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="1">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="1">
+        <v>2</v>
+      </c>
+      <c r="C5" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="1">
+        <v>3</v>
+      </c>
+      <c r="C6" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="1">
+        <v>3</v>
+      </c>
+      <c r="C7" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="1">
+        <v>5</v>
+      </c>
+      <c r="C8" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="1">
+        <v>5</v>
+      </c>
+      <c r="C9" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="1">
+        <f>AVERAGE(C2:C9)</f>
+        <v>15.125</v>
+      </c>
+      <c r="D12" s="3"/>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3">
+        <v>2</v>
+      </c>
+      <c r="C15" s="3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="3">
+        <v>3</v>
+      </c>
+      <c r="C16" s="3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="3">
+        <v>3</v>
+      </c>
+      <c r="C17" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="3">
+        <v>4</v>
+      </c>
+      <c r="C18" s="3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="3">
+        <v>6</v>
+      </c>
+      <c r="C19" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" s="3">
+        <v>6</v>
+      </c>
+      <c r="C20" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="4"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="3">
+        <f>AVERAGE(C15:C20)</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B26" s="5">
+        <v>1</v>
+      </c>
+      <c r="C26" s="5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B27" s="5">
+        <v>2</v>
+      </c>
+      <c r="C27" s="5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B28" s="5">
+        <v>2</v>
+      </c>
+      <c r="C28" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B29" s="5">
+        <v>2</v>
+      </c>
+      <c r="C29" s="5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B30" s="5">
+        <v>2</v>
+      </c>
+      <c r="C30" s="5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B31" s="5">
+        <v>5</v>
+      </c>
+      <c r="C31" s="5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="6"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="6"/>
+      <c r="B33" s="6"/>
+      <c r="C33" s="6"/>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C34" s="5">
+        <f>AVERAGE(C26:C31)</f>
+        <v>13.1666666666667</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C37" s="7">
+        <f>AVERAGE(C2:C9,C15:C20,C26:C31)</f>
+        <v>14.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C32"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
+  <cols>
+    <col min="1" max="1" width="17.125" customWidth="1"/>
+    <col min="2" max="2" width="10.25" customWidth="1"/>
+    <col min="3" max="3" width="10.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="1">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="1">
+        <v>5</v>
+      </c>
+      <c r="C4" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="1">
+        <v>5</v>
+      </c>
+      <c r="C5" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="1">
+        <f>AVERAGE(C2:C5)</f>
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="3">
+        <v>2</v>
+      </c>
+      <c r="C11" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="3">
+        <v>2</v>
+      </c>
+      <c r="C12" s="3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="3">
+        <v>2</v>
+      </c>
+      <c r="C13" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="3">
+        <v>3</v>
+      </c>
+      <c r="C14" s="3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="3">
+        <v>3</v>
+      </c>
+      <c r="C15" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" s="3">
+        <v>4</v>
+      </c>
+      <c r="C16" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="3">
+        <v>5</v>
+      </c>
+      <c r="C17" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="3">
+        <v>5</v>
+      </c>
+      <c r="C18" s="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="3">
+        <v>7</v>
+      </c>
+      <c r="C19" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="4"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="3">
+        <f>AVERAGE(C11:C19)</f>
+        <v>13.4444444444444</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B25" s="5">
+        <v>1</v>
+      </c>
+      <c r="C25" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B26" s="5">
+        <v>7</v>
+      </c>
+      <c r="C26" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="6"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="6"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="6"/>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="5">
+        <f>AVERAGE(C25:C26)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C32" s="7">
+        <f>AVERAGE(C2:C5,C11:C19,C25:C26)</f>
+        <v>13.5333333333333</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C32"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
+  <cols>
+    <col min="1" max="1" width="13.75" customWidth="1"/>
+    <col min="2" max="2" width="11.5" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" s="1">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="1">
+        <v>3</v>
+      </c>
+      <c r="C4" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B5" s="1">
+        <v>3</v>
+      </c>
+      <c r="C5" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="1">
+        <v>3</v>
+      </c>
+      <c r="C6" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" s="1">
+        <v>3</v>
+      </c>
+      <c r="C7" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" s="1">
+        <v>3</v>
+      </c>
+      <c r="C8" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" s="1">
+        <v>4</v>
+      </c>
+      <c r="C9" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B10" s="1">
+        <v>5</v>
+      </c>
+      <c r="C10" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="1">
+        <f>AVERAGE(C2:C10)</f>
+        <v>13.7777777777778</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16" s="3">
+        <v>3</v>
+      </c>
+      <c r="C16" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17" s="3">
+        <v>3</v>
+      </c>
+      <c r="C17" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" s="3">
+        <v>4</v>
+      </c>
+      <c r="C18" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B19" s="3">
+        <v>4</v>
+      </c>
+      <c r="C19" s="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B20" s="3">
+        <v>5</v>
+      </c>
+      <c r="C20" s="3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="4"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="3">
+        <f>AVERAGE(C16:C20)</f>
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B26" s="5">
+        <v>4</v>
+      </c>
+      <c r="C26" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="6"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="6"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="6"/>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="5">
+        <f>AVERAGE(C26:C26)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C32" s="7">
+        <f>AVERAGE(C2:C10,C16:C20,C26:C26)</f>
+        <v>13.4666666666667</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="D1:F32"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <cols>
+    <col min="4" max="4" width="13.125" customWidth="1"/>
+    <col min="5" max="5" width="11.25" customWidth="1"/>
+    <col min="6" max="6" width="10.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="4:6">
+      <c r="D1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="4:6">
+      <c r="D2" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="4:6">
+      <c r="D3" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" s="1">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="4:6">
+      <c r="D4" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E4" s="1">
+        <v>2</v>
+      </c>
+      <c r="F4" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="4:6">
+      <c r="D5" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E5" s="1">
+        <v>2</v>
+      </c>
+      <c r="F5" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="4:6">
+      <c r="D6" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E6" s="1">
+        <v>2</v>
+      </c>
+      <c r="F6" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="4:6">
+      <c r="D7" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E7" s="1">
+        <v>3</v>
+      </c>
+      <c r="F7" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="4:6">
+      <c r="D8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E8" s="1">
+        <v>4</v>
+      </c>
+      <c r="F8" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="4:6">
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" spans="4:6">
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+    </row>
+    <row r="11" spans="4:6">
+      <c r="D11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="1">
+        <f>AVERAGE(F2:F8)</f>
+        <v>13.1428571428571</v>
+      </c>
+    </row>
+    <row r="14" spans="4:6">
+      <c r="D14" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E14" s="3">
+        <v>2</v>
+      </c>
+      <c r="F14" s="3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="4:6">
+      <c r="D15" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E15" s="3">
+        <v>2</v>
+      </c>
+      <c r="F15" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="4:6">
+      <c r="D16" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E16" s="3">
+        <v>3</v>
+      </c>
+      <c r="F16" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="4:6">
+      <c r="D17" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E17" s="3">
+        <v>3</v>
+      </c>
+      <c r="F17" s="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="4:6">
+      <c r="D18" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E18" s="3">
+        <v>4</v>
+      </c>
+      <c r="F18" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="4:6">
+      <c r="D19" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E19" s="3">
+        <v>5</v>
+      </c>
+      <c r="F19" s="3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="4:6">
+      <c r="D20" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E20" s="3">
+        <v>5</v>
+      </c>
+      <c r="F20" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="4:6">
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+    </row>
+    <row r="22" spans="4:6">
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+    </row>
+    <row r="23" spans="4:6">
+      <c r="D23" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F23" s="3">
+        <f>AVERAGE(F14:F20)</f>
+        <v>12.1428571428571</v>
+      </c>
+    </row>
+    <row r="26" spans="4:6">
+      <c r="D26" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E26" s="5">
+        <v>2</v>
+      </c>
+      <c r="F26" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="4:6">
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+    </row>
+    <row r="28" spans="4:6">
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+    </row>
+    <row r="29" spans="4:6">
+      <c r="D29" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F29" s="5">
+        <f>AVERAGE(F26:F26)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="4:6">
+      <c r="D32" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F32" s="7">
+        <f>AVERAGE(F2:F8,F14:F20,F26:F26)</f>
+        <v>12.1333333333333</v>
       </c>
     </row>
   </sheetData>

--- a/src/utils/sxsyzlzq/zzz_cardList.xlsx
+++ b/src/utils/sxsyzlzq/zzz_cardList.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28245" windowHeight="12345" activeTab="7"/>
+    <workbookView windowWidth="28245" windowHeight="12345" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="伊萝莲" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="90">
   <si>
     <t>名称</t>
   </si>
@@ -80,105 +80,105 @@
     <t>边境高墙</t>
   </si>
   <si>
+    <t>学仆-脉冲型</t>
+  </si>
+  <si>
+    <t>幻域秘树</t>
+  </si>
+  <si>
+    <t>召集护卫</t>
+  </si>
+  <si>
+    <t>观星台大预言家</t>
+  </si>
+  <si>
+    <t>惩戒天使</t>
+  </si>
+  <si>
+    <t>禁卫指挥官</t>
+  </si>
+  <si>
+    <t>米拉方舟</t>
+  </si>
+  <si>
+    <t>紫色卡等：</t>
+  </si>
+  <si>
+    <t>花光春影·安娜贝尔</t>
+  </si>
+  <si>
+    <t>橙色</t>
+  </si>
+  <si>
+    <t>百花长枪·卡罗琳</t>
+  </si>
+  <si>
+    <t>明日香·露娜</t>
+  </si>
+  <si>
+    <t>永恒之王·莱哈特</t>
+  </si>
+  <si>
+    <t>月之神·米拉</t>
+  </si>
+  <si>
+    <t>白袍·伊恩</t>
+  </si>
+  <si>
+    <t>火蛇巫女·沃凡瑞拉</t>
+  </si>
+  <si>
+    <t>武圣·云长</t>
+  </si>
+  <si>
+    <t>橙色卡等：</t>
+  </si>
+  <si>
+    <t>总计：</t>
+  </si>
+  <si>
+    <t>学仆-观测型</t>
+  </si>
+  <si>
+    <t>卜命道长</t>
+  </si>
+  <si>
+    <t>旅行背包</t>
+  </si>
+  <si>
+    <t>重装固守</t>
+  </si>
+  <si>
+    <t>执剑道人</t>
+  </si>
+  <si>
+    <t>连击</t>
+  </si>
+  <si>
+    <t>龟族僧人</t>
+  </si>
+  <si>
+    <t>深山采药人</t>
+  </si>
+  <si>
+    <t>叶幻师</t>
+  </si>
+  <si>
+    <t>风卷残云</t>
+  </si>
+  <si>
+    <t>祥云师太</t>
+  </si>
+  <si>
+    <t>驱魔道人</t>
+  </si>
+  <si>
+    <t>扫叶僧</t>
+  </si>
+  <si>
     <t>冲锋装备</t>
   </si>
   <si>
-    <t>学仆-脉冲型</t>
-  </si>
-  <si>
-    <t>幻域秘树</t>
-  </si>
-  <si>
-    <t>召集护卫</t>
-  </si>
-  <si>
-    <t>观星台大预言家</t>
-  </si>
-  <si>
-    <t>惩戒天使</t>
-  </si>
-  <si>
-    <t>禁卫指挥官</t>
-  </si>
-  <si>
-    <t>米拉方舟</t>
-  </si>
-  <si>
-    <t>紫色卡等：</t>
-  </si>
-  <si>
-    <t>花光春影·安娜贝尔</t>
-  </si>
-  <si>
-    <t>橙色</t>
-  </si>
-  <si>
-    <t>百花长枪·卡罗琳</t>
-  </si>
-  <si>
-    <t>明日香·露娜</t>
-  </si>
-  <si>
-    <t>永恒之王·莱哈特</t>
-  </si>
-  <si>
-    <t>月之神·米拉</t>
-  </si>
-  <si>
-    <t>白袍·伊恩</t>
-  </si>
-  <si>
-    <t>火蛇巫女·沃凡瑞拉</t>
-  </si>
-  <si>
-    <t>武圣·云长</t>
-  </si>
-  <si>
-    <t>橙色卡等：</t>
-  </si>
-  <si>
-    <t>总计：</t>
-  </si>
-  <si>
-    <t>学仆-观测型</t>
-  </si>
-  <si>
-    <t>卜命道长</t>
-  </si>
-  <si>
-    <t>旅行背包</t>
-  </si>
-  <si>
-    <t>重装固守</t>
-  </si>
-  <si>
-    <t>执剑道人</t>
-  </si>
-  <si>
-    <t>连击</t>
-  </si>
-  <si>
-    <t>龟族僧人</t>
-  </si>
-  <si>
-    <t>深山采药人</t>
-  </si>
-  <si>
-    <t>叶幻师</t>
-  </si>
-  <si>
-    <t>风卷残云</t>
-  </si>
-  <si>
-    <t>祥云师太</t>
-  </si>
-  <si>
-    <t>驱魔道人</t>
-  </si>
-  <si>
-    <t>扫叶僧</t>
-  </si>
-  <si>
     <t>御风武者</t>
   </si>
   <si>
@@ -221,10 +221,31 @@
     <t>No.6沃凡瑞拉</t>
   </si>
   <si>
+    <t>箭竹守卫</t>
+  </si>
+  <si>
+    <t>白羊药师</t>
+  </si>
+  <si>
+    <t>树木之怒</t>
+  </si>
+  <si>
+    <t>苦行武僧</t>
+  </si>
+  <si>
     <t>执剑道者</t>
   </si>
   <si>
-    <t>悟能禅杖</t>
+    <t>疾风猎手</t>
+  </si>
+  <si>
+    <t>风铃道人</t>
+  </si>
+  <si>
+    <t>逍遥琴师</t>
+  </si>
+  <si>
+    <t>神机玄女·轩</t>
   </si>
   <si>
     <t>冥河守卫</t>
@@ -239,9 +260,6 @@
     <t>残暴爪钩</t>
   </si>
   <si>
-    <t>狂暴炎球</t>
-  </si>
-  <si>
     <t>烈焰风暴</t>
   </si>
   <si>
@@ -266,7 +284,13 @@
     <t>地狱屠夫</t>
   </si>
   <si>
+    <t>恶灵魔焰</t>
+  </si>
+  <si>
     <t>痛苦之心</t>
+  </si>
+  <si>
+    <t>橙色色卡等：</t>
   </si>
 </sst>
 </file>
@@ -275,8 +299,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
@@ -317,7 +341,69 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -337,90 +423,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -428,9 +430,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -445,16 +446,39 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -469,13 +493,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -493,163 +667,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -666,8 +690,19 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -683,6 +718,45 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -706,57 +780,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -768,10 +792,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -780,147 +804,141 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1422,359 +1440,359 @@
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" s="3">
+      <c r="B16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="2">
         <v>2</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="2">
         <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" s="3">
+      <c r="B17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="2">
         <v>2</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="2">
+        <v>2</v>
+      </c>
+      <c r="D18" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18" s="3">
+      <c r="B19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="2">
         <v>2</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D19" s="2">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="3" t="s">
+    <row r="20" spans="1:4">
+      <c r="A20" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="3">
-        <v>3</v>
-      </c>
-      <c r="D19" s="3">
+      <c r="B20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="2">
+        <v>3</v>
+      </c>
+      <c r="D20" s="2">
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="3" t="s">
+    <row r="21" spans="1:4">
+      <c r="A21" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="3">
-        <v>3</v>
-      </c>
-      <c r="D20" s="3">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="3" t="s">
+      <c r="B21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="2">
+        <v>3</v>
+      </c>
+      <c r="D21" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="2">
+        <v>3</v>
+      </c>
+      <c r="D22" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C21" s="3">
-        <v>3</v>
-      </c>
-      <c r="D21" s="3">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C22" s="3">
-        <v>3</v>
-      </c>
-      <c r="D22" s="3">
+      <c r="B23" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="2">
+        <v>4</v>
+      </c>
+      <c r="D23" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" s="2">
+        <v>4</v>
+      </c>
+      <c r="D24" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" s="2">
+        <v>5</v>
+      </c>
+      <c r="D25" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="2">
+        <v>6</v>
+      </c>
+      <c r="D26" s="2">
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C23" s="3">
+    <row r="27" spans="1:4">
+      <c r="A27" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" s="2">
+        <v>6</v>
+      </c>
+      <c r="D27" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C28" s="2">
+        <v>7</v>
+      </c>
+      <c r="D28" s="2">
+        <v>14</v>
+      </c>
+      <c r="F28" s="6"/>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2">
+        <f>AVERAGE(D16:D28)</f>
+        <v>14.2307692307692</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C34" s="3">
+        <v>3</v>
+      </c>
+      <c r="D34" s="3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C35" s="3">
         <v>4</v>
       </c>
-      <c r="D23" s="3">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C24" s="3">
+      <c r="D35" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C36" s="3">
         <v>4</v>
       </c>
-      <c r="D24" s="3">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C25" s="3">
-        <v>5</v>
-      </c>
-      <c r="D25" s="3">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C26" s="3">
+      <c r="D36" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C37" s="3">
+        <v>5</v>
+      </c>
+      <c r="D37" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C38" s="3">
+        <v>5</v>
+      </c>
+      <c r="D38" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C39" s="3">
         <v>6</v>
       </c>
-      <c r="D26" s="3">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C27" s="3">
-        <v>6</v>
-      </c>
-      <c r="D27" s="3">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C28" s="3">
+      <c r="D39" s="3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C40" s="3">
         <v>7</v>
       </c>
-      <c r="D28" s="3">
-        <v>14</v>
-      </c>
-      <c r="F28" s="8"/>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="3"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3">
-        <f>AVERAGE(D16:D28)</f>
-        <v>14.4615384615385</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" s="5" t="s">
+      <c r="D40" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B41" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C34" s="5">
-        <v>3</v>
-      </c>
-      <c r="D34" s="5">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C35" s="5">
-        <v>4</v>
-      </c>
-      <c r="D35" s="5">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C36" s="5">
-        <v>4</v>
-      </c>
-      <c r="D36" s="5">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
-      <c r="A37" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C37" s="5">
-        <v>5</v>
-      </c>
-      <c r="D37" s="5">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
-      <c r="A38" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C38" s="5">
-        <v>5</v>
-      </c>
-      <c r="D38" s="5">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C39" s="5">
-        <v>6</v>
-      </c>
-      <c r="D39" s="5">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
-      <c r="A40" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C40" s="5">
-        <v>7</v>
-      </c>
-      <c r="D40" s="5">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
-      <c r="A41" s="5" t="s">
+      <c r="C41" s="3">
+        <v>8</v>
+      </c>
+      <c r="D41" s="3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="3"/>
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="3"/>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B44" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B41" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C41" s="5">
-        <v>8</v>
-      </c>
-      <c r="D41" s="5">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
-      <c r="A42" s="5"/>
-      <c r="B42" s="5"/>
-      <c r="C42" s="5"/>
-      <c r="D42" s="5"/>
-    </row>
-    <row r="43" spans="1:4">
-      <c r="A43" s="5"/>
-      <c r="B43" s="5"/>
-      <c r="C43" s="5"/>
-      <c r="D43" s="5"/>
-    </row>
-    <row r="44" spans="1:4">
-      <c r="A44" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C44" s="5"/>
-      <c r="D44" s="5">
+      <c r="C44" s="3"/>
+      <c r="D44" s="3">
         <f>AVERAGE(D34:D41)</f>
         <v>12.875</v>
       </c>
     </row>
     <row r="47" spans="1:4">
-      <c r="A47" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B47" s="7"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="7">
+      <c r="A47" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B47" s="5"/>
+      <c r="C47" s="5"/>
+      <c r="D47" s="5">
         <f>AVERAGE(D2:D10,D16:D28,D34:D41)</f>
-        <v>14.3666666666667</v>
+        <v>14.2666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -1824,7 +1842,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>5</v>
@@ -1838,7 +1856,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>5</v>
@@ -1974,338 +1992,338 @@
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" s="3">
+      <c r="B17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="2">
         <v>2</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="2">
         <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18" s="3">
+      <c r="B18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="2">
         <v>2</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="3">
+      <c r="B19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="2">
         <v>2</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="2">
         <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="3">
+      <c r="B20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="2">
         <v>2</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="2">
         <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C21" s="3">
-        <v>3</v>
-      </c>
-      <c r="D21" s="3">
+      <c r="B21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="2">
+        <v>3</v>
+      </c>
+      <c r="D21" s="2">
         <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="2">
+        <v>3</v>
+      </c>
+      <c r="D22" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="2">
+        <v>3</v>
+      </c>
+      <c r="D23" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C22" s="3">
-        <v>3</v>
-      </c>
-      <c r="D22" s="3">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C23" s="3">
-        <v>3</v>
-      </c>
-      <c r="D23" s="3">
+      <c r="B24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" s="2">
+        <v>4</v>
+      </c>
+      <c r="D24" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" s="2">
+        <v>4</v>
+      </c>
+      <c r="D25" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="2">
+        <v>5</v>
+      </c>
+      <c r="D26" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" s="2">
+        <v>5</v>
+      </c>
+      <c r="D27" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C28" s="2">
+        <v>6</v>
+      </c>
+      <c r="D28" s="2">
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C24" s="3">
-        <v>4</v>
-      </c>
-      <c r="D24" s="3">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C25" s="3">
-        <v>4</v>
-      </c>
-      <c r="D25" s="3">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C26" s="3">
-        <v>5</v>
-      </c>
-      <c r="D26" s="3">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C27" s="3">
-        <v>5</v>
-      </c>
-      <c r="D27" s="3">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="3" t="s">
+    <row r="29" spans="1:4">
+      <c r="A29" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C28" s="3">
+      <c r="B29" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C29" s="2">
         <v>6</v>
       </c>
-      <c r="D28" s="3">
+      <c r="D29" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="2">
+        <v>7</v>
+      </c>
+      <c r="D30" s="2">
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C29" s="3">
-        <v>6</v>
-      </c>
-      <c r="D29" s="3">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="3" t="s">
+    <row r="31" spans="1:4">
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C30" s="3">
-        <v>7</v>
-      </c>
-      <c r="D30" s="3">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="3"/>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="3"/>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3">
+      <c r="C33" s="2"/>
+      <c r="D33" s="2">
         <f>AVERAGE(D17:D30)</f>
         <v>14</v>
       </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="5" t="s">
+      <c r="A36" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="C36" s="3">
+        <v>3</v>
+      </c>
+      <c r="D36" s="3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C36" s="5">
-        <v>3</v>
-      </c>
-      <c r="D36" s="5">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
-      <c r="A37" s="5" t="s">
+      <c r="B37" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C37" s="3">
+        <v>4</v>
+      </c>
+      <c r="D37" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C37" s="5">
+      <c r="B38" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C38" s="3">
         <v>4</v>
       </c>
-      <c r="D37" s="5">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
-      <c r="A38" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C38" s="5">
-        <v>4</v>
-      </c>
-      <c r="D38" s="5">
+      <c r="D38" s="3">
         <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="5" t="s">
+      <c r="A39" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C39" s="3">
+        <v>5</v>
+      </c>
+      <c r="D39" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C39" s="5">
-        <v>5</v>
-      </c>
-      <c r="D39" s="5">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
-      <c r="A40" s="5" t="s">
+      <c r="B40" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C40" s="3">
+        <v>6</v>
+      </c>
+      <c r="D40" s="3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B40" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C40" s="5">
-        <v>6</v>
-      </c>
-      <c r="D40" s="5">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
-      <c r="A41" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C41" s="5">
+      <c r="B41" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C41" s="3">
         <v>7</v>
       </c>
-      <c r="D41" s="5">
+      <c r="D41" s="3">
         <v>12</v>
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="5"/>
-      <c r="B42" s="5"/>
-      <c r="C42" s="5"/>
-      <c r="D42" s="5"/>
+      <c r="A42" s="3"/>
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="5"/>
-      <c r="B43" s="5"/>
-      <c r="C43" s="5"/>
-      <c r="D43" s="5"/>
+      <c r="A43" s="3"/>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C44" s="5"/>
-      <c r="D44" s="5">
+      <c r="A44" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3">
         <f>AVERAGE(D36:D41)</f>
         <v>12.6666666666667</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D47">
         <f>AVERAGE(D2:D11,D17:D30,D36:D41)</f>
@@ -2359,7 +2377,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>5</v>
@@ -2373,7 +2391,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>5</v>
@@ -2387,7 +2405,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>5</v>
@@ -2401,7 +2419,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>5</v>
@@ -2429,7 +2447,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>5</v>
@@ -2443,7 +2461,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>5</v>
@@ -2457,7 +2475,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>5</v>
@@ -2471,7 +2489,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>5</v>
@@ -2485,7 +2503,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>5</v>
@@ -2499,7 +2517,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>5</v>
@@ -2513,7 +2531,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>5</v>
@@ -2579,268 +2597,268 @@
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C22" s="3">
+      <c r="B22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="2">
         <v>2</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="2">
         <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="2">
+        <v>3</v>
+      </c>
+      <c r="D23" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C23" s="3">
-        <v>3</v>
-      </c>
-      <c r="D23" s="3">
+      <c r="B24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" s="2">
+        <v>3</v>
+      </c>
+      <c r="D24" s="2">
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="3" t="s">
+    <row r="25" spans="1:4">
+      <c r="A25" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C24" s="3">
-        <v>3</v>
-      </c>
-      <c r="D24" s="3">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C25" s="3">
-        <v>3</v>
-      </c>
-      <c r="D25" s="3">
+      <c r="B25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" s="2">
+        <v>3</v>
+      </c>
+      <c r="D25" s="2">
         <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C26" s="3">
+      <c r="B26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="2">
         <v>4</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C27" s="3">
+      <c r="B27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" s="2">
         <v>4</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="2">
         <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C28" s="3">
-        <v>5</v>
-      </c>
-      <c r="D28" s="3">
+      <c r="B28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C28" s="2">
+        <v>5</v>
+      </c>
+      <c r="D28" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C29" s="3">
+      <c r="A29" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C29" s="2">
         <v>6</v>
       </c>
-      <c r="D29" s="3">
+      <c r="D29" s="2">
         <v>15</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="3"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="3"/>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3">
+      <c r="A32" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2">
         <f>AVERAGE(D22:D29)</f>
         <v>14</v>
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="5" t="s">
+      <c r="A35" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="C35" s="3">
+        <v>3</v>
+      </c>
+      <c r="D35" s="3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C35" s="5">
-        <v>3</v>
-      </c>
-      <c r="D35" s="5">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" s="5" t="s">
+      <c r="B36" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C36" s="3">
+        <v>4</v>
+      </c>
+      <c r="D36" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C37" s="3">
+        <v>4</v>
+      </c>
+      <c r="D37" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C36" s="5">
+      <c r="B38" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C38" s="3">
         <v>4</v>
       </c>
-      <c r="D36" s="5">
+      <c r="D38" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C39" s="3">
+        <v>5</v>
+      </c>
+      <c r="D39" s="3">
         <v>14</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
-      <c r="A37" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C37" s="5">
-        <v>4</v>
-      </c>
-      <c r="D37" s="5">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
-      <c r="A38" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C38" s="5">
-        <v>4</v>
-      </c>
-      <c r="D38" s="5">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C39" s="5">
-        <v>5</v>
-      </c>
-      <c r="D39" s="5">
-        <v>14</v>
-      </c>
-    </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C40" s="5">
+      <c r="A40" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C40" s="3">
         <v>6</v>
       </c>
-      <c r="D40" s="5">
+      <c r="D40" s="3">
         <v>13</v>
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="5" t="s">
+      <c r="A41" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C41" s="3">
+        <v>8</v>
+      </c>
+      <c r="D41" s="3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="3"/>
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="3"/>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B44" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B41" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C41" s="5">
-        <v>8</v>
-      </c>
-      <c r="D41" s="5">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
-      <c r="A42" s="5"/>
-      <c r="B42" s="5"/>
-      <c r="C42" s="5"/>
-      <c r="D42" s="5"/>
-    </row>
-    <row r="43" spans="1:4">
-      <c r="A43" s="5"/>
-      <c r="B43" s="5"/>
-      <c r="C43" s="5"/>
-      <c r="D43" s="5"/>
-    </row>
-    <row r="44" spans="1:4">
-      <c r="A44" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C44" s="5"/>
-      <c r="D44" s="5">
+      <c r="C44" s="3"/>
+      <c r="D44" s="3">
         <f>AVERAGE(D35:D41)</f>
         <v>13</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D47">
         <f>AVERAGE(D2:D16,D22:D29,D35:D41)</f>
@@ -2894,7 +2912,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>5</v>
@@ -2908,7 +2926,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>5</v>
@@ -2922,7 +2940,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>5</v>
@@ -2936,7 +2954,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>5</v>
@@ -2978,7 +2996,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>5</v>
@@ -2992,7 +3010,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>5</v>
@@ -3006,7 +3024,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>5</v>
@@ -3020,7 +3038,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>5</v>
@@ -3034,7 +3052,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>5</v>
@@ -3086,296 +3104,296 @@
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="3">
+      <c r="B20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="2">
         <v>2</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="2">
         <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C21" s="3">
-        <v>3</v>
-      </c>
-      <c r="D21" s="3">
+      <c r="B21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="2">
+        <v>3</v>
+      </c>
+      <c r="D21" s="2">
         <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="2">
+        <v>3</v>
+      </c>
+      <c r="D22" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C22" s="3">
-        <v>3</v>
-      </c>
-      <c r="D22" s="3">
+      <c r="B23" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="2">
+        <v>3</v>
+      </c>
+      <c r="D23" s="2">
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="3" t="s">
+    <row r="24" spans="1:4">
+      <c r="A24" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C23" s="3">
-        <v>3</v>
-      </c>
-      <c r="D23" s="3">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C24" s="3">
-        <v>3</v>
-      </c>
-      <c r="D24" s="3">
+      <c r="B24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" s="2">
+        <v>3</v>
+      </c>
+      <c r="D24" s="2">
         <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C25" s="3">
+      <c r="B25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" s="2">
         <v>4</v>
       </c>
-      <c r="D25" s="3">
+      <c r="D25" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C26" s="3">
+      <c r="A26" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="2">
         <v>4</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C27" s="3">
-        <v>5</v>
-      </c>
-      <c r="D27" s="3">
+      <c r="B27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" s="2">
+        <v>5</v>
+      </c>
+      <c r="D27" s="2">
         <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C28" s="3">
-        <v>5</v>
-      </c>
-      <c r="D28" s="3">
+      <c r="B28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C28" s="2">
+        <v>5</v>
+      </c>
+      <c r="D28" s="2">
         <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C29" s="3">
+      <c r="A29" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C29" s="2">
         <v>6</v>
       </c>
-      <c r="D29" s="3">
+      <c r="D29" s="2">
         <v>15</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="3"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="3"/>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3">
+      <c r="A32" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2">
         <f>AVERAGE(D20:D29)</f>
         <v>14.4</v>
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="5" t="s">
+      <c r="A35" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="C35" s="3">
+        <v>3</v>
+      </c>
+      <c r="D35" s="3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C35" s="5">
-        <v>3</v>
-      </c>
-      <c r="D35" s="5">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" s="5" t="s">
+      <c r="B36" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C36" s="3">
+        <v>4</v>
+      </c>
+      <c r="D36" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C37" s="3">
+        <v>4</v>
+      </c>
+      <c r="D37" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C36" s="5">
+      <c r="B38" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C38" s="3">
         <v>4</v>
       </c>
-      <c r="D36" s="5">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
-      <c r="A37" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C37" s="5">
-        <v>4</v>
-      </c>
-      <c r="D37" s="5">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
-      <c r="A38" s="5" t="s">
+      <c r="D38" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C38" s="5">
-        <v>4</v>
-      </c>
-      <c r="D38" s="5">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C39" s="5">
-        <v>5</v>
-      </c>
-      <c r="D39" s="5">
+      <c r="B39" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C39" s="3">
+        <v>5</v>
+      </c>
+      <c r="D39" s="3">
         <v>13</v>
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C40" s="5">
+      <c r="A40" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C40" s="3">
         <v>6</v>
       </c>
-      <c r="D40" s="5">
+      <c r="D40" s="3">
         <v>13</v>
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="5" t="s">
+      <c r="A41" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C41" s="3">
+        <v>8</v>
+      </c>
+      <c r="D41" s="3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="3"/>
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="3"/>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B44" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B41" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C41" s="5">
-        <v>8</v>
-      </c>
-      <c r="D41" s="5">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
-      <c r="A42" s="5"/>
-      <c r="B42" s="5"/>
-      <c r="C42" s="5"/>
-      <c r="D42" s="5"/>
-    </row>
-    <row r="43" spans="1:4">
-      <c r="A43" s="5"/>
-      <c r="B43" s="5"/>
-      <c r="C43" s="5"/>
-      <c r="D43" s="5"/>
-    </row>
-    <row r="44" spans="1:4">
-      <c r="A44" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C44" s="5"/>
-      <c r="D44" s="5">
+      <c r="C44" s="3"/>
+      <c r="D44" s="3">
         <f>AVERAGE(D35:D41)</f>
         <v>12.8571428571429</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D47">
         <f>AVERAGE(D2:D14,D20:D29,D35:D41)</f>
@@ -3391,7 +3409,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="16.375" customWidth="1"/>
@@ -3423,32 +3441,32 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="1">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="B4" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C4" s="1">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B5" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" s="1">
         <v>16</v>
@@ -3456,257 +3474,224 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B6" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C6" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B7" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C7" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="1">
+        <f>AVERAGE(C2:C7)</f>
+        <v>15.8333333333333</v>
+      </c>
+      <c r="D10" s="2"/>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="2">
+        <v>2</v>
+      </c>
+      <c r="C13" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="2">
+        <v>3</v>
+      </c>
+      <c r="C14" s="2">
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="1">
-        <v>5</v>
-      </c>
-      <c r="C8" s="1">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="1">
-        <v>5</v>
-      </c>
-      <c r="C9" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="1">
-        <f>AVERAGE(C2:C9)</f>
-        <v>15.125</v>
-      </c>
-      <c r="D12" s="3"/>
-    </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="2">
+        <v>4</v>
+      </c>
+      <c r="C15" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="2">
+        <v>6</v>
+      </c>
+      <c r="C16" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="2">
+        <v>6</v>
+      </c>
+      <c r="C17" s="2">
         <v>14</v>
       </c>
-      <c r="B15" s="3">
-        <v>2</v>
-      </c>
-      <c r="C15" s="3">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" s="3">
-        <v>3</v>
-      </c>
-      <c r="C16" s="3">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B17" s="3">
-        <v>3</v>
-      </c>
-      <c r="C17" s="3">
-        <v>15</v>
-      </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" s="3">
-        <v>4</v>
-      </c>
-      <c r="C18" s="3">
-        <v>13</v>
-      </c>
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" s="3">
-        <v>6</v>
-      </c>
-      <c r="C19" s="3">
-        <v>15</v>
-      </c>
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B20" s="3">
-        <v>6</v>
-      </c>
-      <c r="C20" s="3">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
+      <c r="A20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" s="2">
+        <f>AVERAGE(C13:C17)</f>
+        <v>15</v>
+      </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>27</v>
+        <v>57</v>
+      </c>
+      <c r="B23" s="3">
+        <v>1</v>
       </c>
       <c r="C23" s="3">
-        <f>AVERAGE(C15:C20)</f>
-        <v>15</v>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B24" s="3">
+        <v>2</v>
+      </c>
+      <c r="C24" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B25" s="3">
+        <v>2</v>
+      </c>
+      <c r="C25" s="3">
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B26" s="5">
-        <v>1</v>
-      </c>
-      <c r="C26" s="5">
-        <v>13</v>
+      <c r="A26" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B26" s="3">
+        <v>2</v>
+      </c>
+      <c r="C26" s="3">
+        <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="B27" s="5">
+      <c r="A27" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B27" s="3">
         <v>2</v>
       </c>
-      <c r="C27" s="5">
-        <v>14</v>
+      <c r="C27" s="3">
+        <v>13</v>
       </c>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B28" s="5">
-        <v>2</v>
-      </c>
-      <c r="C28" s="5">
-        <v>12</v>
+      <c r="A28" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B28" s="3">
+        <v>5</v>
+      </c>
+      <c r="C28" s="3">
+        <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B29" s="5">
-        <v>2</v>
-      </c>
-      <c r="C29" s="5">
-        <v>14</v>
-      </c>
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B30" s="5">
-        <v>2</v>
-      </c>
-      <c r="C30" s="5">
-        <v>13</v>
-      </c>
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B31" s="5">
-        <v>5</v>
-      </c>
-      <c r="C31" s="5">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="6"/>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="6"/>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
+      <c r="A31" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31" s="3">
+        <f>AVERAGE(C23:C28)</f>
+        <v>13.1666666666667</v>
+      </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="5" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="C34" s="5">
-        <f>AVERAGE(C26:C31)</f>
-        <v>13.1666666666667</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C37" s="7">
-        <f>AVERAGE(C2:C9,C15:C20,C26:C31)</f>
-        <v>14.5</v>
+        <f>AVERAGE(C2:C7,C13:C17,C23:C28)</f>
+        <v>14.6470588235294</v>
       </c>
     </row>
   </sheetData>
@@ -3739,7 +3724,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
@@ -3750,7 +3735,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
@@ -3782,14 +3767,14 @@
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
@@ -3804,178 +3789,178 @@
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="2">
         <v>2</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="2">
         <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="2">
         <v>2</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="2">
         <v>2</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="2">
         <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="2">
+        <v>3</v>
+      </c>
+      <c r="C14" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="2">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="3">
-        <v>3</v>
-      </c>
-      <c r="C14" s="3">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="3">
-        <v>3</v>
-      </c>
-      <c r="C15" s="3">
+      <c r="B16" s="2">
+        <v>4</v>
+      </c>
+      <c r="C16" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="2">
+        <v>5</v>
+      </c>
+      <c r="C17" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="2">
+        <v>5</v>
+      </c>
+      <c r="C18" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="2">
+        <v>7</v>
+      </c>
+      <c r="C19" s="2">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" s="3">
-        <v>4</v>
-      </c>
-      <c r="C16" s="3">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B17" s="3">
-        <v>5</v>
-      </c>
-      <c r="C17" s="3">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" s="3">
-        <v>5</v>
-      </c>
-      <c r="C18" s="3">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="3" t="s">
+    <row r="20" spans="1:3">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="3">
-        <v>7</v>
-      </c>
-      <c r="C19" s="3">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C22" s="3">
+      <c r="C22" s="2">
         <f>AVERAGE(C11:C19)</f>
         <v>13.4444444444444</v>
       </c>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B25" s="5">
+      <c r="B25" s="3">
         <v>1</v>
       </c>
-      <c r="C25" s="5">
+      <c r="C25" s="3">
         <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B26" s="5">
+      <c r="B26" s="3">
         <v>7</v>
       </c>
-      <c r="C26" s="5">
+      <c r="C26" s="3">
         <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="6"/>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="6"/>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C29" s="5">
+      <c r="A29" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="3">
         <f>AVERAGE(C25:C26)</f>
         <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="7" t="s">
+      <c r="A32" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C32" s="7">
+      <c r="C32" s="5">
         <f>AVERAGE(C2:C5,C11:C19,C25:C26)</f>
         <v>13.5333333333333</v>
       </c>
@@ -4010,245 +3995,245 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
       </c>
       <c r="C2" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="B3" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C3" s="1">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="B4" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C4" s="1">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B5" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="B6" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" s="1">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="B7" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" s="1">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="B8" s="1">
         <v>3</v>
       </c>
       <c r="C8" s="1">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="1" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B9" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" s="1">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B10" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C10" s="1">
         <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
+      <c r="A11" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B11" s="1">
+        <v>3</v>
+      </c>
+      <c r="C11" s="1">
+        <v>13</v>
+      </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
+      <c r="A12" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B12" s="1">
+        <v>4</v>
+      </c>
+      <c r="C12" s="1">
+        <v>15</v>
+      </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="1">
-        <f>AVERAGE(C2:C10)</f>
-        <v>13.7777777777778</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B16" s="3">
-        <v>3</v>
-      </c>
-      <c r="C16" s="3">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" s="1">
+        <f>AVERAGE(C2:C12)</f>
+        <v>14.2727272727273</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" s="2">
+        <v>3</v>
+      </c>
+      <c r="C18" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" s="2">
+        <v>3</v>
+      </c>
+      <c r="C19" s="2">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B17" s="3">
-        <v>3</v>
-      </c>
-      <c r="C17" s="3">
+    <row r="20" spans="1:3">
+      <c r="A20" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" s="2">
+        <v>4</v>
+      </c>
+      <c r="C20" s="2">
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B18" s="3">
+    <row r="21" spans="1:3">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" s="2">
+        <f>AVERAGE(C18:C20)</f>
+        <v>14.3333333333333</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B26" s="3">
         <v>4</v>
       </c>
-      <c r="C18" s="3">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B19" s="3">
-        <v>4</v>
-      </c>
-      <c r="C19" s="3">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B20" s="3">
-        <v>5</v>
-      </c>
-      <c r="C20" s="3">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C23" s="3">
-        <f>AVERAGE(C16:C20)</f>
-        <v>13.2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B26" s="5">
-        <v>4</v>
-      </c>
-      <c r="C26" s="5">
-        <v>12</v>
+      <c r="C26" s="3">
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="6"/>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="6"/>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C29" s="5">
+      <c r="A29" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="3">
         <f>AVERAGE(C26:C26)</f>
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="7" t="s">
+      <c r="A32" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C32" s="7">
-        <f>AVERAGE(C2:C10,C16:C20,C26:C26)</f>
-        <v>13.4666666666667</v>
+      <c r="C32" s="5">
+        <f>AVERAGE(C2:C12,C18:C20,C26:C26)</f>
+        <v>13.7333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -4260,7 +4245,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="D1:F32"/>
+  <dimension ref="D1:F33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="4" max="4" width="13.125" customWidth="1"/>
@@ -4281,7 +4266,7 @@
     </row>
     <row r="2" spans="4:6">
       <c r="D2" s="1" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="E2" s="1">
         <v>1</v>
@@ -4292,7 +4277,7 @@
     </row>
     <row r="3" spans="4:6">
       <c r="D3" s="1" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="E3" s="1">
         <v>1</v>
@@ -4303,7 +4288,7 @@
     </row>
     <row r="4" spans="4:6">
       <c r="D4" s="1" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="E4" s="1">
         <v>2</v>
@@ -4314,7 +4299,7 @@
     </row>
     <row r="5" spans="4:6">
       <c r="D5" s="1" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="E5" s="1">
         <v>2</v>
@@ -4325,7 +4310,7 @@
     </row>
     <row r="6" spans="4:6">
       <c r="D6" s="1" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
@@ -4336,190 +4321,201 @@
     </row>
     <row r="7" spans="4:6">
       <c r="D7" s="1" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="E7" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="4:6">
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+    </row>
+    <row r="9" spans="4:6">
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+    </row>
+    <row r="10" spans="4:6">
+      <c r="D10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="1">
+        <f>AVERAGE(F2:F7)</f>
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="13" spans="4:6">
+      <c r="D13" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E13" s="2">
+        <v>2</v>
+      </c>
+      <c r="F13" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="4:6">
+      <c r="D14" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E14" s="2">
+        <v>2</v>
+      </c>
+      <c r="F14" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="4:6">
+      <c r="D15" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E15" s="2">
+        <v>3</v>
+      </c>
+      <c r="F15" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="4:6">
+      <c r="D16" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E16" s="2">
+        <v>3</v>
+      </c>
+      <c r="F16" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="4:6">
+      <c r="D17" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E17" s="2">
+        <v>4</v>
+      </c>
+      <c r="F17" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="4:6">
+      <c r="D18" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E18" s="2">
+        <v>5</v>
+      </c>
+      <c r="F18" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="4:6">
+      <c r="D19" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E19" s="2">
+        <v>5</v>
+      </c>
+      <c r="F19" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="4:6">
+      <c r="D20" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E20" s="2">
+        <v>6</v>
+      </c>
+      <c r="F20" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="4:6">
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+    </row>
+    <row r="22" spans="4:6">
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+    </row>
+    <row r="23" spans="4:6">
+      <c r="D23" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F23" s="2">
+        <f>AVERAGE(F13:F20)</f>
+        <v>12.25</v>
+      </c>
+    </row>
+    <row r="26" spans="4:6">
+      <c r="D26" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E26" s="4">
+        <v>2</v>
+      </c>
+      <c r="F26" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="4:6">
+      <c r="D27" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E27" s="3">
+        <v>2</v>
+      </c>
+      <c r="F27" s="3">
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="4:6">
-      <c r="D8" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E8" s="1">
-        <v>4</v>
-      </c>
-      <c r="F8" s="1">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="4:6">
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-    </row>
-    <row r="10" spans="4:6">
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-    </row>
-    <row r="11" spans="4:6">
-      <c r="D11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="1">
-        <f>AVERAGE(F2:F8)</f>
-        <v>13.1428571428571</v>
-      </c>
-    </row>
-    <row r="14" spans="4:6">
-      <c r="D14" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E14" s="3">
-        <v>2</v>
-      </c>
-      <c r="F14" s="3">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="4:6">
-      <c r="D15" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E15" s="3">
-        <v>2</v>
-      </c>
-      <c r="F15" s="3">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="4:6">
-      <c r="D16" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E16" s="3">
-        <v>3</v>
-      </c>
-      <c r="F16" s="3">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="4:6">
-      <c r="D17" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E17" s="3">
-        <v>3</v>
-      </c>
-      <c r="F17" s="3">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="4:6">
-      <c r="D18" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="E18" s="3">
-        <v>4</v>
-      </c>
-      <c r="F18" s="3">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="4:6">
-      <c r="D19" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="E19" s="3">
-        <v>5</v>
-      </c>
-      <c r="F19" s="3">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="4:6">
-      <c r="D20" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="E20" s="3">
-        <v>5</v>
-      </c>
-      <c r="F20" s="3">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="4:6">
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-    </row>
-    <row r="22" spans="4:6">
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-    </row>
-    <row r="23" spans="4:6">
-      <c r="D23" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F23" s="3">
-        <f>AVERAGE(F14:F20)</f>
-        <v>12.1428571428571</v>
-      </c>
-    </row>
-    <row r="26" spans="4:6">
-      <c r="D26" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="E26" s="5">
-        <v>2</v>
-      </c>
-      <c r="F26" s="5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="4:6">
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-    </row>
     <row r="28" spans="4:6">
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
     </row>
     <row r="29" spans="4:6">
-      <c r="D29" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F29" s="5">
-        <f>AVERAGE(F26:F26)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32" spans="4:6">
-      <c r="D32" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E32" s="7" t="s">
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+    </row>
+    <row r="30" spans="4:6">
+      <c r="D30" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F30" s="3">
+        <f>AVERAGE(F26,F27)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="4:6">
+      <c r="D33" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E33" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="F32" s="7">
-        <f>AVERAGE(F2:F8,F14:F20,F26:F26)</f>
-        <v>12.1333333333333</v>
+      <c r="F33" s="5">
+        <f>AVERAGE(F2,F3,F4,F5,F6,F7,F13:F20,F26:F27)</f>
+        <v>12.1875</v>
       </c>
     </row>
   </sheetData>

--- a/src/utils/sxsyzlzq/zzz_cardList.xlsx
+++ b/src/utils/sxsyzlzq/zzz_cardList.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28245" windowHeight="12345" activeTab="6"/>
+    <workbookView windowWidth="28245" windowHeight="12345" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="伊萝莲" sheetId="1" r:id="rId1"/>
@@ -15,13 +15,15 @@
     <sheet name="隐秘" sheetId="6" r:id="rId6"/>
     <sheet name="禅意" sheetId="7" r:id="rId7"/>
     <sheet name="炼狱" sheetId="8" r:id="rId8"/>
+    <sheet name="熙" sheetId="9" r:id="rId9"/>
+    <sheet name="希拉" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="91">
   <si>
     <t>名称</t>
   </si>
@@ -291,6 +293,9 @@
   </si>
   <si>
     <t>橙色色卡等：</t>
+  </si>
+  <si>
+    <t>怨魂饕餮兽</t>
   </si>
 </sst>
 </file>
@@ -298,9 +303,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
@@ -327,6 +332,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFFC000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="5"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -334,21 +346,44 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFFC000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -362,76 +397,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -439,7 +406,7 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -461,10 +428,40 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -473,6 +470,14 @@
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -493,7 +498,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -505,13 +534,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -523,7 +594,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -535,25 +618,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -565,67 +654,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -637,43 +678,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -689,35 +694,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
       <bottom style="double">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -746,6 +727,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -757,6 +747,30 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -775,15 +789,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -792,10 +797,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -804,137 +809,137 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -947,13 +952,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1620,7 +1622,7 @@
       <c r="D28" s="2">
         <v>14</v>
       </c>
-      <c r="F28" s="6"/>
+      <c r="F28" s="3"/>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2"/>
@@ -1648,138 +1650,138 @@
       </c>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="3" t="s">
+      <c r="A34" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C34" s="3">
-        <v>3</v>
-      </c>
-      <c r="D34" s="3">
+      <c r="C34" s="4">
+        <v>3</v>
+      </c>
+      <c r="D34" s="4">
         <v>13</v>
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="3" t="s">
+      <c r="A35" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C35" s="3">
+      <c r="C35" s="4">
         <v>4</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="4">
         <v>14</v>
       </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="3" t="s">
+      <c r="A36" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C36" s="3">
+      <c r="C36" s="4">
         <v>4</v>
       </c>
-      <c r="D36" s="3">
+      <c r="D36" s="4">
         <v>12</v>
       </c>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="3" t="s">
+      <c r="A37" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="3">
-        <v>5</v>
-      </c>
-      <c r="D37" s="3">
+      <c r="C37" s="4">
+        <v>5</v>
+      </c>
+      <c r="D37" s="4">
         <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="3" t="s">
+      <c r="A38" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C38" s="3">
-        <v>5</v>
-      </c>
-      <c r="D38" s="3">
+      <c r="C38" s="4">
+        <v>5</v>
+      </c>
+      <c r="D38" s="4">
         <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="3" t="s">
+      <c r="A39" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C39" s="3">
+      <c r="C39" s="4">
         <v>6</v>
       </c>
-      <c r="D39" s="3">
+      <c r="D39" s="4">
         <v>13</v>
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="3" t="s">
+      <c r="A40" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B40" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C40" s="3">
+      <c r="C40" s="4">
         <v>7</v>
       </c>
-      <c r="D40" s="3">
+      <c r="D40" s="4">
         <v>12</v>
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="3" t="s">
+      <c r="A41" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B41" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C41" s="3">
+      <c r="C41" s="4">
         <v>8</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="4">
         <v>13</v>
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="3"/>
-      <c r="B42" s="3"/>
-      <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
+      <c r="A42" s="4"/>
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="3"/>
-      <c r="B43" s="3"/>
-      <c r="C43" s="3"/>
-      <c r="D43" s="3"/>
+      <c r="A43" s="4"/>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B44" s="3" t="s">
+      <c r="A44" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B44" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C44" s="3"/>
-      <c r="D44" s="3">
+      <c r="C44" s="4"/>
+      <c r="D44" s="4">
         <f>AVERAGE(D34:D41)</f>
         <v>12.875</v>
       </c>
@@ -1798,6 +1800,549 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F47"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="17.875" customWidth="1"/>
+    <col min="4" max="4" width="12.625"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="1">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="1">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2</v>
+      </c>
+      <c r="D7" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2</v>
+      </c>
+      <c r="D8" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2</v>
+      </c>
+      <c r="D9" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2</v>
+      </c>
+      <c r="D10" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2</v>
+      </c>
+      <c r="D11" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="1">
+        <v>2</v>
+      </c>
+      <c r="D12" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="1">
+        <v>3</v>
+      </c>
+      <c r="D13" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="1">
+        <v>3</v>
+      </c>
+      <c r="D14" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="1">
+        <v>3</v>
+      </c>
+      <c r="D15" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="1">
+        <v>3</v>
+      </c>
+      <c r="D16" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="1">
+        <v>4</v>
+      </c>
+      <c r="D17" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="1">
+        <v>4</v>
+      </c>
+      <c r="D18" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1">
+        <f>AVERAGE(D2:D18)</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" customFormat="1"/>
+    <row r="23" customFormat="1"/>
+    <row r="24" spans="1:4">
+      <c r="A24" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" s="2">
+        <v>2</v>
+      </c>
+      <c r="D24" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" s="2">
+        <v>2</v>
+      </c>
+      <c r="D25" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="2">
+        <v>3</v>
+      </c>
+      <c r="D26" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" s="2">
+        <v>3</v>
+      </c>
+      <c r="D27" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C28" s="2">
+        <v>3</v>
+      </c>
+      <c r="D28" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C29" s="2">
+        <v>3</v>
+      </c>
+      <c r="D29" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="2">
+        <v>4</v>
+      </c>
+      <c r="D30" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C31" s="2">
+        <v>4</v>
+      </c>
+      <c r="D31" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" s="2">
+        <v>5</v>
+      </c>
+      <c r="D32" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C33" s="2">
+        <v>5</v>
+      </c>
+      <c r="D33" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C34" s="2">
+        <v>6</v>
+      </c>
+      <c r="D34" s="2">
+        <v>11</v>
+      </c>
+      <c r="F34" s="3"/>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2">
+        <f>AVERAGE(D24:D34)</f>
+        <v>12.7272727272727</v>
+      </c>
+    </row>
+    <row r="38" customFormat="1"/>
+    <row r="39" customFormat="1"/>
+    <row r="40" spans="1:4">
+      <c r="A40" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C40" s="4">
+        <v>2</v>
+      </c>
+      <c r="D40" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C41" s="4">
+        <v>5</v>
+      </c>
+      <c r="D41" s="4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="4"/>
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="4"/>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4">
+        <f>AVERAGE(D40:D41)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" customFormat="1"/>
+    <row r="46" customFormat="1"/>
+    <row r="47" spans="1:4">
+      <c r="A47" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B47" s="5"/>
+      <c r="C47" s="5"/>
+      <c r="D47" s="5">
+        <f>AVERAGE(D2:D18,D24:D34,D40:D41)</f>
+        <v>13.1333333333333</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -2213,110 +2758,110 @@
       </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="3" t="s">
+      <c r="A36" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C36" s="3">
-        <v>3</v>
-      </c>
-      <c r="D36" s="3">
+      <c r="C36" s="4">
+        <v>3</v>
+      </c>
+      <c r="D36" s="4">
         <v>13</v>
       </c>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="3" t="s">
+      <c r="A37" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="3">
+      <c r="C37" s="4">
         <v>4</v>
       </c>
-      <c r="D37" s="3">
+      <c r="D37" s="4">
         <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="3" t="s">
+      <c r="A38" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C38" s="3">
+      <c r="C38" s="4">
         <v>4</v>
       </c>
-      <c r="D38" s="3">
+      <c r="D38" s="4">
         <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="3" t="s">
+      <c r="A39" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C39" s="3">
-        <v>5</v>
-      </c>
-      <c r="D39" s="3">
+      <c r="C39" s="4">
+        <v>5</v>
+      </c>
+      <c r="D39" s="4">
         <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="3" t="s">
+      <c r="A40" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B40" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C40" s="3">
+      <c r="C40" s="4">
         <v>6</v>
       </c>
-      <c r="D40" s="3">
+      <c r="D40" s="4">
         <v>13</v>
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="3" t="s">
+      <c r="A41" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B41" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C41" s="3">
+      <c r="C41" s="4">
         <v>7</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="4">
         <v>12</v>
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="3"/>
-      <c r="B42" s="3"/>
-      <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
+      <c r="A42" s="4"/>
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="3"/>
-      <c r="B43" s="3"/>
-      <c r="C43" s="3"/>
-      <c r="D43" s="3"/>
+      <c r="A43" s="4"/>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B44" s="3" t="s">
+      <c r="A44" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B44" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C44" s="3"/>
-      <c r="D44" s="3">
+      <c r="C44" s="4"/>
+      <c r="D44" s="4">
         <f>AVERAGE(D36:D41)</f>
         <v>12.6666666666667</v>
       </c>
@@ -2734,124 +3279,124 @@
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="3" t="s">
+      <c r="A35" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C35" s="3">
-        <v>3</v>
-      </c>
-      <c r="D35" s="3">
+      <c r="C35" s="4">
+        <v>3</v>
+      </c>
+      <c r="D35" s="4">
         <v>13</v>
       </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="3" t="s">
+      <c r="A36" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C36" s="3">
+      <c r="C36" s="4">
         <v>4</v>
       </c>
-      <c r="D36" s="3">
+      <c r="D36" s="4">
         <v>14</v>
       </c>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="3" t="s">
+      <c r="A37" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="3">
+      <c r="C37" s="4">
         <v>4</v>
       </c>
-      <c r="D37" s="3">
+      <c r="D37" s="4">
         <v>12</v>
       </c>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="3" t="s">
+      <c r="A38" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C38" s="3">
+      <c r="C38" s="4">
         <v>4</v>
       </c>
-      <c r="D38" s="3">
+      <c r="D38" s="4">
         <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="3" t="s">
+      <c r="A39" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C39" s="3">
-        <v>5</v>
-      </c>
-      <c r="D39" s="3">
+      <c r="C39" s="4">
+        <v>5</v>
+      </c>
+      <c r="D39" s="4">
         <v>14</v>
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="3" t="s">
+      <c r="A40" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B40" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C40" s="3">
+      <c r="C40" s="4">
         <v>6</v>
       </c>
-      <c r="D40" s="3">
+      <c r="D40" s="4">
         <v>13</v>
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="3" t="s">
+      <c r="A41" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B41" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C41" s="3">
+      <c r="C41" s="4">
         <v>8</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="4">
         <v>13</v>
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="3"/>
-      <c r="B42" s="3"/>
-      <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
+      <c r="A42" s="4"/>
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="3"/>
-      <c r="B43" s="3"/>
-      <c r="C43" s="3"/>
-      <c r="D43" s="3"/>
+      <c r="A43" s="4"/>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B44" s="3" t="s">
+      <c r="A44" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B44" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C44" s="3"/>
-      <c r="D44" s="3">
+      <c r="C44" s="4"/>
+      <c r="D44" s="4">
         <f>AVERAGE(D35:D41)</f>
         <v>13</v>
       </c>
@@ -3269,124 +3814,124 @@
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="3" t="s">
+      <c r="A35" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C35" s="3">
-        <v>3</v>
-      </c>
-      <c r="D35" s="3">
+      <c r="C35" s="4">
+        <v>3</v>
+      </c>
+      <c r="D35" s="4">
         <v>13</v>
       </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="3" t="s">
+      <c r="A36" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C36" s="3">
+      <c r="C36" s="4">
         <v>4</v>
       </c>
-      <c r="D36" s="3">
+      <c r="D36" s="4">
         <v>14</v>
       </c>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="3" t="s">
+      <c r="A37" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="3">
+      <c r="C37" s="4">
         <v>4</v>
       </c>
-      <c r="D37" s="3">
+      <c r="D37" s="4">
         <v>12</v>
       </c>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="3" t="s">
+      <c r="A38" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C38" s="3">
+      <c r="C38" s="4">
         <v>4</v>
       </c>
-      <c r="D38" s="3">
+      <c r="D38" s="4">
         <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="3" t="s">
+      <c r="A39" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C39" s="3">
-        <v>5</v>
-      </c>
-      <c r="D39" s="3">
+      <c r="C39" s="4">
+        <v>5</v>
+      </c>
+      <c r="D39" s="4">
         <v>13</v>
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="3" t="s">
+      <c r="A40" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B40" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C40" s="3">
+      <c r="C40" s="4">
         <v>6</v>
       </c>
-      <c r="D40" s="3">
+      <c r="D40" s="4">
         <v>13</v>
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="3" t="s">
+      <c r="A41" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B41" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C41" s="3">
+      <c r="C41" s="4">
         <v>8</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="4">
         <v>13</v>
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="3"/>
-      <c r="B42" s="3"/>
-      <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
+      <c r="A42" s="4"/>
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="3"/>
-      <c r="B43" s="3"/>
-      <c r="C43" s="3"/>
-      <c r="D43" s="3"/>
+      <c r="A43" s="4"/>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B44" s="3" t="s">
+      <c r="A44" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B44" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C44" s="3"/>
-      <c r="D44" s="3">
+      <c r="C44" s="4"/>
+      <c r="D44" s="4">
         <f>AVERAGE(D35:D41)</f>
         <v>12.8571428571429</v>
       </c>
@@ -3595,89 +4140,89 @@
       </c>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B23" s="3">
+      <c r="B23" s="4">
         <v>1</v>
       </c>
-      <c r="C23" s="3">
+      <c r="C23" s="4">
         <v>13</v>
       </c>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B24" s="3">
-        <v>2</v>
-      </c>
-      <c r="C24" s="3">
+      <c r="B24" s="4">
+        <v>2</v>
+      </c>
+      <c r="C24" s="4">
         <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B25" s="3">
-        <v>2</v>
-      </c>
-      <c r="C25" s="3">
+      <c r="B25" s="4">
+        <v>2</v>
+      </c>
+      <c r="C25" s="4">
         <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B26" s="3">
-        <v>2</v>
-      </c>
-      <c r="C26" s="3">
+      <c r="B26" s="4">
+        <v>2</v>
+      </c>
+      <c r="C26" s="4">
         <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B27" s="3">
-        <v>2</v>
-      </c>
-      <c r="C27" s="3">
+      <c r="B27" s="4">
+        <v>2</v>
+      </c>
+      <c r="C27" s="4">
         <v>13</v>
       </c>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B28" s="3">
-        <v>5</v>
-      </c>
-      <c r="C28" s="3">
+      <c r="B28" s="4">
+        <v>5</v>
+      </c>
+      <c r="C28" s="4">
         <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
+      <c r="A29" s="4"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="3"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
+      <c r="A30" s="4"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C31" s="3">
+      <c r="A31" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31" s="4">
         <f>AVERAGE(C23:C28)</f>
         <v>13.1666666666667</v>
       </c>
@@ -3910,45 +4455,45 @@
       </c>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="B25" s="3">
+      <c r="B25" s="4">
         <v>1</v>
       </c>
-      <c r="C25" s="3">
+      <c r="C25" s="4">
         <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B26" s="3">
+      <c r="B26" s="4">
         <v>7</v>
       </c>
-      <c r="C26" s="3">
+      <c r="C26" s="4">
         <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
+      <c r="A27" s="4"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
+      <c r="A28" s="4"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C29" s="3">
+      <c r="A29" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="4">
         <f>AVERAGE(C25:C26)</f>
         <v>12</v>
       </c>
@@ -4192,34 +4737,34 @@
       </c>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B26" s="3">
+      <c r="B26" s="4">
         <v>4</v>
       </c>
-      <c r="C26" s="3">
+      <c r="C26" s="4">
         <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
+      <c r="A27" s="4"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
+      <c r="A28" s="4"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C29" s="3">
+      <c r="A29" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="4">
         <f>AVERAGE(C26:C26)</f>
         <v>6</v>
       </c>
@@ -4463,7 +5008,7 @@
       </c>
     </row>
     <row r="26" spans="4:6">
-      <c r="D26" s="3" t="s">
+      <c r="D26" s="4" t="s">
         <v>88</v>
       </c>
       <c r="E26" s="4">
@@ -4474,34 +5019,34 @@
       </c>
     </row>
     <row r="27" spans="4:6">
-      <c r="D27" s="3" t="s">
+      <c r="D27" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="E27" s="3">
-        <v>2</v>
-      </c>
-      <c r="F27" s="3">
+      <c r="E27" s="4">
+        <v>2</v>
+      </c>
+      <c r="F27" s="4">
         <v>11</v>
       </c>
     </row>
     <row r="28" spans="4:6">
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
     </row>
     <row r="29" spans="4:6">
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
     </row>
     <row r="30" spans="4:6">
-      <c r="D30" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E30" s="3" t="s">
+      <c r="D30" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E30" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="F30" s="3">
+      <c r="F30" s="4">
         <f>AVERAGE(F26,F27)</f>
         <v>8</v>
       </c>
@@ -4516,6 +5061,549 @@
       <c r="F33" s="5">
         <f>AVERAGE(F2,F3,F4,F5,F6,F7,F13:F20,F26:F27)</f>
         <v>12.1875</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F47"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="17.875" customWidth="1"/>
+    <col min="4" max="4" width="12.625"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="1">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="1">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2</v>
+      </c>
+      <c r="D7" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2</v>
+      </c>
+      <c r="D8" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2</v>
+      </c>
+      <c r="D9" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2</v>
+      </c>
+      <c r="D10" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2</v>
+      </c>
+      <c r="D11" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="1">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="1">
+        <v>3</v>
+      </c>
+      <c r="D13" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="1">
+        <v>3</v>
+      </c>
+      <c r="D14" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="1">
+        <v>3</v>
+      </c>
+      <c r="D15" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="1">
+        <v>4</v>
+      </c>
+      <c r="D16" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="1">
+        <v>4</v>
+      </c>
+      <c r="D17" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1">
+        <f>AVERAGE(D2:D17)</f>
+        <v>14.125</v>
+      </c>
+    </row>
+    <row r="21" customFormat="1"/>
+    <row r="22" customFormat="1"/>
+    <row r="23" spans="1:4">
+      <c r="A23" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="2">
+        <v>2</v>
+      </c>
+      <c r="D23" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" s="2">
+        <v>2</v>
+      </c>
+      <c r="D24" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" s="2">
+        <v>3</v>
+      </c>
+      <c r="D25" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="2">
+        <v>3</v>
+      </c>
+      <c r="D26" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" s="2">
+        <v>3</v>
+      </c>
+      <c r="D27" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C28" s="2">
+        <v>3</v>
+      </c>
+      <c r="D28" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C29" s="2">
+        <v>4</v>
+      </c>
+      <c r="D29" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="2">
+        <v>4</v>
+      </c>
+      <c r="D30" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C31" s="2">
+        <v>5</v>
+      </c>
+      <c r="D31" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" s="2">
+        <v>5</v>
+      </c>
+      <c r="D32" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C33" s="2">
+        <v>6</v>
+      </c>
+      <c r="D33" s="2">
+        <v>11</v>
+      </c>
+      <c r="F33" s="3"/>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2">
+        <f>AVERAGE(D23:D33)</f>
+        <v>12.7272727272727</v>
+      </c>
+    </row>
+    <row r="37" customFormat="1"/>
+    <row r="38" customFormat="1"/>
+    <row r="39" spans="1:4">
+      <c r="A39" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C39" s="4">
+        <v>2</v>
+      </c>
+      <c r="D39" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C40" s="4">
+        <v>4</v>
+      </c>
+      <c r="D40" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C41" s="4">
+        <v>5</v>
+      </c>
+      <c r="D41" s="4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="4"/>
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="4"/>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4">
+        <f>AVERAGE(D39:D41)</f>
+        <v>7.33333333333333</v>
+      </c>
+    </row>
+    <row r="45" customFormat="1"/>
+    <row r="46" customFormat="1"/>
+    <row r="47" spans="1:4">
+      <c r="A47" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B47" s="5"/>
+      <c r="C47" s="5"/>
+      <c r="D47" s="5">
+        <f>AVERAGE(D2:D17,D23:D33,D39:D41)</f>
+        <v>12.9333333333333</v>
       </c>
     </row>
   </sheetData>

--- a/src/utils/sxsyzlzq/zzz_cardList.xlsx
+++ b/src/utils/sxsyzlzq/zzz_cardList.xlsx
@@ -303,9 +303,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
@@ -346,29 +346,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
@@ -376,45 +353,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -429,22 +368,39 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -452,6 +408,20 @@
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -465,11 +435,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -482,8 +459,31 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -498,7 +498,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -510,73 +570,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -594,43 +606,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -642,25 +624,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -672,13 +654,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -694,10 +694,8 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -718,11 +716,52 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -750,45 +789,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -797,10 +797,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -809,133 +809,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1998,7 +1998,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>5</v>
@@ -2007,12 +2007,12 @@
         <v>3</v>
       </c>
       <c r="D14" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="1" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>5</v>
@@ -2021,26 +2021,26 @@
         <v>3</v>
       </c>
       <c r="D15" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C16" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D16" s="1">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="1" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>5</v>
@@ -2049,22 +2049,14 @@
         <v>4</v>
       </c>
       <c r="D17" s="1">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C18" s="1">
-        <v>4</v>
-      </c>
-      <c r="D18" s="1">
-        <v>13</v>
-      </c>
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="1"/>
@@ -2073,29 +2065,35 @@
       <c r="D19" s="1"/>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
+      <c r="A20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1">
-        <f>AVERAGE(D2:D18)</f>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22" customFormat="1"/>
-    <row r="23" customFormat="1"/>
+      <c r="D20" s="1">
+        <f>AVERAGE(D2:D17)</f>
+        <v>13.9375</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="2">
+        <v>2</v>
+      </c>
+      <c r="D23" s="2">
+        <v>13</v>
+      </c>
+    </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>15</v>
@@ -2104,26 +2102,26 @@
         <v>2</v>
       </c>
       <c r="D24" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2" t="s">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C25" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D25" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>15</v>
@@ -2132,12 +2130,12 @@
         <v>3</v>
       </c>
       <c r="D26" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>15</v>
@@ -2146,12 +2144,12 @@
         <v>3</v>
       </c>
       <c r="D27" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>15</v>
@@ -2165,21 +2163,21 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C29" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D29" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2" t="s">
-        <v>52</v>
+        <v>84</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>15</v>
@@ -2188,26 +2186,26 @@
         <v>4</v>
       </c>
       <c r="D30" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C31" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D31" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>15</v>
@@ -2216,37 +2214,29 @@
         <v>5</v>
       </c>
       <c r="D32" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
       <c r="A33" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C33" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D33" s="2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C34" s="2">
-        <v>6</v>
-      </c>
-      <c r="D34" s="2">
         <v>11</v>
       </c>
-      <c r="F34" s="3"/>
+      <c r="F33" s="3"/>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2"/>
@@ -2255,38 +2245,44 @@
       <c r="D35" s="2"/>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="2"/>
-      <c r="B36" s="2"/>
+      <c r="A36" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-    </row>
-    <row r="37" spans="1:4">
-      <c r="A37" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2">
-        <f>AVERAGE(D24:D34)</f>
+      <c r="D36" s="2">
+        <f>AVERAGE(D23:D33)</f>
         <v>12.7272727272727</v>
       </c>
     </row>
-    <row r="38" customFormat="1"/>
-    <row r="39" customFormat="1"/>
+    <row r="39" spans="1:4">
+      <c r="A39" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C39" s="4">
+        <v>2</v>
+      </c>
+      <c r="D39" s="4">
+        <v>7</v>
+      </c>
+    </row>
     <row r="40" spans="1:4">
       <c r="A40" s="4" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>28</v>
       </c>
       <c r="C40" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D40" s="4">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2324,12 +2320,10 @@
       </c>
       <c r="C44" s="4"/>
       <c r="D44" s="4">
-        <f>AVERAGE(D40:D41)</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="45" customFormat="1"/>
-    <row r="46" customFormat="1"/>
+        <f>AVERAGE(D39:D41)</f>
+        <v>9.66666666666667</v>
+      </c>
+    </row>
     <row r="47" spans="1:4">
       <c r="A47" s="5" t="s">
         <v>37</v>
@@ -2337,8 +2331,8 @@
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
       <c r="D47" s="5">
-        <f>AVERAGE(D2:D18,D24:D34,D40:D41)</f>
-        <v>13.1333333333333</v>
+        <f>AVERAGE(D2:D17,D23:D33,D39:D41)</f>
+        <v>13.0666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -5342,8 +5336,6 @@
         <v>14.125</v>
       </c>
     </row>
-    <row r="21" customFormat="1"/>
-    <row r="22" customFormat="1"/>
     <row r="23" spans="1:4">
       <c r="A23" s="2" t="s">
         <v>80</v>
@@ -5524,8 +5516,6 @@
         <v>12.7272727272727</v>
       </c>
     </row>
-    <row r="37" customFormat="1"/>
-    <row r="38" customFormat="1"/>
     <row r="39" spans="1:4">
       <c r="A39" s="4" t="s">
         <v>88</v>
@@ -5537,7 +5527,7 @@
         <v>2</v>
       </c>
       <c r="D39" s="4">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -5551,7 +5541,7 @@
         <v>4</v>
       </c>
       <c r="D40" s="4">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -5590,11 +5580,9 @@
       <c r="C44" s="4"/>
       <c r="D44" s="4">
         <f>AVERAGE(D39:D41)</f>
-        <v>7.33333333333333</v>
-      </c>
-    </row>
-    <row r="45" customFormat="1"/>
-    <row r="46" customFormat="1"/>
+        <v>9.66666666666667</v>
+      </c>
+    </row>
     <row r="47" spans="1:4">
       <c r="A47" s="5" t="s">
         <v>37</v>
@@ -5603,7 +5591,7 @@
       <c r="C47" s="5"/>
       <c r="D47" s="5">
         <f>AVERAGE(D2:D17,D23:D33,D39:D41)</f>
-        <v>12.9333333333333</v>
+        <v>13.1666666666667</v>
       </c>
     </row>
   </sheetData>

--- a/src/utils/sxsyzlzq/zzz_cardList.xlsx
+++ b/src/utils/sxsyzlzq/zzz_cardList.xlsx
@@ -4,26 +4,27 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28245" windowHeight="12345" activeTab="9"/>
+    <workbookView windowWidth="28245" windowHeight="12345" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="伊萝莲" sheetId="1" r:id="rId1"/>
     <sheet name="阿斯塔拉" sheetId="2" r:id="rId2"/>
-    <sheet name="梅" sheetId="3" r:id="rId3"/>
-    <sheet name="白处尊" sheetId="4" r:id="rId4"/>
+    <sheet name="熙" sheetId="9" r:id="rId3"/>
+    <sheet name="洛" sheetId="11" r:id="rId4"/>
     <sheet name="帝国" sheetId="5" r:id="rId5"/>
     <sheet name="隐秘" sheetId="6" r:id="rId6"/>
     <sheet name="禅意" sheetId="7" r:id="rId7"/>
     <sheet name="炼狱" sheetId="8" r:id="rId8"/>
-    <sheet name="熙" sheetId="9" r:id="rId9"/>
-    <sheet name="希拉" sheetId="10" r:id="rId10"/>
+    <sheet name="白处尊" sheetId="4" r:id="rId9"/>
+    <sheet name="梅" sheetId="3" r:id="rId10"/>
+    <sheet name="希拉" sheetId="10" r:id="rId11"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="95">
   <si>
     <t>名称</t>
   </si>
@@ -55,247 +56,259 @@
     <t>塔楼弓手</t>
   </si>
   <si>
+    <t>光明惩戒</t>
+  </si>
+  <si>
+    <t>小计：</t>
+  </si>
+  <si>
+    <t>蓝色卡等：</t>
+  </si>
+  <si>
+    <t>隐形术</t>
+  </si>
+  <si>
+    <t>紫色</t>
+  </si>
+  <si>
+    <t>圣殿御卫</t>
+  </si>
+  <si>
+    <t>破魔系教授</t>
+  </si>
+  <si>
+    <t>克隆术</t>
+  </si>
+  <si>
+    <t>边境高墙</t>
+  </si>
+  <si>
+    <t>学仆-脉冲型</t>
+  </si>
+  <si>
+    <t>幻域秘树</t>
+  </si>
+  <si>
+    <t>夺取阵地</t>
+  </si>
+  <si>
+    <t>召集护卫</t>
+  </si>
+  <si>
+    <t>观星台大预言家</t>
+  </si>
+  <si>
+    <t>惩戒天使</t>
+  </si>
+  <si>
+    <t>禁卫指挥官</t>
+  </si>
+  <si>
+    <t>米拉方舟</t>
+  </si>
+  <si>
+    <t>紫色卡等：</t>
+  </si>
+  <si>
+    <t>花光春影·安娜贝尔</t>
+  </si>
+  <si>
+    <t>橙色</t>
+  </si>
+  <si>
+    <t>百花长枪·卡罗琳</t>
+  </si>
+  <si>
+    <t>明日香·露娜</t>
+  </si>
+  <si>
+    <t>月之神·米拉</t>
+  </si>
+  <si>
+    <t>白袍·伊恩</t>
+  </si>
+  <si>
+    <t>火蛇巫女·沃凡瑞拉</t>
+  </si>
+  <si>
+    <t>武圣·云长</t>
+  </si>
+  <si>
+    <t>橙色卡等：</t>
+  </si>
+  <si>
+    <t>总计：</t>
+  </si>
+  <si>
+    <t>学仆-观测型</t>
+  </si>
+  <si>
+    <t>冥河守卫</t>
+  </si>
+  <si>
+    <t>卜命道长</t>
+  </si>
+  <si>
+    <t>箭竹守卫</t>
+  </si>
+  <si>
+    <t>落雷击</t>
+  </si>
+  <si>
+    <t>白羊药师</t>
+  </si>
+  <si>
+    <t>树木之怒</t>
+  </si>
+  <si>
+    <t>苦行武僧</t>
+  </si>
+  <si>
+    <t>残暴爪钩</t>
+  </si>
+  <si>
+    <t>邪眼魔</t>
+  </si>
+  <si>
+    <t>执剑道者</t>
+  </si>
+  <si>
+    <t>连击</t>
+  </si>
+  <si>
+    <t>深山采药人</t>
+  </si>
+  <si>
+    <t>疾风猎手</t>
+  </si>
+  <si>
+    <t>风铃道人</t>
+  </si>
+  <si>
+    <t>烈焰风暴</t>
+  </si>
+  <si>
+    <t>碎颅魔</t>
+  </si>
+  <si>
+    <t>觅食大嘴兽</t>
+  </si>
+  <si>
+    <t>扫叶僧</t>
+  </si>
+  <si>
+    <t>逍遥琴师</t>
+  </si>
+  <si>
+    <t>绝望镰魔</t>
+  </si>
+  <si>
+    <t>岩浆球</t>
+  </si>
+  <si>
+    <t>御风武者</t>
+  </si>
+  <si>
+    <t>灼神双炎</t>
+  </si>
+  <si>
+    <t>雷光炼狱</t>
+  </si>
+  <si>
+    <t>地狱屠夫</t>
+  </si>
+  <si>
+    <t>恶灵魔焰</t>
+  </si>
+  <si>
+    <t>痛苦之心</t>
+  </si>
+  <si>
+    <t>神机玄女·轩</t>
+  </si>
+  <si>
+    <t>怨魂饕餮兽</t>
+  </si>
+  <si>
+    <t>铁山靠</t>
+  </si>
+  <si>
+    <t>万物之灵</t>
+  </si>
+  <si>
+    <t>上宝沁金耙</t>
+  </si>
+  <si>
+    <t>火蛇巫女</t>
+  </si>
+  <si>
+    <t>曙光·安娜贝尔</t>
+  </si>
+  <si>
+    <t>圣枪·卡罗琳</t>
+  </si>
+  <si>
+    <t>明日之音·露娜</t>
+  </si>
+  <si>
+    <t>正阳大主教·伊恩</t>
+  </si>
+  <si>
+    <t>钢铁统帅·雷蒙德</t>
+  </si>
+  <si>
+    <t>帝国卡等：</t>
+  </si>
+  <si>
+    <t>No.2时光·米拉</t>
+  </si>
+  <si>
+    <t>No.6沃凡瑞拉</t>
+  </si>
+  <si>
+    <t>悟能禅杖</t>
+  </si>
+  <si>
+    <t>橙色色卡等：</t>
+  </si>
+  <si>
+    <t>旅行背包</t>
+  </si>
+  <si>
+    <t>重装固守</t>
+  </si>
+  <si>
+    <t>执剑道人</t>
+  </si>
+  <si>
     <t>圣殿弩手</t>
   </si>
   <si>
-    <t>光明惩戒</t>
-  </si>
-  <si>
-    <t>小计：</t>
-  </si>
-  <si>
-    <t>蓝色卡等：</t>
-  </si>
-  <si>
-    <t>圣殿御卫</t>
-  </si>
-  <si>
-    <t>紫色</t>
-  </si>
-  <si>
-    <t>破魔系教授</t>
-  </si>
-  <si>
-    <t>克隆术</t>
-  </si>
-  <si>
-    <t>边境高墙</t>
-  </si>
-  <si>
-    <t>学仆-脉冲型</t>
-  </si>
-  <si>
-    <t>幻域秘树</t>
-  </si>
-  <si>
-    <t>召集护卫</t>
-  </si>
-  <si>
-    <t>观星台大预言家</t>
-  </si>
-  <si>
-    <t>惩戒天使</t>
-  </si>
-  <si>
-    <t>禁卫指挥官</t>
-  </si>
-  <si>
-    <t>米拉方舟</t>
-  </si>
-  <si>
-    <t>紫色卡等：</t>
-  </si>
-  <si>
-    <t>花光春影·安娜贝尔</t>
-  </si>
-  <si>
-    <t>橙色</t>
-  </si>
-  <si>
-    <t>百花长枪·卡罗琳</t>
-  </si>
-  <si>
-    <t>明日香·露娜</t>
+    <t>龟族僧人</t>
+  </si>
+  <si>
+    <t>风卷残云</t>
+  </si>
+  <si>
+    <t>驱魔道人</t>
+  </si>
+  <si>
+    <t>冲锋装备</t>
+  </si>
+  <si>
+    <t>禁卫百夫长</t>
   </si>
   <si>
     <t>永恒之王·莱哈特</t>
   </si>
   <si>
-    <t>月之神·米拉</t>
-  </si>
-  <si>
-    <t>白袍·伊恩</t>
-  </si>
-  <si>
-    <t>火蛇巫女·沃凡瑞拉</t>
-  </si>
-  <si>
-    <t>武圣·云长</t>
-  </si>
-  <si>
-    <t>橙色卡等：</t>
-  </si>
-  <si>
-    <t>总计：</t>
-  </si>
-  <si>
-    <t>学仆-观测型</t>
-  </si>
-  <si>
-    <t>卜命道长</t>
-  </si>
-  <si>
-    <t>旅行背包</t>
-  </si>
-  <si>
-    <t>重装固守</t>
-  </si>
-  <si>
-    <t>执剑道人</t>
-  </si>
-  <si>
-    <t>连击</t>
-  </si>
-  <si>
-    <t>龟族僧人</t>
-  </si>
-  <si>
-    <t>深山采药人</t>
-  </si>
-  <si>
     <t>叶幻师</t>
   </si>
   <si>
-    <t>风卷残云</t>
-  </si>
-  <si>
     <t>祥云师太</t>
   </si>
   <si>
-    <t>驱魔道人</t>
-  </si>
-  <si>
-    <t>扫叶僧</t>
-  </si>
-  <si>
-    <t>冲锋装备</t>
-  </si>
-  <si>
-    <t>御风武者</t>
-  </si>
-  <si>
     <t>蟠桃会</t>
-  </si>
-  <si>
-    <t>万物之灵</t>
-  </si>
-  <si>
-    <t>上宝沁金耙</t>
-  </si>
-  <si>
-    <t>禁卫百夫长</t>
-  </si>
-  <si>
-    <t>曙光·安娜贝尔</t>
-  </si>
-  <si>
-    <t>圣枪·卡罗琳</t>
-  </si>
-  <si>
-    <t>明日之音·露娜</t>
-  </si>
-  <si>
-    <t>帝国军魂·莱哈特</t>
-  </si>
-  <si>
-    <t>正阳大主教·伊恩</t>
-  </si>
-  <si>
-    <t>钢铁统帅·雷蒙德</t>
-  </si>
-  <si>
-    <t>帝国卡等：</t>
-  </si>
-  <si>
-    <t>No.2时光·米拉</t>
-  </si>
-  <si>
-    <t>No.6沃凡瑞拉</t>
-  </si>
-  <si>
-    <t>箭竹守卫</t>
-  </si>
-  <si>
-    <t>白羊药师</t>
-  </si>
-  <si>
-    <t>树木之怒</t>
-  </si>
-  <si>
-    <t>苦行武僧</t>
-  </si>
-  <si>
-    <t>执剑道者</t>
-  </si>
-  <si>
-    <t>疾风猎手</t>
-  </si>
-  <si>
-    <t>风铃道人</t>
-  </si>
-  <si>
-    <t>逍遥琴师</t>
-  </si>
-  <si>
-    <t>神机玄女·轩</t>
-  </si>
-  <si>
-    <t>冥河守卫</t>
-  </si>
-  <si>
-    <t>落雷击</t>
-  </si>
-  <si>
-    <t>邪眼魔</t>
-  </si>
-  <si>
-    <t>残暴爪钩</t>
-  </si>
-  <si>
-    <t>烈焰风暴</t>
-  </si>
-  <si>
-    <t>碎颅魔</t>
-  </si>
-  <si>
-    <t>觅食大嘴兽</t>
-  </si>
-  <si>
-    <t>绝望镰魔</t>
-  </si>
-  <si>
-    <t>岩浆球</t>
-  </si>
-  <si>
-    <t>灼神双炎</t>
-  </si>
-  <si>
-    <t>雷光炼狱</t>
-  </si>
-  <si>
-    <t>地狱屠夫</t>
-  </si>
-  <si>
-    <t>恶灵魔焰</t>
-  </si>
-  <si>
-    <t>痛苦之心</t>
-  </si>
-  <si>
-    <t>橙色色卡等：</t>
-  </si>
-  <si>
-    <t>怨魂饕餮兽</t>
   </si>
 </sst>
 </file>
@@ -304,8 +317,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
@@ -352,8 +365,47 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -367,14 +419,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -384,44 +428,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -452,30 +459,21 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -484,6 +482,21 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -498,7 +511,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -510,7 +565,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -522,25 +613,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -558,19 +649,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -582,31 +661,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -618,31 +673,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -654,31 +691,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -689,6 +702,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -717,21 +745,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -748,20 +761,20 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -797,10 +810,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -809,133 +822,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1315,12 +1328,12 @@
         <v>2</v>
       </c>
       <c r="D3" s="1">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>5</v>
@@ -1334,7 +1347,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>5</v>
@@ -1343,7 +1356,7 @@
         <v>2</v>
       </c>
       <c r="D5" s="1">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1382,15 +1395,15 @@
         <v>5</v>
       </c>
       <c r="C8" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D8" s="1">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>5</v>
@@ -1399,22 +1412,14 @@
         <v>5</v>
       </c>
       <c r="D9" s="1">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" s="1">
-        <v>5</v>
-      </c>
-      <c r="D10" s="1">
-        <v>15</v>
-      </c>
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1"/>
@@ -1423,30 +1428,38 @@
       <c r="D11" s="1"/>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
+      <c r="A12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="1" t="s">
+      <c r="D12" s="1">
+        <f>AVERAGE(D2:D9)</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="2">
+        <v>1</v>
+      </c>
+      <c r="D15" s="2">
         <v>12</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1">
-        <f>AVERAGE(D2:D10)</f>
-        <v>15.5555555555556</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C16" s="2">
         <v>2</v>
@@ -1460,55 +1473,55 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="2">
+        <v>2</v>
+      </c>
+      <c r="D17" s="2">
         <v>15</v>
-      </c>
-      <c r="C17" s="2">
-        <v>2</v>
-      </c>
-      <c r="D17" s="2">
-        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C18" s="2">
         <v>2</v>
       </c>
       <c r="D18" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C19" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D19" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C20" s="2">
         <v>3</v>
       </c>
       <c r="D20" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1516,13 +1529,13 @@
         <v>19</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C21" s="2">
         <v>3</v>
       </c>
       <c r="D21" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1530,13 +1543,13 @@
         <v>19</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C22" s="2">
         <v>3</v>
       </c>
       <c r="D22" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -1544,7 +1557,7 @@
         <v>20</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C23" s="2">
         <v>4</v>
@@ -1558,13 +1571,13 @@
         <v>21</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C24" s="2">
         <v>4</v>
       </c>
       <c r="D24" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -1572,13 +1585,13 @@
         <v>22</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C25" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D25" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -1586,13 +1599,13 @@
         <v>23</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C26" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D26" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1600,35 +1613,43 @@
         <v>24</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C27" s="2">
         <v>6</v>
       </c>
       <c r="D27" s="2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
       <c r="A28" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" s="2">
+        <v>6</v>
+      </c>
+      <c r="D28" s="2">
         <v>15</v>
       </c>
-      <c r="C28" s="2">
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" s="2">
         <v>7</v>
       </c>
-      <c r="D28" s="2">
-        <v>14</v>
-      </c>
-      <c r="F28" s="3"/>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
+      <c r="D29" s="2">
+        <v>14</v>
+      </c>
+      <c r="F29" s="3"/>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2"/>
@@ -1637,44 +1658,36 @@
       <c r="D30" s="2"/>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>26</v>
-      </c>
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
       <c r="C31" s="2"/>
-      <c r="D31" s="2">
-        <f>AVERAGE(D16:D28)</f>
-        <v>14.2307692307692</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" s="4" t="s">
+      <c r="D31" s="2"/>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B34" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C34" s="4">
-        <v>3</v>
-      </c>
-      <c r="D34" s="4">
-        <v>13</v>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2">
+        <f>AVERAGE(D15:D29)</f>
+        <v>14.1333333333333</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B35" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B35" s="4" t="s">
-        <v>28</v>
-      </c>
       <c r="C35" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D35" s="4">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -1682,13 +1695,13 @@
         <v>30</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C36" s="4">
         <v>4</v>
       </c>
       <c r="D36" s="4">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1696,13 +1709,13 @@
         <v>31</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C37" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D37" s="4">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -1710,7 +1723,7 @@
         <v>32</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C38" s="4">
         <v>5</v>
@@ -1724,7 +1737,7 @@
         <v>33</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C39" s="4">
         <v>6</v>
@@ -1738,7 +1751,7 @@
         <v>34</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C40" s="4">
         <v>7</v>
@@ -1752,7 +1765,7 @@
         <v>35</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C41" s="4">
         <v>8</v>
@@ -1775,15 +1788,15 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>36</v>
       </c>
       <c r="C44" s="4"/>
       <c r="D44" s="4">
-        <f>AVERAGE(D34:D41)</f>
-        <v>12.875</v>
+        <f>AVERAGE(D35:D41)</f>
+        <v>12.7142857142857</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1793,8 +1806,8 @@
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
       <c r="D47" s="5">
-        <f>AVERAGE(D2:D10,D16:D28,D34:D41)</f>
-        <v>14.2666666666667</v>
+        <f>AVERAGE(D2:D9,D15:D29,D35:D41)</f>
+        <v>14.0333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -1805,6 +1818,541 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D47"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="18.125" customWidth="1"/>
+    <col min="4" max="4" width="12.625"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="1">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="1">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="1">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="1">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="1">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="1">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="1">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="1">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="1">
+        <v>4</v>
+      </c>
+      <c r="D13" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="1">
+        <v>4</v>
+      </c>
+      <c r="D14" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="1">
+        <v>5</v>
+      </c>
+      <c r="D15" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="1">
+        <v>5</v>
+      </c>
+      <c r="D16" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1">
+        <f>AVERAGE(D2:D16)</f>
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" s="2">
+        <v>2</v>
+      </c>
+      <c r="D22" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" s="2">
+        <v>3</v>
+      </c>
+      <c r="D23" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="2">
+        <v>3</v>
+      </c>
+      <c r="D24" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" s="2">
+        <v>3</v>
+      </c>
+      <c r="D25" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26" s="2">
+        <v>4</v>
+      </c>
+      <c r="D26" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" s="2">
+        <v>4</v>
+      </c>
+      <c r="D27" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" s="2">
+        <v>5</v>
+      </c>
+      <c r="D28" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" s="2">
+        <v>6</v>
+      </c>
+      <c r="D29" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2">
+        <f>AVERAGE(D22:D29)</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C35" s="4">
+        <v>3</v>
+      </c>
+      <c r="D35" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C36" s="4">
+        <v>4</v>
+      </c>
+      <c r="D36" s="4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C37" s="4">
+        <v>4</v>
+      </c>
+      <c r="D37" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C38" s="4">
+        <v>4</v>
+      </c>
+      <c r="D38" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C39" s="4">
+        <v>5</v>
+      </c>
+      <c r="D39" s="4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C40" s="4">
+        <v>6</v>
+      </c>
+      <c r="D40" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C41" s="4">
+        <v>8</v>
+      </c>
+      <c r="D41" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="4"/>
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="4"/>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4">
+        <f>AVERAGE(D35:D41)</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" t="s">
+        <v>37</v>
+      </c>
+      <c r="D47">
+        <f>AVERAGE(D2:D16,D22:D29,D35:D41)</f>
+        <v>13.8666666666667</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F47"/>
@@ -1830,7 +2378,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>75</v>
+        <v>39</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
@@ -1844,7 +2392,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>5</v>
@@ -1858,7 +2406,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>5</v>
@@ -1872,7 +2420,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>5</v>
@@ -1886,7 +2434,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>5</v>
@@ -1900,7 +2448,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>5</v>
@@ -1914,7 +2462,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>5</v>
@@ -1928,7 +2476,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>5</v>
@@ -1942,7 +2490,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>5</v>
@@ -1956,7 +2504,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>5</v>
@@ -1970,7 +2518,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>5</v>
@@ -1984,7 +2532,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>5</v>
@@ -1998,7 +2546,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>5</v>
@@ -2012,7 +2560,7 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="1" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>5</v>
@@ -2026,7 +2574,7 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="1" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>5</v>
@@ -2040,7 +2588,7 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="1" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>5</v>
@@ -2066,10 +2614,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1">
@@ -2079,10 +2627,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C23" s="2">
         <v>2</v>
@@ -2093,10 +2641,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2" t="s">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C24" s="2">
         <v>2</v>
@@ -2107,10 +2655,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C25" s="2">
         <v>3</v>
@@ -2121,10 +2669,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C26" s="2">
         <v>3</v>
@@ -2135,10 +2683,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C27" s="2">
         <v>3</v>
@@ -2149,10 +2697,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C28" s="2">
         <v>3</v>
@@ -2163,10 +2711,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C29" s="2">
         <v>4</v>
@@ -2177,10 +2725,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C30" s="2">
         <v>4</v>
@@ -2191,10 +2739,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C31" s="2">
         <v>5</v>
@@ -2205,10 +2753,10 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C32" s="2">
         <v>5</v>
@@ -2219,10 +2767,10 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2" t="s">
-        <v>87</v>
+        <v>64</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C33" s="2">
         <v>6</v>
@@ -2246,10 +2794,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" s="2">
@@ -2259,10 +2807,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="4" t="s">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C39" s="4">
         <v>2</v>
@@ -2273,10 +2821,10 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C40" s="4">
         <v>4</v>
@@ -2287,10 +2835,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="4" t="s">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C41" s="4">
         <v>5</v>
@@ -2313,7 +2861,7 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>36</v>
@@ -2390,12 +2938,12 @@
         <v>2</v>
       </c>
       <c r="D3" s="1">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>5</v>
@@ -2409,7 +2957,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>5</v>
@@ -2418,7 +2966,7 @@
         <v>2</v>
       </c>
       <c r="D5" s="1">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2437,30 +2985,30 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" s="1">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D8" s="1">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2471,116 +3019,116 @@
         <v>5</v>
       </c>
       <c r="C9" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D9" s="1">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" s="1">
-        <v>5</v>
-      </c>
-      <c r="D10" s="1">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="1">
-        <v>5</v>
-      </c>
-      <c r="D11" s="1">
+      <c r="B12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1">
+        <f>AVERAGE(D2:D9)</f>
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="1" t="s">
+    <row r="15" spans="1:4">
+      <c r="A15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="2">
+        <v>1</v>
+      </c>
+      <c r="D15" s="2">
         <v>12</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1">
-        <f>AVERAGE(D2:D11)</f>
-        <v>15.3</v>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="2">
+        <v>2</v>
+      </c>
+      <c r="D16" s="2">
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="2">
+        <v>2</v>
+      </c>
+      <c r="D17" s="2">
         <v>15</v>
-      </c>
-      <c r="C17" s="2">
-        <v>2</v>
-      </c>
-      <c r="D17" s="2">
-        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C18" s="2">
         <v>2</v>
       </c>
       <c r="D18" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="2">
+        <v>3</v>
+      </c>
+      <c r="D19" s="2">
         <v>16</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="2">
-        <v>2</v>
-      </c>
-      <c r="D19" s="2">
-        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C20" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20" s="2">
         <v>14</v>
@@ -2588,16 +3136,16 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C21" s="2">
         <v>3</v>
       </c>
       <c r="D21" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2605,49 +3153,49 @@
         <v>19</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C22" s="2">
         <v>3</v>
       </c>
       <c r="D22" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" s="2">
+        <v>4</v>
+      </c>
+      <c r="D23" s="2">
         <v>15</v>
-      </c>
-      <c r="C23" s="2">
-        <v>3</v>
-      </c>
-      <c r="D23" s="2">
-        <v>14</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C24" s="2">
         <v>4</v>
       </c>
       <c r="D24" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C25" s="2">
         <v>4</v>
@@ -2658,10 +3206,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C26" s="2">
         <v>5</v>
@@ -2672,10 +3220,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C27" s="2">
         <v>5</v>
@@ -2686,10 +3234,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C28" s="2">
         <v>6</v>
@@ -2700,10 +3248,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C29" s="2">
         <v>6</v>
@@ -2714,10 +3262,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C30" s="2">
         <v>7</v>
@@ -2740,23 +3288,23 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" s="2">
-        <f>AVERAGE(D17:D30)</f>
-        <v>14</v>
+        <f>AVERAGE(D15:D30)</f>
+        <v>13.9375</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C36" s="4">
         <v>3</v>
@@ -2767,10 +3315,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B37" s="4" t="s">
         <v>29</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>28</v>
       </c>
       <c r="C37" s="4">
         <v>4</v>
@@ -2781,10 +3329,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C38" s="4">
         <v>4</v>
@@ -2798,7 +3346,7 @@
         <v>32</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C39" s="4">
         <v>5</v>
@@ -2812,7 +3360,7 @@
         <v>33</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C40" s="4">
         <v>6</v>
@@ -2826,7 +3374,7 @@
         <v>34</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C41" s="4">
         <v>7</v>
@@ -2849,7 +3397,7 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>36</v>
@@ -2865,8 +3413,8 @@
         <v>37</v>
       </c>
       <c r="D47">
-        <f>AVERAGE(D2:D11,D17:D30,D36:D41)</f>
-        <v>14.1666666666667</v>
+        <f>AVERAGE(D2:D9,D15:D30,D36:D41)</f>
+        <v>13.9666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -2879,543 +3427,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D47"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
-  <cols>
-    <col min="1" max="1" width="18.125" customWidth="1"/>
-    <col min="4" max="4" width="12.625"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="1">
-        <v>1</v>
-      </c>
-      <c r="D2" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="1">
-        <v>1</v>
-      </c>
-      <c r="D3" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="1">
-        <v>1</v>
-      </c>
-      <c r="D4" s="1">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="1">
-        <v>1</v>
-      </c>
-      <c r="D5" s="1">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="1">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="1">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="1">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="1">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" s="1">
-        <v>3</v>
-      </c>
-      <c r="D10" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="1">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" s="1">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="1">
-        <v>4</v>
-      </c>
-      <c r="D13" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" s="1">
-        <v>4</v>
-      </c>
-      <c r="D14" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15" s="1">
-        <v>5</v>
-      </c>
-      <c r="D15" s="1">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C16" s="1">
-        <v>5</v>
-      </c>
-      <c r="D16" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1">
-        <f>AVERAGE(D2:D16)</f>
-        <v>14.2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C22" s="2">
-        <v>2</v>
-      </c>
-      <c r="D22" s="2">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C23" s="2">
-        <v>3</v>
-      </c>
-      <c r="D23" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C24" s="2">
-        <v>3</v>
-      </c>
-      <c r="D24" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C25" s="2">
-        <v>3</v>
-      </c>
-      <c r="D25" s="2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C26" s="2">
-        <v>4</v>
-      </c>
-      <c r="D26" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C27" s="2">
-        <v>4</v>
-      </c>
-      <c r="D27" s="2">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C28" s="2">
-        <v>5</v>
-      </c>
-      <c r="D28" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C29" s="2">
-        <v>6</v>
-      </c>
-      <c r="D29" s="2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2">
-        <f>AVERAGE(D22:D29)</f>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C35" s="4">
-        <v>3</v>
-      </c>
-      <c r="D35" s="4">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C36" s="4">
-        <v>4</v>
-      </c>
-      <c r="D36" s="4">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
-      <c r="A37" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C37" s="4">
-        <v>4</v>
-      </c>
-      <c r="D37" s="4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
-      <c r="A38" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C38" s="4">
-        <v>4</v>
-      </c>
-      <c r="D38" s="4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C39" s="4">
-        <v>5</v>
-      </c>
-      <c r="D39" s="4">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
-      <c r="A40" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C40" s="4">
-        <v>6</v>
-      </c>
-      <c r="D40" s="4">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
-      <c r="A41" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C41" s="4">
-        <v>8</v>
-      </c>
-      <c r="D41" s="4">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
-      <c r="A42" s="4"/>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
-    </row>
-    <row r="43" spans="1:4">
-      <c r="A43" s="4"/>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
-    </row>
-    <row r="44" spans="1:4">
-      <c r="A44" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4">
-        <f>AVERAGE(D35:D41)</f>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
-      <c r="A47" t="s">
-        <v>37</v>
-      </c>
-      <c r="D47">
-        <f>AVERAGE(D2:D16,D22:D29,D35:D41)</f>
-        <v>13.8666666666667</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:D47"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <dimension ref="A1:F47"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="17.875" customWidth="1"/>
     <col min="4" max="4" width="12.625"/>
@@ -3437,7 +3450,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
@@ -3446,12 +3459,12 @@
         <v>1</v>
       </c>
       <c r="D2" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>5</v>
@@ -3460,12 +3473,12 @@
         <v>1</v>
       </c>
       <c r="D3" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>5</v>
@@ -3474,7 +3487,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="1">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -3488,7 +3501,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="1">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -3499,63 +3512,63 @@
         <v>5</v>
       </c>
       <c r="C6" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6" s="1">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" s="1">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9" s="1">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" s="1">
         <v>13</v>
@@ -3563,21 +3576,21 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>5</v>
@@ -3586,42 +3599,587 @@
         <v>3</v>
       </c>
       <c r="D12" s="1">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D13" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="1">
+        <v>3</v>
+      </c>
+      <c r="D14" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="1">
+        <v>3</v>
+      </c>
+      <c r="D15" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="1">
+        <v>4</v>
+      </c>
+      <c r="D16" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="1">
+        <v>4</v>
+      </c>
+      <c r="D17" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="B20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1">
+        <f>AVERAGE(D2:D17)</f>
+        <v>14.125</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" s="2">
+        <v>2</v>
+      </c>
+      <c r="D23" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="2">
+        <v>2</v>
+      </c>
+      <c r="D24" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" s="2">
+        <v>3</v>
+      </c>
+      <c r="D25" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26" s="2">
+        <v>3</v>
+      </c>
+      <c r="D26" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" s="2">
+        <v>3</v>
+      </c>
+      <c r="D27" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" s="2">
+        <v>3</v>
+      </c>
+      <c r="D28" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" s="2">
+        <v>4</v>
+      </c>
+      <c r="D29" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30" s="2">
+        <v>4</v>
+      </c>
+      <c r="D30" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C31" s="2">
+        <v>5</v>
+      </c>
+      <c r="D31" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="2">
+        <v>5</v>
+      </c>
+      <c r="D32" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C33" s="2">
+        <v>6</v>
+      </c>
+      <c r="D33" s="2">
+        <v>11</v>
+      </c>
+      <c r="F33" s="3"/>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2">
+        <f>AVERAGE(D23:D33)</f>
+        <v>12.7272727272727</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C39" s="4">
+        <v>2</v>
+      </c>
+      <c r="D39" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C40" s="4">
+        <v>4</v>
+      </c>
+      <c r="D40" s="4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C41" s="4">
+        <v>5</v>
+      </c>
+      <c r="D41" s="4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="4"/>
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="4"/>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4">
+        <f>AVERAGE(D39:D41)</f>
+        <v>9.66666666666667</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B47" s="5"/>
+      <c r="C47" s="5"/>
+      <c r="D47" s="5">
+        <f>AVERAGE(D2:D17,D23:D33,D39:D41)</f>
+        <v>13.1666666666667</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F47"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="17.875" customWidth="1"/>
+    <col min="4" max="4" width="12.625"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2</v>
+      </c>
+      <c r="D4" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2</v>
+      </c>
+      <c r="D5" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2</v>
+      </c>
+      <c r="D6" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2</v>
+      </c>
+      <c r="D7" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2</v>
+      </c>
+      <c r="D8" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2</v>
+      </c>
+      <c r="D9" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="1">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2</v>
+      </c>
+      <c r="D11" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="1">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="1">
+        <v>3</v>
+      </c>
+      <c r="D13" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="B14" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D14" s="1">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
+      <c r="A15" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="1">
+        <v>4</v>
+      </c>
+      <c r="D15" s="1">
+        <v>15</v>
+      </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="1"/>
@@ -3630,69 +4188,63 @@
       <c r="D16" s="1"/>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1">
-        <f>AVERAGE(D2:D14)</f>
-        <v>14.5384615384615</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="2">
-        <v>2</v>
-      </c>
-      <c r="D20" s="2">
-        <v>17</v>
-      </c>
-    </row>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1">
+        <f>AVERAGE(D2:D15)</f>
+        <v>14.7142857142857</v>
+      </c>
+    </row>
+    <row r="19" customFormat="1"/>
+    <row r="20" customFormat="1"/>
     <row r="21" spans="1:4">
       <c r="A21" s="2" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C21" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D21" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" s="2">
+        <v>2</v>
+      </c>
+      <c r="D22" s="2">
         <v>15</v>
-      </c>
-      <c r="C22" s="2">
-        <v>3</v>
-      </c>
-      <c r="D22" s="2">
-        <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C23" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D23" s="2">
         <v>14</v>
@@ -3700,10 +4252,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C24" s="2">
         <v>3</v>
@@ -3714,195 +4266,198 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C25" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D25" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C26" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D26" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C27" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D27" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C28" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D28" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C29" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D29" s="2">
         <v>15</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
+      <c r="A30" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30" s="2">
+        <v>4</v>
+      </c>
+      <c r="D30" s="2">
+        <v>14</v>
+      </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
+      <c r="A31" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C31" s="2">
+        <v>5</v>
+      </c>
+      <c r="D31" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="2">
+        <v>5</v>
+      </c>
+      <c r="D32" s="2">
         <v>12</v>
       </c>
-      <c r="B32" s="2" t="s">
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2">
-        <f>AVERAGE(D20:D29)</f>
-        <v>14.4</v>
-      </c>
+      <c r="B33" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C33" s="2">
+        <v>7</v>
+      </c>
+      <c r="D33" s="2">
+        <v>14</v>
+      </c>
+      <c r="F33" s="3"/>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B36" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B35" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C35" s="4">
-        <v>3</v>
-      </c>
-      <c r="D35" s="4">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C36" s="4">
-        <v>4</v>
-      </c>
-      <c r="D36" s="4">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
-      <c r="A37" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C37" s="4">
-        <v>4</v>
-      </c>
-      <c r="D37" s="4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
-      <c r="A38" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C38" s="4">
-        <v>4</v>
-      </c>
-      <c r="D38" s="4">
-        <v>12</v>
-      </c>
-    </row>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2">
+        <f>AVERAGE(D21:D33)</f>
+        <v>13.7692307692308</v>
+      </c>
+    </row>
+    <row r="37" customFormat="1"/>
+    <row r="38" customFormat="1"/>
     <row r="39" spans="1:4">
       <c r="A39" s="4" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C39" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D39" s="4">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="4" t="s">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C40" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D40" s="4">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="4" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C41" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D41" s="4">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -3919,24 +4474,28 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>36</v>
       </c>
       <c r="C44" s="4"/>
       <c r="D44" s="4">
-        <f>AVERAGE(D35:D41)</f>
-        <v>12.8571428571429</v>
-      </c>
-    </row>
+        <f>AVERAGE(D39:D41)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" customFormat="1"/>
+    <row r="46" customFormat="1"/>
     <row r="47" spans="1:4">
-      <c r="A47" t="s">
+      <c r="A47" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D47">
-        <f>AVERAGE(D2:D14,D20:D29,D35:D41)</f>
-        <v>14.1</v>
+      <c r="B47" s="5"/>
+      <c r="C47" s="5"/>
+      <c r="D47" s="5">
+        <f>AVERAGE(D2:D15,D21:D33,D39:D41)</f>
+        <v>14.0333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -3948,7 +4507,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="16.375" customWidth="1"/>
@@ -4005,82 +4564,82 @@
         <v>10</v>
       </c>
       <c r="B5" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C5" s="1">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6" s="1">
         <v>5</v>
       </c>
       <c r="C6" s="1">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="1">
-        <v>5</v>
-      </c>
-      <c r="C7" s="1">
-        <v>15</v>
-      </c>
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
     </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
+    <row r="9" spans="1:4">
+      <c r="A9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="1">
-        <f>AVERAGE(C2:C7)</f>
-        <v>15.8333333333333</v>
-      </c>
-      <c r="D10" s="2"/>
+      <c r="C9" s="1">
+        <f>AVERAGE(C2:C6)</f>
+        <v>15.2</v>
+      </c>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="2">
+        <v>2</v>
+      </c>
+      <c r="C12" s="2">
+        <v>17</v>
+      </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B13" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B14" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C14" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B15" s="2">
         <v>4</v>
@@ -4091,7 +4650,7 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B16" s="2">
         <v>6</v>
@@ -4102,7 +4661,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B17" s="2">
         <v>6</v>
@@ -4123,19 +4682,19 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" s="2">
-        <f>AVERAGE(C13:C17)</f>
-        <v>15</v>
+        <f>AVERAGE(C12:C17)</f>
+        <v>14.8333333333333</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="4" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="B23" s="4">
         <v>1</v>
@@ -4146,7 +4705,7 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="4" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="B24" s="4">
         <v>2</v>
@@ -4157,7 +4716,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="4" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="B25" s="4">
         <v>2</v>
@@ -4168,36 +4727,30 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="4" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="B26" s="4">
         <v>2</v>
       </c>
       <c r="C26" s="4">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="4" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="B27" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C27" s="4">
         <v>13</v>
       </c>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B28" s="4">
-        <v>5</v>
-      </c>
-      <c r="C28" s="4">
-        <v>13</v>
-      </c>
+      <c r="A28" s="4"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="4"/>
@@ -4205,32 +4758,27 @@
       <c r="C29" s="4"/>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="4"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="4" t="s">
+      <c r="A30" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B30" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B31" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C31" s="4">
-        <f>AVERAGE(C23:C28)</f>
-        <v>13.1666666666667</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="5" t="s">
+      <c r="C30" s="4">
+        <f>AVERAGE(C23:C27)</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C34" s="5">
-        <f>AVERAGE(C2:C7,C13:C17,C23:C28)</f>
-        <v>14.6470588235294</v>
+      <c r="B33" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C33" s="5">
+        <f>AVERAGE(C2:C6,C12:C17,C23:C27)</f>
+        <v>14.375</v>
       </c>
     </row>
   </sheetData>
@@ -4269,18 +4817,18 @@
         <v>1</v>
       </c>
       <c r="C2" s="1">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="B3" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C3" s="1">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -4295,15 +4843,9 @@
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="1">
-        <v>5</v>
-      </c>
-      <c r="C5" s="1">
-        <v>13</v>
-      </c>
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1"/>
@@ -4311,53 +4853,59 @@
       <c r="C6" s="1"/>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1" t="s">
+      <c r="A7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="1">
-        <f>AVERAGE(C2:C5)</f>
-        <v>14.5</v>
+      <c r="C7" s="1">
+        <f>AVERAGE(C2:C4)</f>
+        <v>14.6666666666667</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="2">
+        <v>1</v>
+      </c>
+      <c r="C10" s="2">
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B11" s="2">
         <v>2</v>
       </c>
       <c r="C11" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B12" s="2">
         <v>2</v>
       </c>
       <c r="C12" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B13" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4368,7 +4916,7 @@
         <v>3</v>
       </c>
       <c r="C14" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -4379,7 +4927,7 @@
         <v>3</v>
       </c>
       <c r="C15" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -4395,7 +4943,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B17" s="2">
         <v>5</v>
@@ -4406,7 +4954,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B18" s="2">
         <v>5</v>
@@ -4417,7 +4965,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B19" s="2">
         <v>7</v>
@@ -4438,19 +4986,19 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C22" s="2">
-        <f>AVERAGE(C11:C19)</f>
-        <v>13.4444444444444</v>
+        <f>AVERAGE(C10:C19)</f>
+        <v>13.4</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="4" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="B25" s="4">
         <v>1</v>
@@ -4461,7 +5009,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="4" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="B26" s="4">
         <v>7</v>
@@ -4482,10 +5030,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B29" s="4" t="s">
         <v>12</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>13</v>
       </c>
       <c r="C29" s="4">
         <f>AVERAGE(C25:C26)</f>
@@ -4497,11 +5045,11 @@
         <v>37</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="C32" s="5">
-        <f>AVERAGE(C2:C5,C11:C19,C25:C26)</f>
-        <v>13.5333333333333</v>
+        <f>AVERAGE(C2:C4,C10:C19,C25:C26)</f>
+        <v>13.4666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -4513,7 +5061,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="13.75" customWidth="1"/>
@@ -4534,7 +5082,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
@@ -4545,7 +5093,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
@@ -4556,7 +5104,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="B4" s="1">
         <v>1</v>
@@ -4567,7 +5115,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
@@ -4578,7 +5126,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="B6" s="1">
         <v>2</v>
@@ -4589,7 +5137,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="B7" s="1">
         <v>2</v>
@@ -4600,7 +5148,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="B8" s="1">
         <v>3</v>
@@ -4611,7 +5159,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="1" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="B9" s="1">
         <v>3</v>
@@ -4622,18 +5170,18 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B10" s="1">
         <v>3</v>
       </c>
       <c r="C10" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="1" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="B11" s="1">
         <v>3</v>
@@ -4644,135 +5192,179 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="1" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="B12" s="1">
+        <v>3</v>
+      </c>
+      <c r="C12" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13" s="1">
+        <v>3</v>
+      </c>
+      <c r="C13" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" s="1">
         <v>4</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C14" s="1">
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-    </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C15" s="1">
-        <f>AVERAGE(C2:C12)</f>
-        <v>14.2727272727273</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B18" s="2">
-        <v>3</v>
-      </c>
-      <c r="C18" s="2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B19" s="2">
-        <v>3</v>
-      </c>
-      <c r="C19" s="2">
-        <v>14</v>
+      <c r="C17" s="1">
+        <f>AVERAGE(C2:C14)</f>
+        <v>14.2307692307692</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B20" s="2">
+        <v>3</v>
+      </c>
+      <c r="C20" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B21" s="2">
+        <v>3</v>
+      </c>
+      <c r="C21" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B22" s="2">
         <v>4</v>
       </c>
-      <c r="C20" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
+      <c r="C22" s="2">
+        <v>14</v>
+      </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>26</v>
+        <v>69</v>
+      </c>
+      <c r="B23" s="2">
+        <v>5</v>
       </c>
       <c r="C23" s="2">
-        <f>AVERAGE(C18:C20)</f>
-        <v>14.3333333333333</v>
-      </c>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B26" s="4">
-        <v>4</v>
-      </c>
-      <c r="C26" s="4">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="4"/>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
+      <c r="A26" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" s="2">
+        <f>AVERAGE(C20:C23)</f>
+        <v>14</v>
+      </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B29" s="4">
+        <v>4</v>
+      </c>
+      <c r="C29" s="4">
         <v>12</v>
       </c>
-      <c r="B29" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C29" s="4">
-        <f>AVERAGE(C26:C26)</f>
-        <v>6</v>
-      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B30" s="4">
+        <v>4</v>
+      </c>
+      <c r="C30" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="4"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="5" t="s">
+      <c r="A32" s="4"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C33" s="4">
+        <f>AVERAGE(C29:C30)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C32" s="5">
-        <f>AVERAGE(C2:C12,C18:C20,C26:C26)</f>
-        <v>13.7333333333333</v>
+      <c r="B36" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C36" s="5">
+        <f>AVERAGE(C2:C14,C20:C23,C29:C30)</f>
+        <v>13.9473684210526</v>
       </c>
     </row>
   </sheetData>
@@ -4805,7 +5397,7 @@
     </row>
     <row r="2" spans="4:6">
       <c r="D2" s="1" t="s">
-        <v>75</v>
+        <v>39</v>
       </c>
       <c r="E2" s="1">
         <v>1</v>
@@ -4816,7 +5408,7 @@
     </row>
     <row r="3" spans="4:6">
       <c r="D3" s="1" t="s">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="E3" s="1">
         <v>1</v>
@@ -4827,7 +5419,7 @@
     </row>
     <row r="4" spans="4:6">
       <c r="D4" s="1" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="E4" s="1">
         <v>2</v>
@@ -4838,7 +5430,7 @@
     </row>
     <row r="5" spans="4:6">
       <c r="D5" s="1" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="E5" s="1">
         <v>2</v>
@@ -4849,7 +5441,7 @@
     </row>
     <row r="6" spans="4:6">
       <c r="D6" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
@@ -4860,7 +5452,7 @@
     </row>
     <row r="7" spans="4:6">
       <c r="D7" s="1" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="E7" s="1">
         <v>4</v>
@@ -4881,10 +5473,10 @@
     </row>
     <row r="10" spans="4:6">
       <c r="D10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="F10" s="1">
         <f>AVERAGE(F2:F7)</f>
@@ -4893,7 +5485,7 @@
     </row>
     <row r="13" spans="4:6">
       <c r="D13" s="2" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="E13" s="2">
         <v>2</v>
@@ -4904,7 +5496,7 @@
     </row>
     <row r="14" spans="4:6">
       <c r="D14" s="2" t="s">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="E14" s="2">
         <v>2</v>
@@ -4915,7 +5507,7 @@
     </row>
     <row r="15" spans="4:6">
       <c r="D15" s="2" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="E15" s="2">
         <v>3</v>
@@ -4926,7 +5518,7 @@
     </row>
     <row r="16" spans="4:6">
       <c r="D16" s="2" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="E16" s="2">
         <v>3</v>
@@ -4937,7 +5529,7 @@
     </row>
     <row r="17" spans="4:6">
       <c r="D17" s="2" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="E17" s="2">
         <v>4</v>
@@ -4948,7 +5540,7 @@
     </row>
     <row r="18" spans="4:6">
       <c r="D18" s="2" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="E18" s="2">
         <v>5</v>
@@ -4959,7 +5551,7 @@
     </row>
     <row r="19" spans="4:6">
       <c r="D19" s="2" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="E19" s="2">
         <v>5</v>
@@ -4970,7 +5562,7 @@
     </row>
     <row r="20" spans="4:6">
       <c r="D20" s="2" t="s">
-        <v>87</v>
+        <v>64</v>
       </c>
       <c r="E20" s="2">
         <v>6</v>
@@ -4991,10 +5583,10 @@
     </row>
     <row r="23" spans="4:6">
       <c r="D23" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F23" s="2">
         <f>AVERAGE(F13:F20)</f>
@@ -5003,7 +5595,7 @@
     </row>
     <row r="26" spans="4:6">
       <c r="D26" s="4" t="s">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="E26" s="4">
         <v>2</v>
@@ -5014,7 +5606,7 @@
     </row>
     <row r="27" spans="4:6">
       <c r="D27" s="4" t="s">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="E27" s="4">
         <v>2</v>
@@ -5035,10 +5627,10 @@
     </row>
     <row r="30" spans="4:6">
       <c r="D30" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="F30" s="4">
         <f>AVERAGE(F26,F27)</f>
@@ -5050,7 +5642,7 @@
         <v>37</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="F33" s="5">
         <f>AVERAGE(F2,F3,F4,F5,F6,F7,F13:F20,F26:F27)</f>
@@ -5066,8 +5658,8 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F47"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <dimension ref="A1:D47"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="17.875" customWidth="1"/>
     <col min="4" max="4" width="12.625"/>
@@ -5089,7 +5681,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>75</v>
+        <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
@@ -5098,12 +5690,12 @@
         <v>1</v>
       </c>
       <c r="D2" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>5</v>
@@ -5112,12 +5704,12 @@
         <v>1</v>
       </c>
       <c r="D3" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>5</v>
@@ -5126,12 +5718,12 @@
         <v>1</v>
       </c>
       <c r="D4" s="1">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>5</v>
@@ -5140,74 +5732,74 @@
         <v>1</v>
       </c>
       <c r="D5" s="1">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D6" s="1">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>68</v>
+        <v>9</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" s="1">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" s="1">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" s="1">
         <v>13</v>
@@ -5215,21 +5807,21 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>5</v>
@@ -5238,183 +5830,183 @@
         <v>3</v>
       </c>
       <c r="D12" s="1">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>43</v>
+        <v>87</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D13" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D14" s="1">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15" s="1">
-        <v>3</v>
-      </c>
-      <c r="D15" s="1">
-        <v>13</v>
-      </c>
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C16" s="1">
-        <v>4</v>
-      </c>
-      <c r="D16" s="1">
-        <v>15</v>
-      </c>
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="1" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" s="1">
-        <v>4</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="C17" s="1"/>
       <c r="D17" s="1">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
+        <f>AVERAGE(D2:D14)</f>
+        <v>14.5384615384615</v>
+      </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1">
-        <f>AVERAGE(D2:D17)</f>
-        <v>14.125</v>
+      <c r="A20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" s="2">
+        <v>2</v>
+      </c>
+      <c r="D20" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" s="2">
+        <v>3</v>
+      </c>
+      <c r="D21" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" s="2">
+        <v>3</v>
+      </c>
+      <c r="D22" s="2">
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2" t="s">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C23" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D23" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="2">
+        <v>3</v>
+      </c>
+      <c r="D24" s="2">
         <v>15</v>
-      </c>
-      <c r="C24" s="2">
-        <v>2</v>
-      </c>
-      <c r="D24" s="2">
-        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C25" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D25" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2" t="s">
-        <v>73</v>
+        <v>22</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C26" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D26" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" s="2">
+        <v>5</v>
+      </c>
+      <c r="D27" s="2">
         <v>15</v>
-      </c>
-      <c r="C27" s="2">
-        <v>3</v>
-      </c>
-      <c r="D27" s="2">
-        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C28" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D28" s="2">
         <v>12</v>
@@ -5422,140 +6014,139 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2" t="s">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" s="2">
+        <v>6</v>
+      </c>
+      <c r="D29" s="2">
         <v>15</v>
       </c>
-      <c r="C29" s="2">
-        <v>4</v>
-      </c>
-      <c r="D29" s="2">
-        <v>14</v>
-      </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C30" s="2">
-        <v>4</v>
-      </c>
-      <c r="D30" s="2">
-        <v>12</v>
-      </c>
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C31" s="2">
-        <v>5</v>
-      </c>
-      <c r="D31" s="2">
-        <v>13</v>
-      </c>
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2" t="s">
-        <v>86</v>
+        <v>11</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C32" s="2">
-        <v>5</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="C32" s="2"/>
       <c r="D32" s="2">
+        <f>AVERAGE(D20:D29)</f>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C35" s="4">
+        <v>3</v>
+      </c>
+      <c r="D35" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C36" s="4">
+        <v>4</v>
+      </c>
+      <c r="D36" s="4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C37" s="4">
+        <v>4</v>
+      </c>
+      <c r="D37" s="4">
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
-      <c r="A33" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C33" s="2">
-        <v>6</v>
-      </c>
-      <c r="D33" s="2">
-        <v>11</v>
-      </c>
-      <c r="F33" s="3"/>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="2"/>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" s="2" t="s">
+    <row r="38" spans="1:4">
+      <c r="A38" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C38" s="4">
+        <v>4</v>
+      </c>
+      <c r="D38" s="4">
         <v>12</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2">
-        <f>AVERAGE(D23:D33)</f>
-        <v>12.7272727272727</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="4" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C39" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D39" s="4">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="4" t="s">
-        <v>74</v>
+        <v>33</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C40" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D40" s="4">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="4" t="s">
-        <v>90</v>
+        <v>35</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C41" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D41" s="4">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -5572,26 +6163,24 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>36</v>
       </c>
       <c r="C44" s="4"/>
       <c r="D44" s="4">
-        <f>AVERAGE(D39:D41)</f>
-        <v>9.66666666666667</v>
+        <f>AVERAGE(D35:D41)</f>
+        <v>12.8571428571429</v>
       </c>
     </row>
     <row r="47" spans="1:4">
-      <c r="A47" s="5" t="s">
+      <c r="A47" t="s">
         <v>37</v>
       </c>
-      <c r="B47" s="5"/>
-      <c r="C47" s="5"/>
-      <c r="D47" s="5">
-        <f>AVERAGE(D2:D17,D23:D33,D39:D41)</f>
-        <v>13.1666666666667</v>
+      <c r="D47">
+        <f>AVERAGE(D2:D14,D20:D29,D35:D41)</f>
+        <v>14.1</v>
       </c>
     </row>
   </sheetData>

--- a/src/utils/sxsyzlzq/zzz_cardList.xlsx
+++ b/src/utils/sxsyzlzq/zzz_cardList.xlsx
@@ -4,27 +4,28 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28245" windowHeight="12345" activeTab="6"/>
+    <workbookView windowWidth="24345" windowHeight="12345" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="伊萝莲" sheetId="1" r:id="rId1"/>
     <sheet name="阿斯塔拉" sheetId="2" r:id="rId2"/>
     <sheet name="熙" sheetId="9" r:id="rId3"/>
-    <sheet name="洛" sheetId="11" r:id="rId4"/>
-    <sheet name="帝国" sheetId="5" r:id="rId5"/>
-    <sheet name="隐秘" sheetId="6" r:id="rId6"/>
-    <sheet name="禅意" sheetId="7" r:id="rId7"/>
-    <sheet name="炼狱" sheetId="8" r:id="rId8"/>
-    <sheet name="白处尊" sheetId="4" r:id="rId9"/>
-    <sheet name="梅" sheetId="3" r:id="rId10"/>
-    <sheet name="希拉" sheetId="10" r:id="rId11"/>
+    <sheet name="尤瑞艾莉" sheetId="12" r:id="rId4"/>
+    <sheet name="洛" sheetId="11" r:id="rId5"/>
+    <sheet name="帝国" sheetId="5" r:id="rId6"/>
+    <sheet name="隐秘" sheetId="6" r:id="rId7"/>
+    <sheet name="禅意" sheetId="7" r:id="rId8"/>
+    <sheet name="炼狱" sheetId="8" r:id="rId9"/>
+    <sheet name="白处尊" sheetId="4" r:id="rId10"/>
+    <sheet name="梅" sheetId="3" r:id="rId11"/>
+    <sheet name="希拉" sheetId="10" r:id="rId12"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="679" uniqueCount="96">
   <si>
     <t>名称</t>
   </si>
@@ -228,6 +229,9 @@
   </si>
   <si>
     <t>怨魂饕餮兽</t>
+  </si>
+  <si>
+    <t>猩红勇士</t>
   </si>
   <si>
     <t>铁山靠</t>
@@ -317,8 +321,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
@@ -365,6 +369,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
@@ -380,18 +399,26 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -405,7 +432,7 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -419,18 +446,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -449,9 +476,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -459,14 +485,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -482,21 +501,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -517,7 +521,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -529,7 +539,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -541,7 +587,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -553,7 +599,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -565,37 +659,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -607,73 +683,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -685,13 +695,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -702,6 +706,17 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -716,6 +731,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -744,28 +774,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -775,15 +788,6 @@
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -810,10 +814,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -822,16 +826,16 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -840,115 +844,115 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1314,7 +1318,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1437,7 +1441,7 @@
       <c r="C12" s="1"/>
       <c r="D12" s="1">
         <f>AVERAGE(D2:D9)</f>
-        <v>15</v>
+        <v>15.125</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1577,7 +1581,7 @@
         <v>4</v>
       </c>
       <c r="D24" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -1673,7 +1677,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2">
         <f>AVERAGE(D15:D29)</f>
-        <v>14.1333333333333</v>
+        <v>14.0666666666667</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -1823,6 +1827,540 @@
   <dimension ref="A1:D47"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
+    <col min="1" max="1" width="17.875" customWidth="1"/>
+    <col min="4" max="4" width="12.625"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="1">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="1">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="1">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="1">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="1">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="1">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="1">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="1">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="1">
+        <v>4</v>
+      </c>
+      <c r="D13" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="1">
+        <v>5</v>
+      </c>
+      <c r="D14" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1">
+        <f>AVERAGE(D2:D14)</f>
+        <v>14.5384615384615</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" s="2">
+        <v>2</v>
+      </c>
+      <c r="D20" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" s="2">
+        <v>3</v>
+      </c>
+      <c r="D21" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" s="2">
+        <v>3</v>
+      </c>
+      <c r="D22" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" s="2">
+        <v>3</v>
+      </c>
+      <c r="D23" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="2">
+        <v>3</v>
+      </c>
+      <c r="D24" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" s="2">
+        <v>4</v>
+      </c>
+      <c r="D25" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26" s="2">
+        <v>4</v>
+      </c>
+      <c r="D26" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" s="2">
+        <v>5</v>
+      </c>
+      <c r="D27" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" s="2">
+        <v>5</v>
+      </c>
+      <c r="D28" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" s="2">
+        <v>6</v>
+      </c>
+      <c r="D29" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2">
+        <f>AVERAGE(D20:D29)</f>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C35" s="4">
+        <v>3</v>
+      </c>
+      <c r="D35" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C36" s="4">
+        <v>4</v>
+      </c>
+      <c r="D36" s="4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C37" s="4">
+        <v>4</v>
+      </c>
+      <c r="D37" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C38" s="4">
+        <v>4</v>
+      </c>
+      <c r="D38" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C39" s="4">
+        <v>5</v>
+      </c>
+      <c r="D39" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C40" s="4">
+        <v>6</v>
+      </c>
+      <c r="D40" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C41" s="4">
+        <v>8</v>
+      </c>
+      <c r="D41" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="4"/>
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="4"/>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4">
+        <f>AVERAGE(D35:D41)</f>
+        <v>12.8571428571429</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" t="s">
+        <v>37</v>
+      </c>
+      <c r="D47">
+        <f>AVERAGE(D2:D14,D20:D29,D35:D41)</f>
+        <v>14.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D47"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <cols>
     <col min="1" max="1" width="18.125" customWidth="1"/>
     <col min="4" max="4" width="12.625"/>
   </cols>
@@ -1871,7 +2409,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>5</v>
@@ -1885,7 +2423,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>5</v>
@@ -1899,7 +2437,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>5</v>
@@ -1955,7 +2493,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>5</v>
@@ -1983,7 +2521,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>5</v>
@@ -1997,7 +2535,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>5</v>
@@ -2011,7 +2549,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>5</v>
@@ -2092,7 +2630,7 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>14</v>
@@ -2120,7 +2658,7 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>14</v>
@@ -2148,7 +2686,7 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>14</v>
@@ -2162,7 +2700,7 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>14</v>
@@ -2243,7 +2781,7 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>29</v>
@@ -2271,7 +2809,7 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>29</v>
@@ -2352,7 +2890,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F47"/>
@@ -2924,7 +3462,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -3047,7 +3585,7 @@
       <c r="C12" s="1"/>
       <c r="D12" s="1">
         <f>AVERAGE(D2:D9)</f>
-        <v>15</v>
+        <v>15.125</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -3187,7 +3725,7 @@
         <v>4</v>
       </c>
       <c r="D24" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -3296,7 +3834,7 @@
       <c r="C33" s="2"/>
       <c r="D33" s="2">
         <f>AVERAGE(D15:D30)</f>
-        <v>13.9375</v>
+        <v>13.875</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -3964,6 +4502,546 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1:D47"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="18.25" customWidth="1"/>
+    <col min="4" max="4" width="12.625"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2</v>
+      </c>
+      <c r="D4" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2</v>
+      </c>
+      <c r="D5" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2</v>
+      </c>
+      <c r="D6" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2</v>
+      </c>
+      <c r="D7" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2</v>
+      </c>
+      <c r="D8" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2</v>
+      </c>
+      <c r="D9" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="1">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="1">
+        <v>4</v>
+      </c>
+      <c r="D11" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1">
+        <f>AVERAGE(D2:D11)</f>
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="15" customFormat="1"/>
+    <row r="16" customFormat="1"/>
+    <row r="17" spans="1:4">
+      <c r="A17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="2">
+        <v>1</v>
+      </c>
+      <c r="D17" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="2">
+        <v>2</v>
+      </c>
+      <c r="D18" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="2">
+        <v>2</v>
+      </c>
+      <c r="D19" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" s="2">
+        <v>2</v>
+      </c>
+      <c r="D20" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" s="2">
+        <v>3</v>
+      </c>
+      <c r="D21" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" s="2">
+        <v>3</v>
+      </c>
+      <c r="D22" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" s="2">
+        <v>3</v>
+      </c>
+      <c r="D23" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="2">
+        <v>3</v>
+      </c>
+      <c r="D24" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" s="2">
+        <v>3</v>
+      </c>
+      <c r="D25" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26" s="2">
+        <v>4</v>
+      </c>
+      <c r="D26" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" s="2">
+        <v>4</v>
+      </c>
+      <c r="D27" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" s="2">
+        <v>5</v>
+      </c>
+      <c r="D28" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" s="2">
+        <v>5</v>
+      </c>
+      <c r="D29" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30" s="2">
+        <v>5</v>
+      </c>
+      <c r="D30" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C31" s="2">
+        <v>6</v>
+      </c>
+      <c r="D31" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="2">
+        <v>7</v>
+      </c>
+      <c r="D32" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2">
+        <f>AVERAGE(D17:D32)</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" customFormat="1"/>
+    <row r="37" customFormat="1"/>
+    <row r="38" spans="1:4">
+      <c r="A38" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C38" s="4">
+        <v>2</v>
+      </c>
+      <c r="D38" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C39" s="4">
+        <v>5</v>
+      </c>
+      <c r="D39" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C40" s="4">
+        <v>5</v>
+      </c>
+      <c r="D40" s="4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C41" s="4">
+        <v>7</v>
+      </c>
+      <c r="D41" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="4"/>
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="4"/>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4">
+        <f>AVERAGE(D38:D41)</f>
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="45" customFormat="1"/>
+    <row r="46" customFormat="1"/>
+    <row r="47" spans="1:4">
+      <c r="A47" t="s">
+        <v>37</v>
+      </c>
+      <c r="D47">
+        <f>AVERAGE(D2:D11,D17:D32,D38:D41)</f>
+        <v>12.9333333333333</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:F47"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
@@ -4113,7 +5191,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>5</v>
@@ -4206,8 +5284,6 @@
         <v>14.7142857142857</v>
       </c>
     </row>
-    <row r="19" customFormat="1"/>
-    <row r="20" customFormat="1"/>
     <row r="21" spans="1:4">
       <c r="A21" s="2" t="s">
         <v>13</v>
@@ -4350,7 +5426,7 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>14</v>
@@ -4416,8 +5492,6 @@
         <v>13.7692307692308</v>
       </c>
     </row>
-    <row r="37" customFormat="1"/>
-    <row r="38" customFormat="1"/>
     <row r="39" spans="1:4">
       <c r="A39" s="4" t="s">
         <v>66</v>
@@ -4434,7 +5508,7 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>29</v>
@@ -4448,7 +5522,7 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>29</v>
@@ -4485,8 +5559,6 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" customFormat="1"/>
-    <row r="46" customFormat="1"/>
     <row r="47" spans="1:4">
       <c r="A47" s="5" t="s">
         <v>37</v>
@@ -4504,7 +5576,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D33"/>
@@ -4534,7 +5606,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4600,7 +5672,7 @@
       </c>
       <c r="C9" s="1">
         <f>AVERAGE(C2:C6)</f>
-        <v>15.2</v>
+        <v>15.4</v>
       </c>
       <c r="D9" s="2"/>
     </row>
@@ -4634,7 +5706,7 @@
         <v>4</v>
       </c>
       <c r="C14" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -4689,12 +5761,12 @@
       </c>
       <c r="C20" s="2">
         <f>AVERAGE(C12:C17)</f>
-        <v>14.8333333333333</v>
+        <v>14.6666666666667</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B23" s="4">
         <v>1</v>
@@ -4705,7 +5777,7 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B24" s="4">
         <v>2</v>
@@ -4716,7 +5788,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B25" s="4">
         <v>2</v>
@@ -4727,7 +5799,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B26" s="4">
         <v>2</v>
@@ -4738,7 +5810,7 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B27" s="4">
         <v>5</v>
@@ -4774,7 +5846,7 @@
         <v>37</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C33" s="5">
         <f>AVERAGE(C2:C6,C12:C17,C23:C27)</f>
@@ -4787,7 +5859,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C32"/>
@@ -4998,7 +6070,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B25" s="4">
         <v>1</v>
@@ -5009,7 +6081,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B26" s="4">
         <v>7</v>
@@ -5045,7 +6117,7 @@
         <v>37</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C32" s="5">
         <f>AVERAGE(C2:C4,C10:C19,C25:C26)</f>
@@ -5058,7 +6130,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C36"/>
@@ -5159,7 +6231,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B9" s="1">
         <v>3</v>
@@ -5280,7 +6352,7 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B23" s="2">
         <v>5</v>
@@ -5324,7 +6396,7 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B30" s="4">
         <v>4</v>
@@ -5360,7 +6432,7 @@
         <v>37</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C36" s="5">
         <f>AVERAGE(C2:C14,C20:C23,C29:C30)</f>
@@ -5373,10 +6445,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="D1:F33"/>
+  <dimension ref="D1:F34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="4" max="4" width="13.125" customWidth="1"/>
@@ -5452,19 +6524,25 @@
     </row>
     <row r="7" spans="4:6">
       <c r="D7" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E7" s="1">
+        <v>3</v>
+      </c>
+      <c r="F7" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="4:6">
+      <c r="D8" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E8" s="1">
         <v>4</v>
       </c>
-      <c r="F7" s="1">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="4:6">
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
+      <c r="F8" s="1">
+        <v>13</v>
+      </c>
     </row>
     <row r="9" spans="4:6">
       <c r="D9" s="1"/>
@@ -5472,45 +6550,39 @@
       <c r="F9" s="1"/>
     </row>
     <row r="10" spans="4:6">
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+    </row>
+    <row r="11" spans="4:6">
+      <c r="D11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="1">
-        <f>AVERAGE(F2:F7)</f>
-        <v>13.5</v>
-      </c>
-    </row>
-    <row r="13" spans="4:6">
-      <c r="D13" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E13" s="2">
-        <v>2</v>
-      </c>
-      <c r="F13" s="2">
-        <v>13</v>
+      <c r="E11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="1">
+        <f>AVERAGE(F2:F8)</f>
+        <v>13.4285714285714</v>
       </c>
     </row>
     <row r="14" spans="4:6">
       <c r="D14" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E14" s="2">
         <v>2</v>
       </c>
       <c r="F14" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="4:6">
       <c r="D15" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E15" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F15" s="2">
         <v>12</v>
@@ -5518,7 +6590,7 @@
     </row>
     <row r="16" spans="4:6">
       <c r="D16" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E16" s="2">
         <v>3</v>
@@ -5529,10 +6601,10 @@
     </row>
     <row r="17" spans="4:6">
       <c r="D17" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E17" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F17" s="2">
         <v>12</v>
@@ -5540,41 +6612,47 @@
     </row>
     <row r="18" spans="4:6">
       <c r="D18" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E18" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F18" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="4:6">
       <c r="D19" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E19" s="2">
         <v>5</v>
       </c>
       <c r="F19" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="4:6">
       <c r="D20" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E20" s="2">
+        <v>5</v>
+      </c>
+      <c r="F20" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="4:6">
+      <c r="D21" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E20" s="2">
+      <c r="E21" s="2">
         <v>6</v>
       </c>
-      <c r="F20" s="2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="4:6">
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
+      <c r="F21" s="2">
+        <v>12</v>
+      </c>
     </row>
     <row r="22" spans="4:6">
       <c r="D22" s="2"/>
@@ -5582,26 +6660,20 @@
       <c r="F22" s="2"/>
     </row>
     <row r="23" spans="4:6">
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+    </row>
+    <row r="24" spans="4:6">
+      <c r="D24" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="E24" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F23" s="2">
-        <f>AVERAGE(F13:F20)</f>
+      <c r="F24" s="2">
+        <f>AVERAGE(F14:F21)</f>
         <v>12.25</v>
-      </c>
-    </row>
-    <row r="26" spans="4:6">
-      <c r="D26" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="E26" s="4">
-        <v>2</v>
-      </c>
-      <c r="F26" s="4">
-        <v>5</v>
       </c>
     </row>
     <row r="27" spans="4:6">
@@ -5612,13 +6684,19 @@
         <v>2</v>
       </c>
       <c r="F27" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="4:6">
+      <c r="D28" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E28" s="4">
+        <v>2</v>
+      </c>
+      <c r="F28" s="4">
         <v>11</v>
       </c>
-    </row>
-    <row r="28" spans="4:6">
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
     </row>
     <row r="29" spans="4:6">
       <c r="D29" s="4"/>
@@ -5626,561 +6704,32 @@
       <c r="F29" s="4"/>
     </row>
     <row r="30" spans="4:6">
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+    </row>
+    <row r="31" spans="4:6">
+      <c r="D31" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E30" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F30" s="4">
-        <f>AVERAGE(F26,F27)</f>
+      <c r="E31" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="F31" s="4">
+        <f>AVERAGE(F27,F28)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="4:6">
-      <c r="D33" s="5" t="s">
+    <row r="34" spans="4:6">
+      <c r="D34" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E33" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="F33" s="5">
-        <f>AVERAGE(F2,F3,F4,F5,F6,F7,F13:F20,F26:F27)</f>
+      <c r="E34" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F34" s="5">
+        <f>AVERAGE(F2,F3,F4,F5,F6,F8,F14:F21,F27:F28)</f>
         <v>12.1875</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:D47"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
-  <cols>
-    <col min="1" max="1" width="17.875" customWidth="1"/>
-    <col min="4" max="4" width="12.625"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="1">
-        <v>1</v>
-      </c>
-      <c r="D2" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="1">
-        <v>1</v>
-      </c>
-      <c r="D3" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="1">
-        <v>1</v>
-      </c>
-      <c r="D4" s="1">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="1">
-        <v>1</v>
-      </c>
-      <c r="D5" s="1">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="1">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="1">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="1">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="1">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" s="1">
-        <v>3</v>
-      </c>
-      <c r="D10" s="1">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="1">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" s="1">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="1">
-        <v>4</v>
-      </c>
-      <c r="D13" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" s="1">
-        <v>5</v>
-      </c>
-      <c r="D14" s="1">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1">
-        <f>AVERAGE(D2:D14)</f>
-        <v>14.5384615384615</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C20" s="2">
-        <v>2</v>
-      </c>
-      <c r="D20" s="2">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C21" s="2">
-        <v>3</v>
-      </c>
-      <c r="D21" s="2">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C22" s="2">
-        <v>3</v>
-      </c>
-      <c r="D22" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C23" s="2">
-        <v>3</v>
-      </c>
-      <c r="D23" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C24" s="2">
-        <v>3</v>
-      </c>
-      <c r="D24" s="2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C25" s="2">
-        <v>4</v>
-      </c>
-      <c r="D25" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C26" s="2">
-        <v>4</v>
-      </c>
-      <c r="D26" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C27" s="2">
-        <v>5</v>
-      </c>
-      <c r="D27" s="2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C28" s="2">
-        <v>5</v>
-      </c>
-      <c r="D28" s="2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C29" s="2">
-        <v>6</v>
-      </c>
-      <c r="D29" s="2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2">
-        <f>AVERAGE(D20:D29)</f>
-        <v>14.4</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C35" s="4">
-        <v>3</v>
-      </c>
-      <c r="D35" s="4">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C36" s="4">
-        <v>4</v>
-      </c>
-      <c r="D36" s="4">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
-      <c r="A37" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C37" s="4">
-        <v>4</v>
-      </c>
-      <c r="D37" s="4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
-      <c r="A38" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C38" s="4">
-        <v>4</v>
-      </c>
-      <c r="D38" s="4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C39" s="4">
-        <v>5</v>
-      </c>
-      <c r="D39" s="4">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
-      <c r="A40" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C40" s="4">
-        <v>6</v>
-      </c>
-      <c r="D40" s="4">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
-      <c r="A41" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C41" s="4">
-        <v>8</v>
-      </c>
-      <c r="D41" s="4">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
-      <c r="A42" s="4"/>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
-    </row>
-    <row r="43" spans="1:4">
-      <c r="A43" s="4"/>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
-    </row>
-    <row r="44" spans="1:4">
-      <c r="A44" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4">
-        <f>AVERAGE(D35:D41)</f>
-        <v>12.8571428571429</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
-      <c r="A47" t="s">
-        <v>37</v>
-      </c>
-      <c r="D47">
-        <f>AVERAGE(D2:D14,D20:D29,D35:D41)</f>
-        <v>14.1</v>
       </c>
     </row>
   </sheetData>

--- a/src/utils/sxsyzlzq/zzz_cardList.xlsx
+++ b/src/utils/sxsyzlzq/zzz_cardList.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24345" windowHeight="12345" activeTab="5"/>
+    <workbookView windowWidth="28245" windowHeight="12075" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet name="伊萝莲" sheetId="1" r:id="rId1"/>
@@ -19,13 +19,14 @@
     <sheet name="白处尊" sheetId="4" r:id="rId10"/>
     <sheet name="梅" sheetId="3" r:id="rId11"/>
     <sheet name="希拉" sheetId="10" r:id="rId12"/>
+    <sheet name="统计" sheetId="13" r:id="rId13"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="679" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="129">
   <si>
     <t>名称</t>
   </si>
@@ -313,6 +314,105 @@
   </si>
   <si>
     <t>蟠桃会</t>
+  </si>
+  <si>
+    <t>阵营</t>
+  </si>
+  <si>
+    <t>数量</t>
+  </si>
+  <si>
+    <t>No.8雷鸣·泰拉德</t>
+  </si>
+  <si>
+    <t>隐秘</t>
+  </si>
+  <si>
+    <t>帝国</t>
+  </si>
+  <si>
+    <t>四芒军旗</t>
+  </si>
+  <si>
+    <t>传记·钢铁守卫</t>
+  </si>
+  <si>
+    <t>圣殿卫士</t>
+  </si>
+  <si>
+    <t>圣甲先锋</t>
+  </si>
+  <si>
+    <t>咒术系学士</t>
+  </si>
+  <si>
+    <t>传记·海市蜃楼·蛇</t>
+  </si>
+  <si>
+    <t>No.5咒刃·布雷克</t>
+  </si>
+  <si>
+    <t>增援战线</t>
+  </si>
+  <si>
+    <t>魔像-御咒铁卫</t>
+  </si>
+  <si>
+    <t>缄言法师</t>
+  </si>
+  <si>
+    <t>白袍主教</t>
+  </si>
+  <si>
+    <t>圣殿骑士</t>
+  </si>
+  <si>
+    <t>鬼童7号</t>
+  </si>
+  <si>
+    <t>圣殿精英</t>
+  </si>
+  <si>
+    <t>实验室流浆</t>
+  </si>
+  <si>
+    <t>炽阳坠落</t>
+  </si>
+  <si>
+    <t>钢铁大师</t>
+  </si>
+  <si>
+    <t>学仆-塑钢型</t>
+  </si>
+  <si>
+    <t>帝国军魂·莱哈特</t>
+  </si>
+  <si>
+    <t>田园保卫战</t>
+  </si>
+  <si>
+    <t>幻象巨龙</t>
+  </si>
+  <si>
+    <t>炫目天使·蕾娜</t>
+  </si>
+  <si>
+    <t>心灵控制</t>
+  </si>
+  <si>
+    <t>皇家狮鹫</t>
+  </si>
+  <si>
+    <t>破城者·阿基琉斯</t>
+  </si>
+  <si>
+    <t>睿智史芬斯</t>
+  </si>
+  <si>
+    <t>低费统计：</t>
+  </si>
+  <si>
+    <t>总数：</t>
   </si>
 </sst>
 </file>
@@ -322,13 +422,20 @@
   <numFmts count="4">
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="6"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -339,6 +446,12 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF7030A0"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -363,9 +476,24 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -373,6 +501,82 @@
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -393,60 +597,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
@@ -454,43 +604,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
@@ -515,7 +628,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -527,175 +802,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -706,32 +819,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -753,8 +840,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -786,8 +873,34 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -814,10 +927,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -826,137 +939,137 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -966,10 +1079,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1308,508 +1427,508 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="1">
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2">
         <v>1</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="2">
         <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="1">
-        <v>2</v>
-      </c>
-      <c r="D3" s="1">
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="2">
+        <v>2</v>
+      </c>
+      <c r="D3" s="2">
         <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="1">
-        <v>2</v>
-      </c>
-      <c r="D4" s="1">
+      <c r="B4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2">
+        <v>2</v>
+      </c>
+      <c r="D4" s="2">
         <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="1">
-        <v>2</v>
-      </c>
-      <c r="D5" s="1">
+      <c r="B5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="2">
+        <v>2</v>
+      </c>
+      <c r="D5" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="1">
-        <v>2</v>
-      </c>
-      <c r="D6" s="1">
+      <c r="B6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="2">
+        <v>2</v>
+      </c>
+      <c r="D6" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="1">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1">
+      <c r="B7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="2">
+        <v>3</v>
+      </c>
+      <c r="D7" s="2">
         <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="1">
-        <v>5</v>
-      </c>
-      <c r="D8" s="1">
+      <c r="B8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="2">
+        <v>5</v>
+      </c>
+      <c r="D8" s="2">
         <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="1">
-        <v>5</v>
-      </c>
-      <c r="D9" s="1">
+      <c r="B9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="2">
+        <v>5</v>
+      </c>
+      <c r="D9" s="2">
         <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1">
+      <c r="B12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2">
         <f>AVERAGE(D2:D9)</f>
         <v>15.125</v>
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" s="2">
+      <c r="A15" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="4">
         <v>1</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="4">
         <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C16" s="2">
-        <v>2</v>
-      </c>
-      <c r="D16" s="2">
+      <c r="B16" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="4">
+        <v>2</v>
+      </c>
+      <c r="D16" s="4">
         <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C17" s="2">
-        <v>2</v>
-      </c>
-      <c r="D17" s="2">
+      <c r="B17" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="4">
+        <v>2</v>
+      </c>
+      <c r="D17" s="4">
         <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C18" s="2">
-        <v>2</v>
-      </c>
-      <c r="D18" s="2">
+      <c r="B18" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="4">
+        <v>2</v>
+      </c>
+      <c r="D18" s="4">
         <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C19" s="2">
-        <v>3</v>
-      </c>
-      <c r="D19" s="2">
+      <c r="B19" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="4">
+        <v>3</v>
+      </c>
+      <c r="D19" s="4">
         <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C20" s="2">
-        <v>3</v>
-      </c>
-      <c r="D20" s="2">
+      <c r="B20" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" s="4">
+        <v>3</v>
+      </c>
+      <c r="D20" s="4">
         <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C21" s="2">
-        <v>3</v>
-      </c>
-      <c r="D21" s="2">
+      <c r="B21" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" s="4">
+        <v>3</v>
+      </c>
+      <c r="D21" s="4">
         <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C22" s="2">
-        <v>3</v>
-      </c>
-      <c r="D22" s="2">
+      <c r="B22" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" s="4">
+        <v>3</v>
+      </c>
+      <c r="D22" s="4">
         <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C23" s="2">
+      <c r="B23" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" s="4">
         <v>4</v>
       </c>
-      <c r="D23" s="2">
+      <c r="D23" s="4">
         <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C24" s="2">
+      <c r="B24" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="4">
         <v>4</v>
       </c>
-      <c r="D24" s="2">
+      <c r="D24" s="4">
         <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C25" s="2">
+      <c r="B25" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" s="4">
         <v>4</v>
       </c>
-      <c r="D25" s="2">
+      <c r="D25" s="4">
         <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C26" s="2">
-        <v>5</v>
-      </c>
-      <c r="D26" s="2">
+      <c r="B26" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26" s="4">
+        <v>5</v>
+      </c>
+      <c r="D26" s="4">
         <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C27" s="2">
+      <c r="B27" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" s="4">
         <v>6</v>
       </c>
-      <c r="D27" s="2">
+      <c r="D27" s="4">
         <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C28" s="2">
+      <c r="B28" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" s="4">
         <v>6</v>
       </c>
-      <c r="D28" s="2">
+      <c r="D28" s="4">
         <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:6">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C29" s="2">
+      <c r="B29" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" s="4">
         <v>7</v>
       </c>
-      <c r="D29" s="2">
-        <v>14</v>
-      </c>
-      <c r="F29" s="3"/>
+      <c r="D29" s="4">
+        <v>14</v>
+      </c>
+      <c r="F29" s="5"/>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
+      <c r="A30" s="4"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
+      <c r="A31" s="4"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2">
+      <c r="C32" s="4"/>
+      <c r="D32" s="4">
         <f>AVERAGE(D15:D29)</f>
         <v>14.0666666666667</v>
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C35" s="4">
-        <v>3</v>
-      </c>
-      <c r="D35" s="4">
+      <c r="C35" s="6">
+        <v>3</v>
+      </c>
+      <c r="D35" s="6">
         <v>13</v>
       </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C36" s="4">
+      <c r="C36" s="6">
         <v>4</v>
       </c>
-      <c r="D36" s="4">
+      <c r="D36" s="6">
         <v>14</v>
       </c>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C37" s="4">
+      <c r="C37" s="6">
         <v>4</v>
       </c>
-      <c r="D37" s="4">
+      <c r="D37" s="6">
         <v>12</v>
       </c>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C38" s="4">
-        <v>5</v>
-      </c>
-      <c r="D38" s="4">
+      <c r="C38" s="6">
+        <v>5</v>
+      </c>
+      <c r="D38" s="6">
         <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C39" s="4">
+      <c r="C39" s="6">
         <v>6</v>
       </c>
-      <c r="D39" s="4">
+      <c r="D39" s="6">
         <v>13</v>
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C40" s="4">
+      <c r="C40" s="6">
         <v>7</v>
       </c>
-      <c r="D40" s="4">
+      <c r="D40" s="6">
         <v>12</v>
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="4" t="s">
+      <c r="A41" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C41" s="4">
+      <c r="C41" s="6">
         <v>8</v>
       </c>
-      <c r="D41" s="4">
+      <c r="D41" s="6">
         <v>13</v>
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="4"/>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
+      <c r="A42" s="6"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="4"/>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
+      <c r="A43" s="6"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="4" t="s">
+      <c r="A44" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4">
+      <c r="C44" s="6"/>
+      <c r="D44" s="6">
         <f>AVERAGE(D35:D41)</f>
         <v>12.7142857142857</v>
       </c>
     </row>
     <row r="47" spans="1:4">
-      <c r="A47" s="5" t="s">
+      <c r="A47" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B47" s="5"/>
-      <c r="C47" s="5"/>
-      <c r="D47" s="5">
+      <c r="B47" s="7"/>
+      <c r="C47" s="7"/>
+      <c r="D47" s="7">
         <f>AVERAGE(D2:D9,D15:D29,D35:D41)</f>
         <v>14.0333333333333</v>
       </c>
@@ -1846,496 +1965,496 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="1">
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2">
         <v>1</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="2">
         <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="1">
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="2">
         <v>1</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="2">
         <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="1">
+      <c r="B4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2">
         <v>1</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="1">
+      <c r="B5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="2">
         <v>1</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="1">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1">
+      <c r="B6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="2">
+        <v>3</v>
+      </c>
+      <c r="D6" s="2">
         <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="1">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1">
+      <c r="B7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="2">
+        <v>3</v>
+      </c>
+      <c r="D7" s="2">
         <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="1">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1">
+      <c r="B8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="2">
+        <v>3</v>
+      </c>
+      <c r="D8" s="2">
         <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="1">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1">
+      <c r="B9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="2">
+        <v>3</v>
+      </c>
+      <c r="D9" s="2">
         <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" s="1">
-        <v>3</v>
-      </c>
-      <c r="D10" s="1">
+      <c r="B10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="2">
+        <v>3</v>
+      </c>
+      <c r="D10" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="1">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1">
+      <c r="B11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="2">
+        <v>3</v>
+      </c>
+      <c r="D11" s="2">
         <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" s="1">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1">
+      <c r="B12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="2">
+        <v>3</v>
+      </c>
+      <c r="D12" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="1">
+      <c r="B13" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="2">
         <v>4</v>
       </c>
-      <c r="D13" s="1">
+      <c r="D13" s="2">
         <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" s="1">
-        <v>5</v>
-      </c>
-      <c r="D14" s="1">
+      <c r="B14" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="2">
+        <v>5</v>
+      </c>
+      <c r="D14" s="2">
         <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1">
+      <c r="B17" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2">
         <f>AVERAGE(D2:D14)</f>
         <v>14.5384615384615</v>
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C20" s="2">
-        <v>2</v>
-      </c>
-      <c r="D20" s="2">
+      <c r="B20" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" s="4">
+        <v>2</v>
+      </c>
+      <c r="D20" s="4">
         <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C21" s="2">
-        <v>3</v>
-      </c>
-      <c r="D21" s="2">
+      <c r="B21" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" s="4">
+        <v>3</v>
+      </c>
+      <c r="D21" s="4">
         <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C22" s="2">
-        <v>3</v>
-      </c>
-      <c r="D22" s="2">
+      <c r="B22" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" s="4">
+        <v>3</v>
+      </c>
+      <c r="D22" s="4">
         <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C23" s="2">
-        <v>3</v>
-      </c>
-      <c r="D23" s="2">
+      <c r="B23" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" s="4">
+        <v>3</v>
+      </c>
+      <c r="D23" s="4">
         <v>14</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C24" s="2">
-        <v>3</v>
-      </c>
-      <c r="D24" s="2">
+      <c r="B24" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="4">
+        <v>3</v>
+      </c>
+      <c r="D24" s="4">
         <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C25" s="2">
+      <c r="B25" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" s="4">
         <v>4</v>
       </c>
-      <c r="D25" s="2">
+      <c r="D25" s="4">
         <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C26" s="2">
+      <c r="B26" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26" s="4">
         <v>4</v>
       </c>
-      <c r="D26" s="2">
+      <c r="D26" s="4">
         <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C27" s="2">
-        <v>5</v>
-      </c>
-      <c r="D27" s="2">
+      <c r="B27" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" s="4">
+        <v>5</v>
+      </c>
+      <c r="D27" s="4">
         <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C28" s="2">
-        <v>5</v>
-      </c>
-      <c r="D28" s="2">
+      <c r="B28" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" s="4">
+        <v>5</v>
+      </c>
+      <c r="D28" s="4">
         <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C29" s="2">
+      <c r="B29" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" s="4">
         <v>6</v>
       </c>
-      <c r="D29" s="2">
+      <c r="D29" s="4">
         <v>15</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
+      <c r="A30" s="4"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
+      <c r="A31" s="4"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2">
+      <c r="C32" s="4"/>
+      <c r="D32" s="4">
         <f>AVERAGE(D20:D29)</f>
         <v>14.4</v>
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C35" s="4">
-        <v>3</v>
-      </c>
-      <c r="D35" s="4">
+      <c r="C35" s="6">
+        <v>3</v>
+      </c>
+      <c r="D35" s="6">
         <v>13</v>
       </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C36" s="4">
+      <c r="C36" s="6">
         <v>4</v>
       </c>
-      <c r="D36" s="4">
+      <c r="D36" s="6">
         <v>14</v>
       </c>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C37" s="4">
+      <c r="C37" s="6">
         <v>4</v>
       </c>
-      <c r="D37" s="4">
+      <c r="D37" s="6">
         <v>12</v>
       </c>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C38" s="4">
+      <c r="C38" s="6">
         <v>4</v>
       </c>
-      <c r="D38" s="4">
+      <c r="D38" s="6">
         <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C39" s="4">
-        <v>5</v>
-      </c>
-      <c r="D39" s="4">
+      <c r="C39" s="6">
+        <v>5</v>
+      </c>
+      <c r="D39" s="6">
         <v>13</v>
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C40" s="4">
+      <c r="C40" s="6">
         <v>6</v>
       </c>
-      <c r="D40" s="4">
+      <c r="D40" s="6">
         <v>13</v>
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="4" t="s">
+      <c r="A41" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C41" s="4">
+      <c r="C41" s="6">
         <v>8</v>
       </c>
-      <c r="D41" s="4">
+      <c r="D41" s="6">
         <v>13</v>
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="4"/>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
+      <c r="A42" s="6"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="4"/>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
+      <c r="A43" s="6"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="4" t="s">
+      <c r="A44" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4">
+      <c r="C44" s="6"/>
+      <c r="D44" s="6">
         <f>AVERAGE(D35:D41)</f>
         <v>12.8571428571429</v>
       </c>
@@ -2380,496 +2499,496 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="1">
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2">
         <v>1</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="2">
         <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="1">
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="2">
         <v>1</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="2">
         <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="1">
+      <c r="B4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2">
         <v>1</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="1">
+      <c r="B5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="2">
         <v>1</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="1">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1">
+      <c r="B6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="2">
+        <v>3</v>
+      </c>
+      <c r="D6" s="2">
         <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="1">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1">
+      <c r="B7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="2">
+        <v>3</v>
+      </c>
+      <c r="D7" s="2">
         <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="1">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1">
+      <c r="B8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="2">
+        <v>3</v>
+      </c>
+      <c r="D8" s="2">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="1">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1">
+      <c r="B9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="2">
+        <v>3</v>
+      </c>
+      <c r="D9" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" s="1">
-        <v>3</v>
-      </c>
-      <c r="D10" s="1">
+      <c r="B10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="2">
+        <v>3</v>
+      </c>
+      <c r="D10" s="2">
         <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="1">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1">
+      <c r="B11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="2">
+        <v>3</v>
+      </c>
+      <c r="D11" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" s="1">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1">
+      <c r="B12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="2">
+        <v>3</v>
+      </c>
+      <c r="D12" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="1">
+      <c r="B13" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="2">
         <v>4</v>
       </c>
-      <c r="D13" s="1">
+      <c r="D13" s="2">
         <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" s="1">
+      <c r="B14" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="2">
         <v>4</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D14" s="2">
         <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15" s="1">
-        <v>5</v>
-      </c>
-      <c r="D15" s="1">
+      <c r="B15" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="2">
+        <v>5</v>
+      </c>
+      <c r="D15" s="2">
         <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C16" s="1">
-        <v>5</v>
-      </c>
-      <c r="D16" s="1">
+      <c r="B16" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="2">
+        <v>5</v>
+      </c>
+      <c r="D16" s="2">
         <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1">
+      <c r="B19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2">
         <f>AVERAGE(D2:D16)</f>
         <v>14.2</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C22" s="2">
-        <v>2</v>
-      </c>
-      <c r="D22" s="2">
+      <c r="B22" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" s="4">
+        <v>2</v>
+      </c>
+      <c r="D22" s="4">
         <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C23" s="2">
-        <v>3</v>
-      </c>
-      <c r="D23" s="2">
+      <c r="B23" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" s="4">
+        <v>3</v>
+      </c>
+      <c r="D23" s="4">
         <v>14</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C24" s="2">
-        <v>3</v>
-      </c>
-      <c r="D24" s="2">
+      <c r="B24" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="4">
+        <v>3</v>
+      </c>
+      <c r="D24" s="4">
         <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C25" s="2">
-        <v>3</v>
-      </c>
-      <c r="D25" s="2">
+      <c r="B25" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" s="4">
+        <v>3</v>
+      </c>
+      <c r="D25" s="4">
         <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C26" s="2">
+      <c r="B26" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26" s="4">
         <v>4</v>
       </c>
-      <c r="D26" s="2">
+      <c r="D26" s="4">
         <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C27" s="2">
+      <c r="B27" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" s="4">
         <v>4</v>
       </c>
-      <c r="D27" s="2">
+      <c r="D27" s="4">
         <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C28" s="2">
-        <v>5</v>
-      </c>
-      <c r="D28" s="2">
+      <c r="B28" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" s="4">
+        <v>5</v>
+      </c>
+      <c r="D28" s="4">
         <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C29" s="2">
+      <c r="B29" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" s="4">
         <v>6</v>
       </c>
-      <c r="D29" s="2">
+      <c r="D29" s="4">
         <v>15</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
+      <c r="A30" s="4"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
+      <c r="A31" s="4"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2">
+      <c r="C32" s="4"/>
+      <c r="D32" s="4">
         <f>AVERAGE(D22:D29)</f>
         <v>14</v>
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C35" s="4">
-        <v>3</v>
-      </c>
-      <c r="D35" s="4">
+      <c r="C35" s="6">
+        <v>3</v>
+      </c>
+      <c r="D35" s="6">
         <v>13</v>
       </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C36" s="4">
+      <c r="C36" s="6">
         <v>4</v>
       </c>
-      <c r="D36" s="4">
+      <c r="D36" s="6">
         <v>14</v>
       </c>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C37" s="4">
+      <c r="C37" s="6">
         <v>4</v>
       </c>
-      <c r="D37" s="4">
+      <c r="D37" s="6">
         <v>12</v>
       </c>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C38" s="4">
+      <c r="C38" s="6">
         <v>4</v>
       </c>
-      <c r="D38" s="4">
+      <c r="D38" s="6">
         <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C39" s="4">
-        <v>5</v>
-      </c>
-      <c r="D39" s="4">
+      <c r="C39" s="6">
+        <v>5</v>
+      </c>
+      <c r="D39" s="6">
         <v>14</v>
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C40" s="4">
+      <c r="C40" s="6">
         <v>6</v>
       </c>
-      <c r="D40" s="4">
+      <c r="D40" s="6">
         <v>13</v>
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="4" t="s">
+      <c r="A41" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C41" s="4">
+      <c r="C41" s="6">
         <v>8</v>
       </c>
-      <c r="D41" s="4">
+      <c r="D41" s="6">
         <v>13</v>
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="4"/>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
+      <c r="A42" s="6"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="4"/>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
+      <c r="A43" s="6"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="4" t="s">
+      <c r="A44" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4">
+      <c r="C44" s="6"/>
+      <c r="D44" s="6">
         <f>AVERAGE(D35:D41)</f>
         <v>13</v>
       </c>
@@ -2915,513 +3034,1583 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="1">
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2">
         <v>1</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="2">
         <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="1">
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="2">
         <v>1</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="2">
         <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="1">
+      <c r="B4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2">
         <v>1</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="2">
         <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="1">
+      <c r="B5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="2">
         <v>1</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="2">
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="1">
+      <c r="B6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="2">
         <v>1</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="2">
         <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="1">
-        <v>2</v>
-      </c>
-      <c r="D7" s="1">
+      <c r="B7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="2">
+        <v>2</v>
+      </c>
+      <c r="D7" s="2">
         <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="1">
-        <v>2</v>
-      </c>
-      <c r="D8" s="1">
+      <c r="B8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="2">
+        <v>2</v>
+      </c>
+      <c r="D8" s="2">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="1">
-        <v>2</v>
-      </c>
-      <c r="D9" s="1">
+      <c r="B9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="2">
+        <v>2</v>
+      </c>
+      <c r="D9" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" s="1">
-        <v>2</v>
-      </c>
-      <c r="D10" s="1">
+      <c r="B10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="2">
+        <v>2</v>
+      </c>
+      <c r="D10" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="1">
-        <v>2</v>
-      </c>
-      <c r="D11" s="1">
+      <c r="B11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="2">
+        <v>2</v>
+      </c>
+      <c r="D11" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" s="1">
-        <v>2</v>
-      </c>
-      <c r="D12" s="1">
+      <c r="B12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="2">
+        <v>2</v>
+      </c>
+      <c r="D12" s="2">
         <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="1">
-        <v>3</v>
-      </c>
-      <c r="D13" s="1">
+      <c r="B13" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="2">
+        <v>3</v>
+      </c>
+      <c r="D13" s="2">
         <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" s="1">
-        <v>3</v>
-      </c>
-      <c r="D14" s="1">
+      <c r="B14" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="2">
+        <v>3</v>
+      </c>
+      <c r="D14" s="2">
         <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15" s="1">
-        <v>3</v>
-      </c>
-      <c r="D15" s="1">
+      <c r="B15" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="2">
+        <v>3</v>
+      </c>
+      <c r="D15" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C16" s="1">
+      <c r="B16" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="2">
         <v>4</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D16" s="2">
         <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" s="1">
+      <c r="B17" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="2">
         <v>4</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D17" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1">
+      <c r="B20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2">
         <f>AVERAGE(D2:D17)</f>
         <v>13.9375</v>
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C23" s="2">
-        <v>2</v>
-      </c>
-      <c r="D23" s="2">
+      <c r="B23" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" s="4">
+        <v>2</v>
+      </c>
+      <c r="D23" s="4">
         <v>13</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C24" s="2">
-        <v>2</v>
-      </c>
-      <c r="D24" s="2">
+      <c r="B24" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="4">
+        <v>2</v>
+      </c>
+      <c r="D24" s="4">
         <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C25" s="2">
-        <v>3</v>
-      </c>
-      <c r="D25" s="2">
+      <c r="B25" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" s="4">
+        <v>3</v>
+      </c>
+      <c r="D25" s="4">
         <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C26" s="2">
-        <v>3</v>
-      </c>
-      <c r="D26" s="2">
+      <c r="B26" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26" s="4">
+        <v>3</v>
+      </c>
+      <c r="D26" s="4">
         <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C27" s="2">
-        <v>3</v>
-      </c>
-      <c r="D27" s="2">
+      <c r="B27" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" s="4">
+        <v>3</v>
+      </c>
+      <c r="D27" s="4">
         <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C28" s="2">
-        <v>3</v>
-      </c>
-      <c r="D28" s="2">
+      <c r="B28" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" s="4">
+        <v>3</v>
+      </c>
+      <c r="D28" s="4">
         <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C29" s="2">
+      <c r="B29" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" s="4">
         <v>4</v>
       </c>
-      <c r="D29" s="2">
+      <c r="D29" s="4">
         <v>14</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C30" s="2">
+      <c r="B30" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30" s="4">
         <v>4</v>
       </c>
-      <c r="D30" s="2">
+      <c r="D30" s="4">
         <v>12</v>
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C31" s="2">
-        <v>5</v>
-      </c>
-      <c r="D31" s="2">
+      <c r="B31" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C31" s="4">
+        <v>5</v>
+      </c>
+      <c r="D31" s="4">
         <v>13</v>
       </c>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C32" s="2">
-        <v>5</v>
-      </c>
-      <c r="D32" s="2">
+      <c r="B32" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="4">
+        <v>5</v>
+      </c>
+      <c r="D32" s="4">
         <v>12</v>
       </c>
     </row>
     <row r="33" spans="1:6">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C33" s="2">
+      <c r="B33" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C33" s="4">
         <v>6</v>
       </c>
-      <c r="D33" s="2">
+      <c r="D33" s="4">
         <v>11</v>
       </c>
-      <c r="F33" s="3"/>
+      <c r="F33" s="5"/>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
+      <c r="A34" s="4"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="2"/>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
+      <c r="A35" s="4"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="2" t="s">
+      <c r="A36" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2">
+      <c r="C36" s="4"/>
+      <c r="D36" s="4">
         <f>AVERAGE(D23:D33)</f>
         <v>12.7272727272727</v>
       </c>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C39" s="4">
-        <v>2</v>
-      </c>
-      <c r="D39" s="4">
+      <c r="C39" s="6">
+        <v>2</v>
+      </c>
+      <c r="D39" s="6">
         <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C40" s="4">
+      <c r="C40" s="6">
         <v>4</v>
       </c>
-      <c r="D40" s="4">
+      <c r="D40" s="6">
         <v>11</v>
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="4" t="s">
+      <c r="A41" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C41" s="4">
-        <v>5</v>
-      </c>
-      <c r="D41" s="4">
+      <c r="C41" s="6">
+        <v>5</v>
+      </c>
+      <c r="D41" s="6">
         <v>11</v>
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="4"/>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
+      <c r="A42" s="6"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="4"/>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
+      <c r="A43" s="6"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="4" t="s">
+      <c r="A44" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4">
+      <c r="C44" s="6"/>
+      <c r="D44" s="6">
         <f>AVERAGE(D39:D41)</f>
         <v>9.66666666666667</v>
       </c>
     </row>
     <row r="47" spans="1:4">
-      <c r="A47" s="5" t="s">
+      <c r="A47" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B47" s="5"/>
-      <c r="C47" s="5"/>
-      <c r="D47" s="5">
+      <c r="B47" s="7"/>
+      <c r="C47" s="7"/>
+      <c r="D47" s="7">
         <f>AVERAGE(D2:D17,D23:D33,D39:D41)</f>
         <v>13.0666666666667</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E66"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="18.125" customWidth="1"/>
+    <col min="4" max="4" width="8.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="2">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="4">
+        <v>1</v>
+      </c>
+      <c r="E6" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="4">
+        <v>1</v>
+      </c>
+      <c r="E7" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="4">
+        <v>1</v>
+      </c>
+      <c r="E8" s="4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="2">
+        <v>2</v>
+      </c>
+      <c r="E9" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" s="2">
+        <v>2</v>
+      </c>
+      <c r="E10" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="2">
+        <v>2</v>
+      </c>
+      <c r="E11" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" s="2">
+        <v>2</v>
+      </c>
+      <c r="E12" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" s="2">
+        <v>2</v>
+      </c>
+      <c r="E13" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="4">
+        <v>2</v>
+      </c>
+      <c r="E14" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="4">
+        <v>2</v>
+      </c>
+      <c r="E15" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" s="4">
+        <v>2</v>
+      </c>
+      <c r="E16" s="4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" s="4">
+        <v>2</v>
+      </c>
+      <c r="E17" s="4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" s="4">
+        <v>2</v>
+      </c>
+      <c r="E18" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" s="5">
+        <v>3</v>
+      </c>
+      <c r="E19" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D20" s="5">
+        <v>3</v>
+      </c>
+      <c r="E20" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" s="5">
+        <v>3</v>
+      </c>
+      <c r="E21" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D22" s="2">
+        <v>3</v>
+      </c>
+      <c r="E22" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D23" s="2">
+        <v>3</v>
+      </c>
+      <c r="E23" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D24" s="2">
+        <v>3</v>
+      </c>
+      <c r="E24" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D25" s="4">
+        <v>3</v>
+      </c>
+      <c r="E25" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D26" s="4">
+        <v>3</v>
+      </c>
+      <c r="E26" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D27" s="4">
+        <v>3</v>
+      </c>
+      <c r="E27" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D28" s="4">
+        <v>3</v>
+      </c>
+      <c r="E28" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D29" s="4">
+        <v>3</v>
+      </c>
+      <c r="E29" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D30" s="4">
+        <v>3</v>
+      </c>
+      <c r="E30" s="4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D31" s="4">
+        <v>3</v>
+      </c>
+      <c r="E31" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D32" s="5">
+        <v>4</v>
+      </c>
+      <c r="E32" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D33" s="5">
+        <v>4</v>
+      </c>
+      <c r="E33" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D34" s="5">
+        <v>4</v>
+      </c>
+      <c r="E34" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D35" s="2">
+        <v>4</v>
+      </c>
+      <c r="E35" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D36" s="4">
+        <v>4</v>
+      </c>
+      <c r="E36" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D37" s="4">
+        <v>4</v>
+      </c>
+      <c r="E37" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D38" s="4">
+        <v>4</v>
+      </c>
+      <c r="E38" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D39" s="4">
+        <v>4</v>
+      </c>
+      <c r="E39" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D40" s="4">
+        <v>4</v>
+      </c>
+      <c r="E40" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D41" s="4">
+        <v>4</v>
+      </c>
+      <c r="E41" s="4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D42" s="4">
+        <v>4</v>
+      </c>
+      <c r="E42" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D43" s="5">
+        <v>5</v>
+      </c>
+      <c r="E43" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D44" s="5">
+        <v>5</v>
+      </c>
+      <c r="E44" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D45" s="2">
+        <v>5</v>
+      </c>
+      <c r="E45" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D46" s="4">
+        <v>5</v>
+      </c>
+      <c r="E46" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D47" s="4">
+        <v>5</v>
+      </c>
+      <c r="E47" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D48" s="4">
+        <v>5</v>
+      </c>
+      <c r="E48" s="4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D49" s="5">
+        <v>6</v>
+      </c>
+      <c r="E49" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D50" s="4">
+        <v>6</v>
+      </c>
+      <c r="E50" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D51" s="4">
+        <v>6</v>
+      </c>
+      <c r="E51" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D52" s="5">
+        <v>7</v>
+      </c>
+      <c r="E52" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D53" s="5">
+        <v>7</v>
+      </c>
+      <c r="E53" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D54" s="4">
+        <v>7</v>
+      </c>
+      <c r="E54" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D55" s="4">
+        <v>7</v>
+      </c>
+      <c r="E55" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D56" s="4">
+        <v>7</v>
+      </c>
+      <c r="E56" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D57" s="4">
+        <v>7</v>
+      </c>
+      <c r="E57" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D58" s="4">
+        <v>7</v>
+      </c>
+      <c r="E58" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="2"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="2"/>
+      <c r="E59" s="2"/>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="2"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="2"/>
+      <c r="E60" s="2"/>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="2"/>
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="2"/>
+      <c r="E61" s="2"/>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="2"/>
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="2"/>
+      <c r="E62" s="2"/>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="2"/>
+      <c r="B63" s="2"/>
+      <c r="C63" s="2"/>
+      <c r="D63" s="2"/>
+      <c r="E63" s="2"/>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B64" s="2"/>
+      <c r="C64" s="2"/>
+      <c r="D64" s="2"/>
+      <c r="E64" s="2"/>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="2"/>
+      <c r="B65" s="2"/>
+      <c r="C65" s="2"/>
+      <c r="D65" s="2"/>
+      <c r="E65" s="2"/>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B66" s="2"/>
+      <c r="C66" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D66" s="2"/>
+      <c r="E66" s="2">
+        <f>SUM(E2:E58)</f>
+        <v>360</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState ref="A2:E58">
+    <sortCondition ref="D2"/>
+  </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -3452,496 +4641,496 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="1">
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2">
         <v>1</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="2">
         <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="1">
-        <v>2</v>
-      </c>
-      <c r="D3" s="1">
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="2">
+        <v>2</v>
+      </c>
+      <c r="D3" s="2">
         <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="1">
-        <v>2</v>
-      </c>
-      <c r="D4" s="1">
+      <c r="B4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2">
+        <v>2</v>
+      </c>
+      <c r="D4" s="2">
         <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="1">
-        <v>2</v>
-      </c>
-      <c r="D5" s="1">
+      <c r="B5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="2">
+        <v>2</v>
+      </c>
+      <c r="D5" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="1">
-        <v>2</v>
-      </c>
-      <c r="D6" s="1">
+      <c r="B6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="2">
+        <v>2</v>
+      </c>
+      <c r="D6" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="1">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1">
+      <c r="B7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="2">
+        <v>3</v>
+      </c>
+      <c r="D7" s="2">
         <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="1">
-        <v>5</v>
-      </c>
-      <c r="D8" s="1">
+      <c r="B8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="2">
+        <v>5</v>
+      </c>
+      <c r="D8" s="2">
         <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="1">
-        <v>5</v>
-      </c>
-      <c r="D9" s="1">
+      <c r="B9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="2">
+        <v>5</v>
+      </c>
+      <c r="D9" s="2">
         <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1">
+      <c r="B12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2">
         <f>AVERAGE(D2:D9)</f>
         <v>15.125</v>
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" s="2">
+      <c r="A15" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="4">
         <v>1</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="4">
         <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C16" s="2">
-        <v>2</v>
-      </c>
-      <c r="D16" s="2">
+      <c r="B16" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="4">
+        <v>2</v>
+      </c>
+      <c r="D16" s="4">
         <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C17" s="2">
-        <v>2</v>
-      </c>
-      <c r="D17" s="2">
+      <c r="B17" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="4">
+        <v>2</v>
+      </c>
+      <c r="D17" s="4">
         <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C18" s="2">
-        <v>2</v>
-      </c>
-      <c r="D18" s="2">
+      <c r="B18" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="4">
+        <v>2</v>
+      </c>
+      <c r="D18" s="4">
         <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C19" s="2">
-        <v>3</v>
-      </c>
-      <c r="D19" s="2">
+      <c r="B19" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="4">
+        <v>3</v>
+      </c>
+      <c r="D19" s="4">
         <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C20" s="2">
-        <v>3</v>
-      </c>
-      <c r="D20" s="2">
+      <c r="B20" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" s="4">
+        <v>3</v>
+      </c>
+      <c r="D20" s="4">
         <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C21" s="2">
-        <v>3</v>
-      </c>
-      <c r="D21" s="2">
+      <c r="B21" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" s="4">
+        <v>3</v>
+      </c>
+      <c r="D21" s="4">
         <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C22" s="2">
-        <v>3</v>
-      </c>
-      <c r="D22" s="2">
+      <c r="B22" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" s="4">
+        <v>3</v>
+      </c>
+      <c r="D22" s="4">
         <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C23" s="2">
+      <c r="B23" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" s="4">
         <v>4</v>
       </c>
-      <c r="D23" s="2">
+      <c r="D23" s="4">
         <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C24" s="2">
+      <c r="B24" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="4">
         <v>4</v>
       </c>
-      <c r="D24" s="2">
+      <c r="D24" s="4">
         <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C25" s="2">
+      <c r="B25" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" s="4">
         <v>4</v>
       </c>
-      <c r="D25" s="2">
+      <c r="D25" s="4">
         <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C26" s="2">
-        <v>5</v>
-      </c>
-      <c r="D26" s="2">
+      <c r="B26" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26" s="4">
+        <v>5</v>
+      </c>
+      <c r="D26" s="4">
         <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C27" s="2">
-        <v>5</v>
-      </c>
-      <c r="D27" s="2">
+      <c r="B27" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" s="4">
+        <v>5</v>
+      </c>
+      <c r="D27" s="4">
         <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C28" s="2">
+      <c r="B28" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" s="4">
         <v>6</v>
       </c>
-      <c r="D28" s="2">
+      <c r="D28" s="4">
         <v>14</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C29" s="2">
+      <c r="B29" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" s="4">
         <v>6</v>
       </c>
-      <c r="D29" s="2">
+      <c r="D29" s="4">
         <v>15</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C30" s="2">
+      <c r="B30" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30" s="4">
         <v>7</v>
       </c>
-      <c r="D30" s="2">
+      <c r="D30" s="4">
         <v>14</v>
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
+      <c r="A31" s="4"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="2"/>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
+      <c r="A32" s="4"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2">
+      <c r="C33" s="4"/>
+      <c r="D33" s="4">
         <f>AVERAGE(D15:D30)</f>
         <v>13.875</v>
       </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C36" s="4">
-        <v>3</v>
-      </c>
-      <c r="D36" s="4">
+      <c r="C36" s="6">
+        <v>3</v>
+      </c>
+      <c r="D36" s="6">
         <v>13</v>
       </c>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C37" s="4">
+      <c r="C37" s="6">
         <v>4</v>
       </c>
-      <c r="D37" s="4">
+      <c r="D37" s="6">
         <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C38" s="4">
+      <c r="C38" s="6">
         <v>4</v>
       </c>
-      <c r="D38" s="4">
+      <c r="D38" s="6">
         <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C39" s="4">
-        <v>5</v>
-      </c>
-      <c r="D39" s="4">
+      <c r="C39" s="6">
+        <v>5</v>
+      </c>
+      <c r="D39" s="6">
         <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C40" s="4">
+      <c r="C40" s="6">
         <v>6</v>
       </c>
-      <c r="D40" s="4">
+      <c r="D40" s="6">
         <v>13</v>
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="4" t="s">
+      <c r="A41" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C41" s="4">
+      <c r="C41" s="6">
         <v>7</v>
       </c>
-      <c r="D41" s="4">
+      <c r="D41" s="6">
         <v>12</v>
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="4"/>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
+      <c r="A42" s="6"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="4"/>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
+      <c r="A43" s="6"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="4" t="s">
+      <c r="A44" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4">
+      <c r="C44" s="6"/>
+      <c r="D44" s="6">
         <f>AVERAGE(D36:D41)</f>
         <v>12.6666666666667</v>
       </c>
@@ -3987,508 +5176,508 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="1">
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2">
         <v>1</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="2">
         <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="1">
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="2">
         <v>1</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="2">
         <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="1">
+      <c r="B4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2">
         <v>1</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="2">
         <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="1">
+      <c r="B5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="2">
         <v>1</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="2">
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="1">
+      <c r="B6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="2">
         <v>1</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="2">
         <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="1">
-        <v>2</v>
-      </c>
-      <c r="D7" s="1">
+      <c r="B7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="2">
+        <v>2</v>
+      </c>
+      <c r="D7" s="2">
         <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="1">
-        <v>2</v>
-      </c>
-      <c r="D8" s="1">
+      <c r="B8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="2">
+        <v>2</v>
+      </c>
+      <c r="D8" s="2">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="1">
-        <v>2</v>
-      </c>
-      <c r="D9" s="1">
+      <c r="B9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="2">
+        <v>2</v>
+      </c>
+      <c r="D9" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" s="1">
-        <v>2</v>
-      </c>
-      <c r="D10" s="1">
+      <c r="B10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="2">
+        <v>2</v>
+      </c>
+      <c r="D10" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="1">
-        <v>2</v>
-      </c>
-      <c r="D11" s="1">
+      <c r="B11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="2">
+        <v>2</v>
+      </c>
+      <c r="D11" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" s="1">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1">
+      <c r="B12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="2">
+        <v>3</v>
+      </c>
+      <c r="D12" s="2">
         <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="1">
-        <v>3</v>
-      </c>
-      <c r="D13" s="1">
+      <c r="B13" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="2">
+        <v>3</v>
+      </c>
+      <c r="D13" s="2">
         <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" s="1">
-        <v>3</v>
-      </c>
-      <c r="D14" s="1">
+      <c r="B14" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="2">
+        <v>3</v>
+      </c>
+      <c r="D14" s="2">
         <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15" s="1">
-        <v>3</v>
-      </c>
-      <c r="D15" s="1">
+      <c r="B15" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="2">
+        <v>3</v>
+      </c>
+      <c r="D15" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C16" s="1">
+      <c r="B16" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="2">
         <v>4</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D16" s="2">
         <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" s="1">
+      <c r="B17" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="2">
         <v>4</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D17" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1">
+      <c r="B20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2">
         <f>AVERAGE(D2:D17)</f>
         <v>14.125</v>
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C23" s="2">
-        <v>2</v>
-      </c>
-      <c r="D23" s="2">
+      <c r="B23" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" s="4">
+        <v>2</v>
+      </c>
+      <c r="D23" s="4">
         <v>13</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C24" s="2">
-        <v>2</v>
-      </c>
-      <c r="D24" s="2">
+      <c r="B24" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="4">
+        <v>2</v>
+      </c>
+      <c r="D24" s="4">
         <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C25" s="2">
-        <v>3</v>
-      </c>
-      <c r="D25" s="2">
+      <c r="B25" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" s="4">
+        <v>3</v>
+      </c>
+      <c r="D25" s="4">
         <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C26" s="2">
-        <v>3</v>
-      </c>
-      <c r="D26" s="2">
+      <c r="B26" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26" s="4">
+        <v>3</v>
+      </c>
+      <c r="D26" s="4">
         <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C27" s="2">
-        <v>3</v>
-      </c>
-      <c r="D27" s="2">
+      <c r="B27" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" s="4">
+        <v>3</v>
+      </c>
+      <c r="D27" s="4">
         <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C28" s="2">
-        <v>3</v>
-      </c>
-      <c r="D28" s="2">
+      <c r="B28" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" s="4">
+        <v>3</v>
+      </c>
+      <c r="D28" s="4">
         <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C29" s="2">
+      <c r="B29" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" s="4">
         <v>4</v>
       </c>
-      <c r="D29" s="2">
+      <c r="D29" s="4">
         <v>14</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C30" s="2">
+      <c r="B30" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30" s="4">
         <v>4</v>
       </c>
-      <c r="D30" s="2">
+      <c r="D30" s="4">
         <v>12</v>
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C31" s="2">
-        <v>5</v>
-      </c>
-      <c r="D31" s="2">
+      <c r="B31" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C31" s="4">
+        <v>5</v>
+      </c>
+      <c r="D31" s="4">
         <v>13</v>
       </c>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C32" s="2">
-        <v>5</v>
-      </c>
-      <c r="D32" s="2">
+      <c r="B32" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="4">
+        <v>5</v>
+      </c>
+      <c r="D32" s="4">
         <v>12</v>
       </c>
     </row>
     <row r="33" spans="1:6">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C33" s="2">
+      <c r="B33" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C33" s="4">
         <v>6</v>
       </c>
-      <c r="D33" s="2">
+      <c r="D33" s="4">
         <v>11</v>
       </c>
-      <c r="F33" s="3"/>
+      <c r="F33" s="5"/>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
+      <c r="A34" s="4"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="2"/>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
+      <c r="A35" s="4"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="2" t="s">
+      <c r="A36" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2">
+      <c r="C36" s="4"/>
+      <c r="D36" s="4">
         <f>AVERAGE(D23:D33)</f>
         <v>12.7272727272727</v>
       </c>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C39" s="4">
-        <v>2</v>
-      </c>
-      <c r="D39" s="4">
+      <c r="C39" s="6">
+        <v>2</v>
+      </c>
+      <c r="D39" s="6">
         <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C40" s="4">
+      <c r="C40" s="6">
         <v>4</v>
       </c>
-      <c r="D40" s="4">
+      <c r="D40" s="6">
         <v>11</v>
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="4" t="s">
+      <c r="A41" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C41" s="4">
-        <v>5</v>
-      </c>
-      <c r="D41" s="4">
+      <c r="C41" s="6">
+        <v>5</v>
+      </c>
+      <c r="D41" s="6">
         <v>11</v>
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="4"/>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
+      <c r="A42" s="6"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="4"/>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
+      <c r="A43" s="6"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="4" t="s">
+      <c r="A44" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4">
+      <c r="C44" s="6"/>
+      <c r="D44" s="6">
         <f>AVERAGE(D39:D41)</f>
         <v>9.66666666666667</v>
       </c>
     </row>
     <row r="47" spans="1:4">
-      <c r="A47" s="5" t="s">
+      <c r="A47" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B47" s="5"/>
-      <c r="C47" s="5"/>
-      <c r="D47" s="5">
+      <c r="B47" s="7"/>
+      <c r="C47" s="7"/>
+      <c r="D47" s="7">
         <f>AVERAGE(D2:D17,D23:D33,D39:D41)</f>
         <v>13.1666666666667</v>
       </c>
@@ -4524,506 +5713,500 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="1">
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2">
         <v>1</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="2">
         <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="1">
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="2">
         <v>1</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="2">
         <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="1">
-        <v>2</v>
-      </c>
-      <c r="D4" s="1">
+      <c r="B4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2">
+        <v>2</v>
+      </c>
+      <c r="D4" s="2">
         <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="1">
-        <v>2</v>
-      </c>
-      <c r="D5" s="1">
+      <c r="B5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="2">
+        <v>2</v>
+      </c>
+      <c r="D5" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="1">
-        <v>2</v>
-      </c>
-      <c r="D6" s="1">
+      <c r="B6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="2">
+        <v>2</v>
+      </c>
+      <c r="D6" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="1">
-        <v>2</v>
-      </c>
-      <c r="D7" s="1">
+      <c r="B7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="2">
+        <v>2</v>
+      </c>
+      <c r="D7" s="2">
         <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="1">
-        <v>2</v>
-      </c>
-      <c r="D8" s="1">
+      <c r="B8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="2">
+        <v>2</v>
+      </c>
+      <c r="D8" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="1">
-        <v>2</v>
-      </c>
-      <c r="D9" s="1">
+      <c r="B9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="2">
+        <v>2</v>
+      </c>
+      <c r="D9" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" s="1">
-        <v>3</v>
-      </c>
-      <c r="D10" s="1">
+      <c r="B10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="2">
+        <v>3</v>
+      </c>
+      <c r="D10" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="1">
+      <c r="B11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="2">
         <v>4</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1">
+      <c r="B14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2">
         <f>AVERAGE(D2:D11)</f>
         <v>13.8</v>
       </c>
     </row>
-    <row r="15" customFormat="1"/>
-    <row r="16" customFormat="1"/>
     <row r="17" spans="1:4">
-      <c r="A17" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C17" s="2">
+      <c r="A17" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="4">
         <v>1</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="4">
         <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C18" s="2">
-        <v>2</v>
-      </c>
-      <c r="D18" s="2">
+      <c r="B18" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="4">
+        <v>2</v>
+      </c>
+      <c r="D18" s="4">
         <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C19" s="2">
-        <v>2</v>
-      </c>
-      <c r="D19" s="2">
+      <c r="B19" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="4">
+        <v>2</v>
+      </c>
+      <c r="D19" s="4">
         <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C20" s="2">
-        <v>2</v>
-      </c>
-      <c r="D20" s="2">
+      <c r="B20" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" s="4">
+        <v>2</v>
+      </c>
+      <c r="D20" s="4">
         <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C21" s="2">
-        <v>3</v>
-      </c>
-      <c r="D21" s="2">
+      <c r="B21" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" s="4">
+        <v>3</v>
+      </c>
+      <c r="D21" s="4">
         <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C22" s="2">
-        <v>3</v>
-      </c>
-      <c r="D22" s="2">
+      <c r="B22" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" s="4">
+        <v>3</v>
+      </c>
+      <c r="D22" s="4">
         <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C23" s="2">
-        <v>3</v>
-      </c>
-      <c r="D23" s="2">
+      <c r="B23" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" s="4">
+        <v>3</v>
+      </c>
+      <c r="D23" s="4">
         <v>13</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C24" s="2">
-        <v>3</v>
-      </c>
-      <c r="D24" s="2">
+      <c r="B24" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="4">
+        <v>3</v>
+      </c>
+      <c r="D24" s="4">
         <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C25" s="2">
-        <v>3</v>
-      </c>
-      <c r="D25" s="2">
+      <c r="B25" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" s="4">
+        <v>3</v>
+      </c>
+      <c r="D25" s="4">
         <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C26" s="2">
+      <c r="B26" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26" s="4">
         <v>4</v>
       </c>
-      <c r="D26" s="2">
+      <c r="D26" s="4">
         <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C27" s="2">
+      <c r="B27" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" s="4">
         <v>4</v>
       </c>
-      <c r="D27" s="2">
+      <c r="D27" s="4">
         <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C28" s="2">
-        <v>5</v>
-      </c>
-      <c r="D28" s="2">
+      <c r="B28" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" s="4">
+        <v>5</v>
+      </c>
+      <c r="D28" s="4">
         <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C29" s="2">
-        <v>5</v>
-      </c>
-      <c r="D29" s="2">
+      <c r="B29" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" s="4">
+        <v>5</v>
+      </c>
+      <c r="D29" s="4">
         <v>12</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C30" s="2">
-        <v>5</v>
-      </c>
-      <c r="D30" s="2">
+      <c r="B30" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30" s="4">
+        <v>5</v>
+      </c>
+      <c r="D30" s="4">
         <v>12</v>
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C31" s="2">
+      <c r="B31" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C31" s="4">
         <v>6</v>
       </c>
-      <c r="D31" s="2">
+      <c r="D31" s="4">
         <v>11</v>
       </c>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C32" s="2">
+      <c r="B32" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="4">
         <v>7</v>
       </c>
-      <c r="D32" s="2">
+      <c r="D32" s="4">
         <v>14</v>
       </c>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
+      <c r="A33" s="4"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
+      <c r="A34" s="4"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="2" t="s">
+      <c r="A35" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2">
+      <c r="C35" s="4"/>
+      <c r="D35" s="4">
         <f>AVERAGE(D17:D32)</f>
         <v>13</v>
       </c>
     </row>
-    <row r="36" customFormat="1"/>
-    <row r="37" customFormat="1"/>
     <row r="38" spans="1:4">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C38" s="4">
-        <v>2</v>
-      </c>
-      <c r="D38" s="4">
+      <c r="C38" s="6">
+        <v>2</v>
+      </c>
+      <c r="D38" s="6">
         <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C39" s="4">
-        <v>5</v>
-      </c>
-      <c r="D39" s="4">
+      <c r="C39" s="6">
+        <v>5</v>
+      </c>
+      <c r="D39" s="6">
         <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C40" s="4">
-        <v>5</v>
-      </c>
-      <c r="D40" s="4">
+      <c r="C40" s="6">
+        <v>5</v>
+      </c>
+      <c r="D40" s="6">
         <v>11</v>
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="4" t="s">
+      <c r="A41" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C41" s="4">
+      <c r="C41" s="6">
         <v>7</v>
       </c>
-      <c r="D41" s="4">
+      <c r="D41" s="6">
         <v>12</v>
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="4"/>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
+      <c r="A42" s="6"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="4"/>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
+      <c r="A43" s="6"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="4" t="s">
+      <c r="A44" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4">
+      <c r="C44" s="6"/>
+      <c r="D44" s="6">
         <f>AVERAGE(D38:D41)</f>
         <v>10.5</v>
       </c>
     </row>
-    <row r="45" customFormat="1"/>
-    <row r="46" customFormat="1"/>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
         <v>37</v>
@@ -5064,508 +6247,508 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="1">
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2">
         <v>1</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="2">
         <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="1">
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="2">
         <v>1</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="2">
         <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="1">
-        <v>2</v>
-      </c>
-      <c r="D4" s="1">
+      <c r="B4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2">
+        <v>2</v>
+      </c>
+      <c r="D4" s="2">
         <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="1">
-        <v>2</v>
-      </c>
-      <c r="D5" s="1">
+      <c r="B5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="2">
+        <v>2</v>
+      </c>
+      <c r="D5" s="2">
         <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="1">
-        <v>2</v>
-      </c>
-      <c r="D6" s="1">
+      <c r="B6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="2">
+        <v>2</v>
+      </c>
+      <c r="D6" s="2">
         <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="1">
-        <v>2</v>
-      </c>
-      <c r="D7" s="1">
+      <c r="B7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="2">
+        <v>2</v>
+      </c>
+      <c r="D7" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="1">
-        <v>2</v>
-      </c>
-      <c r="D8" s="1">
+      <c r="B8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="2">
+        <v>2</v>
+      </c>
+      <c r="D8" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="1">
-        <v>2</v>
-      </c>
-      <c r="D9" s="1">
+      <c r="B9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="2">
+        <v>2</v>
+      </c>
+      <c r="D9" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" s="1">
-        <v>3</v>
-      </c>
-      <c r="D10" s="1">
+      <c r="B10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="2">
+        <v>3</v>
+      </c>
+      <c r="D10" s="2">
         <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="1">
-        <v>2</v>
-      </c>
-      <c r="D11" s="1">
+      <c r="B11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="2">
+        <v>2</v>
+      </c>
+      <c r="D11" s="2">
         <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" s="1">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1">
+      <c r="B12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="2">
+        <v>3</v>
+      </c>
+      <c r="D12" s="2">
         <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="1">
-        <v>3</v>
-      </c>
-      <c r="D13" s="1">
+      <c r="B13" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="2">
+        <v>3</v>
+      </c>
+      <c r="D13" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" s="1">
-        <v>3</v>
-      </c>
-      <c r="D14" s="1">
+      <c r="B14" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="2">
+        <v>3</v>
+      </c>
+      <c r="D14" s="2">
         <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15" s="1">
+      <c r="B15" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="2">
         <v>4</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D15" s="2">
         <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1">
+      <c r="B18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2">
         <f>AVERAGE(D2:D15)</f>
         <v>14.7142857142857</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C21" s="2">
+      <c r="A21" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" s="4">
         <v>1</v>
       </c>
-      <c r="D21" s="2">
+      <c r="D21" s="4">
         <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C22" s="2">
-        <v>2</v>
-      </c>
-      <c r="D22" s="2">
+      <c r="B22" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" s="4">
+        <v>2</v>
+      </c>
+      <c r="D22" s="4">
         <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C23" s="2">
-        <v>2</v>
-      </c>
-      <c r="D23" s="2">
+      <c r="B23" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" s="4">
+        <v>2</v>
+      </c>
+      <c r="D23" s="4">
         <v>14</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C24" s="2">
-        <v>3</v>
-      </c>
-      <c r="D24" s="2">
+      <c r="B24" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="4">
+        <v>3</v>
+      </c>
+      <c r="D24" s="4">
         <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C25" s="2">
-        <v>3</v>
-      </c>
-      <c r="D25" s="2">
+      <c r="B25" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" s="4">
+        <v>3</v>
+      </c>
+      <c r="D25" s="4">
         <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C26" s="2">
-        <v>3</v>
-      </c>
-      <c r="D26" s="2">
+      <c r="B26" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26" s="4">
+        <v>3</v>
+      </c>
+      <c r="D26" s="4">
         <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C27" s="2">
-        <v>3</v>
-      </c>
-      <c r="D27" s="2">
+      <c r="B27" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" s="4">
+        <v>3</v>
+      </c>
+      <c r="D27" s="4">
         <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C28" s="2">
-        <v>3</v>
-      </c>
-      <c r="D28" s="2">
+      <c r="B28" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" s="4">
+        <v>3</v>
+      </c>
+      <c r="D28" s="4">
         <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C29" s="2">
+      <c r="B29" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" s="4">
         <v>4</v>
       </c>
-      <c r="D29" s="2">
+      <c r="D29" s="4">
         <v>15</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C30" s="2">
+      <c r="B30" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30" s="4">
         <v>4</v>
       </c>
-      <c r="D30" s="2">
+      <c r="D30" s="4">
         <v>14</v>
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C31" s="2">
-        <v>5</v>
-      </c>
-      <c r="D31" s="2">
+      <c r="B31" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C31" s="4">
+        <v>5</v>
+      </c>
+      <c r="D31" s="4">
         <v>13</v>
       </c>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C32" s="2">
-        <v>5</v>
-      </c>
-      <c r="D32" s="2">
+      <c r="B32" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="4">
+        <v>5</v>
+      </c>
+      <c r="D32" s="4">
         <v>12</v>
       </c>
     </row>
     <row r="33" spans="1:6">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C33" s="2">
+      <c r="B33" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C33" s="4">
         <v>7</v>
       </c>
-      <c r="D33" s="2">
-        <v>14</v>
-      </c>
-      <c r="F33" s="3"/>
+      <c r="D33" s="4">
+        <v>14</v>
+      </c>
+      <c r="F33" s="5"/>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
+      <c r="A34" s="4"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="2"/>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
+      <c r="A35" s="4"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="2" t="s">
+      <c r="A36" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2">
+      <c r="C36" s="4"/>
+      <c r="D36" s="4">
         <f>AVERAGE(D21:D33)</f>
         <v>13.7692307692308</v>
       </c>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C39" s="4">
+      <c r="C39" s="6">
         <v>4</v>
       </c>
-      <c r="D39" s="4">
+      <c r="D39" s="6">
         <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C40" s="4">
+      <c r="C40" s="6">
         <v>4</v>
       </c>
-      <c r="D40" s="4">
+      <c r="D40" s="6">
         <v>12</v>
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="4" t="s">
+      <c r="A41" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C41" s="4">
+      <c r="C41" s="6">
         <v>7</v>
       </c>
-      <c r="D41" s="4">
+      <c r="D41" s="6">
         <v>12</v>
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="4"/>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
+      <c r="A42" s="6"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="4"/>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
+      <c r="A43" s="6"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="4" t="s">
+      <c r="A44" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4">
+      <c r="C44" s="6"/>
+      <c r="D44" s="6">
         <f>AVERAGE(D39:D41)</f>
         <v>12</v>
       </c>
     </row>
     <row r="47" spans="1:4">
-      <c r="A47" s="5" t="s">
+      <c r="A47" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B47" s="5"/>
-      <c r="C47" s="5"/>
-      <c r="D47" s="5">
+      <c r="B47" s="7"/>
+      <c r="C47" s="7"/>
+      <c r="D47" s="7">
         <f>AVERAGE(D2:D15,D21:D33,D39:D41)</f>
         <v>14.0333333333333</v>
       </c>
@@ -5599,256 +6782,256 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="2">
         <v>1</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" s="2">
         <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="1">
-        <v>2</v>
-      </c>
-      <c r="C3" s="1">
+      <c r="B3" s="2">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2">
         <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="1">
-        <v>3</v>
-      </c>
-      <c r="C4" s="1">
+      <c r="B4" s="2">
+        <v>3</v>
+      </c>
+      <c r="C4" s="2">
         <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="1">
-        <v>5</v>
-      </c>
-      <c r="C5" s="1">
+      <c r="B5" s="2">
+        <v>5</v>
+      </c>
+      <c r="C5" s="2">
         <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="1">
-        <v>5</v>
-      </c>
-      <c r="C6" s="1">
+      <c r="B6" s="2">
+        <v>5</v>
+      </c>
+      <c r="C6" s="2">
         <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="1">
+      <c r="B9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="2">
         <f>AVERAGE(C2:C6)</f>
         <v>15.4</v>
       </c>
-      <c r="D9" s="2"/>
+      <c r="D9" s="4"/>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="2">
-        <v>2</v>
-      </c>
-      <c r="C12" s="2">
+      <c r="B12" s="4">
+        <v>2</v>
+      </c>
+      <c r="C12" s="4">
         <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="2">
-        <v>3</v>
-      </c>
-      <c r="C13" s="2">
+      <c r="B13" s="4">
+        <v>3</v>
+      </c>
+      <c r="C13" s="4">
         <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="4">
         <v>4</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="4">
         <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="4">
         <v>4</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="4">
         <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="4">
         <v>6</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="4">
         <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="4">
         <v>6</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="4">
         <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C20" s="4">
         <f>AVERAGE(C12:C17)</f>
         <v>14.6666666666667</v>
       </c>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B23" s="4">
+      <c r="B23" s="6">
         <v>1</v>
       </c>
-      <c r="C23" s="4">
+      <c r="C23" s="6">
         <v>13</v>
       </c>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="B24" s="4">
-        <v>2</v>
-      </c>
-      <c r="C24" s="4">
+      <c r="B24" s="6">
+        <v>2</v>
+      </c>
+      <c r="C24" s="6">
         <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B25" s="4">
-        <v>2</v>
-      </c>
-      <c r="C25" s="4">
+      <c r="B25" s="6">
+        <v>2</v>
+      </c>
+      <c r="C25" s="6">
         <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B26" s="4">
-        <v>2</v>
-      </c>
-      <c r="C26" s="4">
+      <c r="B26" s="6">
+        <v>2</v>
+      </c>
+      <c r="C26" s="6">
         <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="B27" s="4">
-        <v>5</v>
-      </c>
-      <c r="C27" s="4">
+      <c r="B27" s="6">
+        <v>5</v>
+      </c>
+      <c r="C27" s="6">
         <v>13</v>
       </c>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
+      <c r="A28" s="6"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="6"/>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="4"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
+      <c r="A29" s="6"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="6"/>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B30" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C30" s="4">
+      <c r="B30" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" s="6">
         <f>AVERAGE(C23:C27)</f>
         <v>13</v>
       </c>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="5" t="s">
+      <c r="A33" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="C33" s="5">
+      <c r="C33" s="7">
         <f>AVERAGE(C2:C6,C12:C17,C23:C27)</f>
         <v>14.375</v>
       </c>
@@ -5882,244 +7065,244 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="2">
         <v>1</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" s="2">
         <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="1">
-        <v>5</v>
-      </c>
-      <c r="C3" s="1">
+      <c r="B3" s="2">
+        <v>5</v>
+      </c>
+      <c r="C3" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="1">
-        <v>5</v>
-      </c>
-      <c r="C4" s="1">
+      <c r="B4" s="2">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="1">
+      <c r="B7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="2">
         <f>AVERAGE(C2:C4)</f>
         <v>14.6666666666667</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="2">
+      <c r="A10" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="4">
         <v>1</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="4">
         <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="2">
-        <v>2</v>
-      </c>
-      <c r="C11" s="2">
+      <c r="B11" s="4">
+        <v>2</v>
+      </c>
+      <c r="C11" s="4">
         <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="2">
-        <v>2</v>
-      </c>
-      <c r="C12" s="2">
+      <c r="B12" s="4">
+        <v>2</v>
+      </c>
+      <c r="C12" s="4">
         <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="2">
-        <v>3</v>
-      </c>
-      <c r="C13" s="2">
+      <c r="B13" s="4">
+        <v>3</v>
+      </c>
+      <c r="C13" s="4">
         <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="2">
-        <v>3</v>
-      </c>
-      <c r="C14" s="2">
+      <c r="B14" s="4">
+        <v>3</v>
+      </c>
+      <c r="C14" s="4">
         <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="2">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2">
+      <c r="B15" s="4">
+        <v>3</v>
+      </c>
+      <c r="C15" s="4">
         <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="4">
         <v>4</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="4">
         <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="2">
-        <v>5</v>
-      </c>
-      <c r="C17" s="2">
+      <c r="B17" s="4">
+        <v>5</v>
+      </c>
+      <c r="C17" s="4">
         <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="2">
-        <v>5</v>
-      </c>
-      <c r="C18" s="2">
+      <c r="B18" s="4">
+        <v>5</v>
+      </c>
+      <c r="C18" s="4">
         <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19" s="4">
         <v>7</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19" s="4">
         <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
+      <c r="A20" s="4"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C22" s="4">
         <f>AVERAGE(C10:C19)</f>
         <v>13.4</v>
       </c>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="B25" s="4">
+      <c r="B25" s="6">
         <v>1</v>
       </c>
-      <c r="C25" s="4">
+      <c r="C25" s="6">
         <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="B26" s="4">
+      <c r="B26" s="6">
         <v>7</v>
       </c>
-      <c r="C26" s="4">
+      <c r="C26" s="6">
         <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="4"/>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
+      <c r="A27" s="6"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
+      <c r="A28" s="6"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="6"/>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B29" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C29" s="4">
+      <c r="B29" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29" s="6">
         <f>AVERAGE(C25:C26)</f>
         <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="5" t="s">
+      <c r="A32" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="C32" s="5">
+      <c r="C32" s="7">
         <f>AVERAGE(C2:C4,C10:C19,C25:C26)</f>
         <v>13.4666666666667</v>
       </c>
@@ -6153,288 +7336,288 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="2">
         <v>1</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" s="2">
         <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="2">
         <v>1</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" s="2">
         <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="2">
         <v>1</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" s="2">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B5" s="1">
-        <v>2</v>
-      </c>
-      <c r="C5" s="1">
+      <c r="B5" s="2">
+        <v>2</v>
+      </c>
+      <c r="C5" s="2">
         <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B6" s="1">
-        <v>2</v>
-      </c>
-      <c r="C6" s="1">
+      <c r="B6" s="2">
+        <v>2</v>
+      </c>
+      <c r="C6" s="2">
         <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B7" s="1">
-        <v>2</v>
-      </c>
-      <c r="C7" s="1">
+      <c r="B7" s="2">
+        <v>2</v>
+      </c>
+      <c r="C7" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B8" s="1">
-        <v>3</v>
-      </c>
-      <c r="C8" s="1">
+      <c r="B8" s="2">
+        <v>3</v>
+      </c>
+      <c r="C8" s="2">
         <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B9" s="1">
-        <v>3</v>
-      </c>
-      <c r="C9" s="1">
+      <c r="B9" s="2">
+        <v>3</v>
+      </c>
+      <c r="C9" s="2">
         <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B10" s="1">
-        <v>3</v>
-      </c>
-      <c r="C10" s="1">
+      <c r="B10" s="2">
+        <v>3</v>
+      </c>
+      <c r="C10" s="2">
         <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B11" s="1">
-        <v>3</v>
-      </c>
-      <c r="C11" s="1">
+      <c r="B11" s="2">
+        <v>3</v>
+      </c>
+      <c r="C11" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B12" s="1">
-        <v>3</v>
-      </c>
-      <c r="C12" s="1">
+      <c r="B12" s="2">
+        <v>3</v>
+      </c>
+      <c r="C12" s="2">
         <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B13" s="1">
-        <v>3</v>
-      </c>
-      <c r="C13" s="1">
+      <c r="B13" s="2">
+        <v>3</v>
+      </c>
+      <c r="C13" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B14" s="2">
         <v>4</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C14" s="2">
         <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" s="1">
+      <c r="B17" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="2">
         <f>AVERAGE(C2:C14)</f>
         <v>14.2307692307692</v>
       </c>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B20" s="2">
-        <v>3</v>
-      </c>
-      <c r="C20" s="2">
+      <c r="B20" s="4">
+        <v>3</v>
+      </c>
+      <c r="C20" s="4">
         <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B21" s="2">
-        <v>3</v>
-      </c>
-      <c r="C21" s="2">
+      <c r="B21" s="4">
+        <v>3</v>
+      </c>
+      <c r="C21" s="4">
         <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B22" s="2">
+      <c r="B22" s="4">
         <v>4</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C22" s="4">
         <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B23" s="2">
-        <v>5</v>
-      </c>
-      <c r="C23" s="2">
+      <c r="B23" s="4">
+        <v>5</v>
+      </c>
+      <c r="C23" s="4">
         <v>13</v>
       </c>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
+      <c r="A24" s="4"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
+      <c r="A25" s="4"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C26" s="2">
+      <c r="C26" s="4">
         <f>AVERAGE(C20:C23)</f>
         <v>14</v>
       </c>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B29" s="4">
+      <c r="B29" s="6">
         <v>4</v>
       </c>
-      <c r="C29" s="4">
+      <c r="C29" s="6">
         <v>12</v>
       </c>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="B30" s="4">
+      <c r="B30" s="6">
         <v>4</v>
       </c>
-      <c r="C30" s="4">
+      <c r="C30" s="6">
         <v>12</v>
       </c>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="4"/>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
+      <c r="A31" s="6"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="4"/>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
+      <c r="A32" s="6"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="4" t="s">
+      <c r="A33" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C33" s="4">
+      <c r="C33" s="6">
         <f>AVERAGE(C29:C30)</f>
         <v>12</v>
       </c>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36" s="5" t="s">
+      <c r="A36" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B36" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="C36" s="5">
+      <c r="C36" s="7">
         <f>AVERAGE(C2:C14,C20:C23,C29:C30)</f>
         <v>13.9473684210526</v>
       </c>
@@ -6468,266 +7651,266 @@
       </c>
     </row>
     <row r="2" spans="4:6">
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="2">
         <v>1</v>
       </c>
-      <c r="F2" s="1">
+      <c r="F2" s="2">
         <v>16</v>
       </c>
     </row>
     <row r="3" spans="4:6">
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="2">
         <v>1</v>
       </c>
-      <c r="F3" s="1">
+      <c r="F3" s="2">
         <v>14</v>
       </c>
     </row>
     <row r="4" spans="4:6">
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E4" s="1">
-        <v>2</v>
-      </c>
-      <c r="F4" s="1">
+      <c r="E4" s="2">
+        <v>2</v>
+      </c>
+      <c r="F4" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="5" spans="4:6">
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E5" s="1">
-        <v>2</v>
-      </c>
-      <c r="F5" s="1">
+      <c r="E5" s="2">
+        <v>2</v>
+      </c>
+      <c r="F5" s="2">
         <v>12</v>
       </c>
     </row>
     <row r="6" spans="4:6">
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E6" s="1">
-        <v>2</v>
-      </c>
-      <c r="F6" s="1">
+      <c r="E6" s="2">
+        <v>2</v>
+      </c>
+      <c r="F6" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="7" spans="4:6">
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E7" s="1">
-        <v>3</v>
-      </c>
-      <c r="F7" s="1">
+      <c r="E7" s="2">
+        <v>3</v>
+      </c>
+      <c r="F7" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="8" spans="4:6">
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="2">
         <v>4</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="9" spans="4:6">
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
     </row>
     <row r="10" spans="4:6">
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
     </row>
     <row r="11" spans="4:6">
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="1">
+      <c r="E11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="2">
         <f>AVERAGE(F2:F8)</f>
         <v>13.4285714285714</v>
       </c>
     </row>
     <row r="14" spans="4:6">
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="E14" s="2">
-        <v>2</v>
-      </c>
-      <c r="F14" s="2">
+      <c r="E14" s="4">
+        <v>2</v>
+      </c>
+      <c r="F14" s="4">
         <v>13</v>
       </c>
     </row>
     <row r="15" spans="4:6">
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E15" s="2">
-        <v>2</v>
-      </c>
-      <c r="F15" s="2">
+      <c r="E15" s="4">
+        <v>2</v>
+      </c>
+      <c r="F15" s="4">
         <v>12</v>
       </c>
     </row>
     <row r="16" spans="4:6">
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E16" s="2">
-        <v>3</v>
-      </c>
-      <c r="F16" s="2">
+      <c r="E16" s="4">
+        <v>3</v>
+      </c>
+      <c r="F16" s="4">
         <v>12</v>
       </c>
     </row>
     <row r="17" spans="4:6">
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="E17" s="2">
-        <v>3</v>
-      </c>
-      <c r="F17" s="2">
+      <c r="E17" s="4">
+        <v>3</v>
+      </c>
+      <c r="F17" s="4">
         <v>12</v>
       </c>
     </row>
     <row r="18" spans="4:6">
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="E18" s="2">
+      <c r="E18" s="4">
         <v>4</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18" s="4">
         <v>12</v>
       </c>
     </row>
     <row r="19" spans="4:6">
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="E19" s="2">
-        <v>5</v>
-      </c>
-      <c r="F19" s="2">
+      <c r="E19" s="4">
+        <v>5</v>
+      </c>
+      <c r="F19" s="4">
         <v>13</v>
       </c>
     </row>
     <row r="20" spans="4:6">
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="E20" s="2">
-        <v>5</v>
-      </c>
-      <c r="F20" s="2">
+      <c r="E20" s="4">
+        <v>5</v>
+      </c>
+      <c r="F20" s="4">
         <v>12</v>
       </c>
     </row>
     <row r="21" spans="4:6">
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="E21" s="2">
+      <c r="E21" s="4">
         <v>6</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F21" s="4">
         <v>12</v>
       </c>
     </row>
     <row r="22" spans="4:6">
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
     </row>
     <row r="23" spans="4:6">
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
     </row>
     <row r="24" spans="4:6">
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E24" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F24" s="2">
+      <c r="F24" s="4">
         <f>AVERAGE(F14:F21)</f>
         <v>12.25</v>
       </c>
     </row>
     <row r="27" spans="4:6">
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="E27" s="4">
-        <v>2</v>
-      </c>
-      <c r="F27" s="4">
+      <c r="E27" s="6">
+        <v>2</v>
+      </c>
+      <c r="F27" s="6">
         <v>5</v>
       </c>
     </row>
     <row r="28" spans="4:6">
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="E28" s="4">
-        <v>2</v>
-      </c>
-      <c r="F28" s="4">
+      <c r="E28" s="6">
+        <v>2</v>
+      </c>
+      <c r="F28" s="6">
         <v>11</v>
       </c>
     </row>
     <row r="29" spans="4:6">
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
     </row>
     <row r="30" spans="4:6">
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
     </row>
     <row r="31" spans="4:6">
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E31" s="4" t="s">
+      <c r="E31" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="F31" s="4">
+      <c r="F31" s="6">
         <f>AVERAGE(F27,F28)</f>
         <v>8</v>
       </c>
     </row>
     <row r="34" spans="4:6">
-      <c r="D34" s="5" t="s">
+      <c r="D34" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="E34" s="5" t="s">
+      <c r="E34" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="F34" s="5">
+      <c r="F34" s="7">
         <f>AVERAGE(F2,F3,F4,F5,F6,F8,F14:F21,F27:F28)</f>
         <v>12.1875</v>
       </c>

--- a/src/utils/sxsyzlzq/zzz_cardList.xlsx
+++ b/src/utils/sxsyzlzq/zzz_cardList.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28245" windowHeight="12075" activeTab="12"/>
+    <workbookView windowWidth="28245" windowHeight="12345" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="伊萝莲" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="130">
   <si>
     <t>名称</t>
   </si>
@@ -58,6 +58,9 @@
     <t>塔楼弓手</t>
   </si>
   <si>
+    <t>增援战线</t>
+  </si>
+  <si>
     <t>光明惩戒</t>
   </si>
   <si>
@@ -91,162 +94,165 @@
     <t>幻域秘树</t>
   </si>
   <si>
+    <t>召集护卫</t>
+  </si>
+  <si>
+    <t>观星台大预言家</t>
+  </si>
+  <si>
+    <t>惩戒天使</t>
+  </si>
+  <si>
+    <t>禁卫指挥官</t>
+  </si>
+  <si>
+    <t>米拉方舟</t>
+  </si>
+  <si>
+    <t>紫色卡等：</t>
+  </si>
+  <si>
+    <t>花光春影·安娜贝尔</t>
+  </si>
+  <si>
+    <t>橙色</t>
+  </si>
+  <si>
+    <t>百花长枪·卡罗琳</t>
+  </si>
+  <si>
+    <t>流星7号</t>
+  </si>
+  <si>
+    <t>明日香·露娜</t>
+  </si>
+  <si>
+    <t>月之神·米拉</t>
+  </si>
+  <si>
+    <t>白袍·伊恩</t>
+  </si>
+  <si>
+    <t>火蛇巫女·沃凡瑞拉</t>
+  </si>
+  <si>
+    <t>武圣·云长</t>
+  </si>
+  <si>
+    <t>橙色卡等：</t>
+  </si>
+  <si>
+    <t>总计：</t>
+  </si>
+  <si>
+    <t>学仆-观测型</t>
+  </si>
+  <si>
+    <t>冥河守卫</t>
+  </si>
+  <si>
+    <t>卜命道长</t>
+  </si>
+  <si>
+    <t>箭竹守卫</t>
+  </si>
+  <si>
+    <t>落雷击</t>
+  </si>
+  <si>
+    <t>白羊药师</t>
+  </si>
+  <si>
+    <t>树木之怒</t>
+  </si>
+  <si>
+    <t>苦行武僧</t>
+  </si>
+  <si>
+    <t>残暴爪钩</t>
+  </si>
+  <si>
+    <t>邪眼魔</t>
+  </si>
+  <si>
+    <t>执剑道者</t>
+  </si>
+  <si>
+    <t>连击</t>
+  </si>
+  <si>
+    <t>深山采药人</t>
+  </si>
+  <si>
+    <t>疾风猎手</t>
+  </si>
+  <si>
+    <t>风铃道人</t>
+  </si>
+  <si>
+    <t>烈焰风暴</t>
+  </si>
+  <si>
+    <t>碎颅魔</t>
+  </si>
+  <si>
+    <t>觅食大嘴兽</t>
+  </si>
+  <si>
+    <t>扫叶僧</t>
+  </si>
+  <si>
+    <t>逍遥琴师</t>
+  </si>
+  <si>
+    <t>绝望镰魔</t>
+  </si>
+  <si>
+    <t>岩浆球</t>
+  </si>
+  <si>
+    <t>御风武者</t>
+  </si>
+  <si>
+    <t>灼神双炎</t>
+  </si>
+  <si>
+    <t>雷光炼狱</t>
+  </si>
+  <si>
+    <t>地狱屠夫</t>
+  </si>
+  <si>
+    <t>恶灵魔焰</t>
+  </si>
+  <si>
+    <t>痛苦之心</t>
+  </si>
+  <si>
+    <t>神机玄女·轩</t>
+  </si>
+  <si>
+    <t>怨魂饕餮兽</t>
+  </si>
+  <si>
+    <t>猩红勇士</t>
+  </si>
+  <si>
+    <t>铁山靠</t>
+  </si>
+  <si>
+    <t>万物之灵</t>
+  </si>
+  <si>
+    <t>上宝沁金耙</t>
+  </si>
+  <si>
+    <t>火蛇巫女</t>
+  </si>
+  <si>
     <t>夺取阵地</t>
   </si>
   <si>
-    <t>召集护卫</t>
-  </si>
-  <si>
-    <t>观星台大预言家</t>
-  </si>
-  <si>
-    <t>惩戒天使</t>
-  </si>
-  <si>
-    <t>禁卫指挥官</t>
-  </si>
-  <si>
-    <t>米拉方舟</t>
-  </si>
-  <si>
-    <t>紫色卡等：</t>
-  </si>
-  <si>
-    <t>花光春影·安娜贝尔</t>
-  </si>
-  <si>
-    <t>橙色</t>
-  </si>
-  <si>
-    <t>百花长枪·卡罗琳</t>
-  </si>
-  <si>
-    <t>明日香·露娜</t>
-  </si>
-  <si>
-    <t>月之神·米拉</t>
-  </si>
-  <si>
-    <t>白袍·伊恩</t>
-  </si>
-  <si>
-    <t>火蛇巫女·沃凡瑞拉</t>
-  </si>
-  <si>
-    <t>武圣·云长</t>
-  </si>
-  <si>
-    <t>橙色卡等：</t>
-  </si>
-  <si>
-    <t>总计：</t>
-  </si>
-  <si>
-    <t>学仆-观测型</t>
-  </si>
-  <si>
-    <t>冥河守卫</t>
-  </si>
-  <si>
-    <t>卜命道长</t>
-  </si>
-  <si>
-    <t>箭竹守卫</t>
-  </si>
-  <si>
-    <t>落雷击</t>
-  </si>
-  <si>
-    <t>白羊药师</t>
-  </si>
-  <si>
-    <t>树木之怒</t>
-  </si>
-  <si>
-    <t>苦行武僧</t>
-  </si>
-  <si>
-    <t>残暴爪钩</t>
-  </si>
-  <si>
-    <t>邪眼魔</t>
-  </si>
-  <si>
-    <t>执剑道者</t>
-  </si>
-  <si>
-    <t>连击</t>
-  </si>
-  <si>
-    <t>深山采药人</t>
-  </si>
-  <si>
-    <t>疾风猎手</t>
-  </si>
-  <si>
-    <t>风铃道人</t>
-  </si>
-  <si>
-    <t>烈焰风暴</t>
-  </si>
-  <si>
-    <t>碎颅魔</t>
-  </si>
-  <si>
-    <t>觅食大嘴兽</t>
-  </si>
-  <si>
-    <t>扫叶僧</t>
-  </si>
-  <si>
-    <t>逍遥琴师</t>
-  </si>
-  <si>
-    <t>绝望镰魔</t>
-  </si>
-  <si>
-    <t>岩浆球</t>
-  </si>
-  <si>
-    <t>御风武者</t>
-  </si>
-  <si>
-    <t>灼神双炎</t>
-  </si>
-  <si>
-    <t>雷光炼狱</t>
-  </si>
-  <si>
-    <t>地狱屠夫</t>
-  </si>
-  <si>
-    <t>恶灵魔焰</t>
-  </si>
-  <si>
-    <t>痛苦之心</t>
-  </si>
-  <si>
-    <t>神机玄女·轩</t>
-  </si>
-  <si>
-    <t>怨魂饕餮兽</t>
-  </si>
-  <si>
-    <t>猩红勇士</t>
-  </si>
-  <si>
-    <t>铁山靠</t>
-  </si>
-  <si>
-    <t>万物之灵</t>
-  </si>
-  <si>
-    <t>上宝沁金耙</t>
-  </si>
-  <si>
-    <t>火蛇巫女</t>
-  </si>
-  <si>
     <t>曙光·安娜贝尔</t>
   </si>
   <si>
@@ -350,9 +356,6 @@
   </si>
   <si>
     <t>No.5咒刃·布雷克</t>
-  </si>
-  <si>
-    <t>增援战线</t>
   </si>
   <si>
     <t>魔像-御咒铁卫</t>
@@ -420,10 +423,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -475,8 +478,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -491,9 +495,17 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -505,7 +517,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -519,70 +531,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -605,15 +554,69 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -628,13 +631,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -646,151 +727,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -808,7 +751,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -819,30 +822,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -861,31 +840,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF7F7F7F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -905,6 +870,26 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -919,6 +904,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -927,10 +930,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -939,133 +942,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1484,21 +1487,21 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" s="2">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>5</v>
@@ -1507,12 +1510,12 @@
         <v>3</v>
       </c>
       <c r="D7" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>5</v>
@@ -1526,7 +1529,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>5</v>
@@ -1552,23 +1555,23 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2">
         <f>AVERAGE(D2:D9)</f>
-        <v>15.125</v>
+        <v>15.375</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C15" s="4">
         <v>1</v>
@@ -1579,10 +1582,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C16" s="4">
         <v>2</v>
@@ -1593,10 +1596,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C17" s="4">
         <v>2</v>
@@ -1607,10 +1610,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C18" s="4">
         <v>2</v>
@@ -1621,10 +1624,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C19" s="4">
         <v>3</v>
@@ -1635,10 +1638,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C20" s="4">
         <v>3</v>
@@ -1649,10 +1652,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C21" s="4">
         <v>3</v>
@@ -1663,24 +1666,24 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B22" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="4">
+        <v>3</v>
+      </c>
+      <c r="D22" s="4">
         <v>14</v>
-      </c>
-      <c r="C22" s="4">
-        <v>3</v>
-      </c>
-      <c r="D22" s="4">
-        <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C23" s="4">
         <v>4</v>
@@ -1691,10 +1694,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C24" s="4">
         <v>4</v>
@@ -1705,74 +1708,66 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C25" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D25" s="4">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B26" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="4">
+        <v>6</v>
+      </c>
+      <c r="D26" s="4">
         <v>14</v>
-      </c>
-      <c r="C26" s="4">
-        <v>5</v>
-      </c>
-      <c r="D26" s="4">
-        <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C27" s="4">
         <v>6</v>
       </c>
       <c r="D27" s="4">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
       <c r="A28" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C28" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D28" s="4">
         <v>15</v>
       </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C29" s="4">
-        <v>7</v>
-      </c>
-      <c r="D29" s="4">
-        <v>14</v>
-      </c>
-      <c r="F29" s="5"/>
+      <c r="F28" s="5"/>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="4"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="4"/>
@@ -1781,41 +1776,49 @@
       <c r="D30" s="4"/>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="4"/>
-      <c r="B31" s="4"/>
+      <c r="A31" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>27</v>
+      </c>
       <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4">
-        <f>AVERAGE(D15:D29)</f>
-        <v>14.0666666666667</v>
+      <c r="D31" s="4">
+        <f>AVERAGE(D15:D28)</f>
+        <v>14.2857142857143</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C34" s="6">
+        <v>3</v>
+      </c>
+      <c r="D34" s="6">
+        <v>13</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C35" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D35" s="6">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>29</v>
@@ -1829,7 +1832,7 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>29</v>
@@ -1843,7 +1846,7 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>29</v>
@@ -1857,7 +1860,7 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>29</v>
@@ -1866,12 +1869,12 @@
         <v>6</v>
       </c>
       <c r="D39" s="6">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>29</v>
@@ -1885,7 +1888,7 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>29</v>
@@ -1911,26 +1914,26 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="6">
-        <f>AVERAGE(D35:D41)</f>
-        <v>12.7142857142857</v>
+        <f>AVERAGE(D34:D41)</f>
+        <v>13</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B47" s="7"/>
       <c r="C47" s="7"/>
       <c r="D47" s="7">
-        <f>AVERAGE(D2:D9,D15:D29,D35:D41)</f>
-        <v>14.0333333333333</v>
+        <f>AVERAGE(D2:D9,D15:D28,D34:D41)</f>
+        <v>14.2333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -1980,7 +1983,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
@@ -1994,7 +1997,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
@@ -2008,7 +2011,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -2022,7 +2025,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>5</v>
@@ -2036,7 +2039,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>5</v>
@@ -2064,7 +2067,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>5</v>
@@ -2078,7 +2081,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>5</v>
@@ -2092,7 +2095,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>5</v>
@@ -2106,7 +2109,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>5</v>
@@ -2120,7 +2123,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>5</v>
@@ -2134,7 +2137,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>5</v>
@@ -2160,10 +2163,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2">
@@ -2173,10 +2176,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C20" s="4">
         <v>2</v>
@@ -2187,10 +2190,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C21" s="4">
         <v>3</v>
@@ -2201,10 +2204,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C22" s="4">
         <v>3</v>
@@ -2215,10 +2218,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C23" s="4">
         <v>3</v>
@@ -2229,10 +2232,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C24" s="4">
         <v>3</v>
@@ -2243,10 +2246,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C25" s="4">
         <v>4</v>
@@ -2260,7 +2263,7 @@
         <v>22</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C26" s="4">
         <v>4</v>
@@ -2271,10 +2274,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C27" s="4">
         <v>5</v>
@@ -2285,10 +2288,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C28" s="4">
         <v>5</v>
@@ -2302,7 +2305,7 @@
         <v>25</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C29" s="4">
         <v>6</v>
@@ -2325,7 +2328,7 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>27</v>
@@ -2366,7 +2369,7 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>29</v>
@@ -2380,7 +2383,7 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>29</v>
@@ -2394,7 +2397,7 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>29</v>
@@ -2408,7 +2411,7 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>29</v>
@@ -2422,7 +2425,7 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>29</v>
@@ -2448,10 +2451,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="6">
@@ -2461,7 +2464,7 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D47">
         <f>AVERAGE(D2:D14,D20:D29,D35:D41)</f>
@@ -2514,7 +2517,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
@@ -2528,7 +2531,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
@@ -2542,7 +2545,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -2556,7 +2559,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>5</v>
@@ -2584,7 +2587,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>5</v>
@@ -2598,7 +2601,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>5</v>
@@ -2612,7 +2615,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>5</v>
@@ -2626,7 +2629,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>5</v>
@@ -2640,7 +2643,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>5</v>
@@ -2654,7 +2657,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>5</v>
@@ -2668,7 +2671,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>5</v>
@@ -2682,7 +2685,7 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>5</v>
@@ -2696,7 +2699,7 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>5</v>
@@ -2722,10 +2725,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2">
@@ -2735,10 +2738,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C22" s="4">
         <v>2</v>
@@ -2749,10 +2752,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C23" s="4">
         <v>3</v>
@@ -2763,10 +2766,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C24" s="4">
         <v>3</v>
@@ -2777,10 +2780,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C25" s="4">
         <v>3</v>
@@ -2791,10 +2794,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C26" s="4">
         <v>4</v>
@@ -2805,10 +2808,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C27" s="4">
         <v>4</v>
@@ -2819,10 +2822,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C28" s="4">
         <v>5</v>
@@ -2836,7 +2839,7 @@
         <v>25</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C29" s="4">
         <v>6</v>
@@ -2859,7 +2862,7 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>27</v>
@@ -2900,7 +2903,7 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>29</v>
@@ -2914,7 +2917,7 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>29</v>
@@ -2928,7 +2931,7 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>29</v>
@@ -2942,7 +2945,7 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>29</v>
@@ -2956,7 +2959,7 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>29</v>
@@ -2982,10 +2985,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="6">
@@ -2995,7 +2998,7 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D47">
         <f>AVERAGE(D2:D16,D22:D29,D35:D41)</f>
@@ -3035,7 +3038,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>5</v>
@@ -3049,7 +3052,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
@@ -3063,7 +3066,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
@@ -3077,7 +3080,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -3091,7 +3094,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>5</v>
@@ -3105,7 +3108,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>5</v>
@@ -3119,7 +3122,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>5</v>
@@ -3133,7 +3136,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>5</v>
@@ -3147,7 +3150,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>5</v>
@@ -3161,7 +3164,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>5</v>
@@ -3175,7 +3178,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>5</v>
@@ -3189,7 +3192,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>5</v>
@@ -3203,7 +3206,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>5</v>
@@ -3217,7 +3220,7 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>5</v>
@@ -3231,7 +3234,7 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>5</v>
@@ -3245,7 +3248,7 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>5</v>
@@ -3271,10 +3274,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2">
@@ -3284,10 +3287,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C23" s="4">
         <v>2</v>
@@ -3298,10 +3301,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C24" s="4">
         <v>2</v>
@@ -3312,10 +3315,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C25" s="4">
         <v>3</v>
@@ -3326,10 +3329,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C26" s="4">
         <v>3</v>
@@ -3340,10 +3343,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C27" s="4">
         <v>3</v>
@@ -3354,10 +3357,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C28" s="4">
         <v>3</v>
@@ -3368,10 +3371,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C29" s="4">
         <v>4</v>
@@ -3382,10 +3385,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C30" s="4">
         <v>4</v>
@@ -3396,10 +3399,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C31" s="4">
         <v>5</v>
@@ -3410,10 +3413,10 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C32" s="4">
         <v>5</v>
@@ -3424,10 +3427,10 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C33" s="4">
         <v>6</v>
@@ -3451,7 +3454,7 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>27</v>
@@ -3464,7 +3467,7 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>29</v>
@@ -3478,7 +3481,7 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>29</v>
@@ -3492,7 +3495,7 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>29</v>
@@ -3518,10 +3521,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="6">
@@ -3531,7 +3534,7 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B47" s="7"/>
       <c r="C47" s="7"/>
@@ -3561,7 +3564,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -3570,15 +3573,15 @@
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -3592,10 +3595,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>5</v>
@@ -3609,10 +3612,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>5</v>
@@ -3629,7 +3632,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>5</v>
@@ -3643,13 +3646,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D6" s="4">
         <v>1</v>
@@ -3660,13 +3663,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D7" s="4">
         <v>1</v>
@@ -3677,13 +3680,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>100</v>
-      </c>
       <c r="C8" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D8" s="4">
         <v>1</v>
@@ -3694,10 +3697,10 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>5</v>
@@ -3711,10 +3714,10 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>5</v>
@@ -3731,7 +3734,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>5</v>
@@ -3745,10 +3748,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>5</v>
@@ -3765,7 +3768,7 @@
         <v>8</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>5</v>
@@ -3779,13 +3782,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D14" s="4">
         <v>2</v>
@@ -3796,13 +3799,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D15" s="4">
         <v>2</v>
@@ -3813,13 +3816,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D16" s="4">
         <v>2</v>
@@ -3830,13 +3833,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D17" s="4">
         <v>2</v>
@@ -3847,13 +3850,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D18" s="4">
         <v>2</v>
@@ -3864,10 +3867,10 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>29</v>
@@ -3881,10 +3884,10 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>29</v>
@@ -3898,10 +3901,10 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>29</v>
@@ -3915,10 +3918,10 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>5</v>
@@ -3935,7 +3938,7 @@
         <v>9</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>5</v>
@@ -3949,10 +3952,10 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2" t="s">
-        <v>108</v>
+        <v>10</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>5</v>
@@ -3966,13 +3969,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D25" s="4">
         <v>3</v>
@@ -3983,13 +3986,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D26" s="4">
         <v>3</v>
@@ -4000,13 +4003,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D27" s="4">
         <v>3</v>
@@ -4017,13 +4020,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D28" s="4">
         <v>3</v>
@@ -4034,13 +4037,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D29" s="4">
         <v>3</v>
@@ -4051,13 +4054,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D30" s="4">
         <v>3</v>
@@ -4068,13 +4071,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D31" s="4">
         <v>3</v>
@@ -4085,10 +4088,10 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>29</v>
@@ -4102,10 +4105,10 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>29</v>
@@ -4119,10 +4122,10 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>29</v>
@@ -4136,10 +4139,10 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>5</v>
@@ -4153,13 +4156,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D36" s="4">
         <v>4</v>
@@ -4170,13 +4173,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="4" t="s">
-        <v>21</v>
+        <v>74</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D37" s="4">
         <v>4</v>
@@ -4187,13 +4190,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D38" s="4">
         <v>4</v>
@@ -4204,13 +4207,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D39" s="4">
         <v>4</v>
@@ -4221,13 +4224,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D40" s="4">
         <v>4</v>
@@ -4238,13 +4241,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D41" s="4">
         <v>4</v>
@@ -4258,10 +4261,10 @@
         <v>22</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D42" s="4">
         <v>4</v>
@@ -4272,10 +4275,10 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>29</v>
@@ -4289,10 +4292,10 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>29</v>
@@ -4306,10 +4309,10 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>5</v>
@@ -4323,13 +4326,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D46" s="4">
         <v>5</v>
@@ -4343,10 +4346,10 @@
         <v>23</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D47" s="4">
         <v>5</v>
@@ -4357,13 +4360,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D48" s="4">
         <v>5</v>
@@ -4374,10 +4377,10 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>29</v>
@@ -4391,13 +4394,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D50" s="4">
         <v>6</v>
@@ -4411,10 +4414,10 @@
         <v>25</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D51" s="4">
         <v>6</v>
@@ -4425,10 +4428,10 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>29</v>
@@ -4442,10 +4445,10 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>29</v>
@@ -4459,13 +4462,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D54" s="4">
         <v>7</v>
@@ -4476,13 +4479,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D55" s="4">
         <v>7</v>
@@ -4493,13 +4496,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D56" s="4">
         <v>7</v>
@@ -4510,13 +4513,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D57" s="4">
         <v>7</v>
@@ -4530,10 +4533,10 @@
         <v>26</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D58" s="4">
         <v>7</v>
@@ -4579,7 +4582,7 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -4595,11 +4598,11 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B66" s="2"/>
       <c r="C66" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" s="2">
@@ -4656,7 +4659,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
@@ -4732,15 +4735,15 @@
         <v>5</v>
       </c>
       <c r="C8" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D8" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>5</v>
@@ -4753,10 +4756,18 @@
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
+      <c r="A10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="2">
+        <v>5</v>
+      </c>
+      <c r="D10" s="2">
+        <v>14</v>
+      </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2"/>
@@ -4765,44 +4776,36 @@
       <c r="D11" s="2"/>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
       <c r="C12" s="2"/>
-      <c r="D12" s="2">
-        <f>AVERAGE(D2:D9)</f>
-        <v>15.125</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" s="4">
-        <v>1</v>
-      </c>
-      <c r="D15" s="4">
-        <v>12</v>
+      <c r="D12" s="2"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2">
+        <f>AVERAGE(D2:D10)</f>
+        <v>15.1111111111111</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C16" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" s="4">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -4810,13 +4813,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C17" s="4">
         <v>2</v>
       </c>
       <c r="D17" s="4">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -4824,13 +4827,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C18" s="4">
         <v>2</v>
       </c>
       <c r="D18" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -4838,13 +4841,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="4">
+        <v>2</v>
+      </c>
+      <c r="D19" s="4">
         <v>14</v>
-      </c>
-      <c r="C19" s="4">
-        <v>3</v>
-      </c>
-      <c r="D19" s="4">
-        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -4852,21 +4855,21 @@
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C20" s="4">
         <v>3</v>
       </c>
       <c r="D20" s="4">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C21" s="4">
         <v>3</v>
@@ -4877,16 +4880,16 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B22" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="4">
+        <v>3</v>
+      </c>
+      <c r="D22" s="4">
         <v>14</v>
-      </c>
-      <c r="C22" s="4">
-        <v>3</v>
-      </c>
-      <c r="D22" s="4">
-        <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -4894,13 +4897,13 @@
         <v>20</v>
       </c>
       <c r="B23" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="4">
+        <v>3</v>
+      </c>
+      <c r="D23" s="4">
         <v>14</v>
-      </c>
-      <c r="C23" s="4">
-        <v>4</v>
-      </c>
-      <c r="D23" s="4">
-        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -4908,13 +4911,13 @@
         <v>21</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C24" s="4">
         <v>4</v>
       </c>
       <c r="D24" s="4">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -4922,7 +4925,7 @@
         <v>22</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C25" s="4">
         <v>4</v>
@@ -4936,7 +4939,7 @@
         <v>23</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C26" s="4">
         <v>5</v>
@@ -4947,59 +4950,51 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B27" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" s="4">
+        <v>6</v>
+      </c>
+      <c r="D27" s="4">
         <v>14</v>
-      </c>
-      <c r="C27" s="4">
-        <v>5</v>
-      </c>
-      <c r="D27" s="4">
-        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C28" s="4">
         <v>6</v>
       </c>
       <c r="D28" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C29" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D29" s="4">
         <v>15</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C30" s="4">
-        <v>7</v>
-      </c>
-      <c r="D30" s="4">
-        <v>14</v>
-      </c>
+      <c r="A30" s="4"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="4"/>
@@ -5008,41 +5003,49 @@
       <c r="D31" s="4"/>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="4"/>
-      <c r="B32" s="4"/>
+      <c r="A32" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>27</v>
+      </c>
       <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4">
-        <f>AVERAGE(D15:D30)</f>
-        <v>13.875</v>
+      <c r="D32" s="4">
+        <f>AVERAGE(D16:D29)</f>
+        <v>14.2857142857143</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C35" s="6">
+        <v>3</v>
+      </c>
+      <c r="D35" s="6">
+        <v>13</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C36" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D36" s="6">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>29</v>
@@ -5056,7 +5059,7 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>29</v>
@@ -5070,7 +5073,7 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>29</v>
@@ -5084,7 +5087,7 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>29</v>
@@ -5093,12 +5096,12 @@
         <v>6</v>
       </c>
       <c r="D40" s="6">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>29</v>
@@ -5124,24 +5127,24 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="6">
-        <f>AVERAGE(D36:D41)</f>
-        <v>12.6666666666667</v>
+        <f>AVERAGE(D35:D41)</f>
+        <v>13</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D47">
-        <f>AVERAGE(D2:D9,D15:D30,D36:D41)</f>
-        <v>13.9666666666667</v>
+        <f>AVERAGE(D2:D10,D16:D29,D35:D41)</f>
+        <v>14.2333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -5177,7 +5180,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>5</v>
@@ -5191,7 +5194,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
@@ -5205,7 +5208,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
@@ -5219,7 +5222,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -5233,7 +5236,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>5</v>
@@ -5247,7 +5250,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>5</v>
@@ -5261,7 +5264,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>5</v>
@@ -5275,7 +5278,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>5</v>
@@ -5289,7 +5292,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>5</v>
@@ -5303,7 +5306,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>5</v>
@@ -5317,7 +5320,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>5</v>
@@ -5331,7 +5334,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>5</v>
@@ -5345,7 +5348,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>5</v>
@@ -5359,7 +5362,7 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>5</v>
@@ -5373,7 +5376,7 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>5</v>
@@ -5387,7 +5390,7 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>5</v>
@@ -5413,10 +5416,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2">
@@ -5426,10 +5429,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C23" s="4">
         <v>2</v>
@@ -5440,10 +5443,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C24" s="4">
         <v>2</v>
@@ -5454,10 +5457,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C25" s="4">
         <v>3</v>
@@ -5468,10 +5471,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C26" s="4">
         <v>3</v>
@@ -5482,10 +5485,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C27" s="4">
         <v>3</v>
@@ -5496,10 +5499,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C28" s="4">
         <v>3</v>
@@ -5510,10 +5513,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C29" s="4">
         <v>4</v>
@@ -5524,10 +5527,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C30" s="4">
         <v>4</v>
@@ -5538,10 +5541,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C31" s="4">
         <v>5</v>
@@ -5552,10 +5555,10 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C32" s="4">
         <v>5</v>
@@ -5566,10 +5569,10 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C33" s="4">
         <v>6</v>
@@ -5593,7 +5596,7 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>27</v>
@@ -5606,7 +5609,7 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>29</v>
@@ -5620,7 +5623,7 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>29</v>
@@ -5634,7 +5637,7 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>29</v>
@@ -5660,10 +5663,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="6">
@@ -5673,7 +5676,7 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B47" s="7"/>
       <c r="C47" s="7"/>
@@ -5714,7 +5717,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>5</v>
@@ -5728,7 +5731,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
@@ -5742,7 +5745,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
@@ -5756,7 +5759,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -5770,7 +5773,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>5</v>
@@ -5784,7 +5787,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>5</v>
@@ -5826,7 +5829,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>5</v>
@@ -5840,7 +5843,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>5</v>
@@ -5866,10 +5869,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2">
@@ -5879,10 +5882,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C17" s="4">
         <v>1</v>
@@ -5893,10 +5896,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C18" s="4">
         <v>2</v>
@@ -5907,10 +5910,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C19" s="4">
         <v>2</v>
@@ -5921,10 +5924,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C20" s="4">
         <v>2</v>
@@ -5935,10 +5938,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C21" s="4">
         <v>3</v>
@@ -5949,10 +5952,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C22" s="4">
         <v>3</v>
@@ -5963,10 +5966,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C23" s="4">
         <v>3</v>
@@ -5977,10 +5980,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C24" s="4">
         <v>3</v>
@@ -5991,10 +5994,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C25" s="4">
         <v>3</v>
@@ -6005,10 +6008,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C26" s="4">
         <v>4</v>
@@ -6019,10 +6022,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C27" s="4">
         <v>4</v>
@@ -6033,10 +6036,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C28" s="4">
         <v>5</v>
@@ -6047,10 +6050,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C29" s="4">
         <v>5</v>
@@ -6064,7 +6067,7 @@
         <v>23</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C30" s="4">
         <v>5</v>
@@ -6075,10 +6078,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C31" s="4">
         <v>6</v>
@@ -6092,7 +6095,7 @@
         <v>26</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C32" s="4">
         <v>7</v>
@@ -6115,7 +6118,7 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>27</v>
@@ -6128,7 +6131,7 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>29</v>
@@ -6142,7 +6145,7 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>29</v>
@@ -6156,7 +6159,7 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>29</v>
@@ -6170,7 +6173,7 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>29</v>
@@ -6196,10 +6199,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="6">
@@ -6209,7 +6212,7 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D47">
         <f>AVERAGE(D2:D11,D17:D32,D38:D41)</f>
@@ -6248,7 +6251,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>5</v>
@@ -6262,7 +6265,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
@@ -6276,7 +6279,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
@@ -6290,7 +6293,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -6304,7 +6307,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>5</v>
@@ -6318,7 +6321,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>5</v>
@@ -6360,7 +6363,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>5</v>
@@ -6374,7 +6377,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>5</v>
@@ -6388,7 +6391,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>5</v>
@@ -6402,7 +6405,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>5</v>
@@ -6416,7 +6419,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>5</v>
@@ -6430,7 +6433,7 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>5</v>
@@ -6456,10 +6459,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2">
@@ -6469,10 +6472,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C21" s="4">
         <v>1</v>
@@ -6483,10 +6486,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C22" s="4">
         <v>2</v>
@@ -6497,10 +6500,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C23" s="4">
         <v>2</v>
@@ -6511,10 +6514,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C24" s="4">
         <v>3</v>
@@ -6525,10 +6528,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C25" s="4">
         <v>3</v>
@@ -6539,10 +6542,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C26" s="4">
         <v>3</v>
@@ -6553,10 +6556,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C27" s="4">
         <v>3</v>
@@ -6567,10 +6570,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C28" s="4">
         <v>3</v>
@@ -6581,10 +6584,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C29" s="4">
         <v>4</v>
@@ -6595,10 +6598,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C30" s="4">
         <v>4</v>
@@ -6609,10 +6612,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C31" s="4">
         <v>5</v>
@@ -6626,7 +6629,7 @@
         <v>23</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C32" s="4">
         <v>5</v>
@@ -6640,7 +6643,7 @@
         <v>26</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C33" s="4">
         <v>7</v>
@@ -6664,7 +6667,7 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>27</v>
@@ -6677,7 +6680,7 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>29</v>
@@ -6691,7 +6694,7 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>29</v>
@@ -6705,7 +6708,7 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>29</v>
@@ -6731,10 +6734,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="6">
@@ -6744,7 +6747,7 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B47" s="7"/>
       <c r="C47" s="7"/>
@@ -6816,7 +6819,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" s="2">
         <v>5</v>
@@ -6827,7 +6830,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6" s="2">
         <v>5</v>
@@ -6848,10 +6851,10 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" s="2">
         <f>AVERAGE(C2:C6)</f>
@@ -6861,7 +6864,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B12" s="4">
         <v>2</v>
@@ -6872,7 +6875,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B13" s="4">
         <v>3</v>
@@ -6883,7 +6886,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>21</v>
+        <v>74</v>
       </c>
       <c r="B14" s="4">
         <v>4</v>
@@ -6937,7 +6940,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>27</v>
@@ -6949,7 +6952,7 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B23" s="6">
         <v>1</v>
@@ -6960,7 +6963,7 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B24" s="6">
         <v>2</v>
@@ -6971,7 +6974,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B25" s="6">
         <v>2</v>
@@ -6982,7 +6985,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B26" s="6">
         <v>2</v>
@@ -6993,7 +6996,7 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B27" s="6">
         <v>5</v>
@@ -7014,10 +7017,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C30" s="6">
         <f>AVERAGE(C23:C27)</f>
@@ -7026,10 +7029,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C33" s="7">
         <f>AVERAGE(C2:C6,C12:C17,C23:C27)</f>
@@ -7066,7 +7069,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B2" s="2">
         <v>1</v>
@@ -7109,10 +7112,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" s="2">
         <f>AVERAGE(C2:C4)</f>
@@ -7121,7 +7124,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B10" s="4">
         <v>1</v>
@@ -7132,7 +7135,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B11" s="4">
         <v>2</v>
@@ -7143,7 +7146,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B12" s="4">
         <v>2</v>
@@ -7154,7 +7157,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13" s="4">
         <v>3</v>
@@ -7165,7 +7168,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B14" s="4">
         <v>3</v>
@@ -7176,7 +7179,7 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B15" s="4">
         <v>3</v>
@@ -7187,7 +7190,7 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B16" s="4">
         <v>4</v>
@@ -7241,7 +7244,7 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>27</v>
@@ -7253,7 +7256,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B25" s="6">
         <v>1</v>
@@ -7264,7 +7267,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B26" s="6">
         <v>7</v>
@@ -7285,10 +7288,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C29" s="6">
         <f>AVERAGE(C25:C26)</f>
@@ -7297,10 +7300,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C32" s="7">
         <f>AVERAGE(C2:C4,C10:C19,C25:C26)</f>
@@ -7337,7 +7340,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B2" s="2">
         <v>1</v>
@@ -7348,7 +7351,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3" s="2">
         <v>1</v>
@@ -7359,7 +7362,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B4" s="2">
         <v>1</v>
@@ -7370,7 +7373,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B5" s="2">
         <v>2</v>
@@ -7381,7 +7384,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B6" s="2">
         <v>2</v>
@@ -7392,7 +7395,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B7" s="2">
         <v>2</v>
@@ -7403,7 +7406,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B8" s="2">
         <v>3</v>
@@ -7414,7 +7417,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B9" s="2">
         <v>3</v>
@@ -7425,7 +7428,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B10" s="2">
         <v>3</v>
@@ -7436,7 +7439,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B11" s="2">
         <v>3</v>
@@ -7447,7 +7450,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B12" s="2">
         <v>3</v>
@@ -7458,7 +7461,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B13" s="2">
         <v>3</v>
@@ -7469,7 +7472,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B14" s="2">
         <v>4</v>
@@ -7490,10 +7493,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C17" s="2">
         <f>AVERAGE(C2:C14)</f>
@@ -7502,7 +7505,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B20" s="4">
         <v>3</v>
@@ -7513,7 +7516,7 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B21" s="4">
         <v>3</v>
@@ -7524,7 +7527,7 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B22" s="4">
         <v>4</v>
@@ -7535,7 +7538,7 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B23" s="4">
         <v>5</v>
@@ -7556,7 +7559,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>27</v>
@@ -7568,7 +7571,7 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B29" s="6">
         <v>4</v>
@@ -7579,7 +7582,7 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B30" s="6">
         <v>4</v>
@@ -7600,10 +7603,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C33" s="6">
         <f>AVERAGE(C29:C30)</f>
@@ -7612,10 +7615,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C36" s="7">
         <f>AVERAGE(C2:C14,C20:C23,C29:C30)</f>
@@ -7652,7 +7655,7 @@
     </row>
     <row r="2" spans="4:6">
       <c r="D2" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E2" s="2">
         <v>1</v>
@@ -7663,7 +7666,7 @@
     </row>
     <row r="3" spans="4:6">
       <c r="D3" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E3" s="2">
         <v>1</v>
@@ -7674,7 +7677,7 @@
     </row>
     <row r="4" spans="4:6">
       <c r="D4" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E4" s="2">
         <v>2</v>
@@ -7685,7 +7688,7 @@
     </row>
     <row r="5" spans="4:6">
       <c r="D5" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E5" s="2">
         <v>2</v>
@@ -7696,7 +7699,7 @@
     </row>
     <row r="6" spans="4:6">
       <c r="D6" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E6" s="2">
         <v>2</v>
@@ -7707,7 +7710,7 @@
     </row>
     <row r="7" spans="4:6">
       <c r="D7" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E7" s="2">
         <v>3</v>
@@ -7718,7 +7721,7 @@
     </row>
     <row r="8" spans="4:6">
       <c r="D8" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E8" s="2">
         <v>4</v>
@@ -7739,10 +7742,10 @@
     </row>
     <row r="11" spans="4:6">
       <c r="D11" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F11" s="2">
         <f>AVERAGE(F2:F8)</f>
@@ -7751,7 +7754,7 @@
     </row>
     <row r="14" spans="4:6">
       <c r="D14" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E14" s="4">
         <v>2</v>
@@ -7762,7 +7765,7 @@
     </row>
     <row r="15" spans="4:6">
       <c r="D15" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E15" s="4">
         <v>2</v>
@@ -7773,7 +7776,7 @@
     </row>
     <row r="16" spans="4:6">
       <c r="D16" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E16" s="4">
         <v>3</v>
@@ -7784,7 +7787,7 @@
     </row>
     <row r="17" spans="4:6">
       <c r="D17" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E17" s="4">
         <v>3</v>
@@ -7795,7 +7798,7 @@
     </row>
     <row r="18" spans="4:6">
       <c r="D18" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E18" s="4">
         <v>4</v>
@@ -7806,7 +7809,7 @@
     </row>
     <row r="19" spans="4:6">
       <c r="D19" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E19" s="4">
         <v>5</v>
@@ -7817,7 +7820,7 @@
     </row>
     <row r="20" spans="4:6">
       <c r="D20" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E20" s="4">
         <v>5</v>
@@ -7828,7 +7831,7 @@
     </row>
     <row r="21" spans="4:6">
       <c r="D21" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E21" s="4">
         <v>6</v>
@@ -7849,7 +7852,7 @@
     </row>
     <row r="24" spans="4:6">
       <c r="D24" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>27</v>
@@ -7861,7 +7864,7 @@
     </row>
     <row r="27" spans="4:6">
       <c r="D27" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E27" s="6">
         <v>2</v>
@@ -7872,7 +7875,7 @@
     </row>
     <row r="28" spans="4:6">
       <c r="D28" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E28" s="6">
         <v>2</v>
@@ -7893,10 +7896,10 @@
     </row>
     <row r="31" spans="4:6">
       <c r="D31" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F31" s="6">
         <f>AVERAGE(F27,F28)</f>
@@ -7905,10 +7908,10 @@
     </row>
     <row r="34" spans="4:6">
       <c r="D34" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F34" s="7">
         <f>AVERAGE(F2,F3,F4,F5,F6,F8,F14:F21,F27:F28)</f>

--- a/src/utils/sxsyzlzq/zzz_cardList.xlsx
+++ b/src/utils/sxsyzlzq/zzz_cardList.xlsx
@@ -4,19 +4,19 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28245" windowHeight="12345" activeTab="1"/>
+    <workbookView windowWidth="28245" windowHeight="12345" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="伊萝莲" sheetId="1" r:id="rId1"/>
     <sheet name="阿斯塔拉" sheetId="2" r:id="rId2"/>
     <sheet name="熙" sheetId="9" r:id="rId3"/>
-    <sheet name="尤瑞艾莉" sheetId="12" r:id="rId4"/>
-    <sheet name="洛" sheetId="11" r:id="rId5"/>
-    <sheet name="帝国" sheetId="5" r:id="rId6"/>
-    <sheet name="隐秘" sheetId="6" r:id="rId7"/>
-    <sheet name="禅意" sheetId="7" r:id="rId8"/>
-    <sheet name="炼狱" sheetId="8" r:id="rId9"/>
-    <sheet name="白处尊" sheetId="4" r:id="rId10"/>
+    <sheet name="洛" sheetId="11" r:id="rId4"/>
+    <sheet name="帝国" sheetId="5" r:id="rId5"/>
+    <sheet name="隐秘" sheetId="6" r:id="rId6"/>
+    <sheet name="禅意" sheetId="7" r:id="rId7"/>
+    <sheet name="炼狱" sheetId="8" r:id="rId8"/>
+    <sheet name="白处尊" sheetId="4" r:id="rId9"/>
+    <sheet name="尤瑞艾莉" sheetId="12" r:id="rId10"/>
     <sheet name="梅" sheetId="3" r:id="rId11"/>
     <sheet name="希拉" sheetId="10" r:id="rId12"/>
     <sheet name="统计" sheetId="13" r:id="rId13"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="136">
   <si>
     <t>名称</t>
   </si>
@@ -232,166 +232,184 @@
     <t>神机玄女·轩</t>
   </si>
   <si>
+    <t>上宝沁金耙</t>
+  </si>
+  <si>
     <t>怨魂饕餮兽</t>
   </si>
   <si>
+    <t>铁山靠</t>
+  </si>
+  <si>
+    <t>驱魔道人</t>
+  </si>
+  <si>
+    <t>流岚刃·琳</t>
+  </si>
+  <si>
+    <t>流星七号</t>
+  </si>
+  <si>
+    <t>九天玄女·轩</t>
+  </si>
+  <si>
+    <t>火蛇巫女</t>
+  </si>
+  <si>
+    <t>曙光·安娜贝尔</t>
+  </si>
+  <si>
+    <t>圣枪·卡罗琳</t>
+  </si>
+  <si>
+    <t>明日之音·露娜</t>
+  </si>
+  <si>
+    <t>正阳大主教·伊恩</t>
+  </si>
+  <si>
+    <t>钢铁统帅·雷蒙德</t>
+  </si>
+  <si>
+    <t>帝国卡等：</t>
+  </si>
+  <si>
+    <t>鬼童7号</t>
+  </si>
+  <si>
+    <t>No.2时光·米拉</t>
+  </si>
+  <si>
+    <t>No.6沃凡瑞拉</t>
+  </si>
+  <si>
+    <t>隐秘卡等：</t>
+  </si>
+  <si>
+    <t>悟能禅杖</t>
+  </si>
+  <si>
+    <t>帝禅意卡等：</t>
+  </si>
+  <si>
+    <t>橙色色卡等：</t>
+  </si>
+  <si>
+    <t>炼狱卡等：</t>
+  </si>
+  <si>
+    <t>执剑道人</t>
+  </si>
+  <si>
     <t>猩红勇士</t>
   </si>
   <si>
-    <t>铁山靠</t>
+    <t>旅行背包</t>
+  </si>
+  <si>
+    <t>重装固守</t>
+  </si>
+  <si>
+    <t>龟族僧人</t>
+  </si>
+  <si>
+    <t>叶幻师</t>
+  </si>
+  <si>
+    <t>风卷残云</t>
+  </si>
+  <si>
+    <t>祥云师太</t>
+  </si>
+  <si>
+    <t>冲锋装备</t>
+  </si>
+  <si>
+    <t>蟠桃会</t>
   </si>
   <si>
     <t>万物之灵</t>
   </si>
   <si>
-    <t>上宝沁金耙</t>
-  </si>
-  <si>
-    <t>火蛇巫女</t>
+    <t>永恒之王·莱哈特</t>
+  </si>
+  <si>
+    <t>阵营</t>
+  </si>
+  <si>
+    <t>数量</t>
+  </si>
+  <si>
+    <t>No.8雷鸣·泰拉德</t>
+  </si>
+  <si>
+    <t>隐秘</t>
+  </si>
+  <si>
+    <t>帝国</t>
+  </si>
+  <si>
+    <t>四芒军旗</t>
+  </si>
+  <si>
+    <t>传记·钢铁守卫</t>
+  </si>
+  <si>
+    <t>圣殿卫士</t>
+  </si>
+  <si>
+    <t>圣甲先锋</t>
+  </si>
+  <si>
+    <t>咒术系学士</t>
+  </si>
+  <si>
+    <t>传记·海市蜃楼·蛇</t>
+  </si>
+  <si>
+    <t>No.5咒刃·布雷克</t>
+  </si>
+  <si>
+    <t>圣殿弩手</t>
+  </si>
+  <si>
+    <t>魔像-御咒铁卫</t>
+  </si>
+  <si>
+    <t>缄言法师</t>
+  </si>
+  <si>
+    <t>白袍主教</t>
+  </si>
+  <si>
+    <t>圣殿骑士</t>
+  </si>
+  <si>
+    <t>圣殿精英</t>
+  </si>
+  <si>
+    <t>实验室流浆</t>
   </si>
   <si>
     <t>夺取阵地</t>
   </si>
   <si>
-    <t>曙光·安娜贝尔</t>
-  </si>
-  <si>
-    <t>圣枪·卡罗琳</t>
-  </si>
-  <si>
-    <t>明日之音·露娜</t>
-  </si>
-  <si>
-    <t>正阳大主教·伊恩</t>
-  </si>
-  <si>
-    <t>钢铁统帅·雷蒙德</t>
-  </si>
-  <si>
-    <t>帝国卡等：</t>
-  </si>
-  <si>
-    <t>No.2时光·米拉</t>
-  </si>
-  <si>
-    <t>No.6沃凡瑞拉</t>
-  </si>
-  <si>
-    <t>悟能禅杖</t>
-  </si>
-  <si>
-    <t>橙色色卡等：</t>
-  </si>
-  <si>
-    <t>旅行背包</t>
-  </si>
-  <si>
-    <t>重装固守</t>
-  </si>
-  <si>
-    <t>执剑道人</t>
-  </si>
-  <si>
-    <t>圣殿弩手</t>
-  </si>
-  <si>
-    <t>龟族僧人</t>
-  </si>
-  <si>
-    <t>风卷残云</t>
-  </si>
-  <si>
-    <t>驱魔道人</t>
-  </si>
-  <si>
-    <t>冲锋装备</t>
+    <t>炽阳坠落</t>
+  </si>
+  <si>
+    <t>钢铁大师</t>
+  </si>
+  <si>
+    <t>学仆-塑钢型</t>
+  </si>
+  <si>
+    <t>帝国军魂·莱哈特</t>
+  </si>
+  <si>
+    <t>田园保卫战</t>
   </si>
   <si>
     <t>禁卫百夫长</t>
-  </si>
-  <si>
-    <t>永恒之王·莱哈特</t>
-  </si>
-  <si>
-    <t>叶幻师</t>
-  </si>
-  <si>
-    <t>祥云师太</t>
-  </si>
-  <si>
-    <t>蟠桃会</t>
-  </si>
-  <si>
-    <t>阵营</t>
-  </si>
-  <si>
-    <t>数量</t>
-  </si>
-  <si>
-    <t>No.8雷鸣·泰拉德</t>
-  </si>
-  <si>
-    <t>隐秘</t>
-  </si>
-  <si>
-    <t>帝国</t>
-  </si>
-  <si>
-    <t>四芒军旗</t>
-  </si>
-  <si>
-    <t>传记·钢铁守卫</t>
-  </si>
-  <si>
-    <t>圣殿卫士</t>
-  </si>
-  <si>
-    <t>圣甲先锋</t>
-  </si>
-  <si>
-    <t>咒术系学士</t>
-  </si>
-  <si>
-    <t>传记·海市蜃楼·蛇</t>
-  </si>
-  <si>
-    <t>No.5咒刃·布雷克</t>
-  </si>
-  <si>
-    <t>魔像-御咒铁卫</t>
-  </si>
-  <si>
-    <t>缄言法师</t>
-  </si>
-  <si>
-    <t>白袍主教</t>
-  </si>
-  <si>
-    <t>圣殿骑士</t>
-  </si>
-  <si>
-    <t>鬼童7号</t>
-  </si>
-  <si>
-    <t>圣殿精英</t>
-  </si>
-  <si>
-    <t>实验室流浆</t>
-  </si>
-  <si>
-    <t>炽阳坠落</t>
-  </si>
-  <si>
-    <t>钢铁大师</t>
-  </si>
-  <si>
-    <t>学仆-塑钢型</t>
-  </si>
-  <si>
-    <t>帝国军魂·莱哈特</t>
-  </si>
-  <si>
-    <t>田园保卫战</t>
   </si>
   <si>
     <t>幻象巨龙</t>
@@ -423,10 +441,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -478,14 +496,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -493,108 +503,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -616,7 +526,115 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -631,19 +649,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -655,25 +697,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -691,19 +727,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -721,7 +817,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -733,85 +829,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -825,17 +843,22 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -872,11 +895,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -884,8 +905,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -904,24 +940,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -930,10 +948,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -942,7 +960,7 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -951,124 +969,124 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1949,7 +1967,7 @@
   <dimension ref="A1:D47"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="17.875" customWidth="1"/>
+    <col min="1" max="1" width="18.25" customWidth="1"/>
     <col min="4" max="4" width="12.625"/>
   </cols>
   <sheetData>
@@ -1969,7 +1987,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>5</v>
@@ -1978,12 +1996,12 @@
         <v>1</v>
       </c>
       <c r="D2" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
@@ -1997,27 +2015,27 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>85</v>
+        <v>39</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="2">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" s="2">
         <v>13</v>
@@ -2025,63 +2043,63 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>87</v>
+        <v>48</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" s="2">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>5</v>
@@ -2095,88 +2113,88 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>89</v>
+        <v>54</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" s="2">
-        <v>3</v>
-      </c>
-      <c r="D12" s="2">
-        <v>13</v>
-      </c>
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="2">
-        <v>4</v>
-      </c>
-      <c r="D13" s="2">
-        <v>14</v>
-      </c>
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" s="2">
-        <v>5</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="C14" s="2"/>
       <c r="D14" s="2">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
+        <f>AVERAGE(D2:D11)</f>
+        <v>13.8</v>
+      </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2">
-        <f>AVERAGE(D2:D14)</f>
-        <v>14.5384615384615</v>
+      <c r="A17" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="4">
+        <v>1</v>
+      </c>
+      <c r="D17" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="4">
+        <v>2</v>
+      </c>
+      <c r="D18" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="4">
+        <v>2</v>
+      </c>
+      <c r="D19" s="4">
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="4" t="s">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>15</v>
@@ -2185,12 +2203,12 @@
         <v>2</v>
       </c>
       <c r="D20" s="4">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>15</v>
@@ -2199,12 +2217,12 @@
         <v>3</v>
       </c>
       <c r="D21" s="4">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="4" t="s">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>15</v>
@@ -2218,7 +2236,7 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="4" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>15</v>
@@ -2227,12 +2245,12 @@
         <v>3</v>
       </c>
       <c r="D23" s="4">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="4" t="s">
-        <v>92</v>
+        <v>59</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>15</v>
@@ -2241,26 +2259,26 @@
         <v>3</v>
       </c>
       <c r="D24" s="4">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C25" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D25" s="4">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>15</v>
@@ -2269,26 +2287,26 @@
         <v>4</v>
       </c>
       <c r="D26" s="4">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="4" t="s">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C27" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D27" s="4">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="4" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>15</v>
@@ -2297,107 +2315,107 @@
         <v>5</v>
       </c>
       <c r="D28" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="4" t="s">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C29" s="4">
+        <v>5</v>
+      </c>
+      <c r="D29" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="4">
+        <v>5</v>
+      </c>
+      <c r="D30" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C31" s="4">
         <v>6</v>
       </c>
-      <c r="D29" s="4">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="4"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="4"/>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
+      <c r="D31" s="4">
+        <v>11</v>
+      </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="4" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="B32" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" s="4">
+        <v>7</v>
+      </c>
+      <c r="D32" s="4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="4"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="4"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B35" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4">
-        <f>AVERAGE(D20:D29)</f>
-        <v>14.4</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C35" s="6">
-        <v>3</v>
-      </c>
-      <c r="D35" s="6">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C36" s="6">
-        <v>4</v>
-      </c>
-      <c r="D36" s="6">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
-      <c r="A37" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C37" s="6">
-        <v>4</v>
-      </c>
-      <c r="D37" s="6">
-        <v>12</v>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4">
+        <f>AVERAGE(D17:D32)</f>
+        <v>13</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="6" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C38" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D38" s="6">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="6" t="s">
-        <v>94</v>
+        <v>33</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>29</v>
@@ -2406,35 +2424,35 @@
         <v>5</v>
       </c>
       <c r="D39" s="6">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="6" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C40" s="6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D40" s="6">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C41" s="6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D41" s="6">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2458,8 +2476,8 @@
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="6">
-        <f>AVERAGE(D35:D41)</f>
-        <v>12.8571428571429</v>
+        <f>AVERAGE(D38:D41)</f>
+        <v>10.5</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2467,8 +2485,8 @@
         <v>38</v>
       </c>
       <c r="D47">
-        <f>AVERAGE(D2:D14,D20:D29,D35:D41)</f>
-        <v>14.1</v>
+        <f>AVERAGE(D2:D11,D17:D32,D38:D41)</f>
+        <v>12.9333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -2531,7 +2549,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
@@ -2545,7 +2563,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -2559,7 +2577,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>5</v>
@@ -2615,7 +2633,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>5</v>
@@ -2657,7 +2675,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>5</v>
@@ -2671,7 +2689,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>5</v>
@@ -2752,7 +2770,7 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="4" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>15</v>
@@ -2780,7 +2798,7 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="4" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>15</v>
@@ -2808,7 +2826,7 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>15</v>
@@ -2822,7 +2840,7 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="4" t="s">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>15</v>
@@ -2903,7 +2921,7 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="6" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>29</v>
@@ -2931,7 +2949,7 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="6" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>29</v>
@@ -3495,7 +3513,7 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>29</v>
@@ -3564,7 +3582,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -3573,15 +3591,15 @@
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -3595,10 +3613,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>5</v>
@@ -3612,10 +3630,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>5</v>
@@ -3632,7 +3650,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>5</v>
@@ -3646,10 +3664,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="3" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>15</v>
@@ -3666,7 +3684,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>15</v>
@@ -3680,10 +3698,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="4" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>15</v>
@@ -3697,10 +3715,10 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>5</v>
@@ -3717,7 +3735,7 @@
         <v>39</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>5</v>
@@ -3734,7 +3752,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>5</v>
@@ -3748,10 +3766,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>102</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>5</v>
@@ -3768,7 +3786,7 @@
         <v>8</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>5</v>
@@ -3782,10 +3800,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="4" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>15</v>
@@ -3799,10 +3817,10 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="4" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>15</v>
@@ -3819,7 +3837,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>15</v>
@@ -3836,7 +3854,7 @@
         <v>18</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>15</v>
@@ -3853,7 +3871,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>15</v>
@@ -3867,10 +3885,10 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>29</v>
@@ -3884,10 +3902,10 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>29</v>
@@ -3901,10 +3919,10 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>29</v>
@@ -3918,10 +3936,10 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2" t="s">
-        <v>88</v>
+        <v>114</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>5</v>
@@ -3938,7 +3956,7 @@
         <v>9</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>5</v>
@@ -3955,7 +3973,7 @@
         <v>10</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>5</v>
@@ -3969,10 +3987,10 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="4" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>15</v>
@@ -3986,10 +4004,10 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="4" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>15</v>
@@ -4006,7 +4024,7 @@
         <v>20</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>15</v>
@@ -4023,7 +4041,7 @@
         <v>19</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>15</v>
@@ -4037,10 +4055,10 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="4" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>15</v>
@@ -4054,10 +4072,10 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="4" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>15</v>
@@ -4071,10 +4089,10 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="4" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>15</v>
@@ -4088,10 +4106,10 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>29</v>
@@ -4105,10 +4123,10 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>29</v>
@@ -4122,10 +4140,10 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>29</v>
@@ -4139,10 +4157,10 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>5</v>
@@ -4156,10 +4174,10 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="4" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>15</v>
@@ -4173,10 +4191,10 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="4" t="s">
-        <v>74</v>
+        <v>121</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>15</v>
@@ -4190,10 +4208,10 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="4" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>15</v>
@@ -4210,7 +4228,7 @@
         <v>21</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>15</v>
@@ -4224,10 +4242,10 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="4" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>15</v>
@@ -4241,10 +4259,10 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="4" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>15</v>
@@ -4261,7 +4279,7 @@
         <v>22</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>15</v>
@@ -4275,10 +4293,10 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>29</v>
@@ -4292,10 +4310,10 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>29</v>
@@ -4312,7 +4330,7 @@
         <v>11</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>5</v>
@@ -4326,10 +4344,10 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="4" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>15</v>
@@ -4346,7 +4364,7 @@
         <v>23</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>15</v>
@@ -4360,10 +4378,10 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="4" t="s">
-        <v>93</v>
+        <v>127</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>15</v>
@@ -4377,10 +4395,10 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>29</v>
@@ -4394,10 +4412,10 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="4" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>15</v>
@@ -4414,7 +4432,7 @@
         <v>25</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>15</v>
@@ -4428,10 +4446,10 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>29</v>
@@ -4445,10 +4463,10 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>29</v>
@@ -4462,10 +4480,10 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="4" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>15</v>
@@ -4479,10 +4497,10 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="4" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>15</v>
@@ -4496,10 +4514,10 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="4" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>15</v>
@@ -4513,10 +4531,10 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="4" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>15</v>
@@ -4533,7 +4551,7 @@
         <v>26</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>15</v>
@@ -4582,7 +4600,7 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -4602,7 +4620,7 @@
       </c>
       <c r="B66" s="2"/>
       <c r="C66" s="2" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" s="2">
@@ -5217,12 +5235,12 @@
         <v>1</v>
       </c>
       <c r="D4" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -5231,26 +5249,26 @@
         <v>1</v>
       </c>
       <c r="D5" s="2">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>5</v>
@@ -5264,7 +5282,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>5</v>
@@ -5273,12 +5291,12 @@
         <v>2</v>
       </c>
       <c r="D8" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>5</v>
@@ -5292,7 +5310,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>5</v>
@@ -5306,21 +5324,21 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>5</v>
@@ -5329,12 +5347,12 @@
         <v>3</v>
       </c>
       <c r="D12" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>5</v>
@@ -5343,12 +5361,12 @@
         <v>3</v>
       </c>
       <c r="D13" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>5</v>
@@ -5357,26 +5375,26 @@
         <v>3</v>
       </c>
       <c r="D14" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C15" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D15" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>5</v>
@@ -5385,22 +5403,14 @@
         <v>4</v>
       </c>
       <c r="D16" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" s="2">
-        <v>4</v>
-      </c>
-      <c r="D17" s="2">
-        <v>13</v>
-      </c>
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2"/>
@@ -5409,27 +5419,35 @@
       <c r="D18" s="2"/>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
+      <c r="A19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2">
-        <f>AVERAGE(D2:D17)</f>
-        <v>14.125</v>
+      <c r="D19" s="2">
+        <f>AVERAGE(D2:D16)</f>
+        <v>14.4666666666667</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="4">
+        <v>2</v>
+      </c>
+      <c r="D22" s="4">
+        <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>15</v>
@@ -5438,26 +5456,26 @@
         <v>2</v>
       </c>
       <c r="D23" s="4">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C24" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D24" s="4">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>15</v>
@@ -5466,12 +5484,12 @@
         <v>3</v>
       </c>
       <c r="D25" s="4">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>15</v>
@@ -5480,12 +5498,12 @@
         <v>3</v>
       </c>
       <c r="D26" s="4">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>15</v>
@@ -5499,21 +5517,21 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C28" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D28" s="4">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>15</v>
@@ -5522,26 +5540,26 @@
         <v>4</v>
       </c>
       <c r="D29" s="4">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C30" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D30" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>15</v>
@@ -5550,37 +5568,29 @@
         <v>5</v>
       </c>
       <c r="D31" s="4">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
       <c r="A32" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C32" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D32" s="4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C33" s="4">
-        <v>6</v>
-      </c>
-      <c r="D33" s="4">
         <v>11</v>
       </c>
-      <c r="F33" s="5"/>
+      <c r="F32" s="5"/>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="4"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="4"/>
@@ -5589,41 +5599,49 @@
       <c r="D34" s="4"/>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="4"/>
-      <c r="B35" s="4"/>
+      <c r="A35" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>27</v>
+      </c>
       <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4">
-        <f>AVERAGE(D23:D33)</f>
+      <c r="D35" s="4">
+        <f>AVERAGE(D22:D32)</f>
         <v>12.7272727272727</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C38" s="6">
+        <v>2</v>
+      </c>
+      <c r="D38" s="6">
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C39" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D39" s="6">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>29</v>
@@ -5632,12 +5650,12 @@
         <v>4</v>
       </c>
       <c r="D40" s="6">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>29</v>
@@ -5670,8 +5688,8 @@
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="6">
-        <f>AVERAGE(D39:D41)</f>
-        <v>9.66666666666667</v>
+        <f>AVERAGE(D38:D41)</f>
+        <v>10.5</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -5681,8 +5699,8 @@
       <c r="B47" s="7"/>
       <c r="C47" s="7"/>
       <c r="D47" s="7">
-        <f>AVERAGE(D2:D17,D23:D33,D39:D41)</f>
-        <v>13.1666666666667</v>
+        <f>AVERAGE(D2:D16,D22:D32,D38:D41)</f>
+        <v>13.3</v>
       </c>
     </row>
   </sheetData>
@@ -5692,540 +5710,6 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:D47"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
-  <cols>
-    <col min="1" max="1" width="18.25" customWidth="1"/>
-    <col min="4" max="4" width="12.625"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="2">
-        <v>1</v>
-      </c>
-      <c r="D2" s="2">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="2">
-        <v>1</v>
-      </c>
-      <c r="D3" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="2">
-        <v>2</v>
-      </c>
-      <c r="D4" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="2">
-        <v>2</v>
-      </c>
-      <c r="D5" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="2">
-        <v>2</v>
-      </c>
-      <c r="D6" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="2">
-        <v>2</v>
-      </c>
-      <c r="D7" s="2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="2">
-        <v>2</v>
-      </c>
-      <c r="D8" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="2">
-        <v>2</v>
-      </c>
-      <c r="D9" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" s="2">
-        <v>3</v>
-      </c>
-      <c r="D10" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="2">
-        <v>4</v>
-      </c>
-      <c r="D11" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2">
-        <f>AVERAGE(D2:D11)</f>
-        <v>13.8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" s="4">
-        <v>1</v>
-      </c>
-      <c r="D17" s="4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18" s="4">
-        <v>2</v>
-      </c>
-      <c r="D18" s="4">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="4">
-        <v>2</v>
-      </c>
-      <c r="D19" s="4">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="4">
-        <v>2</v>
-      </c>
-      <c r="D20" s="4">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C21" s="4">
-        <v>3</v>
-      </c>
-      <c r="D21" s="4">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C22" s="4">
-        <v>3</v>
-      </c>
-      <c r="D22" s="4">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C23" s="4">
-        <v>3</v>
-      </c>
-      <c r="D23" s="4">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C24" s="4">
-        <v>3</v>
-      </c>
-      <c r="D24" s="4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C25" s="4">
-        <v>3</v>
-      </c>
-      <c r="D25" s="4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C26" s="4">
-        <v>4</v>
-      </c>
-      <c r="D26" s="4">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C27" s="4">
-        <v>4</v>
-      </c>
-      <c r="D27" s="4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C28" s="4">
-        <v>5</v>
-      </c>
-      <c r="D28" s="4">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C29" s="4">
-        <v>5</v>
-      </c>
-      <c r="D29" s="4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C30" s="4">
-        <v>5</v>
-      </c>
-      <c r="D30" s="4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C31" s="4">
-        <v>6</v>
-      </c>
-      <c r="D31" s="4">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C32" s="4">
-        <v>7</v>
-      </c>
-      <c r="D32" s="4">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="4"/>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" s="4"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4">
-        <f>AVERAGE(D17:D32)</f>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
-      <c r="A38" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C38" s="6">
-        <v>2</v>
-      </c>
-      <c r="D38" s="6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C39" s="6">
-        <v>5</v>
-      </c>
-      <c r="D39" s="6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
-      <c r="A40" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C40" s="6">
-        <v>5</v>
-      </c>
-      <c r="D40" s="6">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
-      <c r="A41" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C41" s="6">
-        <v>7</v>
-      </c>
-      <c r="D41" s="6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
-      <c r="A42" s="6"/>
-      <c r="B42" s="6"/>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6"/>
-    </row>
-    <row r="43" spans="1:4">
-      <c r="A43" s="6"/>
-      <c r="B43" s="6"/>
-      <c r="C43" s="6"/>
-      <c r="D43" s="6"/>
-    </row>
-    <row r="44" spans="1:4">
-      <c r="A44" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C44" s="6"/>
-      <c r="D44" s="6">
-        <f>AVERAGE(D38:D41)</f>
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
-      <c r="A47" t="s">
-        <v>38</v>
-      </c>
-      <c r="D47">
-        <f>AVERAGE(D2:D11,D17:D32,D38:D41)</f>
-        <v>12.9333333333333</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F47"/>
@@ -6274,7 +5758,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -6349,41 +5833,41 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" s="2">
         <v>15</v>
@@ -6391,7 +5875,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>5</v>
@@ -6400,99 +5884,99 @@
         <v>3</v>
       </c>
       <c r="D12" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D13" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" s="2">
-        <v>3</v>
-      </c>
-      <c r="D14" s="2">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2">
+        <f>AVERAGE(D2:D13)</f>
+        <v>15.0833333333333</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15" s="2">
-        <v>4</v>
-      </c>
-      <c r="D15" s="2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2">
-        <f>AVERAGE(D2:D15)</f>
-        <v>14.7142857142857</v>
+      <c r="B19" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="4">
+        <v>1</v>
+      </c>
+      <c r="D19" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="4">
+        <v>2</v>
+      </c>
+      <c r="D20" s="4">
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="4">
+        <v>2</v>
+      </c>
+      <c r="D21" s="4">
         <v>14</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C21" s="4">
-        <v>1</v>
-      </c>
-      <c r="D21" s="4">
-        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="4" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C22" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D22" s="4">
         <v>15</v>
@@ -6500,13 +5984,13 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="4" t="s">
-        <v>18</v>
+        <v>71</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C23" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D23" s="4">
         <v>14</v>
@@ -6514,7 +5998,7 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="4" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>15</v>
@@ -6523,12 +6007,12 @@
         <v>3</v>
       </c>
       <c r="D24" s="4">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="4" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>15</v>
@@ -6556,131 +6040,131 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C27" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D27" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="4" t="s">
-        <v>20</v>
+        <v>61</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C28" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D28" s="4">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C29" s="4">
+        <v>5</v>
+      </c>
+      <c r="D29" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="4">
+        <v>7</v>
+      </c>
+      <c r="D30" s="4">
+        <v>15</v>
+      </c>
+      <c r="F30" s="5"/>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="4"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="4"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4">
+        <f>AVERAGE(D19:D30)</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C36" s="6">
+        <v>3</v>
+      </c>
+      <c r="D36" s="6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C37" s="6">
         <v>4</v>
       </c>
-      <c r="D29" s="4">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C30" s="4">
+      <c r="D37" s="6">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C38" s="6">
         <v>4</v>
       </c>
-      <c r="D30" s="4">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C31" s="4">
-        <v>5</v>
-      </c>
-      <c r="D31" s="4">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C32" s="4">
-        <v>5</v>
-      </c>
-      <c r="D32" s="4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C33" s="4">
-        <v>7</v>
-      </c>
-      <c r="D33" s="4">
-        <v>14</v>
-      </c>
-      <c r="F33" s="5"/>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" s="4"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="4"/>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4">
-        <f>AVERAGE(D21:D33)</f>
-        <v>13.7692307692308</v>
+      <c r="D38" s="6">
+        <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>29</v>
@@ -6694,13 +6178,13 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="6" t="s">
-        <v>72</v>
+        <v>33</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C40" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D40" s="6">
         <v>12</v>
@@ -6708,7 +6192,7 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>29</v>
@@ -6741,8 +6225,8 @@
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="6">
-        <f>AVERAGE(D39:D41)</f>
-        <v>12</v>
+        <f>AVERAGE(D36:D41)</f>
+        <v>12.1666666666667</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -6752,8 +6236,8 @@
       <c r="B47" s="7"/>
       <c r="C47" s="7"/>
       <c r="D47" s="7">
-        <f>AVERAGE(D2:D15,D21:D33,D39:D41)</f>
-        <v>14.0333333333333</v>
+        <f>AVERAGE(D2:D13,D19:D30,D36:D41)</f>
+        <v>14.0666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -6762,7 +6246,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D33"/>
@@ -6819,13 +6303,13 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C5" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -6840,59 +6324,59 @@
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
+      <c r="A7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="2">
+        <v>5</v>
+      </c>
+      <c r="C7" s="2">
+        <v>14</v>
+      </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
     </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="2">
-        <f>AVERAGE(C2:C6)</f>
-        <v>15.4</v>
-      </c>
-      <c r="D9" s="4"/>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="4">
-        <v>2</v>
-      </c>
-      <c r="C12" s="4">
-        <v>17</v>
-      </c>
+    <row r="9" spans="1:3">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="2">
+        <f>AVERAGE(C2:C7)</f>
+        <v>15.3333333333333</v>
+      </c>
+      <c r="D10" s="4"/>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B13" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C13" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>74</v>
+        <v>19</v>
       </c>
       <c r="B14" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C14" s="4">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -6946,13 +6430,13 @@
         <v>27</v>
       </c>
       <c r="C20" s="4">
-        <f>AVERAGE(C12:C17)</f>
-        <v>14.6666666666667</v>
+        <f>AVERAGE(C13:C17)</f>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B23" s="6">
         <v>1</v>
@@ -6963,7 +6447,7 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B24" s="6">
         <v>2</v>
@@ -6974,7 +6458,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B25" s="6">
         <v>2</v>
@@ -6985,18 +6469,18 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B26" s="6">
         <v>2</v>
       </c>
       <c r="C26" s="6">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B27" s="6">
         <v>5</v>
@@ -7024,7 +6508,7 @@
       </c>
       <c r="C30" s="6">
         <f>AVERAGE(C23:C27)</f>
-        <v>13</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -7032,11 +6516,11 @@
         <v>38</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C33" s="7">
-        <f>AVERAGE(C2:C6,C12:C17,C23:C27)</f>
-        <v>14.375</v>
+        <f>AVERAGE(C2:C7,C13:C17,C23:C27)</f>
+        <v>14.5625</v>
       </c>
     </row>
   </sheetData>
@@ -7045,7 +6529,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C32"/>
@@ -7185,7 +6669,7 @@
         <v>3</v>
       </c>
       <c r="C15" s="4">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -7212,25 +6696,19 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B18" s="4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C18" s="4">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" s="4">
-        <v>7</v>
-      </c>
-      <c r="C19" s="4">
-        <v>14</v>
-      </c>
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4"/>
@@ -7238,28 +6716,34 @@
       <c r="C20" s="4"/>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B22" s="4" t="s">
+      <c r="A21" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C22" s="4">
-        <f>AVERAGE(C10:C19)</f>
-        <v>13.4</v>
+      <c r="C21" s="4">
+        <f>AVERAGE(C10:C18)</f>
+        <v>13.7777777777778</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B24" s="6">
+        <v>4</v>
+      </c>
+      <c r="C24" s="6">
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B25" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C25" s="6">
         <v>12</v>
@@ -7267,7 +6751,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B26" s="6">
         <v>7</v>
@@ -7294,8 +6778,8 @@
         <v>13</v>
       </c>
       <c r="C29" s="6">
-        <f>AVERAGE(C25:C26)</f>
-        <v>12</v>
+        <f>AVERAGE(C24:C26)</f>
+        <v>12.6666666666667</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -7303,11 +6787,11 @@
         <v>38</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C32" s="7">
-        <f>AVERAGE(C2:C4,C10:C19,C25:C26)</f>
-        <v>13.4666666666667</v>
+        <f>AVERAGE(C2:C4,C10:C18,C24:C26)</f>
+        <v>13.7333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -7316,10 +6800,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="13.75" customWidth="1"/>
@@ -7357,23 +6841,23 @@
         <v>1</v>
       </c>
       <c r="C3" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B4" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B5" s="2">
         <v>2</v>
@@ -7384,40 +6868,40 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B6" s="2">
         <v>2</v>
       </c>
       <c r="C6" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B7" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="B8" s="2">
         <v>3</v>
       </c>
       <c r="C8" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="B9" s="2">
         <v>3</v>
@@ -7434,52 +6918,46 @@
         <v>3</v>
       </c>
       <c r="C10" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B11" s="2">
         <v>3</v>
       </c>
       <c r="C11" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B12" s="2">
         <v>3</v>
       </c>
       <c r="C12" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B13" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C13" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B14" s="2">
-        <v>4</v>
-      </c>
-      <c r="C14" s="2">
-        <v>15</v>
-      </c>
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2"/>
@@ -7487,142 +6965,397 @@
       <c r="C15" s="2"/>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C17" s="2">
-        <f>AVERAGE(C2:C14)</f>
-        <v>14.2307692307692</v>
+      <c r="A16" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="2">
+        <f>AVERAGE(C2:C13)</f>
+        <v>14.6666666666667</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B19" s="4">
+        <v>3</v>
+      </c>
+      <c r="C19" s="4">
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B20" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C20" s="4">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B21" s="4">
-        <v>3</v>
-      </c>
-      <c r="C21" s="4">
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="4"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="4">
+        <f>AVERAGE(C19:C20)</f>
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B26" s="6">
+        <v>3</v>
+      </c>
+      <c r="C26" s="6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B27" s="6">
+        <v>4</v>
+      </c>
+      <c r="C27" s="6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B28" s="6">
+        <v>4</v>
+      </c>
+      <c r="C28" s="6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="6"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="6"/>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="6"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C31" s="6">
+        <f>AVERAGE(C26:C28)</f>
+        <v>11.6666666666667</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C34" s="7">
+        <f>AVERAGE(C2:C13,C19:C20,C26:C28)</f>
+        <v>14.1176470588235</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C32"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
+  <cols>
+    <col min="1" max="1" width="13.125" customWidth="1"/>
+    <col min="2" max="2" width="11.25" customWidth="1"/>
+    <col min="3" max="3" width="11.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="2">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2">
         <v>14</v>
       </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" s="2">
+        <v>2</v>
+      </c>
+      <c r="C4" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="2">
+        <v>2</v>
+      </c>
+      <c r="C5" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6" s="2">
+        <v>4</v>
+      </c>
+      <c r="C6" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="2">
+        <f>AVERAGE(C2:C6)</f>
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" s="4">
+        <v>2</v>
+      </c>
+      <c r="C12" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" s="4">
+        <v>2</v>
+      </c>
+      <c r="C13" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" s="4">
+        <v>3</v>
+      </c>
+      <c r="C14" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B15" s="4">
+        <v>3</v>
+      </c>
+      <c r="C15" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B16" s="4">
+        <v>4</v>
+      </c>
+      <c r="C16" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17" s="4">
+        <v>5</v>
+      </c>
+      <c r="C17" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B18" s="4">
+        <v>5</v>
+      </c>
+      <c r="C18" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B19" s="4">
+        <v>6</v>
+      </c>
+      <c r="C19" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="4"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B22" s="4">
-        <v>4</v>
+        <v>12</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C22" s="4">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="B23" s="4">
-        <v>5</v>
-      </c>
-      <c r="C23" s="4">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
+        <f>AVERAGE(C12:C19)</f>
+        <v>12.25</v>
+      </c>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="4"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
+      <c r="A25" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B25" s="6">
+        <v>2</v>
+      </c>
+      <c r="C25" s="6">
+        <v>7</v>
+      </c>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C26" s="4">
-        <f>AVERAGE(C20:C23)</f>
-        <v>14</v>
-      </c>
+      <c r="A26" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B26" s="6">
+        <v>5</v>
+      </c>
+      <c r="C26" s="6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="6"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="6"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="6"/>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="B29" s="6">
-        <v>4</v>
+        <v>12</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>88</v>
       </c>
       <c r="C29" s="6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="B30" s="6">
-        <v>4</v>
-      </c>
-      <c r="C30" s="6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="6"/>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
+        <f>AVERAGE(C25,C26)</f>
+        <v>9</v>
+      </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="6"/>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C33" s="6">
-        <f>AVERAGE(C29:C30)</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="7" t="s">
+      <c r="A32" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="C36" s="7">
-        <f>AVERAGE(C2:C14,C20:C23,C29:C30)</f>
-        <v>13.9473684210526</v>
+      <c r="B32" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C32" s="7">
+        <f>AVERAGE(C2:C6,C12:C19,C25:C26)</f>
+        <v>12.3333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -7634,288 +7367,529 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="D1:F34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <dimension ref="A1:D47"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
-    <col min="4" max="4" width="13.125" customWidth="1"/>
-    <col min="5" max="5" width="11.25" customWidth="1"/>
-    <col min="6" max="6" width="10.625" customWidth="1"/>
+    <col min="1" max="1" width="17.875" customWidth="1"/>
+    <col min="4" max="4" width="12.625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="4:6">
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
       <c r="D1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="4:6">
-      <c r="D2" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E2" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2">
         <v>1</v>
       </c>
-      <c r="F2" s="2">
+      <c r="D2" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="4:6">
-      <c r="D3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E3" s="2">
+    <row r="4" spans="1:4">
+      <c r="A4" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2">
         <v>1</v>
       </c>
-      <c r="F3" s="2">
+      <c r="D4" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="2">
+        <v>2</v>
+      </c>
+      <c r="D5" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="2">
+        <v>2</v>
+      </c>
+      <c r="D6" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="2">
+        <v>2</v>
+      </c>
+      <c r="D7" s="2">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="4:6">
-      <c r="D4" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E4" s="2">
-        <v>2</v>
-      </c>
-      <c r="F4" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="4:6">
-      <c r="D5" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E5" s="2">
-        <v>2</v>
-      </c>
-      <c r="F5" s="2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="4:6">
-      <c r="D6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E6" s="2">
-        <v>2</v>
-      </c>
-      <c r="F6" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="4:6">
-      <c r="D7" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E7" s="2">
-        <v>3</v>
-      </c>
-      <c r="F7" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="4:6">
-      <c r="D8" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E8" s="2">
+    <row r="8" spans="1:4">
+      <c r="A8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="2">
+        <v>2</v>
+      </c>
+      <c r="D8" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="2">
+        <v>3</v>
+      </c>
+      <c r="D9" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="2">
+        <v>3</v>
+      </c>
+      <c r="D10" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="2">
+        <v>3</v>
+      </c>
+      <c r="D11" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="2">
+        <v>3</v>
+      </c>
+      <c r="D12" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="2">
+        <v>3</v>
+      </c>
+      <c r="D13" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="2">
+        <v>3</v>
+      </c>
+      <c r="D14" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="2">
         <v>4</v>
       </c>
-      <c r="F8" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="4:6">
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-    </row>
-    <row r="10" spans="4:6">
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-    </row>
-    <row r="11" spans="4:6">
-      <c r="D11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="2">
-        <f>AVERAGE(F2:F8)</f>
-        <v>13.4285714285714</v>
-      </c>
-    </row>
-    <row r="14" spans="4:6">
-      <c r="D14" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E14" s="4">
-        <v>2</v>
-      </c>
-      <c r="F14" s="4">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="4:6">
-      <c r="D15" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E15" s="4">
-        <v>2</v>
-      </c>
-      <c r="F15" s="4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="4:6">
-      <c r="D16" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E16" s="4">
-        <v>3</v>
-      </c>
-      <c r="F16" s="4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="4:6">
-      <c r="D17" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="E17" s="4">
-        <v>3</v>
-      </c>
-      <c r="F17" s="4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="4:6">
-      <c r="D18" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="E18" s="4">
+      <c r="D15" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="2">
+        <v>5</v>
+      </c>
+      <c r="D16" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="2">
+        <v>5</v>
+      </c>
+      <c r="D17" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2">
+        <f>AVERAGE(D2:D17)</f>
+        <v>14.875</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="4">
+        <v>2</v>
+      </c>
+      <c r="D23" s="4">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" s="4">
+        <v>3</v>
+      </c>
+      <c r="D24" s="4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" s="4">
+        <v>3</v>
+      </c>
+      <c r="D25" s="4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="4">
+        <v>3</v>
+      </c>
+      <c r="D26" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" s="4">
         <v>4</v>
       </c>
-      <c r="F18" s="4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="4:6">
-      <c r="D19" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E19" s="4">
-        <v>5</v>
-      </c>
-      <c r="F19" s="4">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="4:6">
-      <c r="D20" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E20" s="4">
-        <v>5</v>
-      </c>
-      <c r="F20" s="4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="4:6">
-      <c r="D21" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="E21" s="4">
+      <c r="D27" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C28" s="4">
+        <v>4</v>
+      </c>
+      <c r="D28" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C29" s="4">
         <v>6</v>
       </c>
-      <c r="F21" s="4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="22" spans="4:6">
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-    </row>
-    <row r="23" spans="4:6">
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-    </row>
-    <row r="24" spans="4:6">
-      <c r="D24" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E24" s="4" t="s">
+      <c r="D29" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="4"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="4"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B32" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F24" s="4">
-        <f>AVERAGE(F14:F21)</f>
-        <v>12.25</v>
-      </c>
-    </row>
-    <row r="27" spans="4:6">
-      <c r="D27" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="E27" s="6">
-        <v>2</v>
-      </c>
-      <c r="F27" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="4:6">
-      <c r="D28" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="E28" s="6">
-        <v>2</v>
-      </c>
-      <c r="F28" s="6">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="29" spans="4:6">
-      <c r="D29" s="6"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
-    </row>
-    <row r="30" spans="4:6">
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
-    </row>
-    <row r="31" spans="4:6">
-      <c r="D31" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="F31" s="6">
-        <f>AVERAGE(F27,F28)</f>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4">
+        <f>AVERAGE(D23:D29)</f>
+        <v>14.7142857142857</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C35" s="6">
+        <v>3</v>
+      </c>
+      <c r="D35" s="6">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C36" s="6">
+        <v>4</v>
+      </c>
+      <c r="D36" s="6">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C37" s="6">
+        <v>4</v>
+      </c>
+      <c r="D37" s="6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C38" s="6">
+        <v>4</v>
+      </c>
+      <c r="D38" s="6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C39" s="6">
+        <v>4</v>
+      </c>
+      <c r="D39" s="6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C40" s="6">
+        <v>6</v>
+      </c>
+      <c r="D40" s="6">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C41" s="6">
         <v>8</v>
       </c>
-    </row>
-    <row r="34" spans="4:6">
-      <c r="D34" s="7" t="s">
+      <c r="D41" s="6">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="6"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="6"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6">
+        <f>AVERAGE(D35:D41)</f>
+        <v>12.8571428571429</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" t="s">
         <v>38</v>
       </c>
-      <c r="E34" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="F34" s="7">
-        <f>AVERAGE(F2,F3,F4,F5,F6,F8,F14:F21,F27:F28)</f>
-        <v>12.1875</v>
+      <c r="D47">
+        <f>AVERAGE(D2:D17,D23:D29,D35:D41)</f>
+        <v>14.3666666666667</v>
       </c>
     </row>
   </sheetData>

--- a/src/utils/sxsyzlzq/zzz_cardList.xlsx
+++ b/src/utils/sxsyzlzq/zzz_cardList.xlsx
@@ -4,29 +4,30 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28245" windowHeight="12345" activeTab="8"/>
+    <workbookView windowWidth="28245" windowHeight="12345" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="伊萝莲" sheetId="1" r:id="rId1"/>
     <sheet name="阿斯塔拉" sheetId="2" r:id="rId2"/>
-    <sheet name="熙" sheetId="9" r:id="rId3"/>
-    <sheet name="洛" sheetId="11" r:id="rId4"/>
-    <sheet name="帝国" sheetId="5" r:id="rId5"/>
-    <sheet name="隐秘" sheetId="6" r:id="rId6"/>
-    <sheet name="禅意" sheetId="7" r:id="rId7"/>
-    <sheet name="炼狱" sheetId="8" r:id="rId8"/>
-    <sheet name="白处尊" sheetId="4" r:id="rId9"/>
-    <sheet name="尤瑞艾莉" sheetId="12" r:id="rId10"/>
-    <sheet name="梅" sheetId="3" r:id="rId11"/>
-    <sheet name="希拉" sheetId="10" r:id="rId12"/>
-    <sheet name="统计" sheetId="13" r:id="rId13"/>
+    <sheet name="洛" sheetId="11" r:id="rId3"/>
+    <sheet name="白处尊" sheetId="4" r:id="rId4"/>
+    <sheet name="格纳罗尔" sheetId="14" r:id="rId5"/>
+    <sheet name="帝国" sheetId="5" r:id="rId6"/>
+    <sheet name="隐秘" sheetId="6" r:id="rId7"/>
+    <sheet name="禅意" sheetId="7" r:id="rId8"/>
+    <sheet name="炼狱" sheetId="8" r:id="rId9"/>
+    <sheet name="梅" sheetId="3" r:id="rId10"/>
+    <sheet name="熙" sheetId="9" r:id="rId11"/>
+    <sheet name="尤瑞艾莉" sheetId="12" r:id="rId12"/>
+    <sheet name="希拉" sheetId="10" r:id="rId13"/>
+    <sheet name="统计" sheetId="13" r:id="rId14"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="142">
   <si>
     <t>名称</t>
   </si>
@@ -148,48 +149,135 @@
     <t>学仆-观测型</t>
   </si>
   <si>
+    <t>卜命道长</t>
+  </si>
+  <si>
+    <t>箭竹守卫</t>
+  </si>
+  <si>
+    <t>白羊药师</t>
+  </si>
+  <si>
+    <t>树木之怒</t>
+  </si>
+  <si>
+    <t>苦行武僧</t>
+  </si>
+  <si>
+    <t>执剑道者</t>
+  </si>
+  <si>
+    <t>铁山靠</t>
+  </si>
+  <si>
+    <t>连击</t>
+  </si>
+  <si>
+    <t>深山采药人</t>
+  </si>
+  <si>
+    <t>风铃道人</t>
+  </si>
+  <si>
+    <t>扫叶僧</t>
+  </si>
+  <si>
+    <t>驱魔道人</t>
+  </si>
+  <si>
+    <t>御风武者</t>
+  </si>
+  <si>
+    <t>流岚刃·琳</t>
+  </si>
+  <si>
+    <t>流星七号</t>
+  </si>
+  <si>
+    <t>九天玄女·轩</t>
+  </si>
+  <si>
+    <t>上宝沁金耙</t>
+  </si>
+  <si>
+    <t>火蛇巫女</t>
+  </si>
+  <si>
+    <t>执剑道人</t>
+  </si>
+  <si>
+    <t>神机玄女·轩</t>
+  </si>
+  <si>
+    <t>暗潮涌动</t>
+  </si>
+  <si>
+    <t>心灵黑洞</t>
+  </si>
+  <si>
+    <t>狡诈学徒</t>
+  </si>
+  <si>
+    <t>黑夜突袭</t>
+  </si>
+  <si>
+    <t>热血矿工</t>
+  </si>
+  <si>
+    <t>不法交易</t>
+  </si>
+  <si>
+    <t>曙光·安娜贝尔</t>
+  </si>
+  <si>
+    <t>圣枪·卡罗琳</t>
+  </si>
+  <si>
+    <t>明日之音·露娜</t>
+  </si>
+  <si>
+    <t>正阳大主教·伊恩</t>
+  </si>
+  <si>
+    <t>钢铁统帅·雷蒙德</t>
+  </si>
+  <si>
+    <t>帝国卡等：</t>
+  </si>
+  <si>
+    <t>鬼童7号</t>
+  </si>
+  <si>
+    <t>No.2时光·米拉</t>
+  </si>
+  <si>
+    <t>No.6沃凡瑞拉</t>
+  </si>
+  <si>
+    <t>隐秘卡等：</t>
+  </si>
+  <si>
+    <t>疾风猎手</t>
+  </si>
+  <si>
+    <t>悟能禅杖</t>
+  </si>
+  <si>
+    <t>帝禅意卡等：</t>
+  </si>
+  <si>
     <t>冥河守卫</t>
   </si>
   <si>
-    <t>卜命道长</t>
-  </si>
-  <si>
-    <t>箭竹守卫</t>
-  </si>
-  <si>
     <t>落雷击</t>
   </si>
   <si>
-    <t>白羊药师</t>
-  </si>
-  <si>
-    <t>树木之怒</t>
-  </si>
-  <si>
-    <t>苦行武僧</t>
+    <t>邪眼魔</t>
   </si>
   <si>
     <t>残暴爪钩</t>
   </si>
   <si>
-    <t>邪眼魔</t>
-  </si>
-  <si>
-    <t>执剑道者</t>
-  </si>
-  <si>
-    <t>连击</t>
-  </si>
-  <si>
-    <t>深山采药人</t>
-  </si>
-  <si>
-    <t>疾风猎手</t>
-  </si>
-  <si>
-    <t>风铃道人</t>
-  </si>
-  <si>
     <t>烈焰风暴</t>
   </si>
   <si>
@@ -199,7 +287,46 @@
     <t>觅食大嘴兽</t>
   </si>
   <si>
-    <t>扫叶僧</t>
+    <t>灼神双炎</t>
+  </si>
+  <si>
+    <t>雷光炼狱</t>
+  </si>
+  <si>
+    <t>橙色色卡等：</t>
+  </si>
+  <si>
+    <t>炼狱卡等：</t>
+  </si>
+  <si>
+    <t>旅行背包</t>
+  </si>
+  <si>
+    <t>重装固守</t>
+  </si>
+  <si>
+    <t>龟族僧人</t>
+  </si>
+  <si>
+    <t>叶幻师</t>
+  </si>
+  <si>
+    <t>风卷残云</t>
+  </si>
+  <si>
+    <t>祥云师太</t>
+  </si>
+  <si>
+    <t>冲锋装备</t>
+  </si>
+  <si>
+    <t>蟠桃会</t>
+  </si>
+  <si>
+    <t>万物之灵</t>
+  </si>
+  <si>
+    <t>永恒之王·莱哈特</t>
   </si>
   <si>
     <t>逍遥琴师</t>
@@ -211,15 +338,6 @@
     <t>岩浆球</t>
   </si>
   <si>
-    <t>御风武者</t>
-  </si>
-  <si>
-    <t>灼神双炎</t>
-  </si>
-  <si>
-    <t>雷光炼狱</t>
-  </si>
-  <si>
     <t>地狱屠夫</t>
   </si>
   <si>
@@ -229,109 +347,10 @@
     <t>痛苦之心</t>
   </si>
   <si>
-    <t>神机玄女·轩</t>
-  </si>
-  <si>
-    <t>上宝沁金耙</t>
-  </si>
-  <si>
     <t>怨魂饕餮兽</t>
   </si>
   <si>
-    <t>铁山靠</t>
-  </si>
-  <si>
-    <t>驱魔道人</t>
-  </si>
-  <si>
-    <t>流岚刃·琳</t>
-  </si>
-  <si>
-    <t>流星七号</t>
-  </si>
-  <si>
-    <t>九天玄女·轩</t>
-  </si>
-  <si>
-    <t>火蛇巫女</t>
-  </si>
-  <si>
-    <t>曙光·安娜贝尔</t>
-  </si>
-  <si>
-    <t>圣枪·卡罗琳</t>
-  </si>
-  <si>
-    <t>明日之音·露娜</t>
-  </si>
-  <si>
-    <t>正阳大主教·伊恩</t>
-  </si>
-  <si>
-    <t>钢铁统帅·雷蒙德</t>
-  </si>
-  <si>
-    <t>帝国卡等：</t>
-  </si>
-  <si>
-    <t>鬼童7号</t>
-  </si>
-  <si>
-    <t>No.2时光·米拉</t>
-  </si>
-  <si>
-    <t>No.6沃凡瑞拉</t>
-  </si>
-  <si>
-    <t>隐秘卡等：</t>
-  </si>
-  <si>
-    <t>悟能禅杖</t>
-  </si>
-  <si>
-    <t>帝禅意卡等：</t>
-  </si>
-  <si>
-    <t>橙色色卡等：</t>
-  </si>
-  <si>
-    <t>炼狱卡等：</t>
-  </si>
-  <si>
-    <t>执剑道人</t>
-  </si>
-  <si>
     <t>猩红勇士</t>
-  </si>
-  <si>
-    <t>旅行背包</t>
-  </si>
-  <si>
-    <t>重装固守</t>
-  </si>
-  <si>
-    <t>龟族僧人</t>
-  </si>
-  <si>
-    <t>叶幻师</t>
-  </si>
-  <si>
-    <t>风卷残云</t>
-  </si>
-  <si>
-    <t>祥云师太</t>
-  </si>
-  <si>
-    <t>冲锋装备</t>
-  </si>
-  <si>
-    <t>蟠桃会</t>
-  </si>
-  <si>
-    <t>万物之灵</t>
-  </si>
-  <si>
-    <t>永恒之王·莱哈特</t>
   </si>
   <si>
     <t>阵营</t>
@@ -441,10 +460,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -496,6 +515,7 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -504,22 +524,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -534,14 +553,53 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -556,37 +614,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
@@ -594,16 +621,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -619,7 +638,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -634,7 +653,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -649,25 +668,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -679,13 +698,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -697,7 +722,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -715,13 +740,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -733,13 +770,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -751,37 +812,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -793,43 +836,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -843,11 +862,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -896,8 +921,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -905,23 +930,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -940,6 +950,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -948,10 +967,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -960,7 +979,7 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -969,124 +988,124 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1967,540 +1986,6 @@
   <dimension ref="A1:D47"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="18.25" customWidth="1"/>
-    <col min="4" max="4" width="12.625"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="2">
-        <v>1</v>
-      </c>
-      <c r="D2" s="2">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="2">
-        <v>1</v>
-      </c>
-      <c r="D3" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="2">
-        <v>2</v>
-      </c>
-      <c r="D4" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="2">
-        <v>2</v>
-      </c>
-      <c r="D5" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="2">
-        <v>2</v>
-      </c>
-      <c r="D6" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="2">
-        <v>2</v>
-      </c>
-      <c r="D7" s="2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="2">
-        <v>2</v>
-      </c>
-      <c r="D8" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="2">
-        <v>2</v>
-      </c>
-      <c r="D9" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" s="2">
-        <v>3</v>
-      </c>
-      <c r="D10" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="2">
-        <v>4</v>
-      </c>
-      <c r="D11" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2">
-        <f>AVERAGE(D2:D11)</f>
-        <v>13.8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" s="4">
-        <v>1</v>
-      </c>
-      <c r="D17" s="4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18" s="4">
-        <v>2</v>
-      </c>
-      <c r="D18" s="4">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="4">
-        <v>2</v>
-      </c>
-      <c r="D19" s="4">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="4">
-        <v>2</v>
-      </c>
-      <c r="D20" s="4">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C21" s="4">
-        <v>3</v>
-      </c>
-      <c r="D21" s="4">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C22" s="4">
-        <v>3</v>
-      </c>
-      <c r="D22" s="4">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C23" s="4">
-        <v>3</v>
-      </c>
-      <c r="D23" s="4">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C24" s="4">
-        <v>3</v>
-      </c>
-      <c r="D24" s="4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C25" s="4">
-        <v>3</v>
-      </c>
-      <c r="D25" s="4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C26" s="4">
-        <v>4</v>
-      </c>
-      <c r="D26" s="4">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C27" s="4">
-        <v>4</v>
-      </c>
-      <c r="D27" s="4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C28" s="4">
-        <v>5</v>
-      </c>
-      <c r="D28" s="4">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C29" s="4">
-        <v>5</v>
-      </c>
-      <c r="D29" s="4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C30" s="4">
-        <v>5</v>
-      </c>
-      <c r="D30" s="4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C31" s="4">
-        <v>6</v>
-      </c>
-      <c r="D31" s="4">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C32" s="4">
-        <v>7</v>
-      </c>
-      <c r="D32" s="4">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="4"/>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" s="4"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4">
-        <f>AVERAGE(D17:D32)</f>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
-      <c r="A38" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C38" s="6">
-        <v>2</v>
-      </c>
-      <c r="D38" s="6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C39" s="6">
-        <v>5</v>
-      </c>
-      <c r="D39" s="6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
-      <c r="A40" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C40" s="6">
-        <v>5</v>
-      </c>
-      <c r="D40" s="6">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
-      <c r="A41" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C41" s="6">
-        <v>7</v>
-      </c>
-      <c r="D41" s="6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
-      <c r="A42" s="6"/>
-      <c r="B42" s="6"/>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6"/>
-    </row>
-    <row r="43" spans="1:4">
-      <c r="A43" s="6"/>
-      <c r="B43" s="6"/>
-      <c r="C43" s="6"/>
-      <c r="D43" s="6"/>
-    </row>
-    <row r="44" spans="1:4">
-      <c r="A44" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C44" s="6"/>
-      <c r="D44" s="6">
-        <f>AVERAGE(D38:D41)</f>
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
-      <c r="A47" t="s">
-        <v>38</v>
-      </c>
-      <c r="D47">
-        <f>AVERAGE(D2:D11,D17:D32,D38:D41)</f>
-        <v>12.9333333333333</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:D47"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
-  <cols>
     <col min="1" max="1" width="18.125" customWidth="1"/>
     <col min="4" max="4" width="12.625"/>
   </cols>
@@ -2535,7 +2020,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
@@ -2549,7 +2034,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
@@ -2563,7 +2048,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -2577,7 +2062,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>90</v>
+        <v>58</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>5</v>
@@ -2605,7 +2090,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>5</v>
@@ -2619,7 +2104,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>5</v>
@@ -2633,7 +2118,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>5</v>
@@ -2647,7 +2132,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>5</v>
@@ -2661,7 +2146,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>5</v>
@@ -2675,7 +2160,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>5</v>
@@ -2689,7 +2174,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>5</v>
@@ -2770,7 +2255,7 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="4" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>15</v>
@@ -2784,7 +2269,7 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="4" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>15</v>
@@ -2798,7 +2283,7 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>15</v>
@@ -2812,7 +2297,7 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="4" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>15</v>
@@ -2826,7 +2311,7 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>15</v>
@@ -2840,7 +2325,7 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>15</v>
@@ -2921,7 +2406,7 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="6" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>29</v>
@@ -2949,7 +2434,7 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>29</v>
@@ -3030,7 +2515,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F47"/>
@@ -3056,7 +2541,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>5</v>
@@ -3070,7 +2555,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
@@ -3084,7 +2569,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
@@ -3093,12 +2578,12 @@
         <v>1</v>
       </c>
       <c r="D4" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -3107,26 +2592,26 @@
         <v>1</v>
       </c>
       <c r="D5" s="2">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>5</v>
@@ -3140,7 +2625,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>5</v>
@@ -3149,12 +2634,12 @@
         <v>2</v>
       </c>
       <c r="D8" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>5</v>
@@ -3168,7 +2653,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>5</v>
@@ -3182,35 +2667,35 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C12" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>5</v>
@@ -3219,12 +2704,12 @@
         <v>3</v>
       </c>
       <c r="D13" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>5</v>
@@ -3233,26 +2718,26 @@
         <v>3</v>
       </c>
       <c r="D14" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C15" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D15" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>5</v>
@@ -3261,22 +2746,14 @@
         <v>4</v>
       </c>
       <c r="D16" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" s="2">
-        <v>4</v>
-      </c>
-      <c r="D17" s="2">
-        <v>13</v>
-      </c>
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2"/>
@@ -3285,27 +2762,35 @@
       <c r="D18" s="2"/>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
+      <c r="A19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B20" s="2" t="s">
+      <c r="D19" s="2">
+        <f>AVERAGE(D2:D16)</f>
+        <v>14.4666666666667</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="4">
+        <v>2</v>
+      </c>
+      <c r="D22" s="4">
         <v>13</v>
-      </c>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2">
-        <f>AVERAGE(D2:D17)</f>
-        <v>13.9375</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="4" t="s">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>15</v>
@@ -3314,26 +2799,26 @@
         <v>2</v>
       </c>
       <c r="D23" s="4">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="4" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C24" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D24" s="4">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="4" t="s">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>15</v>
@@ -3342,12 +2827,12 @@
         <v>3</v>
       </c>
       <c r="D25" s="4">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="4" t="s">
-        <v>58</v>
+        <v>101</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>15</v>
@@ -3356,12 +2841,12 @@
         <v>3</v>
       </c>
       <c r="D26" s="4">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="4" t="s">
-        <v>59</v>
+        <v>102</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>15</v>
@@ -3375,21 +2860,21 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="4" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C28" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D28" s="4">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="4" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>15</v>
@@ -3398,26 +2883,26 @@
         <v>4</v>
       </c>
       <c r="D29" s="4">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="4" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C30" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D30" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="4" t="s">
-        <v>63</v>
+        <v>103</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>15</v>
@@ -3426,37 +2911,29 @@
         <v>5</v>
       </c>
       <c r="D31" s="4">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
       <c r="A32" s="4" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C32" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D32" s="4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C33" s="4">
-        <v>6</v>
-      </c>
-      <c r="D33" s="4">
         <v>11</v>
       </c>
-      <c r="F33" s="5"/>
+      <c r="F32" s="5"/>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="4"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="4"/>
@@ -3465,41 +2942,49 @@
       <c r="D34" s="4"/>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="4"/>
-      <c r="B35" s="4"/>
+      <c r="A35" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>27</v>
+      </c>
       <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4">
-        <f>AVERAGE(D23:D33)</f>
+      <c r="D35" s="4">
+        <f>AVERAGE(D22:D32)</f>
         <v>12.7272727272727</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C38" s="6">
+        <v>2</v>
+      </c>
+      <c r="D38" s="6">
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="6" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C39" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D39" s="6">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="6" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>29</v>
@@ -3508,12 +2993,12 @@
         <v>4</v>
       </c>
       <c r="D40" s="6">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="6" t="s">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>29</v>
@@ -3546,8 +3031,8 @@
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="6">
-        <f>AVERAGE(D39:D41)</f>
-        <v>9.66666666666667</v>
+        <f>AVERAGE(D38:D41)</f>
+        <v>10.5</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -3557,8 +3042,542 @@
       <c r="B47" s="7"/>
       <c r="C47" s="7"/>
       <c r="D47" s="7">
-        <f>AVERAGE(D2:D17,D23:D33,D39:D41)</f>
-        <v>13.0666666666667</v>
+        <f>AVERAGE(D2:D16,D22:D32,D38:D41)</f>
+        <v>13.3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D47"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="18.25" customWidth="1"/>
+    <col min="4" max="4" width="12.625"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2">
+        <v>2</v>
+      </c>
+      <c r="D4" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="2">
+        <v>2</v>
+      </c>
+      <c r="D5" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="2">
+        <v>2</v>
+      </c>
+      <c r="D6" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="2">
+        <v>2</v>
+      </c>
+      <c r="D7" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="2">
+        <v>2</v>
+      </c>
+      <c r="D8" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="2">
+        <v>2</v>
+      </c>
+      <c r="D9" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="2">
+        <v>3</v>
+      </c>
+      <c r="D10" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="2">
+        <v>4</v>
+      </c>
+      <c r="D11" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2">
+        <f>AVERAGE(D2:D11)</f>
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="4">
+        <v>1</v>
+      </c>
+      <c r="D17" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="4">
+        <v>2</v>
+      </c>
+      <c r="D18" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="4">
+        <v>2</v>
+      </c>
+      <c r="D19" s="4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="4">
+        <v>2</v>
+      </c>
+      <c r="D20" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="4">
+        <v>3</v>
+      </c>
+      <c r="D21" s="4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="4">
+        <v>3</v>
+      </c>
+      <c r="D22" s="4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="4">
+        <v>3</v>
+      </c>
+      <c r="D23" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" s="4">
+        <v>3</v>
+      </c>
+      <c r="D24" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" s="4">
+        <v>3</v>
+      </c>
+      <c r="D25" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="4">
+        <v>4</v>
+      </c>
+      <c r="D26" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" s="4">
+        <v>4</v>
+      </c>
+      <c r="D27" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C28" s="4">
+        <v>5</v>
+      </c>
+      <c r="D28" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C29" s="4">
+        <v>5</v>
+      </c>
+      <c r="D29" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="4">
+        <v>5</v>
+      </c>
+      <c r="D30" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C31" s="4">
+        <v>6</v>
+      </c>
+      <c r="D31" s="4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" s="4">
+        <v>7</v>
+      </c>
+      <c r="D32" s="4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="4"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="4"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4">
+        <f>AVERAGE(D17:D32)</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C38" s="6">
+        <v>2</v>
+      </c>
+      <c r="D38" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C39" s="6">
+        <v>5</v>
+      </c>
+      <c r="D39" s="6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C40" s="6">
+        <v>5</v>
+      </c>
+      <c r="D40" s="6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C41" s="6">
+        <v>7</v>
+      </c>
+      <c r="D41" s="6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="6"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="6"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6">
+        <f>AVERAGE(D38:D41)</f>
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" t="s">
+        <v>38</v>
+      </c>
+      <c r="D47">
+        <f>AVERAGE(D2:D11,D17:D32,D38:D41)</f>
+        <v>12.9333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -3568,6 +3587,543 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F47"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="17.875" customWidth="1"/>
+    <col min="4" max="4" width="12.625"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="2">
+        <v>1</v>
+      </c>
+      <c r="D5" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="2">
+        <v>1</v>
+      </c>
+      <c r="D6" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="2">
+        <v>2</v>
+      </c>
+      <c r="D7" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="2">
+        <v>2</v>
+      </c>
+      <c r="D8" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="2">
+        <v>2</v>
+      </c>
+      <c r="D9" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="2">
+        <v>2</v>
+      </c>
+      <c r="D10" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="2">
+        <v>2</v>
+      </c>
+      <c r="D11" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="2">
+        <v>2</v>
+      </c>
+      <c r="D12" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="2">
+        <v>3</v>
+      </c>
+      <c r="D13" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="2">
+        <v>3</v>
+      </c>
+      <c r="D14" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="2">
+        <v>3</v>
+      </c>
+      <c r="D15" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="2">
+        <v>4</v>
+      </c>
+      <c r="D16" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="2">
+        <v>4</v>
+      </c>
+      <c r="D17" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2">
+        <f>AVERAGE(D2:D17)</f>
+        <v>13.9375</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="4">
+        <v>2</v>
+      </c>
+      <c r="D23" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" s="4">
+        <v>2</v>
+      </c>
+      <c r="D24" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" s="4">
+        <v>3</v>
+      </c>
+      <c r="D25" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="4">
+        <v>3</v>
+      </c>
+      <c r="D26" s="4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" s="4">
+        <v>3</v>
+      </c>
+      <c r="D27" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C28" s="4">
+        <v>3</v>
+      </c>
+      <c r="D28" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C29" s="4">
+        <v>4</v>
+      </c>
+      <c r="D29" s="4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="4">
+        <v>4</v>
+      </c>
+      <c r="D30" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C31" s="4">
+        <v>5</v>
+      </c>
+      <c r="D31" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" s="4">
+        <v>5</v>
+      </c>
+      <c r="D32" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C33" s="4">
+        <v>6</v>
+      </c>
+      <c r="D33" s="4">
+        <v>11</v>
+      </c>
+      <c r="F33" s="5"/>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="4"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="4"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4">
+        <f>AVERAGE(D23:D33)</f>
+        <v>12.7272727272727</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C39" s="6">
+        <v>2</v>
+      </c>
+      <c r="D39" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C40" s="6">
+        <v>4</v>
+      </c>
+      <c r="D40" s="6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C41" s="6">
+        <v>5</v>
+      </c>
+      <c r="D41" s="6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="6"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="6"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6">
+        <f>AVERAGE(D39:D41)</f>
+        <v>9.66666666666667</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B47" s="7"/>
+      <c r="C47" s="7"/>
+      <c r="D47" s="7">
+        <f>AVERAGE(D2:D17,D23:D33,D39:D41)</f>
+        <v>13.0666666666667</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E66"/>
@@ -3582,7 +4138,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -3591,15 +4147,15 @@
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -3613,10 +4169,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>5</v>
@@ -3630,10 +4186,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>5</v>
@@ -3650,7 +4206,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>5</v>
@@ -3664,10 +4220,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="3" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>15</v>
@@ -3684,7 +4240,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>15</v>
@@ -3698,10 +4254,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="4" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>15</v>
@@ -3715,10 +4271,10 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>5</v>
@@ -3735,7 +4291,7 @@
         <v>39</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>5</v>
@@ -3752,7 +4308,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>5</v>
@@ -3766,10 +4322,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>5</v>
@@ -3786,7 +4342,7 @@
         <v>8</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>5</v>
@@ -3800,10 +4356,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>111</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>105</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>15</v>
@@ -3817,10 +4373,10 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="4" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>15</v>
@@ -3837,7 +4393,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>15</v>
@@ -3854,7 +4410,7 @@
         <v>18</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>15</v>
@@ -3871,7 +4427,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>15</v>
@@ -3885,10 +4441,10 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>29</v>
@@ -3902,10 +4458,10 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>29</v>
@@ -3919,10 +4475,10 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>29</v>
@@ -3936,10 +4492,10 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>5</v>
@@ -3956,7 +4512,7 @@
         <v>9</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>5</v>
@@ -3973,7 +4529,7 @@
         <v>10</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>5</v>
@@ -3987,10 +4543,10 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="4" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>15</v>
@@ -4004,10 +4560,10 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="4" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>15</v>
@@ -4024,7 +4580,7 @@
         <v>20</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>15</v>
@@ -4041,7 +4597,7 @@
         <v>19</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>15</v>
@@ -4055,10 +4611,10 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="4" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>15</v>
@@ -4072,10 +4628,10 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>15</v>
@@ -4089,10 +4645,10 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="4" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>15</v>
@@ -4106,10 +4662,10 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>29</v>
@@ -4123,10 +4679,10 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>29</v>
@@ -4140,10 +4696,10 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>29</v>
@@ -4157,10 +4713,10 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>5</v>
@@ -4174,10 +4730,10 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="4" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>15</v>
@@ -4191,10 +4747,10 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="4" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>15</v>
@@ -4208,10 +4764,10 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="4" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>15</v>
@@ -4228,7 +4784,7 @@
         <v>21</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>15</v>
@@ -4242,10 +4798,10 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="4" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>15</v>
@@ -4259,10 +4815,10 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="4" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>15</v>
@@ -4279,7 +4835,7 @@
         <v>22</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>15</v>
@@ -4293,10 +4849,10 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>29</v>
@@ -4310,10 +4866,10 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>29</v>
@@ -4330,7 +4886,7 @@
         <v>11</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>5</v>
@@ -4344,10 +4900,10 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="4" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>15</v>
@@ -4364,7 +4920,7 @@
         <v>23</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>15</v>
@@ -4378,10 +4934,10 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="4" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>15</v>
@@ -4395,10 +4951,10 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>29</v>
@@ -4412,10 +4968,10 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="4" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>15</v>
@@ -4432,7 +4988,7 @@
         <v>25</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>15</v>
@@ -4446,10 +5002,10 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>29</v>
@@ -4463,10 +5019,10 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>29</v>
@@ -4480,10 +5036,10 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="4" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>15</v>
@@ -4497,10 +5053,10 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="4" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>15</v>
@@ -4514,10 +5070,10 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="4" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>15</v>
@@ -4531,10 +5087,10 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="4" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>15</v>
@@ -4551,7 +5107,7 @@
         <v>26</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>15</v>
@@ -4600,7 +5156,7 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -4620,7 +5176,7 @@
       </c>
       <c r="B66" s="2"/>
       <c r="C66" s="2" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" s="2">
@@ -5207,7 +5763,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -5221,40 +5777,40 @@
         <v>1</v>
       </c>
       <c r="D3" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>5</v>
@@ -5268,7 +5824,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>5</v>
@@ -5277,12 +5833,12 @@
         <v>2</v>
       </c>
       <c r="D7" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>5</v>
@@ -5296,21 +5852,21 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>5</v>
@@ -5319,12 +5875,12 @@
         <v>2</v>
       </c>
       <c r="D10" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>5</v>
@@ -5333,12 +5889,12 @@
         <v>3</v>
       </c>
       <c r="D11" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>5</v>
@@ -5347,121 +5903,121 @@
         <v>3</v>
       </c>
       <c r="D12" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D13" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" s="2">
-        <v>3</v>
-      </c>
-      <c r="D14" s="2">
-        <v>13</v>
-      </c>
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15" s="2">
-        <v>4</v>
-      </c>
-      <c r="D15" s="2">
-        <v>15</v>
-      </c>
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C16" s="2">
-        <v>4</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="C16" s="2"/>
       <c r="D16" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
+        <f>AVERAGE(D2:D13)</f>
+        <v>15.0833333333333</v>
+      </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2">
-        <f>AVERAGE(D2:D16)</f>
-        <v>14.4666666666667</v>
+      <c r="A19" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="4">
+        <v>1</v>
+      </c>
+      <c r="D19" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="4">
+        <v>2</v>
+      </c>
+      <c r="D20" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="4">
+        <v>2</v>
+      </c>
+      <c r="D21" s="4">
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C22" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D22" s="4">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C23" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D23" s="4">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="4" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>15</v>
@@ -5470,12 +6026,12 @@
         <v>3</v>
       </c>
       <c r="D24" s="4">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="4" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>15</v>
@@ -5489,7 +6045,7 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="4" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>15</v>
@@ -5498,26 +6054,26 @@
         <v>3</v>
       </c>
       <c r="D26" s="4">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="4" t="s">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C27" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D27" s="4">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="4" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>15</v>
@@ -5531,103 +6087,103 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="4" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C29" s="4">
+        <v>5</v>
+      </c>
+      <c r="D29" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="4">
+        <v>7</v>
+      </c>
+      <c r="D30" s="4">
+        <v>15</v>
+      </c>
+      <c r="F30" s="5"/>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="4"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="4"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4">
+        <f>AVERAGE(D19:D30)</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C36" s="6">
+        <v>3</v>
+      </c>
+      <c r="D36" s="6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C37" s="6">
         <v>4</v>
       </c>
-      <c r="D29" s="4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C30" s="4">
-        <v>5</v>
-      </c>
-      <c r="D30" s="4">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C31" s="4">
-        <v>5</v>
-      </c>
-      <c r="D31" s="4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C32" s="4">
-        <v>6</v>
-      </c>
-      <c r="D32" s="4">
-        <v>11</v>
-      </c>
-      <c r="F32" s="5"/>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="4"/>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" s="4"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4">
-        <f>AVERAGE(D22:D32)</f>
-        <v>12.7272727272727</v>
+      <c r="D37" s="6">
+        <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="6" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C38" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D38" s="6">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="6" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>29</v>
@@ -5641,13 +6197,13 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="6" t="s">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C40" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D40" s="6">
         <v>12</v>
@@ -5655,16 +6211,16 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="6" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C41" s="6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D41" s="6">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -5688,8 +6244,8 @@
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="6">
-        <f>AVERAGE(D38:D41)</f>
-        <v>10.5</v>
+        <f>AVERAGE(D36:D41)</f>
+        <v>12.1666666666667</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -5699,8 +6255,8 @@
       <c r="B47" s="7"/>
       <c r="C47" s="7"/>
       <c r="D47" s="7">
-        <f>AVERAGE(D2:D16,D22:D32,D38:D41)</f>
-        <v>13.3</v>
+        <f>AVERAGE(D2:D13,D19:D30,D36:D41)</f>
+        <v>14.0666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -5712,7 +6268,541 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:D47"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="17.875" customWidth="1"/>
+    <col min="4" max="4" width="12.625"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="2">
+        <v>2</v>
+      </c>
+      <c r="D5" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="2">
+        <v>2</v>
+      </c>
+      <c r="D6" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="2">
+        <v>2</v>
+      </c>
+      <c r="D7" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="2">
+        <v>2</v>
+      </c>
+      <c r="D8" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="2">
+        <v>3</v>
+      </c>
+      <c r="D9" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="2">
+        <v>3</v>
+      </c>
+      <c r="D10" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="2">
+        <v>3</v>
+      </c>
+      <c r="D11" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="2">
+        <v>3</v>
+      </c>
+      <c r="D12" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="2">
+        <v>3</v>
+      </c>
+      <c r="D13" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="2">
+        <v>3</v>
+      </c>
+      <c r="D14" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="2">
+        <v>4</v>
+      </c>
+      <c r="D15" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="2">
+        <v>5</v>
+      </c>
+      <c r="D16" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="2">
+        <v>5</v>
+      </c>
+      <c r="D17" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2">
+        <f>AVERAGE(D2:D17)</f>
+        <v>14.875</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="4">
+        <v>2</v>
+      </c>
+      <c r="D23" s="4">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" s="4">
+        <v>3</v>
+      </c>
+      <c r="D24" s="4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" s="4">
+        <v>3</v>
+      </c>
+      <c r="D25" s="4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="4">
+        <v>3</v>
+      </c>
+      <c r="D26" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" s="4">
+        <v>4</v>
+      </c>
+      <c r="D27" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C28" s="4">
+        <v>4</v>
+      </c>
+      <c r="D28" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C29" s="4">
+        <v>6</v>
+      </c>
+      <c r="D29" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="4"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="4"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4">
+        <f>AVERAGE(D23:D29)</f>
+        <v>14.7142857142857</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C35" s="6">
+        <v>3</v>
+      </c>
+      <c r="D35" s="6">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C36" s="6">
+        <v>4</v>
+      </c>
+      <c r="D36" s="6">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C37" s="6">
+        <v>4</v>
+      </c>
+      <c r="D37" s="6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C38" s="6">
+        <v>4</v>
+      </c>
+      <c r="D38" s="6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C39" s="6">
+        <v>4</v>
+      </c>
+      <c r="D39" s="6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C40" s="6">
+        <v>6</v>
+      </c>
+      <c r="D40" s="6">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C41" s="6">
+        <v>8</v>
+      </c>
+      <c r="D41" s="6">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="6"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="6"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6">
+        <f>AVERAGE(D35:D41)</f>
+        <v>12.8571428571429</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" t="s">
+        <v>38</v>
+      </c>
+      <c r="D47">
+        <f>AVERAGE(D2:D17,D23:D29,D35:D41)</f>
+        <v>14.3666666666667</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="17.875" customWidth="1"/>
@@ -5735,7 +6825,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>5</v>
@@ -5744,12 +6834,12 @@
         <v>1</v>
       </c>
       <c r="D2" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
@@ -5758,26 +6848,26 @@
         <v>1</v>
       </c>
       <c r="D3" s="2">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" s="2">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -5786,12 +6876,12 @@
         <v>2</v>
       </c>
       <c r="D5" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>5</v>
@@ -5800,12 +6890,12 @@
         <v>2</v>
       </c>
       <c r="D6" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>5</v>
@@ -5819,7 +6909,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>5</v>
@@ -5828,26 +6918,26 @@
         <v>2</v>
       </c>
       <c r="D8" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>5</v>
@@ -5856,12 +6946,12 @@
         <v>2</v>
       </c>
       <c r="D10" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>5</v>
@@ -5870,12 +6960,12 @@
         <v>3</v>
       </c>
       <c r="D11" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>5</v>
@@ -5884,22 +6974,14 @@
         <v>3</v>
       </c>
       <c r="D12" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="2">
-        <v>4</v>
-      </c>
-      <c r="D13" s="2">
-        <v>15</v>
-      </c>
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2"/>
@@ -5908,41 +6990,51 @@
       <c r="D14" s="2"/>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
+      <c r="A15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2">
-        <f>AVERAGE(D2:D13)</f>
-        <v>15.0833333333333</v>
+      <c r="D15" s="2">
+        <f>AVERAGE(D2:D12)</f>
+        <v>12.7272727272727</v>
+      </c>
+    </row>
+    <row r="16" customFormat="1"/>
+    <row r="17" customFormat="1"/>
+    <row r="18" spans="1:4">
+      <c r="A18" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="4">
+        <v>1</v>
+      </c>
+      <c r="D18" s="4">
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C19" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" s="4">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>15</v>
@@ -5951,26 +7043,26 @@
         <v>2</v>
       </c>
       <c r="D20" s="4">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="4" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C21" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D21" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="4" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>15</v>
@@ -5979,12 +7071,12 @@
         <v>3</v>
       </c>
       <c r="D22" s="4">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="4" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>15</v>
@@ -6026,21 +7118,21 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C26" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D26" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="4" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>15</v>
@@ -6049,51 +7141,43 @@
         <v>4</v>
       </c>
       <c r="D27" s="4">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="4" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C28" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D28" s="4">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
       <c r="A29" s="4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C29" s="4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D29" s="4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C30" s="4">
-        <v>7</v>
-      </c>
-      <c r="D30" s="4">
-        <v>15</v>
-      </c>
-      <c r="F30" s="5"/>
+        <v>15</v>
+      </c>
+      <c r="F29" s="5"/>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="4"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="4"/>
@@ -6102,41 +7186,51 @@
       <c r="D31" s="4"/>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="4"/>
-      <c r="B32" s="4"/>
+      <c r="A32" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>27</v>
+      </c>
       <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4">
-        <f>AVERAGE(D19:D30)</f>
+      <c r="D32" s="4">
+        <f>AVERAGE(D18:D29)</f>
         <v>14</v>
+      </c>
+    </row>
+    <row r="33" customFormat="1"/>
+    <row r="34" customFormat="1"/>
+    <row r="35" spans="1:4">
+      <c r="A35" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C35" s="6">
+        <v>3</v>
+      </c>
+      <c r="D35" s="6">
+        <v>11</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="6" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C36" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D36" s="6">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="6" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>29</v>
@@ -6145,12 +7239,12 @@
         <v>4</v>
       </c>
       <c r="D37" s="6">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="6" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>29</v>
@@ -6164,13 +7258,13 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="6" t="s">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C39" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D39" s="6">
         <v>12</v>
@@ -6178,31 +7272,23 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="6" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C40" s="6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D40" s="6">
         <v>12</v>
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C41" s="6">
-        <v>7</v>
-      </c>
-      <c r="D41" s="6">
-        <v>12</v>
-      </c>
+      <c r="A41" s="6"/>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="6"/>
@@ -6211,33 +7297,29 @@
       <c r="D42" s="6"/>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="6"/>
-      <c r="B43" s="6"/>
+      <c r="A43" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>37</v>
+      </c>
       <c r="C43" s="6"/>
-      <c r="D43" s="6"/>
-    </row>
-    <row r="44" spans="1:4">
-      <c r="A44" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C44" s="6"/>
-      <c r="D44" s="6">
-        <f>AVERAGE(D36:D41)</f>
+      <c r="D43" s="6">
+        <f>AVERAGE(D35:D40)</f>
         <v>12.1666666666667</v>
       </c>
     </row>
-    <row r="47" spans="1:4">
-      <c r="A47" s="7" t="s">
+    <row r="44" customFormat="1"/>
+    <row r="45" customFormat="1"/>
+    <row r="46" spans="1:4">
+      <c r="A46" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B47" s="7"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="7">
-        <f>AVERAGE(D2:D13,D19:D30,D36:D41)</f>
-        <v>14.0666666666667</v>
+      <c r="B46" s="7"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="7">
+        <f>AVERAGE(D2:D12,D18:D29,D35:D40)</f>
+        <v>13.1379310344828</v>
       </c>
     </row>
   </sheetData>
@@ -6246,7 +7328,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D33"/>
@@ -6320,7 +7402,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -6331,7 +7413,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -6353,7 +7435,7 @@
       </c>
       <c r="C10" s="2">
         <f>AVERAGE(C2:C7)</f>
-        <v>15.3333333333333</v>
+        <v>15.8333333333333</v>
       </c>
       <c r="D10" s="4"/>
     </row>
@@ -6436,7 +7518,7 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="6" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="B23" s="6">
         <v>1</v>
@@ -6447,18 +7529,18 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="6" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="B24" s="6">
         <v>2</v>
       </c>
       <c r="C24" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="6" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="B25" s="6">
         <v>2</v>
@@ -6469,7 +7551,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="6" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B26" s="6">
         <v>2</v>
@@ -6480,7 +7562,7 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="6" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="B27" s="6">
         <v>5</v>
@@ -6508,7 +7590,7 @@
       </c>
       <c r="C30" s="6">
         <f>AVERAGE(C23:C27)</f>
-        <v>13.2</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -6516,11 +7598,11 @@
         <v>38</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="C33" s="7">
         <f>AVERAGE(C2:C7,C13:C17,C23:C27)</f>
-        <v>14.5625</v>
+        <v>14.8125</v>
       </c>
     </row>
   </sheetData>
@@ -6529,7 +7611,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C32"/>
@@ -6702,7 +7784,7 @@
         <v>7</v>
       </c>
       <c r="C18" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -6724,12 +7806,12 @@
       </c>
       <c r="C21" s="4">
         <f>AVERAGE(C10:C18)</f>
-        <v>13.7777777777778</v>
+        <v>13.8888888888889</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="6" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="B24" s="6">
         <v>4</v>
@@ -6740,7 +7822,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="6" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B25" s="6">
         <v>4</v>
@@ -6751,7 +7833,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="6" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="B26" s="6">
         <v>7</v>
@@ -6787,11 +7869,11 @@
         <v>38</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="C32" s="7">
         <f>AVERAGE(C2:C4,C10:C18,C24:C26)</f>
-        <v>13.7333333333333</v>
+        <v>13.8</v>
       </c>
     </row>
   </sheetData>
@@ -6800,10 +7882,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="13.75" customWidth="1"/>
@@ -6824,7 +7906,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B2" s="2">
         <v>1</v>
@@ -6835,7 +7917,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B3" s="2">
         <v>1</v>
@@ -6846,7 +7928,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B4" s="2">
         <v>2</v>
@@ -6857,7 +7939,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B5" s="2">
         <v>2</v>
@@ -6868,7 +7950,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B6" s="2">
         <v>2</v>
@@ -6879,7 +7961,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B7" s="2">
         <v>3</v>
@@ -6890,7 +7972,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="B8" s="2">
         <v>3</v>
@@ -6901,7 +7983,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B9" s="2">
         <v>3</v>
@@ -6912,7 +7994,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B10" s="2">
         <v>3</v>
@@ -6923,7 +8005,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B11" s="2">
         <v>3</v>
@@ -6934,7 +8016,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="B12" s="2">
         <v>3</v>
@@ -6945,7 +8027,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B13" s="2">
         <v>4</v>
@@ -6978,7 +8060,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B19" s="4">
         <v>3</v>
@@ -6989,19 +8071,25 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="B20" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C20" s="4">
         <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
+      <c r="A21" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" s="4">
+        <v>4</v>
+      </c>
+      <c r="C21" s="4">
+        <v>14</v>
+      </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="4"/>
@@ -7009,42 +8097,36 @@
       <c r="C22" s="4"/>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B23" s="4" t="s">
+      <c r="A23" s="4"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B24" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C23" s="4">
-        <f>AVERAGE(C19:C20)</f>
-        <v>14.5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="B26" s="6">
-        <v>3</v>
-      </c>
-      <c r="C26" s="6">
-        <v>11</v>
+      <c r="C24" s="4">
+        <f>AVERAGE(C19:C21)</f>
+        <v>14.3333333333333</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="6" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="B27" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C27" s="6">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="6" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="B28" s="6">
         <v>4</v>
@@ -7054,9 +8136,15 @@
       </c>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="6"/>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
+      <c r="A29" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B29" s="6">
+        <v>4</v>
+      </c>
+      <c r="C29" s="6">
+        <v>12</v>
+      </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="6"/>
@@ -7064,27 +8152,32 @@
       <c r="C30" s="6"/>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B31" s="6" t="s">
+      <c r="A31" s="6"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B32" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C31" s="6">
-        <f>AVERAGE(C26:C28)</f>
+      <c r="C32" s="6">
+        <f>AVERAGE(C27:C29)</f>
         <v>11.6666666666667</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="7" t="s">
+    <row r="35" spans="1:3">
+      <c r="A35" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B34" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="C34" s="7">
-        <f>AVERAGE(C2:C13,C19:C20,C26:C28)</f>
-        <v>14.1176470588235</v>
+      <c r="B35" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C35" s="7">
+        <f>AVERAGE(C2:C13,C19:C21,C27:C29)</f>
+        <v>14.1111111111111</v>
       </c>
     </row>
   </sheetData>
@@ -7093,10 +8186,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
@@ -7117,7 +8210,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="B2" s="2">
         <v>1</v>
@@ -7128,7 +8221,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="B3" s="2">
         <v>1</v>
@@ -7139,7 +8232,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="B4" s="2">
         <v>2</v>
@@ -7150,7 +8243,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="B5" s="2">
         <v>2</v>
@@ -7161,7 +8254,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="B6" s="2">
         <v>4</v>
@@ -7194,7 +8287,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="B12" s="4">
         <v>2</v>
@@ -7205,7 +8298,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="B13" s="4">
         <v>2</v>
@@ -7216,10 +8309,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B14" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C14" s="4">
         <v>12</v>
@@ -7227,669 +8320,79 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="B15" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C15" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B16" s="4">
-        <v>4</v>
-      </c>
-      <c r="C16" s="4">
-        <v>12</v>
-      </c>
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B17" s="4">
-        <v>5</v>
-      </c>
-      <c r="C17" s="4">
-        <v>13</v>
-      </c>
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B18" s="4">
-        <v>5</v>
+        <v>12</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C18" s="4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B19" s="4">
-        <v>6</v>
-      </c>
-      <c r="C19" s="4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
+        <f>AVERAGE(C12:C15)</f>
+        <v>12.5</v>
+      </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
+      <c r="A21" s="6"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C22" s="4">
-        <f>AVERAGE(C12:C19)</f>
-        <v>12.25</v>
-      </c>
+      <c r="A22" s="6"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="6"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="6"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="B25" s="6">
-        <v>2</v>
-      </c>
-      <c r="C25" s="6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="B26" s="6">
-        <v>5</v>
-      </c>
-      <c r="C26" s="6">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="6"/>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
+        <v>12</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C25" s="6" t="e">
+        <f>AVERAGE(C21,C22)</f>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="6"/>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="C29" s="6">
-        <f>AVERAGE(C25,C26)</f>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="7" t="s">
+      <c r="A28" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B32" s="7" t="s">
+      <c r="B28" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C32" s="7">
-        <f>AVERAGE(C2:C6,C12:C19,C25:C26)</f>
-        <v>12.3333333333333</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:D47"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
-  <cols>
-    <col min="1" max="1" width="17.875" customWidth="1"/>
-    <col min="4" max="4" width="12.625"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="2">
-        <v>1</v>
-      </c>
-      <c r="D2" s="2">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="2">
-        <v>1</v>
-      </c>
-      <c r="D3" s="2">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="2">
-        <v>1</v>
-      </c>
-      <c r="D4" s="2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="2">
-        <v>2</v>
-      </c>
-      <c r="D5" s="2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="2">
-        <v>2</v>
-      </c>
-      <c r="D6" s="2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="2">
-        <v>2</v>
-      </c>
-      <c r="D7" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="2">
-        <v>2</v>
-      </c>
-      <c r="D8" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="2">
-        <v>3</v>
-      </c>
-      <c r="D9" s="2">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" s="2">
-        <v>3</v>
-      </c>
-      <c r="D10" s="2">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="2">
-        <v>3</v>
-      </c>
-      <c r="D11" s="2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" s="2">
-        <v>3</v>
-      </c>
-      <c r="D12" s="2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="2">
-        <v>3</v>
-      </c>
-      <c r="D13" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" s="2">
-        <v>3</v>
-      </c>
-      <c r="D14" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15" s="2">
-        <v>4</v>
-      </c>
-      <c r="D15" s="2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C16" s="2">
-        <v>5</v>
-      </c>
-      <c r="D16" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" s="2">
-        <v>5</v>
-      </c>
-      <c r="D17" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2">
-        <f>AVERAGE(D2:D17)</f>
-        <v>14.875</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C23" s="4">
-        <v>2</v>
-      </c>
-      <c r="D23" s="4">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C24" s="4">
-        <v>3</v>
-      </c>
-      <c r="D24" s="4">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C25" s="4">
-        <v>3</v>
-      </c>
-      <c r="D25" s="4">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C26" s="4">
-        <v>3</v>
-      </c>
-      <c r="D26" s="4">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C27" s="4">
-        <v>4</v>
-      </c>
-      <c r="D27" s="4">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C28" s="4">
-        <v>4</v>
-      </c>
-      <c r="D28" s="4">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C29" s="4">
-        <v>6</v>
-      </c>
-      <c r="D29" s="4">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="4"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="4"/>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4">
-        <f>AVERAGE(D23:D29)</f>
-        <v>14.7142857142857</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C35" s="6">
-        <v>3</v>
-      </c>
-      <c r="D35" s="6">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C36" s="6">
-        <v>4</v>
-      </c>
-      <c r="D36" s="6">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
-      <c r="A37" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C37" s="6">
-        <v>4</v>
-      </c>
-      <c r="D37" s="6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
-      <c r="A38" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C38" s="6">
-        <v>4</v>
-      </c>
-      <c r="D38" s="6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C39" s="6">
-        <v>4</v>
-      </c>
-      <c r="D39" s="6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
-      <c r="A40" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C40" s="6">
-        <v>6</v>
-      </c>
-      <c r="D40" s="6">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
-      <c r="A41" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C41" s="6">
-        <v>8</v>
-      </c>
-      <c r="D41" s="6">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
-      <c r="A42" s="6"/>
-      <c r="B42" s="6"/>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6"/>
-    </row>
-    <row r="43" spans="1:4">
-      <c r="A43" s="6"/>
-      <c r="B43" s="6"/>
-      <c r="C43" s="6"/>
-      <c r="D43" s="6"/>
-    </row>
-    <row r="44" spans="1:4">
-      <c r="A44" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C44" s="6"/>
-      <c r="D44" s="6">
-        <f>AVERAGE(D35:D41)</f>
-        <v>12.8571428571429</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
-      <c r="A47" t="s">
-        <v>38</v>
-      </c>
-      <c r="D47">
-        <f>AVERAGE(D2:D17,D23:D29,D35:D41)</f>
-        <v>14.3666666666667</v>
+      <c r="C28" s="7">
+        <f>AVERAGE(C2:C6,C12:C15,C21:C22)</f>
+        <v>13.2222222222222</v>
       </c>
     </row>
   </sheetData>

--- a/src/utils/sxsyzlzq/zzz_cardList.xlsx
+++ b/src/utils/sxsyzlzq/zzz_cardList.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28245" windowHeight="12345" activeTab="4"/>
+    <workbookView windowWidth="28245" windowHeight="12345" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="伊萝莲" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="149">
   <si>
     <t>名称</t>
   </si>
@@ -122,7 +122,7 @@
     <t>百花长枪·卡罗琳</t>
   </si>
   <si>
-    <t>流星7号</t>
+    <t>流星-7号</t>
   </si>
   <si>
     <t>明日香·露娜</t>
@@ -149,12 +149,12 @@
     <t>学仆-观测型</t>
   </si>
   <si>
+    <t>箭竹守卫</t>
+  </si>
+  <si>
     <t>卜命道长</t>
   </si>
   <si>
-    <t>箭竹守卫</t>
-  </si>
-  <si>
     <t>白羊药师</t>
   </si>
   <si>
@@ -191,40 +191,61 @@
     <t>流岚刃·琳</t>
   </si>
   <si>
+    <t>九天玄女·轩</t>
+  </si>
+  <si>
+    <t>上宝沁金耙</t>
+  </si>
+  <si>
+    <t>火蛇巫女</t>
+  </si>
+  <si>
+    <t>执剑道人</t>
+  </si>
+  <si>
+    <t>神机玄女·轩</t>
+  </si>
+  <si>
+    <t>暗潮涌动</t>
+  </si>
+  <si>
+    <t>心灵黑洞</t>
+  </si>
+  <si>
+    <t>狡诈学徒</t>
+  </si>
+  <si>
+    <t>黑夜突袭</t>
+  </si>
+  <si>
+    <t>热血矿工</t>
+  </si>
+  <si>
+    <t>不法交易</t>
+  </si>
+  <si>
+    <t>红海猎魔人</t>
+  </si>
+  <si>
+    <t>海神赐福</t>
+  </si>
+  <si>
+    <t>学仆-猛禽型</t>
+  </si>
+  <si>
+    <t>黑金诈术师</t>
+  </si>
+  <si>
+    <t>圣僧·法海</t>
+  </si>
+  <si>
     <t>流星七号</t>
   </si>
   <si>
-    <t>九天玄女·轩</t>
-  </si>
-  <si>
-    <t>上宝沁金耙</t>
-  </si>
-  <si>
-    <t>火蛇巫女</t>
-  </si>
-  <si>
-    <t>执剑道人</t>
-  </si>
-  <si>
-    <t>神机玄女·轩</t>
-  </si>
-  <si>
-    <t>暗潮涌动</t>
-  </si>
-  <si>
-    <t>心灵黑洞</t>
-  </si>
-  <si>
-    <t>狡诈学徒</t>
-  </si>
-  <si>
-    <t>黑夜突袭</t>
-  </si>
-  <si>
-    <t>热血矿工</t>
-  </si>
-  <si>
-    <t>不法交易</t>
+    <t>赤影·艾希尔</t>
+  </si>
+  <si>
+    <t>滑板少年·迪宁</t>
   </si>
   <si>
     <t>曙光·安娜贝尔</t>
@@ -1561,7 +1582,7 @@
         <v>5</v>
       </c>
       <c r="D8" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1575,7 +1596,7 @@
         <v>5</v>
       </c>
       <c r="D9" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1600,7 +1621,7 @@
       <c r="C12" s="2"/>
       <c r="D12" s="2">
         <f>AVERAGE(D2:D9)</f>
-        <v>15.375</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1850,7 +1871,7 @@
         <v>4</v>
       </c>
       <c r="D35" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -1959,7 +1980,7 @@
       <c r="C44" s="6"/>
       <c r="D44" s="6">
         <f>AVERAGE(D34:D41)</f>
-        <v>13</v>
+        <v>13.125</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1970,7 +1991,7 @@
       <c r="C47" s="7"/>
       <c r="D47" s="7">
         <f>AVERAGE(D2:D9,D15:D28,D34:D41)</f>
-        <v>14.2333333333333</v>
+        <v>14.3666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -2020,7 +2041,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
@@ -2034,7 +2055,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
@@ -2048,7 +2069,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -2062,7 +2083,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>5</v>
@@ -2118,7 +2139,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>5</v>
@@ -2146,7 +2167,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>5</v>
@@ -2160,7 +2181,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>5</v>
@@ -2174,7 +2195,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>5</v>
@@ -2283,7 +2304,7 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="4" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>15</v>
@@ -2311,7 +2332,7 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="4" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>15</v>
@@ -2325,7 +2346,7 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="4" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>15</v>
@@ -2406,7 +2427,7 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>29</v>
@@ -2434,7 +2455,7 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="6" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>29</v>
@@ -2541,7 +2562,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>5</v>
@@ -2555,7 +2576,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
@@ -2569,7 +2590,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
@@ -2583,7 +2604,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -2639,7 +2660,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>5</v>
@@ -2653,7 +2674,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>5</v>
@@ -2709,7 +2730,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>5</v>
@@ -2737,7 +2758,7 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>5</v>
@@ -2776,7 +2797,7 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="4" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>15</v>
@@ -2790,7 +2811,7 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="4" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>15</v>
@@ -2818,7 +2839,7 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="4" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>15</v>
@@ -2832,7 +2853,7 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="4" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>15</v>
@@ -2846,7 +2867,7 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="4" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>15</v>
@@ -2874,7 +2895,7 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="4" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>15</v>
@@ -2888,7 +2909,7 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="4" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>15</v>
@@ -2902,7 +2923,7 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="4" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>15</v>
@@ -2916,7 +2937,7 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="4" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>15</v>
@@ -2956,7 +2977,7 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="6" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>29</v>
@@ -2970,7 +2991,7 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>29</v>
@@ -2984,7 +3005,7 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>29</v>
@@ -2998,7 +3019,7 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="6" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>29</v>
@@ -3078,7 +3099,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>5</v>
@@ -3092,7 +3113,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
@@ -3120,7 +3141,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -3134,7 +3155,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>5</v>
@@ -3148,7 +3169,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>5</v>
@@ -3190,7 +3211,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>5</v>
@@ -3204,7 +3225,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>5</v>
@@ -3285,7 +3306,7 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="4" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>15</v>
@@ -3341,7 +3362,7 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="4" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>15</v>
@@ -3355,7 +3376,7 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="4" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>15</v>
@@ -3383,7 +3404,7 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="4" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>15</v>
@@ -3397,7 +3418,7 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="4" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>15</v>
@@ -3411,7 +3432,7 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="4" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>15</v>
@@ -3439,7 +3460,7 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="4" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>15</v>
@@ -3492,7 +3513,7 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="6" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>29</v>
@@ -3520,7 +3541,7 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="6" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>29</v>
@@ -3612,7 +3633,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>5</v>
@@ -3626,7 +3647,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
@@ -3640,7 +3661,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
@@ -3654,7 +3675,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -3668,7 +3689,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>5</v>
@@ -3724,7 +3745,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>5</v>
@@ -3738,7 +3759,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>5</v>
@@ -3752,7 +3773,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>5</v>
@@ -3794,7 +3815,7 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>5</v>
@@ -3822,7 +3843,7 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>5</v>
@@ -3861,7 +3882,7 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="4" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>15</v>
@@ -3875,7 +3896,7 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="4" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>15</v>
@@ -3903,7 +3924,7 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="4" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>15</v>
@@ -3917,7 +3938,7 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="4" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>15</v>
@@ -3931,7 +3952,7 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="4" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>15</v>
@@ -3959,7 +3980,7 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="4" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>15</v>
@@ -3973,7 +3994,7 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="4" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>15</v>
@@ -3987,7 +4008,7 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="4" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>15</v>
@@ -4001,7 +4022,7 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="4" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>15</v>
@@ -4041,7 +4062,7 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="6" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>29</v>
@@ -4055,7 +4076,7 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>29</v>
@@ -4069,7 +4090,7 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="6" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>29</v>
@@ -4138,7 +4159,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -4147,15 +4168,15 @@
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -4169,10 +4190,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>5</v>
@@ -4186,10 +4207,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>5</v>
@@ -4206,7 +4227,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>5</v>
@@ -4220,10 +4241,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="3" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>15</v>
@@ -4240,7 +4261,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>15</v>
@@ -4254,10 +4275,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="4" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>15</v>
@@ -4271,10 +4292,10 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>5</v>
@@ -4291,7 +4312,7 @@
         <v>39</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>5</v>
@@ -4308,7 +4329,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>5</v>
@@ -4322,10 +4343,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>5</v>
@@ -4342,7 +4363,7 @@
         <v>8</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>5</v>
@@ -4356,10 +4377,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="4" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>15</v>
@@ -4373,10 +4394,10 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>118</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>111</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>15</v>
@@ -4393,7 +4414,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>15</v>
@@ -4410,7 +4431,7 @@
         <v>18</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>15</v>
@@ -4427,7 +4448,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>15</v>
@@ -4441,10 +4462,10 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>29</v>
@@ -4458,10 +4479,10 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>29</v>
@@ -4475,10 +4496,10 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>29</v>
@@ -4492,10 +4513,10 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>5</v>
@@ -4512,7 +4533,7 @@
         <v>9</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>5</v>
@@ -4529,7 +4550,7 @@
         <v>10</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>5</v>
@@ -4543,10 +4564,10 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="4" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>15</v>
@@ -4560,10 +4581,10 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="4" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>15</v>
@@ -4580,7 +4601,7 @@
         <v>20</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>15</v>
@@ -4597,7 +4618,7 @@
         <v>19</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>15</v>
@@ -4611,10 +4632,10 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="4" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>15</v>
@@ -4628,10 +4649,10 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="4" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>15</v>
@@ -4645,10 +4666,10 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="4" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>15</v>
@@ -4662,10 +4683,10 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>29</v>
@@ -4679,10 +4700,10 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>29</v>
@@ -4696,10 +4717,10 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>29</v>
@@ -4713,10 +4734,10 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>5</v>
@@ -4730,10 +4751,10 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="4" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>15</v>
@@ -4747,10 +4768,10 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="4" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>15</v>
@@ -4764,10 +4785,10 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="4" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>15</v>
@@ -4784,7 +4805,7 @@
         <v>21</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>15</v>
@@ -4798,10 +4819,10 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="4" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>15</v>
@@ -4815,10 +4836,10 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="4" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>15</v>
@@ -4835,7 +4856,7 @@
         <v>22</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>15</v>
@@ -4849,10 +4870,10 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>29</v>
@@ -4866,10 +4887,10 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>29</v>
@@ -4886,7 +4907,7 @@
         <v>11</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>5</v>
@@ -4900,10 +4921,10 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="4" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>15</v>
@@ -4920,7 +4941,7 @@
         <v>23</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>15</v>
@@ -4934,10 +4955,10 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="4" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>15</v>
@@ -4951,10 +4972,10 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>29</v>
@@ -4968,10 +4989,10 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="4" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>15</v>
@@ -4988,7 +5009,7 @@
         <v>25</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>15</v>
@@ -5002,10 +5023,10 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>29</v>
@@ -5019,10 +5040,10 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>29</v>
@@ -5036,10 +5057,10 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="4" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>15</v>
@@ -5053,10 +5074,10 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="4" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>15</v>
@@ -5070,10 +5091,10 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="4" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>15</v>
@@ -5087,10 +5108,10 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="4" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>15</v>
@@ -5107,7 +5128,7 @@
         <v>26</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>15</v>
@@ -5156,7 +5177,7 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -5176,7 +5197,7 @@
       </c>
       <c r="B66" s="2"/>
       <c r="C66" s="2" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" s="2">
@@ -5326,7 +5347,7 @@
         <v>5</v>
       </c>
       <c r="D9" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -5340,7 +5361,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -5365,7 +5386,7 @@
       <c r="C13" s="2"/>
       <c r="D13" s="2">
         <f>AVERAGE(D2:D10)</f>
-        <v>15.1111111111111</v>
+        <v>15.4444444444444</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -5614,7 +5635,7 @@
         <v>4</v>
       </c>
       <c r="D36" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -5709,7 +5730,7 @@
       <c r="C44" s="6"/>
       <c r="D44" s="6">
         <f>AVERAGE(D35:D41)</f>
-        <v>13</v>
+        <v>13.1428571428571</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -5718,7 +5739,7 @@
       </c>
       <c r="D47">
         <f>AVERAGE(D2:D10,D16:D29,D35:D41)</f>
-        <v>14.2333333333333</v>
+        <v>14.3666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -5763,7 +5784,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -5777,7 +5798,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -5875,7 +5896,7 @@
         <v>2</v>
       </c>
       <c r="D10" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -5942,7 +5963,7 @@
       <c r="C16" s="2"/>
       <c r="D16" s="2">
         <f>AVERAGE(D2:D13)</f>
-        <v>15.0833333333333</v>
+        <v>14.9166666666667</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -6150,12 +6171,12 @@
         <v>3</v>
       </c>
       <c r="D36" s="6">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="6" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>29</v>
@@ -6169,7 +6190,7 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>29</v>
@@ -6183,7 +6204,7 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>29</v>
@@ -6211,7 +6232,7 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>29</v>
@@ -6245,7 +6266,7 @@
       <c r="C44" s="6"/>
       <c r="D44" s="6">
         <f>AVERAGE(D36:D41)</f>
-        <v>12.1666666666667</v>
+        <v>12.3333333333333</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -6256,7 +6277,7 @@
       <c r="C47" s="7"/>
       <c r="D47" s="7">
         <f>AVERAGE(D2:D13,D19:D30,D36:D41)</f>
-        <v>14.0666666666667</v>
+        <v>14.0333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -6291,7 +6312,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>5</v>
@@ -6319,7 +6340,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
@@ -6333,7 +6354,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -6342,12 +6363,12 @@
         <v>2</v>
       </c>
       <c r="D5" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>5</v>
@@ -6361,7 +6382,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>5</v>
@@ -6370,7 +6391,7 @@
         <v>2</v>
       </c>
       <c r="D7" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -6389,7 +6410,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>58</v>
+        <v>9</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>5</v>
@@ -6398,12 +6419,12 @@
         <v>3</v>
       </c>
       <c r="D9" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>9</v>
+        <v>57</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>5</v>
@@ -6412,7 +6433,7 @@
         <v>3</v>
       </c>
       <c r="D10" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -6496,7 +6517,7 @@
         <v>5</v>
       </c>
       <c r="D16" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -6510,7 +6531,7 @@
         <v>5</v>
       </c>
       <c r="D17" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -6535,7 +6556,7 @@
       <c r="C20" s="2"/>
       <c r="D20" s="2">
         <f>AVERAGE(D2:D17)</f>
-        <v>14.875</v>
+        <v>15.1875</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -6605,7 +6626,7 @@
         <v>4</v>
       </c>
       <c r="D27" s="4">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -6658,7 +6679,7 @@
       <c r="C32" s="4"/>
       <c r="D32" s="4">
         <f>AVERAGE(D23:D29)</f>
-        <v>14.7142857142857</v>
+        <v>14.8571428571429</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -6686,12 +6707,12 @@
         <v>4</v>
       </c>
       <c r="D36" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="6" t="s">
-        <v>59</v>
+        <v>32</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>29</v>
@@ -6705,7 +6726,7 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>29</v>
@@ -6719,7 +6740,7 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="6" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>29</v>
@@ -6781,7 +6802,7 @@
       <c r="C44" s="6"/>
       <c r="D44" s="6">
         <f>AVERAGE(D35:D41)</f>
-        <v>12.8571428571429</v>
+        <v>13</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -6790,7 +6811,7 @@
       </c>
       <c r="D47">
         <f>AVERAGE(D2:D17,D23:D29,D35:D41)</f>
-        <v>14.3666666666667</v>
+        <v>14.6</v>
       </c>
     </row>
   </sheetData>
@@ -6802,7 +6823,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="17.875" customWidth="1"/>
@@ -6825,7 +6846,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>5</v>
@@ -6839,7 +6860,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
@@ -6853,7 +6874,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
@@ -6909,7 +6930,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>5</v>
@@ -6923,7 +6944,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>5</v>
@@ -6937,7 +6958,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>5</v>
@@ -6951,7 +6972,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>5</v>
@@ -6965,7 +6986,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>5</v>
@@ -7048,30 +7069,30 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="4" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C21" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D21" s="4">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="4" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C22" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D22" s="4">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -7118,21 +7139,21 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="4" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C26" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D26" s="4">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="4" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>15</v>
@@ -7141,43 +7162,51 @@
         <v>4</v>
       </c>
       <c r="D27" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C28" s="4">
+        <v>4</v>
+      </c>
+      <c r="D28" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B28" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C28" s="4">
-        <v>5</v>
-      </c>
-      <c r="D28" s="4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" s="4" t="s">
+      <c r="B29" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C29" s="4">
+        <v>5</v>
+      </c>
+      <c r="D29" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B29" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C29" s="4">
+      <c r="B30" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="4">
         <v>7</v>
       </c>
-      <c r="D29" s="4">
-        <v>15</v>
-      </c>
-      <c r="F29" s="5"/>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="4"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
+      <c r="D30" s="4">
+        <v>15</v>
+      </c>
+      <c r="F30" s="5"/>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="4"/>
@@ -7186,51 +7215,43 @@
       <c r="D31" s="4"/>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B32" s="4" t="s">
+      <c r="A32" s="4"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B33" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4">
-        <f>AVERAGE(D18:D29)</f>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="33" customFormat="1"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4">
+        <f>AVERAGE(D18:D30)</f>
+        <v>13.3076923076923</v>
+      </c>
+    </row>
     <row r="34" customFormat="1"/>
-    <row r="35" spans="1:4">
-      <c r="A35" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C35" s="6">
-        <v>3</v>
-      </c>
-      <c r="D35" s="6">
-        <v>11</v>
-      </c>
-    </row>
+    <row r="35" customFormat="1"/>
     <row r="36" spans="1:4">
       <c r="A36" s="6" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C36" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D36" s="6">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="6" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>29</v>
@@ -7239,12 +7260,12 @@
         <v>4</v>
       </c>
       <c r="D37" s="6">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="6" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>29</v>
@@ -7272,23 +7293,31 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="6" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C40" s="6">
+        <v>6</v>
+      </c>
+      <c r="D40" s="6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C41" s="6">
         <v>7</v>
       </c>
-      <c r="D40" s="6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
-      <c r="A41" s="6"/>
-      <c r="B41" s="6"/>
-      <c r="C41" s="6"/>
-      <c r="D41" s="6"/>
+      <c r="D41" s="6">
+        <v>12</v>
+      </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="6"/>
@@ -7297,29 +7326,35 @@
       <c r="D42" s="6"/>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B43" s="6" t="s">
+      <c r="A43" s="6"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B44" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C43" s="6"/>
-      <c r="D43" s="6">
-        <f>AVERAGE(D35:D40)</f>
-        <v>12.1666666666667</v>
-      </c>
-    </row>
-    <row r="44" customFormat="1"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6">
+        <f>AVERAGE(D36:D41)</f>
+        <v>12.3333333333333</v>
+      </c>
+    </row>
     <row r="45" customFormat="1"/>
-    <row r="46" spans="1:4">
-      <c r="A46" s="7" t="s">
+    <row r="46" customFormat="1"/>
+    <row r="47" spans="1:4">
+      <c r="A47" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B46" s="7"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="7">
-        <f>AVERAGE(D2:D12,D18:D29,D35:D40)</f>
-        <v>13.1379310344828</v>
+      <c r="B47" s="7"/>
+      <c r="C47" s="7"/>
+      <c r="D47" s="7">
+        <f>AVERAGE(D2:D12,D18:D30,D36:D41)</f>
+        <v>12.9</v>
       </c>
     </row>
   </sheetData>
@@ -7518,7 +7553,7 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="6" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B23" s="6">
         <v>1</v>
@@ -7529,7 +7564,7 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="6" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="B24" s="6">
         <v>2</v>
@@ -7540,7 +7575,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="6" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="B25" s="6">
         <v>2</v>
@@ -7551,7 +7586,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="6" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="B26" s="6">
         <v>2</v>
@@ -7562,7 +7597,7 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="6" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="B27" s="6">
         <v>5</v>
@@ -7598,7 +7633,7 @@
         <v>38</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="C33" s="7">
         <f>AVERAGE(C2:C7,C13:C17,C23:C27)</f>
@@ -7811,7 +7846,7 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="6" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="B24" s="6">
         <v>4</v>
@@ -7822,7 +7857,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="6" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="B25" s="6">
         <v>4</v>
@@ -7833,7 +7868,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="6" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B26" s="6">
         <v>7</v>
@@ -7869,7 +7904,7 @@
         <v>38</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C32" s="7">
         <f>AVERAGE(C2:C4,C10:C18,C24:C26)</f>
@@ -7906,7 +7941,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B2" s="2">
         <v>1</v>
@@ -7917,7 +7952,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B3" s="2">
         <v>1</v>
@@ -8016,7 +8051,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="B12" s="2">
         <v>3</v>
@@ -8121,12 +8156,12 @@
         <v>3</v>
       </c>
       <c r="C27" s="6">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B28" s="6">
         <v>4</v>
@@ -8137,7 +8172,7 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="6" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="B29" s="6">
         <v>4</v>
@@ -8165,7 +8200,7 @@
       </c>
       <c r="C32" s="6">
         <f>AVERAGE(C27:C29)</f>
-        <v>11.6666666666667</v>
+        <v>12</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -8173,11 +8208,11 @@
         <v>38</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C35" s="7">
         <f>AVERAGE(C2:C13,C19:C21,C27:C29)</f>
-        <v>14.1111111111111</v>
+        <v>14.1666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -8210,7 +8245,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="B2" s="2">
         <v>1</v>
@@ -8221,7 +8256,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="B3" s="2">
         <v>1</v>
@@ -8232,7 +8267,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B4" s="2">
         <v>2</v>
@@ -8243,7 +8278,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="B5" s="2">
         <v>2</v>
@@ -8254,7 +8289,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B6" s="2">
         <v>4</v>
@@ -8287,7 +8322,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="B12" s="4">
         <v>2</v>
@@ -8298,7 +8333,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="B13" s="4">
         <v>2</v>
@@ -8309,7 +8344,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="B14" s="4">
         <v>4</v>
@@ -8320,7 +8355,7 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="B15" s="4">
         <v>5</v>
@@ -8376,7 +8411,7 @@
         <v>12</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C25" s="6" t="e">
         <f>AVERAGE(C21,C22)</f>
@@ -8388,7 +8423,7 @@
         <v>38</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="C28" s="7">
         <f>AVERAGE(C2:C6,C12:C15,C21:C22)</f>

--- a/src/utils/sxsyzlzq/zzz_cardList.xlsx
+++ b/src/utils/sxsyzlzq/zzz_cardList.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28245" windowHeight="12345" activeTab="3"/>
+    <workbookView windowWidth="28800" windowHeight="13380" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="伊萝莲" sheetId="1" r:id="rId1"/>
@@ -77,6 +77,9 @@
     <t>紫色</t>
   </si>
   <si>
+    <t>四芒军旗</t>
+  </si>
+  <si>
     <t>圣殿御卫</t>
   </si>
   <si>
@@ -149,207 +152,207 @@
     <t>学仆-观测型</t>
   </si>
   <si>
+    <t>卜命道长</t>
+  </si>
+  <si>
+    <t>白羊药师</t>
+  </si>
+  <si>
+    <t>树木之怒</t>
+  </si>
+  <si>
+    <t>苦行武僧</t>
+  </si>
+  <si>
+    <t>执剑道者</t>
+  </si>
+  <si>
+    <t>铁山靠</t>
+  </si>
+  <si>
+    <t>连击</t>
+  </si>
+  <si>
+    <t>深山采药人</t>
+  </si>
+  <si>
+    <t>风铃道人</t>
+  </si>
+  <si>
+    <t>扫叶僧</t>
+  </si>
+  <si>
+    <t>驱魔道人</t>
+  </si>
+  <si>
+    <t>御风武者</t>
+  </si>
+  <si>
+    <t>流岚刃·琳</t>
+  </si>
+  <si>
+    <t>九天玄女·轩</t>
+  </si>
+  <si>
+    <t>上宝沁金耙</t>
+  </si>
+  <si>
+    <t>火蛇巫女</t>
+  </si>
+  <si>
+    <t>执剑道人</t>
+  </si>
+  <si>
+    <t>神机玄女·轩</t>
+  </si>
+  <si>
+    <t>暗潮涌动</t>
+  </si>
+  <si>
+    <t>心灵黑洞</t>
+  </si>
+  <si>
+    <t>狡诈学徒</t>
+  </si>
+  <si>
+    <t>黑夜突袭</t>
+  </si>
+  <si>
+    <t>热血矿工</t>
+  </si>
+  <si>
+    <t>不法交易</t>
+  </si>
+  <si>
+    <t>红海猎魔人</t>
+  </si>
+  <si>
+    <t>海神赐福</t>
+  </si>
+  <si>
+    <t>学仆-猛禽型</t>
+  </si>
+  <si>
+    <t>黑金诈术师</t>
+  </si>
+  <si>
+    <t>圣僧·法海</t>
+  </si>
+  <si>
+    <t>流星七号</t>
+  </si>
+  <si>
+    <t>赤影·艾希尔</t>
+  </si>
+  <si>
+    <t>滑板少年·迪宁</t>
+  </si>
+  <si>
+    <t>曙光·安娜贝尔</t>
+  </si>
+  <si>
+    <t>圣枪·卡罗琳</t>
+  </si>
+  <si>
+    <t>明日之音·露娜</t>
+  </si>
+  <si>
+    <t>正阳大主教·伊恩</t>
+  </si>
+  <si>
+    <t>钢铁统帅·雷蒙德</t>
+  </si>
+  <si>
+    <t>帝国卡等：</t>
+  </si>
+  <si>
+    <t>鬼童7号</t>
+  </si>
+  <si>
+    <t>No.2时光·米拉</t>
+  </si>
+  <si>
+    <t>No.6沃凡瑞拉</t>
+  </si>
+  <si>
+    <t>隐秘卡等：</t>
+  </si>
+  <si>
+    <t>疾风猎手</t>
+  </si>
+  <si>
+    <t>悟能禅杖</t>
+  </si>
+  <si>
+    <t>帝禅意卡等：</t>
+  </si>
+  <si>
+    <t>冥河守卫</t>
+  </si>
+  <si>
+    <t>落雷击</t>
+  </si>
+  <si>
+    <t>邪眼魔</t>
+  </si>
+  <si>
+    <t>残暴爪钩</t>
+  </si>
+  <si>
+    <t>烈焰风暴</t>
+  </si>
+  <si>
+    <t>碎颅魔</t>
+  </si>
+  <si>
+    <t>觅食大嘴兽</t>
+  </si>
+  <si>
+    <t>灼神双炎</t>
+  </si>
+  <si>
+    <t>雷光炼狱</t>
+  </si>
+  <si>
+    <t>橙色色卡等：</t>
+  </si>
+  <si>
+    <t>炼狱卡等：</t>
+  </si>
+  <si>
+    <t>旅行背包</t>
+  </si>
+  <si>
+    <t>重装固守</t>
+  </si>
+  <si>
+    <t>龟族僧人</t>
+  </si>
+  <si>
+    <t>叶幻师</t>
+  </si>
+  <si>
+    <t>风卷残云</t>
+  </si>
+  <si>
+    <t>祥云师太</t>
+  </si>
+  <si>
+    <t>冲锋装备</t>
+  </si>
+  <si>
+    <t>蟠桃会</t>
+  </si>
+  <si>
+    <t>万物之灵</t>
+  </si>
+  <si>
+    <t>永恒之王·莱哈特</t>
+  </si>
+  <si>
     <t>箭竹守卫</t>
   </si>
   <si>
-    <t>卜命道长</t>
-  </si>
-  <si>
-    <t>白羊药师</t>
-  </si>
-  <si>
-    <t>树木之怒</t>
-  </si>
-  <si>
-    <t>苦行武僧</t>
-  </si>
-  <si>
-    <t>执剑道者</t>
-  </si>
-  <si>
-    <t>铁山靠</t>
-  </si>
-  <si>
-    <t>连击</t>
-  </si>
-  <si>
-    <t>深山采药人</t>
-  </si>
-  <si>
-    <t>风铃道人</t>
-  </si>
-  <si>
-    <t>扫叶僧</t>
-  </si>
-  <si>
-    <t>驱魔道人</t>
-  </si>
-  <si>
-    <t>御风武者</t>
-  </si>
-  <si>
-    <t>流岚刃·琳</t>
-  </si>
-  <si>
-    <t>九天玄女·轩</t>
-  </si>
-  <si>
-    <t>上宝沁金耙</t>
-  </si>
-  <si>
-    <t>火蛇巫女</t>
-  </si>
-  <si>
-    <t>执剑道人</t>
-  </si>
-  <si>
-    <t>神机玄女·轩</t>
-  </si>
-  <si>
-    <t>暗潮涌动</t>
-  </si>
-  <si>
-    <t>心灵黑洞</t>
-  </si>
-  <si>
-    <t>狡诈学徒</t>
-  </si>
-  <si>
-    <t>黑夜突袭</t>
-  </si>
-  <si>
-    <t>热血矿工</t>
-  </si>
-  <si>
-    <t>不法交易</t>
-  </si>
-  <si>
-    <t>红海猎魔人</t>
-  </si>
-  <si>
-    <t>海神赐福</t>
-  </si>
-  <si>
-    <t>学仆-猛禽型</t>
-  </si>
-  <si>
-    <t>黑金诈术师</t>
-  </si>
-  <si>
-    <t>圣僧·法海</t>
-  </si>
-  <si>
-    <t>流星七号</t>
-  </si>
-  <si>
-    <t>赤影·艾希尔</t>
-  </si>
-  <si>
-    <t>滑板少年·迪宁</t>
-  </si>
-  <si>
-    <t>曙光·安娜贝尔</t>
-  </si>
-  <si>
-    <t>圣枪·卡罗琳</t>
-  </si>
-  <si>
-    <t>明日之音·露娜</t>
-  </si>
-  <si>
-    <t>正阳大主教·伊恩</t>
-  </si>
-  <si>
-    <t>钢铁统帅·雷蒙德</t>
-  </si>
-  <si>
-    <t>帝国卡等：</t>
-  </si>
-  <si>
-    <t>鬼童7号</t>
-  </si>
-  <si>
-    <t>No.2时光·米拉</t>
-  </si>
-  <si>
-    <t>No.6沃凡瑞拉</t>
-  </si>
-  <si>
-    <t>隐秘卡等：</t>
-  </si>
-  <si>
-    <t>疾风猎手</t>
-  </si>
-  <si>
-    <t>悟能禅杖</t>
-  </si>
-  <si>
-    <t>帝禅意卡等：</t>
-  </si>
-  <si>
-    <t>冥河守卫</t>
-  </si>
-  <si>
-    <t>落雷击</t>
-  </si>
-  <si>
-    <t>邪眼魔</t>
-  </si>
-  <si>
-    <t>残暴爪钩</t>
-  </si>
-  <si>
-    <t>烈焰风暴</t>
-  </si>
-  <si>
-    <t>碎颅魔</t>
-  </si>
-  <si>
-    <t>觅食大嘴兽</t>
-  </si>
-  <si>
-    <t>灼神双炎</t>
-  </si>
-  <si>
-    <t>雷光炼狱</t>
-  </si>
-  <si>
-    <t>橙色色卡等：</t>
-  </si>
-  <si>
-    <t>炼狱卡等：</t>
-  </si>
-  <si>
-    <t>旅行背包</t>
-  </si>
-  <si>
-    <t>重装固守</t>
-  </si>
-  <si>
-    <t>龟族僧人</t>
-  </si>
-  <si>
-    <t>叶幻师</t>
-  </si>
-  <si>
-    <t>风卷残云</t>
-  </si>
-  <si>
-    <t>祥云师太</t>
-  </si>
-  <si>
-    <t>冲锋装备</t>
-  </si>
-  <si>
-    <t>蟠桃会</t>
-  </si>
-  <si>
-    <t>万物之灵</t>
-  </si>
-  <si>
-    <t>永恒之王·莱哈特</t>
-  </si>
-  <si>
     <t>逍遥琴师</t>
   </si>
   <si>
@@ -387,9 +390,6 @@
   </si>
   <si>
     <t>帝国</t>
-  </si>
-  <si>
-    <t>四芒军旗</t>
   </si>
   <si>
     <t>传记·钢铁守卫</t>
@@ -483,8 +483,8 @@
   <numFmts count="4">
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -536,21 +536,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
@@ -558,46 +543,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -611,16 +559,22 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -635,6 +589,30 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
@@ -642,8 +620,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -657,14 +651,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
@@ -672,9 +658,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -689,7 +689,145 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -701,43 +839,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -749,67 +857,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -821,55 +869,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -880,6 +880,65 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -900,59 +959,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -971,15 +980,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -988,10 +988,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1000,19 +1000,19 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1021,112 +1021,112 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1554,7 +1554,7 @@
         <v>3</v>
       </c>
       <c r="D6" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1621,7 +1621,7 @@
       <c r="C12" s="2"/>
       <c r="D12" s="2">
         <f>AVERAGE(D2:D9)</f>
-        <v>15.75</v>
+        <v>15.875</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1646,10 +1646,10 @@
         <v>15</v>
       </c>
       <c r="C16" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" s="4">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1663,7 +1663,7 @@
         <v>2</v>
       </c>
       <c r="D17" s="4">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1677,7 +1677,7 @@
         <v>2</v>
       </c>
       <c r="D18" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1688,10 +1688,10 @@
         <v>15</v>
       </c>
       <c r="C19" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D19" s="4">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -1705,12 +1705,12 @@
         <v>3</v>
       </c>
       <c r="D20" s="4">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>15</v>
@@ -1719,12 +1719,12 @@
         <v>3</v>
       </c>
       <c r="D21" s="4">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>15</v>
@@ -1733,12 +1733,12 @@
         <v>3</v>
       </c>
       <c r="D22" s="4">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>15</v>
@@ -1752,7 +1752,7 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>15</v>
@@ -1766,7 +1766,7 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>15</v>
@@ -1780,7 +1780,7 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>15</v>
@@ -1794,7 +1794,7 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>15</v>
@@ -1808,7 +1808,7 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>15</v>
@@ -1838,20 +1838,20 @@
         <v>12</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C31" s="4"/>
       <c r="D31" s="4">
         <f>AVERAGE(D15:D28)</f>
-        <v>14.2857142857143</v>
+        <v>14.4285714285714</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C34" s="6">
         <v>3</v>
@@ -1862,10 +1862,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B35" s="6" t="s">
         <v>30</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>29</v>
       </c>
       <c r="C35" s="6">
         <v>4</v>
@@ -1876,10 +1876,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C36" s="6">
         <v>4</v>
@@ -1890,10 +1890,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C37" s="6">
         <v>4</v>
@@ -1904,10 +1904,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C38" s="6">
         <v>5</v>
@@ -1918,10 +1918,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C39" s="6">
         <v>6</v>
@@ -1932,10 +1932,10 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C40" s="6">
         <v>7</v>
@@ -1946,10 +1946,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C41" s="6">
         <v>8</v>
@@ -1975,7 +1975,7 @@
         <v>12</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="6">
@@ -1985,13 +1985,13 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B47" s="7"/>
       <c r="C47" s="7"/>
       <c r="D47" s="7">
         <f>AVERAGE(D2:D9,D15:D28,D34:D41)</f>
-        <v>14.3666666666667</v>
+        <v>14.4666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -2262,7 +2262,7 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>15</v>
@@ -2360,7 +2360,7 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>15</v>
@@ -2389,7 +2389,7 @@
         <v>12</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C32" s="4"/>
       <c r="D32" s="4">
@@ -2399,10 +2399,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C35" s="6">
         <v>3</v>
@@ -2413,10 +2413,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B36" s="6" t="s">
         <v>30</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>29</v>
       </c>
       <c r="C36" s="6">
         <v>4</v>
@@ -2430,7 +2430,7 @@
         <v>55</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C37" s="6">
         <v>4</v>
@@ -2441,10 +2441,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C38" s="6">
         <v>4</v>
@@ -2458,7 +2458,7 @@
         <v>106</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C39" s="6">
         <v>5</v>
@@ -2469,10 +2469,10 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C40" s="6">
         <v>6</v>
@@ -2483,10 +2483,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C41" s="6">
         <v>8</v>
@@ -2512,7 +2512,7 @@
         <v>12</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="6">
@@ -2522,7 +2522,7 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D47">
         <f>AVERAGE(D2:D16,D22:D29,D35:D41)</f>
@@ -2590,7 +2590,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>40</v>
+        <v>107</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
@@ -2839,7 +2839,7 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>15</v>
@@ -2853,7 +2853,7 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>15</v>
@@ -2867,7 +2867,7 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>15</v>
@@ -2923,7 +2923,7 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>15</v>
@@ -2937,7 +2937,7 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>15</v>
@@ -2967,7 +2967,7 @@
         <v>12</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C35" s="4"/>
       <c r="D35" s="4">
@@ -2977,10 +2977,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C38" s="6">
         <v>2</v>
@@ -2994,7 +2994,7 @@
         <v>58</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C39" s="6">
         <v>4</v>
@@ -3008,7 +3008,7 @@
         <v>55</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C40" s="6">
         <v>4</v>
@@ -3019,10 +3019,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C41" s="6">
         <v>5</v>
@@ -3048,7 +3048,7 @@
         <v>12</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="6">
@@ -3058,7 +3058,7 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B47" s="7"/>
       <c r="C47" s="7"/>
@@ -3127,7 +3127,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
@@ -3211,7 +3211,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>5</v>
@@ -3278,7 +3278,7 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>15</v>
@@ -3292,7 +3292,7 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>15</v>
@@ -3320,7 +3320,7 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>15</v>
@@ -3334,7 +3334,7 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>15</v>
@@ -3348,7 +3348,7 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>15</v>
@@ -3362,7 +3362,7 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>15</v>
@@ -3376,7 +3376,7 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>15</v>
@@ -3390,7 +3390,7 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>15</v>
@@ -3432,7 +3432,7 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>15</v>
@@ -3446,7 +3446,7 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>15</v>
@@ -3460,7 +3460,7 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>15</v>
@@ -3474,7 +3474,7 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>15</v>
@@ -3503,7 +3503,7 @@
         <v>12</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C35" s="4"/>
       <c r="D35" s="4">
@@ -3513,10 +3513,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C38" s="6">
         <v>2</v>
@@ -3527,10 +3527,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C39" s="6">
         <v>5</v>
@@ -3541,10 +3541,10 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C40" s="6">
         <v>5</v>
@@ -3555,10 +3555,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C41" s="6">
         <v>7</v>
@@ -3584,7 +3584,7 @@
         <v>12</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="6">
@@ -3594,7 +3594,7 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D47">
         <f>AVERAGE(D2:D11,D17:D32,D38:D41)</f>
@@ -3661,7 +3661,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>40</v>
+        <v>107</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
@@ -3675,7 +3675,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>40</v>
+        <v>107</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -3924,7 +3924,7 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>15</v>
@@ -3938,7 +3938,7 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>15</v>
@@ -3952,7 +3952,7 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>15</v>
@@ -4008,7 +4008,7 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>15</v>
@@ -4022,7 +4022,7 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>15</v>
@@ -4052,7 +4052,7 @@
         <v>12</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C36" s="4"/>
       <c r="D36" s="4">
@@ -4062,10 +4062,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C39" s="6">
         <v>2</v>
@@ -4079,7 +4079,7 @@
         <v>58</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C40" s="6">
         <v>4</v>
@@ -4090,10 +4090,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C41" s="6">
         <v>5</v>
@@ -4119,7 +4119,7 @@
         <v>12</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="6">
@@ -4129,7 +4129,7 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B47" s="7"/>
       <c r="C47" s="7"/>
@@ -4159,7 +4159,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -4168,18 +4168,18 @@
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -4193,7 +4193,7 @@
         <v>98</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>5</v>
@@ -4210,7 +4210,7 @@
         <v>97</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>5</v>
@@ -4227,7 +4227,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>5</v>
@@ -4241,10 +4241,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>120</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>119</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>15</v>
@@ -4261,7 +4261,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>15</v>
@@ -4278,7 +4278,7 @@
         <v>121</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>15</v>
@@ -4295,7 +4295,7 @@
         <v>122</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>5</v>
@@ -4309,10 +4309,10 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>5</v>
@@ -4329,7 +4329,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>5</v>
@@ -4346,7 +4346,7 @@
         <v>123</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>5</v>
@@ -4363,7 +4363,7 @@
         <v>8</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>5</v>
@@ -4380,7 +4380,7 @@
         <v>124</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>15</v>
@@ -4397,7 +4397,7 @@
         <v>125</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>15</v>
@@ -4411,10 +4411,10 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>15</v>
@@ -4428,10 +4428,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>15</v>
@@ -4445,10 +4445,10 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>15</v>
@@ -4465,10 +4465,10 @@
         <v>126</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D19" s="5">
         <v>3</v>
@@ -4482,10 +4482,10 @@
         <v>73</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D20" s="5">
         <v>3</v>
@@ -4499,10 +4499,10 @@
         <v>77</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D21" s="5">
         <v>3</v>
@@ -4516,7 +4516,7 @@
         <v>127</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>5</v>
@@ -4533,7 +4533,7 @@
         <v>9</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>5</v>
@@ -4550,7 +4550,7 @@
         <v>10</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>5</v>
@@ -4567,7 +4567,7 @@
         <v>128</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>15</v>
@@ -4584,7 +4584,7 @@
         <v>129</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>15</v>
@@ -4598,10 +4598,10 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>15</v>
@@ -4615,10 +4615,10 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>15</v>
@@ -4635,7 +4635,7 @@
         <v>130</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>15</v>
@@ -4652,7 +4652,7 @@
         <v>103</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>15</v>
@@ -4669,7 +4669,7 @@
         <v>131</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>15</v>
@@ -4686,10 +4686,10 @@
         <v>79</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D32" s="5">
         <v>4</v>
@@ -4703,10 +4703,10 @@
         <v>74</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D33" s="5">
         <v>4</v>
@@ -4720,10 +4720,10 @@
         <v>75</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D34" s="5">
         <v>4</v>
@@ -4737,7 +4737,7 @@
         <v>132</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>5</v>
@@ -4754,7 +4754,7 @@
         <v>133</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>15</v>
@@ -4771,7 +4771,7 @@
         <v>134</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>15</v>
@@ -4788,7 +4788,7 @@
         <v>135</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>15</v>
@@ -4802,10 +4802,10 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>15</v>
@@ -4822,7 +4822,7 @@
         <v>136</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>15</v>
@@ -4839,7 +4839,7 @@
         <v>137</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>15</v>
@@ -4853,10 +4853,10 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>15</v>
@@ -4873,10 +4873,10 @@
         <v>138</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D43" s="5">
         <v>5</v>
@@ -4890,10 +4890,10 @@
         <v>80</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D44" s="5">
         <v>5</v>
@@ -4907,7 +4907,7 @@
         <v>11</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>5</v>
@@ -4924,7 +4924,7 @@
         <v>139</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>15</v>
@@ -4938,10 +4938,10 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>15</v>
@@ -4958,7 +4958,7 @@
         <v>140</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>15</v>
@@ -4975,10 +4975,10 @@
         <v>76</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D49" s="5">
         <v>6</v>
@@ -4992,7 +4992,7 @@
         <v>141</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>15</v>
@@ -5006,10 +5006,10 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>15</v>
@@ -5026,10 +5026,10 @@
         <v>142</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D52" s="5">
         <v>7</v>
@@ -5043,10 +5043,10 @@
         <v>81</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D53" s="5">
         <v>7</v>
@@ -5060,7 +5060,7 @@
         <v>143</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>15</v>
@@ -5077,7 +5077,7 @@
         <v>144</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>15</v>
@@ -5094,7 +5094,7 @@
         <v>145</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>15</v>
@@ -5111,7 +5111,7 @@
         <v>146</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>15</v>
@@ -5125,10 +5125,10 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>15</v>
@@ -5254,7 +5254,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
@@ -5268,7 +5268,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
@@ -5277,12 +5277,12 @@
         <v>2</v>
       </c>
       <c r="D4" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -5291,7 +5291,7 @@
         <v>2</v>
       </c>
       <c r="D5" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -5310,21 +5310,21 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" s="2">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>5</v>
@@ -5333,21 +5333,21 @@
         <v>3</v>
       </c>
       <c r="D8" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D9" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -5361,7 +5361,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -5411,10 +5411,10 @@
         <v>15</v>
       </c>
       <c r="C17" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" s="4">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -5428,7 +5428,7 @@
         <v>2</v>
       </c>
       <c r="D18" s="4">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -5442,7 +5442,7 @@
         <v>2</v>
       </c>
       <c r="D19" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -5453,10 +5453,10 @@
         <v>15</v>
       </c>
       <c r="C20" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D20" s="4">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -5470,12 +5470,12 @@
         <v>3</v>
       </c>
       <c r="D21" s="4">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>15</v>
@@ -5484,12 +5484,12 @@
         <v>3</v>
       </c>
       <c r="D22" s="4">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>15</v>
@@ -5498,12 +5498,12 @@
         <v>3</v>
       </c>
       <c r="D23" s="4">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>15</v>
@@ -5517,7 +5517,7 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>15</v>
@@ -5531,7 +5531,7 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>15</v>
@@ -5545,7 +5545,7 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>15</v>
@@ -5559,7 +5559,7 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>15</v>
@@ -5573,7 +5573,7 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>15</v>
@@ -5602,20 +5602,20 @@
         <v>12</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C32" s="4"/>
       <c r="D32" s="4">
         <f>AVERAGE(D16:D29)</f>
-        <v>14.2857142857143</v>
+        <v>14.4285714285714</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C35" s="6">
         <v>3</v>
@@ -5626,10 +5626,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B36" s="6" t="s">
         <v>30</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>29</v>
       </c>
       <c r="C36" s="6">
         <v>4</v>
@@ -5640,10 +5640,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C37" s="6">
         <v>4</v>
@@ -5654,10 +5654,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C38" s="6">
         <v>4</v>
@@ -5668,10 +5668,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C39" s="6">
         <v>5</v>
@@ -5682,10 +5682,10 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C40" s="6">
         <v>6</v>
@@ -5696,10 +5696,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C41" s="6">
         <v>7</v>
@@ -5725,7 +5725,7 @@
         <v>12</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="6">
@@ -5735,11 +5735,11 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D47">
         <f>AVERAGE(D2:D10,D16:D29,D35:D41)</f>
-        <v>14.3666666666667</v>
+        <v>14.4333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -5775,7 +5775,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>5</v>
@@ -5784,26 +5784,26 @@
         <v>1</v>
       </c>
       <c r="D2" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
@@ -5812,12 +5812,12 @@
         <v>2</v>
       </c>
       <c r="D4" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -5831,7 +5831,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>5</v>
@@ -5840,12 +5840,12 @@
         <v>2</v>
       </c>
       <c r="D6" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>5</v>
@@ -5915,7 +5915,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>5</v>
@@ -5924,28 +5924,36 @@
         <v>3</v>
       </c>
       <c r="D12" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="2">
+        <v>3</v>
+      </c>
+      <c r="D13" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="2">
+      <c r="B14" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="2">
         <v>4</v>
       </c>
-      <c r="D13" s="2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
+      <c r="D14" s="2">
+        <v>15</v>
+      </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2"/>
@@ -5954,44 +5962,36 @@
       <c r="D15" s="2"/>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B16" s="2" t="s">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2">
-        <f>AVERAGE(D2:D13)</f>
-        <v>14.9166666666667</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="4">
-        <v>1</v>
-      </c>
-      <c r="D19" s="4">
-        <v>12</v>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2">
+        <f>AVERAGE(D2:D14)</f>
+        <v>14.4615384615385</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C20" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="4">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -6005,26 +6005,26 @@
         <v>2</v>
       </c>
       <c r="D21" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="4" t="s">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C22" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D22" s="4">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>15</v>
@@ -6033,12 +6033,12 @@
         <v>3</v>
       </c>
       <c r="D23" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="4" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>15</v>
@@ -6052,7 +6052,7 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>15</v>
@@ -6061,12 +6061,12 @@
         <v>3</v>
       </c>
       <c r="D25" s="4">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>15</v>
@@ -6075,12 +6075,12 @@
         <v>3</v>
       </c>
       <c r="D26" s="4">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>15</v>
@@ -6108,7 +6108,7 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>15</v>
@@ -6122,7 +6122,7 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>15</v>
@@ -6152,12 +6152,12 @@
         <v>12</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C33" s="4"/>
       <c r="D33" s="4">
-        <f>AVERAGE(D19:D30)</f>
-        <v>14</v>
+        <f>AVERAGE(D20:D30)</f>
+        <v>14.3636363636364</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -6165,7 +6165,7 @@
         <v>53</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C36" s="6">
         <v>3</v>
@@ -6176,10 +6176,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C37" s="6">
         <v>4</v>
@@ -6193,7 +6193,7 @@
         <v>54</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C38" s="6">
         <v>4</v>
@@ -6207,7 +6207,7 @@
         <v>55</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C39" s="6">
         <v>4</v>
@@ -6218,10 +6218,10 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C40" s="6">
         <v>5</v>
@@ -6235,7 +6235,7 @@
         <v>56</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C41" s="6">
         <v>7</v>
@@ -6261,7 +6261,7 @@
         <v>12</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="6">
@@ -6271,13 +6271,13 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B47" s="7"/>
       <c r="C47" s="7"/>
       <c r="D47" s="7">
-        <f>AVERAGE(D2:D13,D19:D30,D36:D41)</f>
-        <v>14.0333333333333</v>
+        <f>AVERAGE(D2:D14,D20:D30,D36:D41)</f>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -6312,7 +6312,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>5</v>
@@ -6321,12 +6321,12 @@
         <v>1</v>
       </c>
       <c r="D2" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
@@ -6335,26 +6335,26 @@
         <v>1</v>
       </c>
       <c r="D3" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -6363,12 +6363,12 @@
         <v>2</v>
       </c>
       <c r="D5" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>5</v>
@@ -6382,7 +6382,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>5</v>
@@ -6391,26 +6391,26 @@
         <v>2</v>
       </c>
       <c r="D7" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" s="2">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>9</v>
+        <v>57</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>5</v>
@@ -6419,12 +6419,12 @@
         <v>3</v>
       </c>
       <c r="D9" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>57</v>
+        <v>10</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>5</v>
@@ -6433,12 +6433,12 @@
         <v>3</v>
       </c>
       <c r="D10" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>5</v>
@@ -6461,12 +6461,12 @@
         <v>3</v>
       </c>
       <c r="D12" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>5</v>
@@ -6475,35 +6475,35 @@
         <v>3</v>
       </c>
       <c r="D13" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D14" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C15" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D15" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -6517,22 +6517,14 @@
         <v>5</v>
       </c>
       <c r="D16" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" s="2">
-        <v>5</v>
-      </c>
-      <c r="D17" s="2">
-        <v>15</v>
-      </c>
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2"/>
@@ -6541,27 +6533,35 @@
       <c r="D18" s="2"/>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
+      <c r="A19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2">
-        <f>AVERAGE(D2:D17)</f>
-        <v>15.1875</v>
+      <c r="D19" s="2">
+        <f>AVERAGE(D2:D16)</f>
+        <v>15.1333333333333</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="4">
+        <v>1</v>
+      </c>
+      <c r="D22" s="4">
+        <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>15</v>
@@ -6575,7 +6575,7 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>15</v>
@@ -6631,7 +6631,7 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>15</v>
@@ -6645,7 +6645,7 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>15</v>
@@ -6674,20 +6674,20 @@
         <v>12</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C32" s="4"/>
       <c r="D32" s="4">
-        <f>AVERAGE(D23:D29)</f>
-        <v>14.8571428571429</v>
+        <f>AVERAGE(D22:D29)</f>
+        <v>14.5</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C35" s="6">
         <v>3</v>
@@ -6698,10 +6698,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B36" s="6" t="s">
         <v>30</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>29</v>
       </c>
       <c r="C36" s="6">
         <v>4</v>
@@ -6712,10 +6712,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C37" s="6">
         <v>4</v>
@@ -6729,7 +6729,7 @@
         <v>58</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C38" s="6">
         <v>4</v>
@@ -6743,7 +6743,7 @@
         <v>55</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C39" s="6">
         <v>4</v>
@@ -6754,10 +6754,10 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C40" s="6">
         <v>6</v>
@@ -6768,10 +6768,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C41" s="6">
         <v>8</v>
@@ -6797,7 +6797,7 @@
         <v>12</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="6">
@@ -6807,11 +6807,11 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D47">
-        <f>AVERAGE(D2:D17,D23:D29,D35:D41)</f>
-        <v>14.6</v>
+        <f>AVERAGE(D2:D16,D22:D29,D35:D41)</f>
+        <v>14.4666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -6888,7 +6888,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -7023,8 +7023,6 @@
         <v>12.7272727272727</v>
       </c>
     </row>
-    <row r="16" customFormat="1"/>
-    <row r="17" customFormat="1"/>
     <row r="18" spans="1:4">
       <c r="A18" s="4" t="s">
         <v>14</v>
@@ -7041,7 +7039,7 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>15</v>
@@ -7055,7 +7053,7 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>15</v>
@@ -7097,7 +7095,7 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>15</v>
@@ -7111,7 +7109,7 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>15</v>
@@ -7125,7 +7123,7 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>15</v>
@@ -7153,7 +7151,7 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>15</v>
@@ -7181,7 +7179,7 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>15</v>
@@ -7195,7 +7193,7 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>15</v>
@@ -7225,7 +7223,7 @@
         <v>12</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C33" s="4"/>
       <c r="D33" s="4">
@@ -7233,14 +7231,12 @@
         <v>13.3076923076923</v>
       </c>
     </row>
-    <row r="34" customFormat="1"/>
-    <row r="35" customFormat="1"/>
     <row r="36" spans="1:4">
       <c r="A36" s="6" t="s">
         <v>69</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C36" s="6">
         <v>1</v>
@@ -7254,7 +7250,7 @@
         <v>70</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C37" s="6">
         <v>4</v>
@@ -7268,7 +7264,7 @@
         <v>71</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C38" s="6">
         <v>4</v>
@@ -7279,10 +7275,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C39" s="6">
         <v>5</v>
@@ -7296,7 +7292,7 @@
         <v>72</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C40" s="6">
         <v>6</v>
@@ -7310,7 +7306,7 @@
         <v>56</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C41" s="6">
         <v>7</v>
@@ -7336,7 +7332,7 @@
         <v>12</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="6">
@@ -7344,11 +7340,9 @@
         <v>12.3333333333333</v>
       </c>
     </row>
-    <row r="45" customFormat="1"/>
-    <row r="46" customFormat="1"/>
     <row r="47" spans="1:4">
       <c r="A47" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B47" s="7"/>
       <c r="C47" s="7"/>
@@ -7366,7 +7360,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="16.375" customWidth="1"/>
@@ -7415,7 +7409,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -7470,7 +7464,7 @@
       </c>
       <c r="C10" s="2">
         <f>AVERAGE(C2:C7)</f>
-        <v>15.8333333333333</v>
+        <v>16</v>
       </c>
       <c r="D10" s="4"/>
     </row>
@@ -7479,60 +7473,66 @@
         <v>16</v>
       </c>
       <c r="B13" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" s="4">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B14" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B15" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" s="4">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B16" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C16" s="4">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B17" s="4">
         <v>6</v>
       </c>
       <c r="C17" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="4">
+        <v>6</v>
+      </c>
+      <c r="C18" s="4">
         <v>14</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4"/>
@@ -7540,76 +7540,76 @@
       <c r="C19" s="4"/>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C20" s="4">
-        <f>AVERAGE(C13:C17)</f>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="B23" s="6">
-        <v>1</v>
-      </c>
-      <c r="C23" s="6">
-        <v>13</v>
+      <c r="A20" s="4"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" s="4">
+        <f>AVERAGE(C13:C18)</f>
+        <v>14.5</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B24" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C24" s="6">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B25" s="6">
         <v>2</v>
       </c>
       <c r="C25" s="6">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B26" s="6">
         <v>2</v>
       </c>
       <c r="C26" s="6">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B27" s="6">
+        <v>2</v>
+      </c>
+      <c r="C27" s="6">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="B27" s="6">
-        <v>5</v>
-      </c>
-      <c r="C27" s="6">
+      <c r="B28" s="6">
+        <v>5</v>
+      </c>
+      <c r="C28" s="6">
         <v>13</v>
       </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="6"/>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="6"/>
@@ -7617,27 +7617,32 @@
       <c r="C29" s="6"/>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B30" s="6" t="s">
+      <c r="A30" s="6"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B31" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="6">
-        <f>AVERAGE(C23:C27)</f>
+      <c r="C31" s="6">
+        <f>AVERAGE(C24:C28)</f>
         <v>13.4</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" s="7" t="s">
+    <row r="34" spans="1:3">
+      <c r="A34" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="C33" s="7">
-        <f>AVERAGE(C2:C7,C13:C17,C23:C27)</f>
-        <v>14.8125</v>
+      <c r="C34" s="7">
+        <f>AVERAGE(C2:C7,C13:C18,C24:C28)</f>
+        <v>14.7058823529412</v>
       </c>
     </row>
   </sheetData>
@@ -7670,10 +7675,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B2" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="2">
         <v>18</v>
@@ -7681,13 +7686,13 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="B3" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C3" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -7695,16 +7700,22 @@
         <v>8</v>
       </c>
       <c r="B4" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C4" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
+      <c r="A5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2">
+        <v>2</v>
+      </c>
+      <c r="C5" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2"/>
@@ -7712,37 +7723,31 @@
       <c r="C6" s="2"/>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="2" t="s">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="2">
-        <f>AVERAGE(C2:C4)</f>
-        <v>14.6666666666667</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="4">
-        <v>1</v>
-      </c>
-      <c r="C10" s="4">
-        <v>12</v>
+      <c r="C8" s="2">
+        <f>AVERAGE(C2:C5)</f>
+        <v>14.5</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B11" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11" s="4">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -7753,15 +7758,15 @@
         <v>2</v>
       </c>
       <c r="C12" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C13" s="4">
         <v>14</v>
@@ -7769,29 +7774,29 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B14" s="4">
         <v>3</v>
       </c>
       <c r="C14" s="4">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B15" s="4">
         <v>3</v>
       </c>
       <c r="C15" s="4">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B16" s="4">
         <v>4</v>
@@ -7802,7 +7807,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B17" s="4">
         <v>5</v>
@@ -7813,7 +7818,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B18" s="4">
         <v>7</v>
@@ -7837,11 +7842,11 @@
         <v>12</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C21" s="4">
-        <f>AVERAGE(C10:C18)</f>
-        <v>13.8888888888889</v>
+        <f>AVERAGE(C11:C18)</f>
+        <v>14.375</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -7901,14 +7906,14 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B32" s="7" t="s">
         <v>82</v>
       </c>
       <c r="C32" s="7">
-        <f>AVERAGE(C2:C4,C10:C18,C24:C26)</f>
-        <v>13.8</v>
+        <f>AVERAGE(C2:C5,C11:C18,C24:C26)</f>
+        <v>14.0666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -7920,7 +7925,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="13.75" customWidth="1"/>
@@ -7952,18 +7957,18 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B3" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B4" s="2">
         <v>2</v>
@@ -7974,40 +7979,40 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B5" s="2">
         <v>2</v>
       </c>
       <c r="C5" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B6" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B7" s="2">
         <v>3</v>
       </c>
       <c r="C7" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B8" s="2">
         <v>3</v>
@@ -8024,52 +8029,46 @@
         <v>3</v>
       </c>
       <c r="C9" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B10" s="2">
         <v>3</v>
       </c>
       <c r="C10" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B11" s="2">
         <v>3</v>
       </c>
       <c r="C11" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2" t="s">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="B12" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C12" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B13" s="2">
-        <v>4</v>
-      </c>
-      <c r="C13" s="2">
-        <v>15</v>
-      </c>
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2"/>
@@ -8077,54 +8076,54 @@
       <c r="C14" s="2"/>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B16" s="2" t="s">
+      <c r="A15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="2">
-        <f>AVERAGE(C2:C13)</f>
-        <v>14.6666666666667</v>
+      <c r="C15" s="2">
+        <f>AVERAGE(C2:C12)</f>
+        <v>14.4545454545455</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" s="4">
+        <v>3</v>
+      </c>
+      <c r="C18" s="4">
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B19" s="4">
         <v>3</v>
       </c>
       <c r="C19" s="4">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B20" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C20" s="4">
         <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B21" s="4">
-        <v>4</v>
-      </c>
-      <c r="C21" s="4">
-        <v>14</v>
-      </c>
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="4"/>
@@ -8132,28 +8131,34 @@
       <c r="C22" s="4"/>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="4"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C24" s="4">
-        <f>AVERAGE(C19:C21)</f>
+      <c r="A23" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" s="4">
+        <f>AVERAGE(C18:C20)</f>
         <v>14.3333333333333</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B26" s="6">
+        <v>3</v>
+      </c>
+      <c r="C26" s="6">
+        <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="6" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B27" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C27" s="6">
         <v>12</v>
@@ -8161,7 +8166,7 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="6" t="s">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="B28" s="6">
         <v>4</v>
@@ -8171,15 +8176,9 @@
       </c>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="B29" s="6">
-        <v>4</v>
-      </c>
-      <c r="C29" s="6">
-        <v>12</v>
-      </c>
+      <c r="A29" s="6"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="6"/>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="6"/>
@@ -8187,32 +8186,27 @@
       <c r="C30" s="6"/>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="6"/>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C32" s="6">
-        <f>AVERAGE(C27:C29)</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="7" t="s">
+      <c r="A31" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B31" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="C31" s="6">
+        <f>AVERAGE(C26:C28)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C35" s="7">
-        <f>AVERAGE(C2:C13,C19:C21,C27:C29)</f>
-        <v>14.1666666666667</v>
+      <c r="C34" s="7">
+        <f>AVERAGE(C2:C12,C18:C20,C26:C28)</f>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -8379,7 +8373,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C18" s="4">
         <f>AVERAGE(C12:C15)</f>
@@ -8420,7 +8414,7 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B28" s="7" t="s">
         <v>96</v>

--- a/src/utils/sxsyzlzq/zzz_cardList.xlsx
+++ b/src/utils/sxsyzlzq/zzz_cardList.xlsx
@@ -4,30 +4,29 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="13380" activeTab="3"/>
+    <workbookView windowWidth="28800" windowHeight="13380" activeTab="11"/>
   </bookViews>
   <sheets>
     <sheet name="伊萝莲" sheetId="1" r:id="rId1"/>
     <sheet name="阿斯塔拉" sheetId="2" r:id="rId2"/>
-    <sheet name="洛" sheetId="11" r:id="rId3"/>
-    <sheet name="白处尊" sheetId="4" r:id="rId4"/>
-    <sheet name="格纳罗尔" sheetId="14" r:id="rId5"/>
+    <sheet name="白处尊" sheetId="4" r:id="rId3"/>
+    <sheet name="洛" sheetId="11" r:id="rId4"/>
+    <sheet name="梅" sheetId="3" r:id="rId5"/>
     <sheet name="帝国" sheetId="5" r:id="rId6"/>
     <sheet name="隐秘" sheetId="6" r:id="rId7"/>
     <sheet name="禅意" sheetId="7" r:id="rId8"/>
     <sheet name="炼狱" sheetId="8" r:id="rId9"/>
-    <sheet name="梅" sheetId="3" r:id="rId10"/>
-    <sheet name="熙" sheetId="9" r:id="rId11"/>
-    <sheet name="尤瑞艾莉" sheetId="12" r:id="rId12"/>
-    <sheet name="希拉" sheetId="10" r:id="rId13"/>
-    <sheet name="统计" sheetId="13" r:id="rId14"/>
+    <sheet name="熙" sheetId="9" r:id="rId10"/>
+    <sheet name="尤瑞艾莉" sheetId="12" r:id="rId11"/>
+    <sheet name="希拉" sheetId="10" r:id="rId12"/>
+    <sheet name="统计" sheetId="13" r:id="rId13"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="135">
   <si>
     <t>名称</t>
   </si>
@@ -164,88 +163,76 @@
     <t>苦行武僧</t>
   </si>
   <si>
+    <t>执剑道人</t>
+  </si>
+  <si>
+    <t>连击</t>
+  </si>
+  <si>
+    <t>深山采药人</t>
+  </si>
+  <si>
+    <t>风铃道人</t>
+  </si>
+  <si>
+    <t>驱魔道人</t>
+  </si>
+  <si>
+    <t>扫叶僧</t>
+  </si>
+  <si>
+    <t>御风武者</t>
+  </si>
+  <si>
+    <t>神机玄女·轩</t>
+  </si>
+  <si>
+    <t>上宝沁金耙</t>
+  </si>
+  <si>
     <t>执剑道者</t>
   </si>
   <si>
     <t>铁山靠</t>
   </si>
   <si>
-    <t>连击</t>
-  </si>
-  <si>
-    <t>深山采药人</t>
-  </si>
-  <si>
-    <t>风铃道人</t>
-  </si>
-  <si>
-    <t>扫叶僧</t>
-  </si>
-  <si>
-    <t>驱魔道人</t>
-  </si>
-  <si>
-    <t>御风武者</t>
-  </si>
-  <si>
     <t>流岚刃·琳</t>
   </si>
   <si>
     <t>九天玄女·轩</t>
   </si>
   <si>
-    <t>上宝沁金耙</t>
-  </si>
-  <si>
     <t>火蛇巫女</t>
   </si>
   <si>
-    <t>执剑道人</t>
-  </si>
-  <si>
-    <t>神机玄女·轩</t>
-  </si>
-  <si>
-    <t>暗潮涌动</t>
-  </si>
-  <si>
-    <t>心灵黑洞</t>
-  </si>
-  <si>
-    <t>狡诈学徒</t>
-  </si>
-  <si>
-    <t>黑夜突袭</t>
-  </si>
-  <si>
-    <t>热血矿工</t>
-  </si>
-  <si>
-    <t>不法交易</t>
-  </si>
-  <si>
-    <t>红海猎魔人</t>
-  </si>
-  <si>
-    <t>海神赐福</t>
-  </si>
-  <si>
-    <t>学仆-猛禽型</t>
-  </si>
-  <si>
-    <t>黑金诈术师</t>
-  </si>
-  <si>
-    <t>圣僧·法海</t>
-  </si>
-  <si>
-    <t>流星七号</t>
-  </si>
-  <si>
-    <t>赤影·艾希尔</t>
-  </si>
-  <si>
-    <t>滑板少年·迪宁</t>
+    <t>旅行背包</t>
+  </si>
+  <si>
+    <t>重装固守</t>
+  </si>
+  <si>
+    <t>龟族僧人</t>
+  </si>
+  <si>
+    <t>叶幻师</t>
+  </si>
+  <si>
+    <t>风卷残云</t>
+  </si>
+  <si>
+    <t>祥云师太</t>
+  </si>
+  <si>
+    <t>冲锋装备</t>
+  </si>
+  <si>
+    <t>蟠桃会</t>
+  </si>
+  <si>
+    <t>万物之灵</t>
+  </si>
+  <si>
+    <t>永恒之王·莱哈特</t>
   </si>
   <si>
     <t>曙光·安娜贝尔</t>
@@ -318,36 +305,6 @@
   </si>
   <si>
     <t>炼狱卡等：</t>
-  </si>
-  <si>
-    <t>旅行背包</t>
-  </si>
-  <si>
-    <t>重装固守</t>
-  </si>
-  <si>
-    <t>龟族僧人</t>
-  </si>
-  <si>
-    <t>叶幻师</t>
-  </si>
-  <si>
-    <t>风卷残云</t>
-  </si>
-  <si>
-    <t>祥云师太</t>
-  </si>
-  <si>
-    <t>冲锋装备</t>
-  </si>
-  <si>
-    <t>蟠桃会</t>
-  </si>
-  <si>
-    <t>万物之灵</t>
-  </si>
-  <si>
-    <t>永恒之王·莱哈特</t>
   </si>
   <si>
     <t>箭竹守卫</t>
@@ -481,10 +438,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -537,7 +494,75 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -567,14 +592,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -585,14 +610,6 @@
       <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -607,66 +624,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -689,7 +646,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -701,37 +664,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -743,13 +676,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -773,6 +742,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -785,13 +772,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -803,73 +820,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -884,50 +841,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
@@ -938,6 +851,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -960,8 +882,43 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -988,10 +945,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1000,133 +957,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2004,10 +1961,10 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D47"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <dimension ref="A1:F47"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="18.125" customWidth="1"/>
+    <col min="1" max="1" width="17.875" customWidth="1"/>
     <col min="4" max="4" width="12.625"/>
   </cols>
   <sheetData>
@@ -2027,7 +1984,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>4</v>
+        <v>82</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>5</v>
@@ -2036,7 +1993,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2050,12 +2007,12 @@
         <v>1</v>
       </c>
       <c r="D3" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
@@ -2064,12 +2021,12 @@
         <v>1</v>
       </c>
       <c r="D4" s="2">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -2078,60 +2035,60 @@
         <v>1</v>
       </c>
       <c r="D5" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>47</v>
+        <v>85</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9" s="2">
         <v>13</v>
@@ -2139,21 +2096,21 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>5</v>
@@ -2162,12 +2119,12 @@
         <v>3</v>
       </c>
       <c r="D11" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>5</v>
@@ -2176,18 +2133,18 @@
         <v>3</v>
       </c>
       <c r="D12" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>101</v>
+        <v>47</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D13" s="2">
         <v>14</v>
@@ -2195,44 +2152,44 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D14" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C15" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D15" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>11</v>
+        <v>86</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C16" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D16" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2257,12 +2214,12 @@
       <c r="C19" s="2"/>
       <c r="D19" s="2">
         <f>AVERAGE(D2:D16)</f>
-        <v>14.2</v>
+        <v>14.4666666666667</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="4" t="s">
-        <v>17</v>
+        <v>87</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>15</v>
@@ -2271,21 +2228,21 @@
         <v>2</v>
       </c>
       <c r="D22" s="4">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="4" t="s">
-        <v>51</v>
+        <v>88</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C23" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D23" s="4">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2299,12 +2256,12 @@
         <v>3</v>
       </c>
       <c r="D24" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="4" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>15</v>
@@ -2313,186 +2270,187 @@
         <v>3</v>
       </c>
       <c r="D25" s="4">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="4" t="s">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C26" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D26" s="4">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="4" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C27" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D27" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="4" t="s">
-        <v>105</v>
+        <v>51</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C28" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D28" s="4">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="4" t="s">
-        <v>26</v>
+        <v>89</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C29" s="4">
+        <v>4</v>
+      </c>
+      <c r="D29" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="4">
+        <v>5</v>
+      </c>
+      <c r="D30" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C31" s="4">
+        <v>5</v>
+      </c>
+      <c r="D31" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" s="4">
         <v>6</v>
       </c>
-      <c r="D29" s="4">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="4"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="4"/>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B32" s="4" t="s">
+      <c r="D32" s="4">
+        <v>11</v>
+      </c>
+      <c r="F32" s="5"/>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="4"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="4"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B35" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4">
-        <f>AVERAGE(D22:D29)</f>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C35" s="6">
-        <v>3</v>
-      </c>
-      <c r="D35" s="6">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C36" s="6">
-        <v>4</v>
-      </c>
-      <c r="D36" s="6">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
-      <c r="A37" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C37" s="6">
-        <v>4</v>
-      </c>
-      <c r="D37" s="6">
-        <v>12</v>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4">
+        <f>AVERAGE(D22:D32)</f>
+        <v>12.7272727272727</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="6" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C38" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D38" s="6">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="6" t="s">
-        <v>106</v>
+        <v>52</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C39" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D39" s="6">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="6" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C40" s="6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D40" s="6">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="6" t="s">
-        <v>37</v>
+        <v>100</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C41" s="6">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D41" s="6">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,27 +2474,562 @@
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="6">
-        <f>AVERAGE(D35:D41)</f>
-        <v>13</v>
+        <f>AVERAGE(D38:D41)</f>
+        <v>10.5</v>
       </c>
     </row>
     <row r="47" spans="1:4">
-      <c r="A47" t="s">
+      <c r="A47" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D47">
-        <f>AVERAGE(D2:D16,D22:D29,D35:D41)</f>
-        <v>13.8666666666667</v>
+      <c r="B47" s="7"/>
+      <c r="C47" s="7"/>
+      <c r="D47" s="7">
+        <f>AVERAGE(D2:D16,D22:D32,D38:D41)</f>
+        <v>13.3</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D47"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="18.25" customWidth="1"/>
+    <col min="4" max="4" width="12.625"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2">
+        <v>2</v>
+      </c>
+      <c r="D4" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="2">
+        <v>2</v>
+      </c>
+      <c r="D5" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="2">
+        <v>2</v>
+      </c>
+      <c r="D6" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="2">
+        <v>2</v>
+      </c>
+      <c r="D7" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="2">
+        <v>2</v>
+      </c>
+      <c r="D8" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="2">
+        <v>2</v>
+      </c>
+      <c r="D9" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="2">
+        <v>3</v>
+      </c>
+      <c r="D10" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="2">
+        <v>4</v>
+      </c>
+      <c r="D11" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2">
+        <f>AVERAGE(D2:D11)</f>
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="4">
+        <v>1</v>
+      </c>
+      <c r="D17" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="4">
+        <v>2</v>
+      </c>
+      <c r="D18" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="4">
+        <v>2</v>
+      </c>
+      <c r="D19" s="4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="4">
+        <v>2</v>
+      </c>
+      <c r="D20" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="4">
+        <v>3</v>
+      </c>
+      <c r="D21" s="4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="4">
+        <v>3</v>
+      </c>
+      <c r="D22" s="4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="4">
+        <v>3</v>
+      </c>
+      <c r="D23" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" s="4">
+        <v>3</v>
+      </c>
+      <c r="D24" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" s="4">
+        <v>3</v>
+      </c>
+      <c r="D25" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="4">
+        <v>4</v>
+      </c>
+      <c r="D26" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" s="4">
+        <v>4</v>
+      </c>
+      <c r="D27" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C28" s="4">
+        <v>5</v>
+      </c>
+      <c r="D28" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C29" s="4">
+        <v>5</v>
+      </c>
+      <c r="D29" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="4">
+        <v>5</v>
+      </c>
+      <c r="D30" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C31" s="4">
+        <v>6</v>
+      </c>
+      <c r="D31" s="4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" s="4">
+        <v>7</v>
+      </c>
+      <c r="D32" s="4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="4"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="4"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4">
+        <f>AVERAGE(D17:D32)</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C38" s="6">
+        <v>2</v>
+      </c>
+      <c r="D38" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C39" s="6">
+        <v>5</v>
+      </c>
+      <c r="D39" s="6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C40" s="6">
+        <v>5</v>
+      </c>
+      <c r="D40" s="6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C41" s="6">
+        <v>7</v>
+      </c>
+      <c r="D41" s="6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="6"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="6"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6">
+        <f>AVERAGE(D38:D41)</f>
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" t="s">
+        <v>39</v>
+      </c>
+      <c r="D47">
+        <f>AVERAGE(D2:D11,D17:D32,D38:D41)</f>
+        <v>12.9333333333333</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F47"/>
@@ -2562,7 +3055,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>5</v>
@@ -2590,7 +3083,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
@@ -2599,12 +3092,12 @@
         <v>1</v>
       </c>
       <c r="D4" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -2613,26 +3106,26 @@
         <v>1</v>
       </c>
       <c r="D5" s="2">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>5</v>
@@ -2646,7 +3139,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>5</v>
@@ -2655,12 +3148,12 @@
         <v>2</v>
       </c>
       <c r="D8" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>89</v>
+        <v>44</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>5</v>
@@ -2674,7 +3167,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>5</v>
@@ -2688,35 +3181,35 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>47</v>
+        <v>84</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C12" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>5</v>
@@ -2725,12 +3218,12 @@
         <v>3</v>
       </c>
       <c r="D13" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>5</v>
@@ -2739,26 +3232,26 @@
         <v>3</v>
       </c>
       <c r="D14" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C15" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D15" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>5</v>
@@ -2767,14 +3260,22 @@
         <v>4</v>
       </c>
       <c r="D16" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
+      <c r="A17" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="2">
+        <v>4</v>
+      </c>
+      <c r="D17" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2"/>
@@ -2783,35 +3284,27 @@
       <c r="D18" s="2"/>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>13</v>
-      </c>
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
       <c r="C19" s="2"/>
-      <c r="D19" s="2">
-        <f>AVERAGE(D2:D16)</f>
-        <v>14.4666666666667</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C22" s="4">
-        <v>2</v>
-      </c>
-      <c r="D22" s="4">
-        <v>13</v>
+      <c r="D19" s="2"/>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2">
+        <f>AVERAGE(D2:D17)</f>
+        <v>13.9375</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="4" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>15</v>
@@ -2820,26 +3313,26 @@
         <v>2</v>
       </c>
       <c r="D23" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="4" t="s">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C24" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D24" s="4">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="4" t="s">
-        <v>108</v>
+        <v>50</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>15</v>
@@ -2848,12 +3341,12 @@
         <v>3</v>
       </c>
       <c r="D25" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="4" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>15</v>
@@ -2862,12 +3355,12 @@
         <v>3</v>
       </c>
       <c r="D26" s="4">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="4" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>15</v>
@@ -2881,21 +3374,21 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="4" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C28" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D28" s="4">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="4" t="s">
-        <v>93</v>
+        <v>51</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>15</v>
@@ -2904,26 +3397,26 @@
         <v>4</v>
       </c>
       <c r="D29" s="4">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="4" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C30" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D30" s="4">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="4" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>15</v>
@@ -2932,29 +3425,37 @@
         <v>5</v>
       </c>
       <c r="D31" s="4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
       <c r="A32" s="4" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C32" s="4">
+        <v>5</v>
+      </c>
+      <c r="D32" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C33" s="4">
         <v>6</v>
       </c>
-      <c r="D32" s="4">
+      <c r="D33" s="4">
         <v>11</v>
       </c>
-      <c r="F32" s="5"/>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="4"/>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
+      <c r="F33" s="5"/>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="4"/>
@@ -2963,49 +3464,41 @@
       <c r="D34" s="4"/>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B35" s="4" t="s">
+      <c r="A35" s="4"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B36" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4">
-        <f>AVERAGE(D22:D32)</f>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4">
+        <f>AVERAGE(D23:D33)</f>
         <v>12.7272727272727</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
-      <c r="A38" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C38" s="6">
-        <v>2</v>
-      </c>
-      <c r="D38" s="6">
-        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="6" t="s">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C39" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D39" s="6">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>30</v>
@@ -3014,12 +3507,12 @@
         <v>4</v>
       </c>
       <c r="D40" s="6">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="6" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>30</v>
@@ -3052,8 +3545,8 @@
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="6">
-        <f>AVERAGE(D38:D41)</f>
-        <v>10.5</v>
+        <f>AVERAGE(D39:D41)</f>
+        <v>9.66666666666667</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -3063,542 +3556,8 @@
       <c r="B47" s="7"/>
       <c r="C47" s="7"/>
       <c r="D47" s="7">
-        <f>AVERAGE(D2:D16,D22:D32,D38:D41)</f>
-        <v>13.3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:D47"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
-  <cols>
-    <col min="1" max="1" width="18.25" customWidth="1"/>
-    <col min="4" max="4" width="12.625"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="2">
-        <v>1</v>
-      </c>
-      <c r="D2" s="2">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="2">
-        <v>1</v>
-      </c>
-      <c r="D3" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="2">
-        <v>2</v>
-      </c>
-      <c r="D4" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="2">
-        <v>2</v>
-      </c>
-      <c r="D5" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="2">
-        <v>2</v>
-      </c>
-      <c r="D6" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="2">
-        <v>2</v>
-      </c>
-      <c r="D7" s="2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="2">
-        <v>2</v>
-      </c>
-      <c r="D8" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="2">
-        <v>2</v>
-      </c>
-      <c r="D9" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" s="2">
-        <v>3</v>
-      </c>
-      <c r="D10" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="2">
-        <v>4</v>
-      </c>
-      <c r="D11" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2">
-        <f>AVERAGE(D2:D11)</f>
-        <v>13.8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" s="4">
-        <v>1</v>
-      </c>
-      <c r="D17" s="4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18" s="4">
-        <v>2</v>
-      </c>
-      <c r="D18" s="4">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="4">
-        <v>2</v>
-      </c>
-      <c r="D19" s="4">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="4">
-        <v>2</v>
-      </c>
-      <c r="D20" s="4">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C21" s="4">
-        <v>3</v>
-      </c>
-      <c r="D21" s="4">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C22" s="4">
-        <v>3</v>
-      </c>
-      <c r="D22" s="4">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C23" s="4">
-        <v>3</v>
-      </c>
-      <c r="D23" s="4">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C24" s="4">
-        <v>3</v>
-      </c>
-      <c r="D24" s="4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C25" s="4">
-        <v>3</v>
-      </c>
-      <c r="D25" s="4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C26" s="4">
-        <v>4</v>
-      </c>
-      <c r="D26" s="4">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C27" s="4">
-        <v>4</v>
-      </c>
-      <c r="D27" s="4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C28" s="4">
-        <v>5</v>
-      </c>
-      <c r="D28" s="4">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C29" s="4">
-        <v>5</v>
-      </c>
-      <c r="D29" s="4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C30" s="4">
-        <v>5</v>
-      </c>
-      <c r="D30" s="4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C31" s="4">
-        <v>6</v>
-      </c>
-      <c r="D31" s="4">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C32" s="4">
-        <v>7</v>
-      </c>
-      <c r="D32" s="4">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="4"/>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" s="4"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4">
-        <f>AVERAGE(D17:D32)</f>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
-      <c r="A38" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C38" s="6">
-        <v>2</v>
-      </c>
-      <c r="D38" s="6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C39" s="6">
-        <v>5</v>
-      </c>
-      <c r="D39" s="6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
-      <c r="A40" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C40" s="6">
-        <v>5</v>
-      </c>
-      <c r="D40" s="6">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
-      <c r="A41" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C41" s="6">
-        <v>7</v>
-      </c>
-      <c r="D41" s="6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
-      <c r="A42" s="6"/>
-      <c r="B42" s="6"/>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6"/>
-    </row>
-    <row r="43" spans="1:4">
-      <c r="A43" s="6"/>
-      <c r="B43" s="6"/>
-      <c r="C43" s="6"/>
-      <c r="D43" s="6"/>
-    </row>
-    <row r="44" spans="1:4">
-      <c r="A44" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C44" s="6"/>
-      <c r="D44" s="6">
-        <f>AVERAGE(D38:D41)</f>
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
-      <c r="A47" t="s">
-        <v>39</v>
-      </c>
-      <c r="D47">
-        <f>AVERAGE(D2:D11,D17:D32,D38:D41)</f>
-        <v>12.9333333333333</v>
+        <f>AVERAGE(D2:D17,D23:D33,D39:D41)</f>
+        <v>13.0666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -3608,543 +3567,6 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:F47"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
-  <cols>
-    <col min="1" max="1" width="17.875" customWidth="1"/>
-    <col min="4" max="4" width="12.625"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="2">
-        <v>1</v>
-      </c>
-      <c r="D2" s="2">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="2">
-        <v>1</v>
-      </c>
-      <c r="D3" s="2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="2">
-        <v>1</v>
-      </c>
-      <c r="D4" s="2">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="2">
-        <v>1</v>
-      </c>
-      <c r="D5" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="2">
-        <v>1</v>
-      </c>
-      <c r="D6" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="2">
-        <v>2</v>
-      </c>
-      <c r="D7" s="2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="2">
-        <v>2</v>
-      </c>
-      <c r="D8" s="2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="2">
-        <v>2</v>
-      </c>
-      <c r="D9" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" s="2">
-        <v>2</v>
-      </c>
-      <c r="D10" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="2">
-        <v>2</v>
-      </c>
-      <c r="D11" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" s="2">
-        <v>2</v>
-      </c>
-      <c r="D12" s="2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="2">
-        <v>3</v>
-      </c>
-      <c r="D13" s="2">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" s="2">
-        <v>3</v>
-      </c>
-      <c r="D14" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15" s="2">
-        <v>3</v>
-      </c>
-      <c r="D15" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C16" s="2">
-        <v>4</v>
-      </c>
-      <c r="D16" s="2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" s="2">
-        <v>4</v>
-      </c>
-      <c r="D17" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2">
-        <f>AVERAGE(D2:D17)</f>
-        <v>13.9375</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C23" s="4">
-        <v>2</v>
-      </c>
-      <c r="D23" s="4">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C24" s="4">
-        <v>2</v>
-      </c>
-      <c r="D24" s="4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C25" s="4">
-        <v>3</v>
-      </c>
-      <c r="D25" s="4">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C26" s="4">
-        <v>3</v>
-      </c>
-      <c r="D26" s="4">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C27" s="4">
-        <v>3</v>
-      </c>
-      <c r="D27" s="4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C28" s="4">
-        <v>3</v>
-      </c>
-      <c r="D28" s="4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C29" s="4">
-        <v>4</v>
-      </c>
-      <c r="D29" s="4">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C30" s="4">
-        <v>4</v>
-      </c>
-      <c r="D30" s="4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C31" s="4">
-        <v>5</v>
-      </c>
-      <c r="D31" s="4">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C32" s="4">
-        <v>5</v>
-      </c>
-      <c r="D32" s="4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C33" s="4">
-        <v>6</v>
-      </c>
-      <c r="D33" s="4">
-        <v>11</v>
-      </c>
-      <c r="F33" s="5"/>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" s="4"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="4"/>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4">
-        <f>AVERAGE(D23:D33)</f>
-        <v>12.7272727272727</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C39" s="6">
-        <v>2</v>
-      </c>
-      <c r="D39" s="6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
-      <c r="A40" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C40" s="6">
-        <v>4</v>
-      </c>
-      <c r="D40" s="6">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
-      <c r="A41" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C41" s="6">
-        <v>5</v>
-      </c>
-      <c r="D41" s="6">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
-      <c r="A42" s="6"/>
-      <c r="B42" s="6"/>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6"/>
-    </row>
-    <row r="43" spans="1:4">
-      <c r="A43" s="6"/>
-      <c r="B43" s="6"/>
-      <c r="C43" s="6"/>
-      <c r="D43" s="6"/>
-    </row>
-    <row r="44" spans="1:4">
-      <c r="A44" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C44" s="6"/>
-      <c r="D44" s="6">
-        <f>AVERAGE(D39:D41)</f>
-        <v>9.66666666666667</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
-      <c r="A47" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B47" s="7"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="7">
-        <f>AVERAGE(D2:D17,D23:D33,D39:D41)</f>
-        <v>13.0666666666667</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E66"/>
@@ -4159,7 +3581,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -4168,15 +3590,15 @@
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>30</v>
@@ -4190,10 +3612,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
-        <v>98</v>
+        <v>60</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>5</v>
@@ -4207,10 +3629,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
-        <v>97</v>
+        <v>59</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>5</v>
@@ -4227,7 +3649,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>5</v>
@@ -4244,7 +3666,7 @@
         <v>16</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>15</v>
@@ -4261,7 +3683,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>15</v>
@@ -4275,10 +3697,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="4" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>15</v>
@@ -4292,10 +3714,10 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>5</v>
@@ -4312,7 +3734,7 @@
         <v>40</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>5</v>
@@ -4329,7 +3751,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>5</v>
@@ -4343,10 +3765,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>5</v>
@@ -4363,7 +3785,7 @@
         <v>8</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>5</v>
@@ -4377,10 +3799,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="4" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>15</v>
@@ -4394,10 +3816,10 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="4" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>15</v>
@@ -4414,7 +3836,7 @@
         <v>17</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>15</v>
@@ -4431,7 +3853,7 @@
         <v>19</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>15</v>
@@ -4448,7 +3870,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>15</v>
@@ -4462,10 +3884,10 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>30</v>
@@ -4479,10 +3901,10 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>30</v>
@@ -4496,10 +3918,10 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>30</v>
@@ -4513,10 +3935,10 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>5</v>
@@ -4533,7 +3955,7 @@
         <v>9</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>5</v>
@@ -4550,7 +3972,7 @@
         <v>10</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>5</v>
@@ -4564,10 +3986,10 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="4" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>15</v>
@@ -4581,10 +4003,10 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="4" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>15</v>
@@ -4601,7 +4023,7 @@
         <v>21</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>15</v>
@@ -4618,7 +4040,7 @@
         <v>20</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>15</v>
@@ -4632,10 +4054,10 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="4" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>15</v>
@@ -4649,10 +4071,10 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="4" t="s">
-        <v>103</v>
+        <v>65</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>15</v>
@@ -4666,10 +4088,10 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="4" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>15</v>
@@ -4683,10 +4105,10 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>30</v>
@@ -4700,10 +4122,10 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>30</v>
@@ -4717,10 +4139,10 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>30</v>
@@ -4734,10 +4156,10 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>5</v>
@@ -4751,10 +4173,10 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="4" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>15</v>
@@ -4768,10 +4190,10 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="4" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>15</v>
@@ -4785,10 +4207,10 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="4" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>15</v>
@@ -4805,7 +4227,7 @@
         <v>22</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>15</v>
@@ -4819,10 +4241,10 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="4" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>15</v>
@@ -4836,10 +4258,10 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="4" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>15</v>
@@ -4856,7 +4278,7 @@
         <v>23</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>15</v>
@@ -4870,10 +4292,10 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>30</v>
@@ -4887,10 +4309,10 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>30</v>
@@ -4907,7 +4329,7 @@
         <v>11</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>5</v>
@@ -4921,10 +4343,10 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="4" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>15</v>
@@ -4941,7 +4363,7 @@
         <v>24</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>15</v>
@@ -4955,10 +4377,10 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="4" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>15</v>
@@ -4972,10 +4394,10 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>30</v>
@@ -4989,10 +4411,10 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="4" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>15</v>
@@ -5009,7 +4431,7 @@
         <v>26</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>15</v>
@@ -5023,10 +4445,10 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>30</v>
@@ -5040,10 +4462,10 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>30</v>
@@ -5057,10 +4479,10 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="4" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>15</v>
@@ -5074,10 +4496,10 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="4" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>15</v>
@@ -5091,10 +4513,10 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="4" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>15</v>
@@ -5108,10 +4530,10 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="4" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>15</v>
@@ -5128,7 +4550,7 @@
         <v>27</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>15</v>
@@ -5177,7 +4599,7 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -5197,7 +4619,7 @@
       </c>
       <c r="B66" s="2"/>
       <c r="C66" s="2" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" s="2">
@@ -5752,543 +5174,6 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F47"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
-  <cols>
-    <col min="1" max="1" width="17.875" customWidth="1"/>
-    <col min="4" max="4" width="12.625"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="2">
-        <v>1</v>
-      </c>
-      <c r="D2" s="2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="2">
-        <v>2</v>
-      </c>
-      <c r="D3" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="2">
-        <v>2</v>
-      </c>
-      <c r="D4" s="2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="2">
-        <v>2</v>
-      </c>
-      <c r="D5" s="2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="2">
-        <v>2</v>
-      </c>
-      <c r="D6" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="2">
-        <v>2</v>
-      </c>
-      <c r="D7" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="2">
-        <v>2</v>
-      </c>
-      <c r="D8" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="2">
-        <v>3</v>
-      </c>
-      <c r="D9" s="2">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" s="2">
-        <v>2</v>
-      </c>
-      <c r="D10" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="2">
-        <v>3</v>
-      </c>
-      <c r="D11" s="2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" s="2">
-        <v>3</v>
-      </c>
-      <c r="D12" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="2">
-        <v>3</v>
-      </c>
-      <c r="D13" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" s="2">
-        <v>4</v>
-      </c>
-      <c r="D14" s="2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2">
-        <f>AVERAGE(D2:D14)</f>
-        <v>14.4615384615385</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="4">
-        <v>1</v>
-      </c>
-      <c r="D20" s="4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C21" s="4">
-        <v>2</v>
-      </c>
-      <c r="D21" s="4">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C22" s="4">
-        <v>2</v>
-      </c>
-      <c r="D22" s="4">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C23" s="4">
-        <v>3</v>
-      </c>
-      <c r="D23" s="4">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C24" s="4">
-        <v>3</v>
-      </c>
-      <c r="D24" s="4">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C25" s="4">
-        <v>3</v>
-      </c>
-      <c r="D25" s="4">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C26" s="4">
-        <v>3</v>
-      </c>
-      <c r="D26" s="4">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C27" s="4">
-        <v>4</v>
-      </c>
-      <c r="D27" s="4">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C28" s="4">
-        <v>4</v>
-      </c>
-      <c r="D28" s="4">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C29" s="4">
-        <v>5</v>
-      </c>
-      <c r="D29" s="4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C30" s="4">
-        <v>7</v>
-      </c>
-      <c r="D30" s="4">
-        <v>15</v>
-      </c>
-      <c r="F30" s="5"/>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="4"/>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="4"/>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4">
-        <f>AVERAGE(D20:D30)</f>
-        <v>14.3636363636364</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C36" s="6">
-        <v>3</v>
-      </c>
-      <c r="D36" s="6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
-      <c r="A37" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C37" s="6">
-        <v>4</v>
-      </c>
-      <c r="D37" s="6">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
-      <c r="A38" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C38" s="6">
-        <v>4</v>
-      </c>
-      <c r="D38" s="6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C39" s="6">
-        <v>4</v>
-      </c>
-      <c r="D39" s="6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
-      <c r="A40" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C40" s="6">
-        <v>5</v>
-      </c>
-      <c r="D40" s="6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
-      <c r="A41" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C41" s="6">
-        <v>7</v>
-      </c>
-      <c r="D41" s="6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
-      <c r="A42" s="6"/>
-      <c r="B42" s="6"/>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6"/>
-    </row>
-    <row r="43" spans="1:4">
-      <c r="A43" s="6"/>
-      <c r="B43" s="6"/>
-      <c r="C43" s="6"/>
-      <c r="D43" s="6"/>
-    </row>
-    <row r="44" spans="1:4">
-      <c r="A44" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C44" s="6"/>
-      <c r="D44" s="6">
-        <f>AVERAGE(D36:D41)</f>
-        <v>12.3333333333333</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
-      <c r="A47" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B47" s="7"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="7">
-        <f>AVERAGE(D2:D14,D20:D30,D36:D41)</f>
-        <v>14</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
   <dimension ref="A1:D47"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
@@ -6410,7 +5295,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>5</v>
@@ -6438,7 +5323,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>5</v>
@@ -6452,7 +5337,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>5</v>
@@ -6466,7 +5351,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>5</v>
@@ -6480,7 +5365,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>5</v>
@@ -6589,7 +5474,7 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>15</v>
@@ -6617,7 +5502,7 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>15</v>
@@ -6726,7 +5611,7 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="6" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>30</v>
@@ -6740,7 +5625,7 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>30</v>
@@ -6820,7 +5705,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F47"/>
@@ -6846,7 +5731,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>5</v>
@@ -6855,40 +5740,40 @@
         <v>1</v>
       </c>
       <c r="D2" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="2">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -6897,12 +5782,12 @@
         <v>2</v>
       </c>
       <c r="D5" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>5</v>
@@ -6930,7 +5815,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>5</v>
@@ -6939,26 +5824,26 @@
         <v>2</v>
       </c>
       <c r="D8" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" s="2">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>5</v>
@@ -6967,12 +5852,12 @@
         <v>2</v>
       </c>
       <c r="D10" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>5</v>
@@ -6981,12 +5866,12 @@
         <v>3</v>
       </c>
       <c r="D11" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>5</v>
@@ -6995,79 +5880,79 @@
         <v>3</v>
       </c>
       <c r="D12" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
+      <c r="A13" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="2">
+        <v>3</v>
+      </c>
+      <c r="D13" s="2">
+        <v>14</v>
+      </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
+      <c r="A14" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="2">
+        <v>4</v>
+      </c>
+      <c r="D14" s="2">
+        <v>15</v>
+      </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>13</v>
-      </c>
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
       <c r="C15" s="2"/>
-      <c r="D15" s="2">
-        <f>AVERAGE(D2:D12)</f>
-        <v>12.7272727272727</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18" s="4">
-        <v>1</v>
-      </c>
-      <c r="D18" s="4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="4">
-        <v>2</v>
-      </c>
-      <c r="D19" s="4">
-        <v>15</v>
+      <c r="D15" s="2"/>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2">
+        <f>AVERAGE(D2:D14)</f>
+        <v>14.4615384615385</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="4" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C20" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="4">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="4" t="s">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>15</v>
@@ -7076,12 +5961,12 @@
         <v>2</v>
       </c>
       <c r="D21" s="4">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="4" t="s">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>15</v>
@@ -7090,12 +5975,12 @@
         <v>2</v>
       </c>
       <c r="D22" s="4">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="4" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>15</v>
@@ -7104,12 +5989,12 @@
         <v>3</v>
       </c>
       <c r="D23" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="4" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>15</v>
@@ -7132,12 +6017,12 @@
         <v>3</v>
       </c>
       <c r="D25" s="4">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="4" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>15</v>
@@ -7146,7 +6031,7 @@
         <v>3</v>
       </c>
       <c r="D26" s="4">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -7165,7 +6050,7 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="4" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>15</v>
@@ -7174,7 +6059,7 @@
         <v>4</v>
       </c>
       <c r="D28" s="4">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -7227,19 +6112,19 @@
       </c>
       <c r="C33" s="4"/>
       <c r="D33" s="4">
-        <f>AVERAGE(D18:D30)</f>
-        <v>13.3076923076923</v>
+        <f>AVERAGE(D20:D30)</f>
+        <v>14.3636363636364</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="6" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C36" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D36" s="6">
         <v>12</v>
@@ -7247,7 +6132,7 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="6" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>30</v>
@@ -7261,7 +6146,7 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="6" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>30</v>
@@ -7275,13 +6160,13 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="6" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C39" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D39" s="6">
         <v>12</v>
@@ -7289,13 +6174,13 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="6" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C40" s="6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D40" s="6">
         <v>12</v>
@@ -7303,7 +6188,7 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>30</v>
@@ -7347,12 +6232,547 @@
       <c r="B47" s="7"/>
       <c r="C47" s="7"/>
       <c r="D47" s="7">
-        <f>AVERAGE(D2:D12,D18:D30,D36:D41)</f>
-        <v>12.9</v>
+        <f>AVERAGE(D2:D14,D20:D30,D36:D41)</f>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D47"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="18.125" customWidth="1"/>
+    <col min="4" max="4" width="12.625"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="2">
+        <v>1</v>
+      </c>
+      <c r="D5" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="2">
+        <v>3</v>
+      </c>
+      <c r="D6" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="2">
+        <v>3</v>
+      </c>
+      <c r="D7" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="2">
+        <v>3</v>
+      </c>
+      <c r="D8" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="2">
+        <v>3</v>
+      </c>
+      <c r="D9" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="2">
+        <v>3</v>
+      </c>
+      <c r="D10" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="2">
+        <v>3</v>
+      </c>
+      <c r="D11" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="2">
+        <v>3</v>
+      </c>
+      <c r="D12" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="2">
+        <v>4</v>
+      </c>
+      <c r="D13" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="2">
+        <v>4</v>
+      </c>
+      <c r="D14" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="2">
+        <v>5</v>
+      </c>
+      <c r="D15" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="2">
+        <v>5</v>
+      </c>
+      <c r="D16" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2">
+        <f>AVERAGE(D2:D16)</f>
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="4">
+        <v>2</v>
+      </c>
+      <c r="D22" s="4">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="4">
+        <v>3</v>
+      </c>
+      <c r="D23" s="4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" s="4">
+        <v>3</v>
+      </c>
+      <c r="D24" s="4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" s="4">
+        <v>3</v>
+      </c>
+      <c r="D25" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="4">
+        <v>4</v>
+      </c>
+      <c r="D26" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" s="4">
+        <v>4</v>
+      </c>
+      <c r="D27" s="4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C28" s="4">
+        <v>5</v>
+      </c>
+      <c r="D28" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C29" s="4">
+        <v>6</v>
+      </c>
+      <c r="D29" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="4"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="4"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4">
+        <f>AVERAGE(D22:D29)</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C35" s="6">
+        <v>3</v>
+      </c>
+      <c r="D35" s="6">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C36" s="6">
+        <v>4</v>
+      </c>
+      <c r="D36" s="6">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C37" s="6">
+        <v>4</v>
+      </c>
+      <c r="D37" s="6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C38" s="6">
+        <v>4</v>
+      </c>
+      <c r="D38" s="6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C39" s="6">
+        <v>5</v>
+      </c>
+      <c r="D39" s="6">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C40" s="6">
+        <v>6</v>
+      </c>
+      <c r="D40" s="6">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C41" s="6">
+        <v>8</v>
+      </c>
+      <c r="D41" s="6">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="6"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="6"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6">
+        <f>AVERAGE(D35:D41)</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" t="s">
+        <v>39</v>
+      </c>
+      <c r="D47">
+        <f>AVERAGE(D2:D16,D22:D29,D35:D41)</f>
+        <v>13.8666666666667</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -7558,7 +6978,7 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="6" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B24" s="6">
         <v>1</v>
@@ -7569,7 +6989,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="6" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B25" s="6">
         <v>2</v>
@@ -7580,7 +7000,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="6" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B26" s="6">
         <v>2</v>
@@ -7591,7 +7011,7 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B27" s="6">
         <v>2</v>
@@ -7602,7 +7022,7 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="6" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B28" s="6">
         <v>5</v>
@@ -7638,7 +7058,7 @@
         <v>39</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C34" s="7">
         <f>AVERAGE(C2:C7,C13:C18,C24:C28)</f>
@@ -7851,7 +7271,7 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B24" s="6">
         <v>4</v>
@@ -7862,7 +7282,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="6" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B25" s="6">
         <v>4</v>
@@ -7873,7 +7293,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="6" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B26" s="6">
         <v>7</v>
@@ -7909,7 +7329,7 @@
         <v>39</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C32" s="7">
         <f>AVERAGE(C2:C5,C11:C18,C24:C26)</f>
@@ -7990,7 +7410,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B6" s="2">
         <v>3</v>
@@ -8001,7 +7421,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B7" s="2">
         <v>3</v>
@@ -8012,7 +7432,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B8" s="2">
         <v>3</v>
@@ -8023,7 +7443,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B9" s="2">
         <v>3</v>
@@ -8034,7 +7454,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B10" s="2">
         <v>3</v>
@@ -8045,7 +7465,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B11" s="2">
         <v>3</v>
@@ -8056,7 +7476,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B12" s="2">
         <v>4</v>
@@ -8100,7 +7520,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B19" s="4">
         <v>3</v>
@@ -8111,7 +7531,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B20" s="4">
         <v>4</v>
@@ -8144,7 +7564,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="6" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B26" s="6">
         <v>3</v>
@@ -8155,7 +7575,7 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="6" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B27" s="6">
         <v>4</v>
@@ -8166,7 +7586,7 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="6" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B28" s="6">
         <v>4</v>
@@ -8202,7 +7622,7 @@
         <v>39</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C34" s="7">
         <f>AVERAGE(C2:C12,C18:C20,C26:C28)</f>
@@ -8239,7 +7659,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B2" s="2">
         <v>1</v>
@@ -8250,7 +7670,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B3" s="2">
         <v>1</v>
@@ -8261,7 +7681,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B4" s="2">
         <v>2</v>
@@ -8272,7 +7692,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B5" s="2">
         <v>2</v>
@@ -8283,7 +7703,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B6" s="2">
         <v>4</v>
@@ -8316,7 +7736,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B12" s="4">
         <v>2</v>
@@ -8327,7 +7747,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B13" s="4">
         <v>2</v>
@@ -8338,7 +7758,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B14" s="4">
         <v>4</v>
@@ -8349,7 +7769,7 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B15" s="4">
         <v>5</v>
@@ -8405,7 +7825,7 @@
         <v>12</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C25" s="6" t="e">
         <f>AVERAGE(C21,C22)</f>
@@ -8417,7 +7837,7 @@
         <v>39</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C28" s="7">
         <f>AVERAGE(C2:C6,C12:C15,C21:C22)</f>

--- a/src/utils/sxsyzlzq/zzz_cardList.xlsx
+++ b/src/utils/sxsyzlzq/zzz_cardList.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="13380" activeTab="11"/>
+    <workbookView windowWidth="28800" windowHeight="13380" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="伊萝莲" sheetId="1" r:id="rId1"/>
@@ -271,7 +271,7 @@
     <t>悟能禅杖</t>
   </si>
   <si>
-    <t>帝禅意卡等：</t>
+    <t>禅意卡等：</t>
   </si>
   <si>
     <t>冥河守卫</t>
@@ -440,8 +440,8 @@
   <numFmts count="4">
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -493,6 +493,22 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -500,9 +516,22 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -517,14 +546,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -555,22 +585,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -586,13 +601,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -623,14 +631,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
@@ -646,7 +646,151 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -658,13 +802,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -676,157 +826,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -857,6 +857,17 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
@@ -879,15 +890,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -906,19 +908,17 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -945,10 +945,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -957,133 +957,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/src/utils/sxsyzlzq/zzz_cardList.xlsx
+++ b/src/utils/sxsyzlzq/zzz_cardList.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="13380" activeTab="7"/>
+    <workbookView windowWidth="28800" windowHeight="13380" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet name="伊萝莲" sheetId="1" r:id="rId1"/>
@@ -19,14 +19,14 @@
     <sheet name="熙" sheetId="9" r:id="rId10"/>
     <sheet name="尤瑞艾莉" sheetId="12" r:id="rId11"/>
     <sheet name="希拉" sheetId="10" r:id="rId12"/>
-    <sheet name="统计" sheetId="13" r:id="rId13"/>
+    <sheet name="圣母统计" sheetId="13" r:id="rId13"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="130">
   <si>
     <t>名称</t>
   </si>
@@ -94,102 +94,108 @@
     <t>学仆-脉冲型</t>
   </si>
   <si>
+    <t>圣殿骑士</t>
+  </si>
+  <si>
     <t>幻域秘树</t>
   </si>
   <si>
     <t>召集护卫</t>
   </si>
   <si>
+    <t>惩戒天使</t>
+  </si>
+  <si>
+    <t>禁卫指挥官</t>
+  </si>
+  <si>
+    <t>米拉方舟</t>
+  </si>
+  <si>
+    <t>紫色卡等：</t>
+  </si>
+  <si>
+    <t>花光春影·安娜贝尔</t>
+  </si>
+  <si>
+    <t>橙色</t>
+  </si>
+  <si>
+    <t>百花长枪·卡罗琳</t>
+  </si>
+  <si>
+    <t>流星-7号</t>
+  </si>
+  <si>
+    <t>明日香·露娜</t>
+  </si>
+  <si>
+    <t>月之神·米拉</t>
+  </si>
+  <si>
+    <t>白袍·伊恩</t>
+  </si>
+  <si>
+    <t>火蛇巫女·沃凡瑞拉</t>
+  </si>
+  <si>
+    <t>武圣·云长</t>
+  </si>
+  <si>
+    <t>橙色卡等：</t>
+  </si>
+  <si>
+    <t>总计：</t>
+  </si>
+  <si>
+    <t>学仆-观测型</t>
+  </si>
+  <si>
     <t>观星台大预言家</t>
   </si>
   <si>
-    <t>惩戒天使</t>
-  </si>
-  <si>
-    <t>禁卫指挥官</t>
-  </si>
-  <si>
-    <t>米拉方舟</t>
-  </si>
-  <si>
-    <t>紫色卡等：</t>
-  </si>
-  <si>
-    <t>花光春影·安娜贝尔</t>
-  </si>
-  <si>
-    <t>橙色</t>
-  </si>
-  <si>
-    <t>百花长枪·卡罗琳</t>
-  </si>
-  <si>
-    <t>流星-7号</t>
-  </si>
-  <si>
-    <t>明日香·露娜</t>
-  </si>
-  <si>
-    <t>月之神·米拉</t>
-  </si>
-  <si>
-    <t>白袍·伊恩</t>
-  </si>
-  <si>
-    <t>火蛇巫女·沃凡瑞拉</t>
-  </si>
-  <si>
-    <t>武圣·云长</t>
-  </si>
-  <si>
-    <t>橙色卡等：</t>
-  </si>
-  <si>
-    <t>总计：</t>
-  </si>
-  <si>
-    <t>学仆-观测型</t>
-  </si>
-  <si>
     <t>卜命道长</t>
   </si>
   <si>
+    <t>苦行武僧</t>
+  </si>
+  <si>
+    <t>执剑道人</t>
+  </si>
+  <si>
+    <t>连击</t>
+  </si>
+  <si>
+    <t>深山采药人</t>
+  </si>
+  <si>
+    <t>风铃道人</t>
+  </si>
+  <si>
+    <t>驱魔道人</t>
+  </si>
+  <si>
+    <t>扫叶僧</t>
+  </si>
+  <si>
+    <t>御风武者</t>
+  </si>
+  <si>
+    <t>万物之灵</t>
+  </si>
+  <si>
+    <t>神机玄女·轩</t>
+  </si>
+  <si>
+    <t>上宝沁金耙</t>
+  </si>
+  <si>
     <t>白羊药师</t>
   </si>
   <si>
     <t>树木之怒</t>
   </si>
   <si>
-    <t>苦行武僧</t>
-  </si>
-  <si>
-    <t>执剑道人</t>
-  </si>
-  <si>
-    <t>连击</t>
-  </si>
-  <si>
-    <t>深山采药人</t>
-  </si>
-  <si>
-    <t>风铃道人</t>
-  </si>
-  <si>
-    <t>驱魔道人</t>
-  </si>
-  <si>
-    <t>扫叶僧</t>
-  </si>
-  <si>
-    <t>御风武者</t>
-  </si>
-  <si>
-    <t>神机玄女·轩</t>
-  </si>
-  <si>
-    <t>上宝沁金耙</t>
-  </si>
-  <si>
     <t>执剑道者</t>
   </si>
   <si>
@@ -208,178 +214,157 @@
     <t>旅行背包</t>
   </si>
   <si>
+    <t>祥云师太</t>
+  </si>
+  <si>
+    <t>曙光·安娜贝尔</t>
+  </si>
+  <si>
+    <t>圣枪·卡罗琳</t>
+  </si>
+  <si>
+    <t>明日之音·露娜</t>
+  </si>
+  <si>
+    <t>正阳大主教·伊恩</t>
+  </si>
+  <si>
+    <t>钢铁统帅·雷蒙德</t>
+  </si>
+  <si>
+    <t>帝国卡等：</t>
+  </si>
+  <si>
+    <t>鬼童7号</t>
+  </si>
+  <si>
+    <t>No.2时光·米拉</t>
+  </si>
+  <si>
+    <t>No.6沃凡瑞拉</t>
+  </si>
+  <si>
+    <t>隐秘卡等：</t>
+  </si>
+  <si>
+    <t>悟能禅杖</t>
+  </si>
+  <si>
+    <t>禅意卡等：</t>
+  </si>
+  <si>
+    <t>冥河守卫</t>
+  </si>
+  <si>
+    <t>落雷击</t>
+  </si>
+  <si>
+    <t>邪眼魔</t>
+  </si>
+  <si>
+    <t>残暴爪钩</t>
+  </si>
+  <si>
+    <t>烈焰风暴</t>
+  </si>
+  <si>
+    <t>碎颅魔</t>
+  </si>
+  <si>
+    <t>觅食大嘴兽</t>
+  </si>
+  <si>
+    <t>灼神双炎</t>
+  </si>
+  <si>
+    <t>雷光炼狱</t>
+  </si>
+  <si>
+    <t>橙色色卡等：</t>
+  </si>
+  <si>
+    <t>炼狱卡等：</t>
+  </si>
+  <si>
+    <t>箭竹守卫</t>
+  </si>
+  <si>
+    <t>疾风猎手</t>
+  </si>
+  <si>
+    <t>逍遥琴师</t>
+  </si>
+  <si>
+    <t>绝望镰魔</t>
+  </si>
+  <si>
+    <t>岩浆球</t>
+  </si>
+  <si>
+    <t>地狱屠夫</t>
+  </si>
+  <si>
+    <t>恶灵魔焰</t>
+  </si>
+  <si>
+    <t>痛苦之心</t>
+  </si>
+  <si>
+    <t>怨魂饕餮兽</t>
+  </si>
+  <si>
+    <t>猩红勇士</t>
+  </si>
+  <si>
+    <t>阵营</t>
+  </si>
+  <si>
+    <t>数量</t>
+  </si>
+  <si>
+    <t>No.8雷鸣·泰拉德</t>
+  </si>
+  <si>
+    <t>隐秘</t>
+  </si>
+  <si>
     <t>重装固守</t>
   </si>
   <si>
-    <t>龟族僧人</t>
-  </si>
-  <si>
-    <t>叶幻师</t>
-  </si>
-  <si>
-    <t>风卷残云</t>
-  </si>
-  <si>
-    <t>祥云师太</t>
+    <t>帝国</t>
+  </si>
+  <si>
+    <t>传记·钢铁守卫</t>
+  </si>
+  <si>
+    <t>圣殿卫士</t>
+  </si>
+  <si>
+    <t>圣甲先锋</t>
+  </si>
+  <si>
+    <t>咒术系学士</t>
+  </si>
+  <si>
+    <t>传记·海市蜃楼·蛇</t>
+  </si>
+  <si>
+    <t>No.5咒刃·布雷克</t>
+  </si>
+  <si>
+    <t>圣殿弩手</t>
+  </si>
+  <si>
+    <t>魔像-御咒铁卫</t>
+  </si>
+  <si>
+    <t>缄言法师</t>
+  </si>
+  <si>
+    <t>白袍主教</t>
   </si>
   <si>
     <t>冲锋装备</t>
-  </si>
-  <si>
-    <t>蟠桃会</t>
-  </si>
-  <si>
-    <t>万物之灵</t>
-  </si>
-  <si>
-    <t>永恒之王·莱哈特</t>
-  </si>
-  <si>
-    <t>曙光·安娜贝尔</t>
-  </si>
-  <si>
-    <t>圣枪·卡罗琳</t>
-  </si>
-  <si>
-    <t>明日之音·露娜</t>
-  </si>
-  <si>
-    <t>正阳大主教·伊恩</t>
-  </si>
-  <si>
-    <t>钢铁统帅·雷蒙德</t>
-  </si>
-  <si>
-    <t>帝国卡等：</t>
-  </si>
-  <si>
-    <t>鬼童7号</t>
-  </si>
-  <si>
-    <t>No.2时光·米拉</t>
-  </si>
-  <si>
-    <t>No.6沃凡瑞拉</t>
-  </si>
-  <si>
-    <t>隐秘卡等：</t>
-  </si>
-  <si>
-    <t>疾风猎手</t>
-  </si>
-  <si>
-    <t>悟能禅杖</t>
-  </si>
-  <si>
-    <t>禅意卡等：</t>
-  </si>
-  <si>
-    <t>冥河守卫</t>
-  </si>
-  <si>
-    <t>落雷击</t>
-  </si>
-  <si>
-    <t>邪眼魔</t>
-  </si>
-  <si>
-    <t>残暴爪钩</t>
-  </si>
-  <si>
-    <t>烈焰风暴</t>
-  </si>
-  <si>
-    <t>碎颅魔</t>
-  </si>
-  <si>
-    <t>觅食大嘴兽</t>
-  </si>
-  <si>
-    <t>灼神双炎</t>
-  </si>
-  <si>
-    <t>雷光炼狱</t>
-  </si>
-  <si>
-    <t>橙色色卡等：</t>
-  </si>
-  <si>
-    <t>炼狱卡等：</t>
-  </si>
-  <si>
-    <t>箭竹守卫</t>
-  </si>
-  <si>
-    <t>逍遥琴师</t>
-  </si>
-  <si>
-    <t>绝望镰魔</t>
-  </si>
-  <si>
-    <t>岩浆球</t>
-  </si>
-  <si>
-    <t>地狱屠夫</t>
-  </si>
-  <si>
-    <t>恶灵魔焰</t>
-  </si>
-  <si>
-    <t>痛苦之心</t>
-  </si>
-  <si>
-    <t>怨魂饕餮兽</t>
-  </si>
-  <si>
-    <t>猩红勇士</t>
-  </si>
-  <si>
-    <t>阵营</t>
-  </si>
-  <si>
-    <t>数量</t>
-  </si>
-  <si>
-    <t>No.8雷鸣·泰拉德</t>
-  </si>
-  <si>
-    <t>隐秘</t>
-  </si>
-  <si>
-    <t>帝国</t>
-  </si>
-  <si>
-    <t>传记·钢铁守卫</t>
-  </si>
-  <si>
-    <t>圣殿卫士</t>
-  </si>
-  <si>
-    <t>圣甲先锋</t>
-  </si>
-  <si>
-    <t>咒术系学士</t>
-  </si>
-  <si>
-    <t>传记·海市蜃楼·蛇</t>
-  </si>
-  <si>
-    <t>No.5咒刃·布雷克</t>
-  </si>
-  <si>
-    <t>圣殿弩手</t>
-  </si>
-  <si>
-    <t>魔像-御咒铁卫</t>
-  </si>
-  <si>
-    <t>缄言法师</t>
-  </si>
-  <si>
-    <t>白袍主教</t>
-  </si>
-  <si>
-    <t>圣殿骑士</t>
   </si>
   <si>
     <t>圣殿精英</t>
@@ -438,10 +423,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -493,9 +478,38 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -508,14 +522,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
@@ -523,15 +529,40 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -553,22 +584,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
@@ -584,23 +599,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -613,25 +614,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -646,7 +631,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -658,19 +661,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -682,7 +733,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -694,55 +757,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -754,19 +769,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -784,49 +793,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -840,28 +825,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
+      <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
+      <bottom style="double">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -871,6 +845,21 @@
       <top/>
       <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -890,26 +879,22 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -923,16 +908,16 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="double">
+      <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
+      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -945,10 +930,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -957,133 +942,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1701,10 +1686,10 @@
         <v>15</v>
       </c>
       <c r="C23" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D23" s="4">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -1718,7 +1703,7 @@
         <v>4</v>
       </c>
       <c r="D24" s="4">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -1729,10 +1714,10 @@
         <v>15</v>
       </c>
       <c r="C25" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D25" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -1800,7 +1785,7 @@
       <c r="C31" s="4"/>
       <c r="D31" s="4">
         <f>AVERAGE(D15:D28)</f>
-        <v>14.4285714285714</v>
+        <v>14.5714285714286</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -1842,7 +1827,7 @@
         <v>4</v>
       </c>
       <c r="D36" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1937,7 +1922,7 @@
       <c r="C44" s="6"/>
       <c r="D44" s="6">
         <f>AVERAGE(D34:D41)</f>
-        <v>13.125</v>
+        <v>13.25</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1948,7 +1933,7 @@
       <c r="C47" s="7"/>
       <c r="D47" s="7">
         <f>AVERAGE(D2:D9,D15:D28,D34:D41)</f>
-        <v>14.4666666666667</v>
+        <v>14.5666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -1984,7 +1969,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>5</v>
@@ -1998,7 +1983,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
@@ -2012,7 +1997,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
@@ -2026,7 +2011,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -2040,7 +2025,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>5</v>
@@ -2054,7 +2039,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>5</v>
@@ -2068,7 +2053,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>5</v>
@@ -2082,7 +2067,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>5</v>
@@ -2096,7 +2081,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>5</v>
@@ -2110,7 +2095,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>5</v>
@@ -2124,7 +2109,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>5</v>
@@ -2138,7 +2123,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>5</v>
@@ -2152,7 +2137,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>5</v>
@@ -2166,7 +2151,7 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>5</v>
@@ -2180,7 +2165,7 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>5</v>
@@ -2219,7 +2204,7 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="4" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>15</v>
@@ -2233,7 +2218,7 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="4" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>15</v>
@@ -2247,7 +2232,7 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>15</v>
@@ -2261,7 +2246,7 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="4" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>15</v>
@@ -2275,7 +2260,7 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="4" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>15</v>
@@ -2289,7 +2274,7 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="4" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>15</v>
@@ -2303,7 +2288,7 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>15</v>
@@ -2317,7 +2302,7 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="4" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>15</v>
@@ -2331,7 +2316,7 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="4" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>15</v>
@@ -2345,7 +2330,7 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="4" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>15</v>
@@ -2359,7 +2344,7 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="4" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>15</v>
@@ -2399,7 +2384,7 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="6" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>30</v>
@@ -2441,7 +2426,7 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="6" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>30</v>
@@ -2521,7 +2506,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>5</v>
@@ -2535,7 +2520,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
@@ -2563,7 +2548,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -2577,7 +2562,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>5</v>
@@ -2591,7 +2576,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>5</v>
@@ -2633,7 +2618,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>5</v>
@@ -2647,7 +2632,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>5</v>
@@ -2728,7 +2713,7 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="4" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>15</v>
@@ -2784,7 +2769,7 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="4" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>15</v>
@@ -2798,7 +2783,7 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="4" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>15</v>
@@ -2812,7 +2797,7 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>15</v>
@@ -2826,7 +2811,7 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="4" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>15</v>
@@ -2840,7 +2825,7 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="4" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>15</v>
@@ -2854,7 +2839,7 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="4" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>15</v>
@@ -2868,7 +2853,7 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="4" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>15</v>
@@ -2882,7 +2867,7 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="4" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>15</v>
@@ -2935,7 +2920,7 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="6" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>30</v>
@@ -2963,7 +2948,7 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="6" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>30</v>
@@ -3055,7 +3040,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>5</v>
@@ -3069,7 +3054,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
@@ -3083,7 +3068,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
@@ -3097,7 +3082,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -3111,7 +3096,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>5</v>
@@ -3125,7 +3110,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>5</v>
@@ -3139,7 +3124,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>5</v>
@@ -3153,7 +3138,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>5</v>
@@ -3167,7 +3152,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>5</v>
@@ -3181,7 +3166,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>5</v>
@@ -3195,7 +3180,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>5</v>
@@ -3209,7 +3194,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>5</v>
@@ -3223,7 +3208,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>5</v>
@@ -3237,7 +3222,7 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>5</v>
@@ -3251,7 +3236,7 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>5</v>
@@ -3265,7 +3250,7 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>5</v>
@@ -3304,7 +3289,7 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="4" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>15</v>
@@ -3318,7 +3303,7 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="4" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>15</v>
@@ -3332,7 +3317,7 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>15</v>
@@ -3346,7 +3331,7 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="4" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>15</v>
@@ -3360,7 +3345,7 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="4" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>15</v>
@@ -3374,7 +3359,7 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="4" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>15</v>
@@ -3388,7 +3373,7 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>15</v>
@@ -3402,7 +3387,7 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="4" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>15</v>
@@ -3416,7 +3401,7 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="4" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>15</v>
@@ -3430,7 +3415,7 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="4" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>15</v>
@@ -3444,7 +3429,7 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="4" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>15</v>
@@ -3484,7 +3469,7 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="6" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>30</v>
@@ -3512,7 +3497,7 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="6" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>30</v>
@@ -3581,7 +3566,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -3590,15 +3575,15 @@
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>30</v>
@@ -3612,10 +3597,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>5</v>
@@ -3629,10 +3614,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>5</v>
@@ -3649,7 +3634,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>5</v>
@@ -3666,7 +3651,7 @@
         <v>16</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>15</v>
@@ -3683,7 +3668,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>15</v>
@@ -3697,10 +3682,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="4" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>15</v>
@@ -3714,10 +3699,10 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>5</v>
@@ -3734,7 +3719,7 @@
         <v>40</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>5</v>
@@ -3751,7 +3736,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>5</v>
@@ -3765,10 +3750,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>5</v>
@@ -3785,7 +3770,7 @@
         <v>8</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>5</v>
@@ -3799,10 +3784,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="4" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>15</v>
@@ -3816,10 +3801,10 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="4" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>15</v>
@@ -3836,7 +3821,7 @@
         <v>17</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>15</v>
@@ -3853,7 +3838,7 @@
         <v>19</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>15</v>
@@ -3870,7 +3855,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>15</v>
@@ -3884,10 +3869,10 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>30</v>
@@ -3901,10 +3886,10 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>30</v>
@@ -3918,10 +3903,10 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>30</v>
@@ -3935,10 +3920,10 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>5</v>
@@ -3955,7 +3940,7 @@
         <v>9</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>5</v>
@@ -3972,7 +3957,7 @@
         <v>10</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>5</v>
@@ -3986,10 +3971,10 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="4" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>15</v>
@@ -4003,10 +3988,10 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="4" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>15</v>
@@ -4023,7 +4008,7 @@
         <v>21</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>15</v>
@@ -4040,7 +4025,7 @@
         <v>20</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>15</v>
@@ -4054,10 +4039,10 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="4" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>15</v>
@@ -4071,10 +4056,10 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="4" t="s">
-        <v>65</v>
+        <v>112</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>15</v>
@@ -4088,10 +4073,10 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="4" t="s">
-        <v>117</v>
+        <v>22</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>15</v>
@@ -4105,10 +4090,10 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>30</v>
@@ -4122,10 +4107,10 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>30</v>
@@ -4139,10 +4124,10 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>30</v>
@@ -4156,10 +4141,10 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>5</v>
@@ -4173,10 +4158,10 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>15</v>
@@ -4190,10 +4175,10 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="4" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>15</v>
@@ -4207,10 +4192,10 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="4" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>15</v>
@@ -4224,10 +4209,10 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>15</v>
@@ -4241,10 +4226,10 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="4" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>15</v>
@@ -4258,10 +4243,10 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="4" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>15</v>
@@ -4275,10 +4260,10 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>15</v>
@@ -4292,10 +4277,10 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>30</v>
@@ -4309,10 +4294,10 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>30</v>
@@ -4329,7 +4314,7 @@
         <v>11</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>5</v>
@@ -4343,10 +4328,10 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="4" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>15</v>
@@ -4360,10 +4345,10 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="4" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>15</v>
@@ -4377,10 +4362,10 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="4" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>15</v>
@@ -4394,10 +4379,10 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>30</v>
@@ -4411,10 +4396,10 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="4" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>15</v>
@@ -4431,7 +4416,7 @@
         <v>26</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>15</v>
@@ -4445,10 +4430,10 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>30</v>
@@ -4462,10 +4447,10 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>30</v>
@@ -4479,10 +4464,10 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="4" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>15</v>
@@ -4496,10 +4481,10 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="4" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>15</v>
@@ -4513,10 +4498,10 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="4" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>15</v>
@@ -4530,10 +4515,10 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="4" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>15</v>
@@ -4550,7 +4535,7 @@
         <v>27</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>15</v>
@@ -4599,7 +4584,7 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -4619,7 +4604,7 @@
       </c>
       <c r="B66" s="2"/>
       <c r="C66" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" s="2">
@@ -4925,7 +4910,7 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>15</v>
@@ -4939,7 +4924,7 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>15</v>
@@ -4953,7 +4938,7 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="4" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>15</v>
@@ -5071,7 +5056,7 @@
         <v>4</v>
       </c>
       <c r="D37" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -5152,7 +5137,7 @@
       <c r="C44" s="6"/>
       <c r="D44" s="6">
         <f>AVERAGE(D35:D41)</f>
-        <v>13.1428571428571</v>
+        <v>13.2857142857143</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -5161,7 +5146,7 @@
       </c>
       <c r="D47">
         <f>AVERAGE(D2:D10,D16:D29,D35:D41)</f>
-        <v>14.4333333333333</v>
+        <v>14.4666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -5174,7 +5159,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D47"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="17.875" customWidth="1"/>
@@ -5211,7 +5196,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
@@ -5239,7 +5224,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -5248,21 +5233,21 @@
         <v>2</v>
       </c>
       <c r="D5" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -5273,15 +5258,15 @@
         <v>5</v>
       </c>
       <c r="C7" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>5</v>
@@ -5290,7 +5275,7 @@
         <v>3</v>
       </c>
       <c r="D8" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -5304,12 +5289,12 @@
         <v>3</v>
       </c>
       <c r="D9" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>5</v>
@@ -5318,7 +5303,7 @@
         <v>3</v>
       </c>
       <c r="D10" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -5332,135 +5317,135 @@
         <v>3</v>
       </c>
       <c r="D11" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C12" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D13" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D14" s="2">
         <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15" s="2">
-        <v>5</v>
-      </c>
-      <c r="D15" s="2">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2">
+        <f>AVERAGE(D2:D14)</f>
+        <v>15.1538461538462</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="4" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C16" s="2">
-        <v>5</v>
-      </c>
-      <c r="D16" s="2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2">
-        <f>AVERAGE(D2:D16)</f>
-        <v>15.1333333333333</v>
+      <c r="B20" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="4">
+        <v>1</v>
+      </c>
+      <c r="D20" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="4">
+        <v>2</v>
+      </c>
+      <c r="D21" s="4">
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="4">
+        <v>3</v>
+      </c>
+      <c r="D22" s="4">
         <v>16</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C22" s="4">
-        <v>1</v>
-      </c>
-      <c r="D22" s="4">
-        <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="4" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C23" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D23" s="4">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="4" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>15</v>
@@ -5469,18 +5454,18 @@
         <v>3</v>
       </c>
       <c r="D24" s="4">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C25" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D25" s="4">
         <v>14</v>
@@ -5488,16 +5473,16 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="4" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C26" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D26" s="4">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -5508,39 +5493,31 @@
         <v>15</v>
       </c>
       <c r="C27" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D27" s="4">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C28" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D28" s="4">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C29" s="4">
-        <v>6</v>
-      </c>
-      <c r="D29" s="4">
-        <v>15</v>
-      </c>
+      <c r="A29" s="4"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="4"/>
@@ -5549,41 +5526,49 @@
       <c r="D30" s="4"/>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="4"/>
-      <c r="B31" s="4"/>
+      <c r="A31" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>28</v>
+      </c>
       <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4">
-        <f>AVERAGE(D22:D29)</f>
-        <v>14.5</v>
+      <c r="D31" s="4">
+        <f>AVERAGE(D20:D28)</f>
+        <v>14.3333333333333</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" s="6">
+        <v>3</v>
+      </c>
+      <c r="D34" s="6">
+        <v>13</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C35" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D35" s="6">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>30</v>
@@ -5592,12 +5577,12 @@
         <v>4</v>
       </c>
       <c r="D36" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="6" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>30</v>
@@ -5611,7 +5596,7 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>30</v>
@@ -5625,45 +5610,37 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="6" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C39" s="6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D39" s="6">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C40" s="6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D40" s="6">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C41" s="6">
-        <v>8</v>
-      </c>
-      <c r="D41" s="6">
-        <v>13</v>
-      </c>
+      <c r="A41" s="6"/>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="6"/>
@@ -5672,31 +5649,25 @@
       <c r="D42" s="6"/>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="6"/>
-      <c r="B43" s="6"/>
+      <c r="A43" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>38</v>
+      </c>
       <c r="C43" s="6"/>
-      <c r="D43" s="6"/>
-    </row>
-    <row r="44" spans="1:4">
-      <c r="A44" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C44" s="6"/>
-      <c r="D44" s="6">
-        <f>AVERAGE(D35:D41)</f>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
-      <c r="A47" t="s">
+      <c r="D43" s="6">
+        <f>AVERAGE(D34:D40)</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" t="s">
         <v>39</v>
       </c>
-      <c r="D47">
-        <f>AVERAGE(D2:D16,D22:D29,D35:D41)</f>
-        <v>14.4666666666667</v>
+      <c r="D46">
+        <f>AVERAGE(D2:D14,D20:D28,D34:D40)</f>
+        <v>14.3793103448276</v>
       </c>
     </row>
   </sheetData>
@@ -5731,7 +5702,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>5</v>
@@ -5759,7 +5730,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
@@ -5773,7 +5744,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -5787,7 +5758,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>5</v>
@@ -5829,7 +5800,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>5</v>
@@ -5843,7 +5814,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>5</v>
@@ -5857,7 +5828,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>5</v>
@@ -5871,7 +5842,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>5</v>
@@ -5885,7 +5856,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>5</v>
@@ -5899,7 +5870,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>5</v>
@@ -5980,7 +5951,7 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>15</v>
@@ -5994,7 +5965,7 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>15</v>
@@ -6036,7 +6007,7 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>15</v>
@@ -6050,7 +6021,7 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>15</v>
@@ -6064,7 +6035,7 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="4" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>15</v>
@@ -6118,7 +6089,7 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>30</v>
@@ -6146,7 +6117,7 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>30</v>
@@ -6188,7 +6159,7 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>30</v>
@@ -6277,12 +6248,12 @@
         <v>1</v>
       </c>
       <c r="D2" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
@@ -6291,12 +6262,12 @@
         <v>1</v>
       </c>
       <c r="D3" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
@@ -6310,30 +6281,30 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -6347,12 +6318,12 @@
         <v>3</v>
       </c>
       <c r="D7" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>5</v>
@@ -6361,12 +6332,12 @@
         <v>3</v>
       </c>
       <c r="D8" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>5</v>
@@ -6375,12 +6346,12 @@
         <v>3</v>
       </c>
       <c r="D9" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>5</v>
@@ -6389,12 +6360,12 @@
         <v>3</v>
       </c>
       <c r="D10" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>5</v>
@@ -6408,21 +6379,21 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C12" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>5</v>
@@ -6431,21 +6402,21 @@
         <v>4</v>
       </c>
       <c r="D13" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D14" s="2">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -6459,22 +6430,14 @@
         <v>5</v>
       </c>
       <c r="D15" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C16" s="2">
-        <v>5</v>
-      </c>
-      <c r="D16" s="2">
-        <v>15</v>
-      </c>
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2"/>
@@ -6483,22 +6446,30 @@
       <c r="D17" s="2"/>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
+      <c r="A18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2">
-        <f>AVERAGE(D2:D16)</f>
-        <v>14.2</v>
+      <c r="D18" s="2">
+        <f>AVERAGE(D2:D15)</f>
+        <v>14.6428571428571</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="4">
+        <v>1</v>
+      </c>
+      <c r="D21" s="4">
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -6517,7 +6488,7 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="4" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>15</v>
@@ -6531,7 +6502,7 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>15</v>
@@ -6545,7 +6516,7 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="4" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>15</v>
@@ -6554,12 +6525,12 @@
         <v>3</v>
       </c>
       <c r="D25" s="4">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>15</v>
@@ -6573,7 +6544,7 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="4" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>15</v>
@@ -6582,12 +6553,12 @@
         <v>4</v>
       </c>
       <c r="D27" s="4">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="4" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>15</v>
@@ -6634,8 +6605,8 @@
       </c>
       <c r="C32" s="4"/>
       <c r="D32" s="4">
-        <f>AVERAGE(D22:D29)</f>
-        <v>14</v>
+        <f>AVERAGE(D21:D29)</f>
+        <v>13.8888888888889</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -6668,7 +6639,7 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="6" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>30</v>
@@ -6682,7 +6653,7 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="6" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>30</v>
@@ -6696,16 +6667,16 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="6" t="s">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C39" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D39" s="6">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -6758,7 +6729,7 @@
       <c r="C44" s="6"/>
       <c r="D44" s="6">
         <f>AVERAGE(D35:D41)</f>
-        <v>13</v>
+        <v>12.7142857142857</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -6766,8 +6737,8 @@
         <v>39</v>
       </c>
       <c r="D47">
-        <f>AVERAGE(D2:D16,D22:D29,D35:D41)</f>
-        <v>13.8666666666667</v>
+        <f>AVERAGE(D2:D15,D21:D29,D35:D41)</f>
+        <v>13.9666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -6780,7 +6751,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="16.375" customWidth="1"/>
@@ -6923,41 +6894,47 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B16" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C16" s="4">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B17" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C17" s="4">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B18" s="4">
         <v>6</v>
       </c>
       <c r="C18" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="4">
+        <v>6</v>
+      </c>
+      <c r="C19" s="4">
         <v>14</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4"/>
@@ -6965,76 +6942,76 @@
       <c r="C20" s="4"/>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B21" s="4" t="s">
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C21" s="4">
-        <f>AVERAGE(C13:C18)</f>
-        <v>14.5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="B24" s="6">
-        <v>1</v>
-      </c>
-      <c r="C24" s="6">
-        <v>13</v>
+      <c r="C22" s="4">
+        <f>AVERAGE(C13:C19)</f>
+        <v>14.4285714285714</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="6" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="B25" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C25" s="6">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="6" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B26" s="6">
         <v>2</v>
       </c>
       <c r="C26" s="6">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="6" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="B27" s="6">
         <v>2</v>
       </c>
       <c r="C27" s="6">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="6" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B28" s="6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C28" s="6">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="6"/>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
+      <c r="A29" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B29" s="6">
+        <v>5</v>
+      </c>
+      <c r="C29" s="6">
+        <v>13</v>
+      </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="6"/>
@@ -7042,27 +7019,32 @@
       <c r="C30" s="6"/>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C31" s="6">
-        <f>AVERAGE(C24:C28)</f>
+      <c r="A31" s="6"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C32" s="6">
+        <f>AVERAGE(C25:C29)</f>
         <v>13.4</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="7" t="s">
+    <row r="35" spans="1:3">
+      <c r="A35" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B34" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="C34" s="7">
-        <f>AVERAGE(C2:C7,C13:C18,C24:C28)</f>
-        <v>14.7058823529412</v>
+      <c r="B35" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C35" s="7">
+        <f>AVERAGE(C2:C7,C13:C19,C25:C29)</f>
+        <v>14.6666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -7216,7 +7198,7 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B16" s="4">
         <v>4</v>
@@ -7227,7 +7209,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="B17" s="4">
         <v>5</v>
@@ -7271,18 +7253,18 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B24" s="6">
         <v>4</v>
       </c>
       <c r="C24" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="6" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B25" s="6">
         <v>4</v>
@@ -7293,7 +7275,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B26" s="6">
         <v>7</v>
@@ -7321,7 +7303,7 @@
       </c>
       <c r="C29" s="6">
         <f>AVERAGE(C24:C26)</f>
-        <v>12.6666666666667</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -7329,11 +7311,11 @@
         <v>39</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C32" s="7">
         <f>AVERAGE(C2:C5,C11:C18,C24:C26)</f>
-        <v>14.0666666666667</v>
+        <v>14.1333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -7366,7 +7348,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B2" s="2">
         <v>1</v>
@@ -7377,7 +7359,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="B3" s="2">
         <v>2</v>
@@ -7388,7 +7370,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="B4" s="2">
         <v>2</v>
@@ -7399,7 +7381,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B5" s="2">
         <v>2</v>
@@ -7410,7 +7392,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B6" s="2">
         <v>3</v>
@@ -7421,7 +7403,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B7" s="2">
         <v>3</v>
@@ -7432,7 +7414,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B8" s="2">
         <v>3</v>
@@ -7443,7 +7425,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B9" s="2">
         <v>3</v>
@@ -7454,7 +7436,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B10" s="2">
         <v>3</v>
@@ -7465,25 +7447,19 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2" t="s">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="B11" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B12" s="2">
-        <v>4</v>
-      </c>
-      <c r="C12" s="2">
-        <v>15</v>
-      </c>
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2"/>
@@ -7491,39 +7467,45 @@
       <c r="C13" s="2"/>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C15" s="2">
-        <f>AVERAGE(C2:C12)</f>
-        <v>14.4545454545455</v>
+      <c r="A14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="2">
+        <f>AVERAGE(C2:C11)</f>
+        <v>14.6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" s="4">
+        <v>3</v>
+      </c>
+      <c r="C17" s="4">
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B18" s="4">
         <v>3</v>
       </c>
       <c r="C18" s="4">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B19" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C19" s="4">
         <v>14</v>
@@ -7534,10 +7516,10 @@
         <v>51</v>
       </c>
       <c r="B20" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C20" s="4">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -7558,13 +7540,13 @@
         <v>28</v>
       </c>
       <c r="C23" s="4">
-        <f>AVERAGE(C18:C20)</f>
-        <v>14.3333333333333</v>
+        <f>AVERAGE(C17:C20)</f>
+        <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B26" s="6">
         <v>3</v>
@@ -7586,7 +7568,7 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="6" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="B28" s="6">
         <v>4</v>
@@ -7622,10 +7604,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C34" s="7">
-        <f>AVERAGE(C2:C12,C18:C20,C26:C28)</f>
+        <f>AVERAGE(C2:C11,C17:C20,C26:C28)</f>
         <v>14</v>
       </c>
     </row>
@@ -7659,7 +7641,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B2" s="2">
         <v>1</v>
@@ -7670,7 +7652,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B3" s="2">
         <v>1</v>
@@ -7681,7 +7663,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B4" s="2">
         <v>2</v>
@@ -7692,7 +7674,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="B5" s="2">
         <v>2</v>
@@ -7703,7 +7685,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="B6" s="2">
         <v>4</v>
@@ -7736,7 +7718,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B12" s="4">
         <v>2</v>
@@ -7747,7 +7729,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="B13" s="4">
         <v>2</v>
@@ -7758,7 +7740,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B14" s="4">
         <v>4</v>
@@ -7769,7 +7751,7 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="B15" s="4">
         <v>5</v>
@@ -7825,7 +7807,7 @@
         <v>12</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="C25" s="6" t="e">
         <f>AVERAGE(C21,C22)</f>
@@ -7837,7 +7819,7 @@
         <v>39</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C28" s="7">
         <f>AVERAGE(C2:C6,C12:C15,C21:C22)</f>

--- a/src/utils/sxsyzlzq/zzz_cardList.xlsx
+++ b/src/utils/sxsyzlzq/zzz_cardList.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="13380" activeTab="12"/>
+    <workbookView windowWidth="28800" windowHeight="13395" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="伊萝莲" sheetId="1" r:id="rId1"/>
@@ -21,12 +21,25 @@
     <sheet name="希拉" sheetId="10" r:id="rId12"/>
     <sheet name="圣母统计" sheetId="13" r:id="rId13"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="131">
   <si>
     <t>名称</t>
   </si>
@@ -163,130 +176,133 @@
     <t>执剑道人</t>
   </si>
   <si>
+    <t>龟族僧人</t>
+  </si>
+  <si>
     <t>连击</t>
   </si>
   <si>
     <t>深山采药人</t>
   </si>
   <si>
+    <t>驱魔道人</t>
+  </si>
+  <si>
+    <t>扫叶僧</t>
+  </si>
+  <si>
+    <t>御风武者</t>
+  </si>
+  <si>
+    <t>万物之灵</t>
+  </si>
+  <si>
+    <t>神机玄女·轩</t>
+  </si>
+  <si>
+    <t>上宝沁金耙</t>
+  </si>
+  <si>
+    <t>执剑道者</t>
+  </si>
+  <si>
+    <t>铁山靠</t>
+  </si>
+  <si>
     <t>风铃道人</t>
   </si>
   <si>
-    <t>驱魔道人</t>
-  </si>
-  <si>
-    <t>扫叶僧</t>
-  </si>
-  <si>
-    <t>御风武者</t>
-  </si>
-  <si>
-    <t>万物之灵</t>
-  </si>
-  <si>
-    <t>神机玄女·轩</t>
-  </si>
-  <si>
-    <t>上宝沁金耙</t>
+    <t>流岚刃·琳</t>
+  </si>
+  <si>
+    <t>九天玄女·轩</t>
+  </si>
+  <si>
+    <t>火蛇巫女</t>
+  </si>
+  <si>
+    <t>旅行背包</t>
+  </si>
+  <si>
+    <t>祥云师太</t>
+  </si>
+  <si>
+    <t>曙光·安娜贝尔</t>
+  </si>
+  <si>
+    <t>圣枪·卡罗琳</t>
+  </si>
+  <si>
+    <t>明日之音·露娜</t>
+  </si>
+  <si>
+    <t>正阳大主教·伊恩</t>
+  </si>
+  <si>
+    <t>钢铁统帅·雷蒙德</t>
+  </si>
+  <si>
+    <t>帝国卡等：</t>
+  </si>
+  <si>
+    <t>鬼童7号</t>
+  </si>
+  <si>
+    <t>No.2时光·米拉</t>
+  </si>
+  <si>
+    <t>No.6沃凡瑞拉</t>
+  </si>
+  <si>
+    <t>隐秘卡等：</t>
+  </si>
+  <si>
+    <t>悟能禅杖</t>
+  </si>
+  <si>
+    <t>禅意卡等：</t>
+  </si>
+  <si>
+    <t>冥河守卫</t>
+  </si>
+  <si>
+    <t>落雷击</t>
+  </si>
+  <si>
+    <t>邪眼魔</t>
+  </si>
+  <si>
+    <t>残暴爪钩</t>
+  </si>
+  <si>
+    <t>烈焰风暴</t>
+  </si>
+  <si>
+    <t>碎颅魔</t>
+  </si>
+  <si>
+    <t>觅食大嘴兽</t>
+  </si>
+  <si>
+    <t>灼神双炎</t>
+  </si>
+  <si>
+    <t>雷光炼狱</t>
+  </si>
+  <si>
+    <t>橙色色卡等：</t>
+  </si>
+  <si>
+    <t>炼狱卡等：</t>
+  </si>
+  <si>
+    <t>箭竹守卫</t>
   </si>
   <si>
     <t>白羊药师</t>
   </si>
   <si>
     <t>树木之怒</t>
-  </si>
-  <si>
-    <t>执剑道者</t>
-  </si>
-  <si>
-    <t>铁山靠</t>
-  </si>
-  <si>
-    <t>流岚刃·琳</t>
-  </si>
-  <si>
-    <t>九天玄女·轩</t>
-  </si>
-  <si>
-    <t>火蛇巫女</t>
-  </si>
-  <si>
-    <t>旅行背包</t>
-  </si>
-  <si>
-    <t>祥云师太</t>
-  </si>
-  <si>
-    <t>曙光·安娜贝尔</t>
-  </si>
-  <si>
-    <t>圣枪·卡罗琳</t>
-  </si>
-  <si>
-    <t>明日之音·露娜</t>
-  </si>
-  <si>
-    <t>正阳大主教·伊恩</t>
-  </si>
-  <si>
-    <t>钢铁统帅·雷蒙德</t>
-  </si>
-  <si>
-    <t>帝国卡等：</t>
-  </si>
-  <si>
-    <t>鬼童7号</t>
-  </si>
-  <si>
-    <t>No.2时光·米拉</t>
-  </si>
-  <si>
-    <t>No.6沃凡瑞拉</t>
-  </si>
-  <si>
-    <t>隐秘卡等：</t>
-  </si>
-  <si>
-    <t>悟能禅杖</t>
-  </si>
-  <si>
-    <t>禅意卡等：</t>
-  </si>
-  <si>
-    <t>冥河守卫</t>
-  </si>
-  <si>
-    <t>落雷击</t>
-  </si>
-  <si>
-    <t>邪眼魔</t>
-  </si>
-  <si>
-    <t>残暴爪钩</t>
-  </si>
-  <si>
-    <t>烈焰风暴</t>
-  </si>
-  <si>
-    <t>碎颅魔</t>
-  </si>
-  <si>
-    <t>觅食大嘴兽</t>
-  </si>
-  <si>
-    <t>灼神双炎</t>
-  </si>
-  <si>
-    <t>雷光炼狱</t>
-  </si>
-  <si>
-    <t>橙色色卡等：</t>
-  </si>
-  <si>
-    <t>炼狱卡等：</t>
-  </si>
-  <si>
-    <t>箭竹守卫</t>
   </si>
   <si>
     <t>疾风猎手</t>
@@ -421,12 +437,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -478,33 +494,19 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -515,17 +517,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -538,6 +534,22 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
@@ -545,16 +557,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -569,31 +581,15 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -608,15 +604,35 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -631,13 +647,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -649,19 +671,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -673,103 +695,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -787,7 +713,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -799,7 +785,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -811,7 +815,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -822,45 +838,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -883,17 +860,6 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -902,8 +868,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -922,153 +903,188 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1100,52 +1116,52 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -1440,7 +1456,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1510,7 +1526,7 @@
         <v>3</v>
       </c>
       <c r="D7" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1563,7 +1579,7 @@
       <c r="C12" s="2"/>
       <c r="D12" s="2">
         <f>AVERAGE(D2:D9)</f>
-        <v>15.875</v>
+        <v>16.125</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1855,7 +1871,7 @@
         <v>5</v>
       </c>
       <c r="D38" s="6">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -1922,7 +1938,7 @@
       <c r="C44" s="6"/>
       <c r="D44" s="6">
         <f>AVERAGE(D34:D41)</f>
-        <v>13.25</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1933,7 +1949,7 @@
       <c r="C47" s="7"/>
       <c r="D47" s="7">
         <f>AVERAGE(D2:D9,D15:D28,D34:D41)</f>
-        <v>14.5666666666667</v>
+        <v>14.7</v>
       </c>
     </row>
   </sheetData>
@@ -1969,7 +1985,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>5</v>
@@ -1997,7 +2013,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
@@ -2011,7 +2027,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -2025,7 +2041,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>5</v>
@@ -2039,7 +2055,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>5</v>
@@ -2067,7 +2083,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>5</v>
@@ -2081,7 +2097,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>5</v>
@@ -2095,7 +2111,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>5</v>
@@ -2109,7 +2125,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>5</v>
@@ -2123,7 +2139,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>5</v>
@@ -2137,7 +2153,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>5</v>
@@ -2151,7 +2167,7 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>5</v>
@@ -2165,7 +2181,7 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>5</v>
@@ -2204,7 +2220,7 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>15</v>
@@ -2218,7 +2234,7 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>15</v>
@@ -2246,7 +2262,7 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>15</v>
@@ -2260,7 +2276,7 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>15</v>
@@ -2274,7 +2290,7 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>15</v>
@@ -2302,7 +2318,7 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>15</v>
@@ -2316,7 +2332,7 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>15</v>
@@ -2330,7 +2346,7 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>15</v>
@@ -2344,7 +2360,7 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>15</v>
@@ -2384,7 +2400,7 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>30</v>
@@ -2426,7 +2442,7 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>30</v>
@@ -2506,7 +2522,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>5</v>
@@ -2520,7 +2536,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
@@ -2548,7 +2564,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -2562,7 +2578,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>5</v>
@@ -2576,7 +2592,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>5</v>
@@ -2618,7 +2634,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>5</v>
@@ -2632,7 +2648,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>5</v>
@@ -2713,7 +2729,7 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>15</v>
@@ -2769,7 +2785,7 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>15</v>
@@ -2783,7 +2799,7 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>15</v>
@@ -2811,7 +2827,7 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>15</v>
@@ -2825,7 +2841,7 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>15</v>
@@ -2839,7 +2855,7 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>15</v>
@@ -2867,7 +2883,7 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>15</v>
@@ -2920,7 +2936,7 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>30</v>
@@ -2948,7 +2964,7 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>30</v>
@@ -3040,7 +3056,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>5</v>
@@ -3068,7 +3084,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
@@ -3082,7 +3098,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -3096,7 +3112,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>5</v>
@@ -3110,7 +3126,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>5</v>
@@ -3124,7 +3140,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>5</v>
@@ -3152,7 +3168,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>5</v>
@@ -3166,7 +3182,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>5</v>
@@ -3180,7 +3196,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>5</v>
@@ -3194,7 +3210,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>5</v>
@@ -3208,7 +3224,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>5</v>
@@ -3222,7 +3238,7 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>5</v>
@@ -3236,7 +3252,7 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>5</v>
@@ -3250,7 +3266,7 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>5</v>
@@ -3289,7 +3305,7 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>15</v>
@@ -3303,7 +3319,7 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>15</v>
@@ -3331,7 +3347,7 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>15</v>
@@ -3345,7 +3361,7 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>15</v>
@@ -3359,7 +3375,7 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>15</v>
@@ -3387,7 +3403,7 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>15</v>
@@ -3401,7 +3417,7 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>15</v>
@@ -3415,7 +3431,7 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>15</v>
@@ -3429,7 +3445,7 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>15</v>
@@ -3469,7 +3485,7 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>30</v>
@@ -3497,7 +3513,7 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>30</v>
@@ -3566,7 +3582,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -3575,15 +3591,15 @@
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>30</v>
@@ -3597,10 +3613,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>5</v>
@@ -3614,10 +3630,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>5</v>
@@ -3634,7 +3650,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>5</v>
@@ -3651,7 +3667,7 @@
         <v>16</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>15</v>
@@ -3668,7 +3684,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>15</v>
@@ -3682,10 +3698,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>102</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>101</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>15</v>
@@ -3699,10 +3715,10 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>5</v>
@@ -3719,7 +3735,7 @@
         <v>40</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>5</v>
@@ -3736,7 +3752,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>5</v>
@@ -3750,10 +3766,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>5</v>
@@ -3770,7 +3786,7 @@
         <v>8</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>5</v>
@@ -3784,10 +3800,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>15</v>
@@ -3801,10 +3817,10 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>15</v>
@@ -3821,7 +3837,7 @@
         <v>17</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>15</v>
@@ -3838,7 +3854,7 @@
         <v>19</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>15</v>
@@ -3855,7 +3871,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>15</v>
@@ -3869,10 +3885,10 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>30</v>
@@ -3886,10 +3902,10 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>30</v>
@@ -3903,10 +3919,10 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>30</v>
@@ -3920,10 +3936,10 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>5</v>
@@ -3940,7 +3956,7 @@
         <v>9</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>5</v>
@@ -3957,7 +3973,7 @@
         <v>10</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>5</v>
@@ -3971,10 +3987,10 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>15</v>
@@ -3988,10 +4004,10 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>15</v>
@@ -4008,7 +4024,7 @@
         <v>21</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>15</v>
@@ -4025,7 +4041,7 @@
         <v>20</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>15</v>
@@ -4039,10 +4055,10 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>15</v>
@@ -4056,10 +4072,10 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>15</v>
@@ -4076,7 +4092,7 @@
         <v>22</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>15</v>
@@ -4090,10 +4106,10 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>30</v>
@@ -4107,10 +4123,10 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>30</v>
@@ -4124,10 +4140,10 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>30</v>
@@ -4141,10 +4157,10 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>5</v>
@@ -4158,10 +4174,10 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>15</v>
@@ -4175,10 +4191,10 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>15</v>
@@ -4192,10 +4208,10 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>15</v>
@@ -4212,7 +4228,7 @@
         <v>23</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>15</v>
@@ -4226,10 +4242,10 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>15</v>
@@ -4243,10 +4259,10 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>15</v>
@@ -4263,7 +4279,7 @@
         <v>24</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>15</v>
@@ -4277,10 +4293,10 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>30</v>
@@ -4294,10 +4310,10 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>30</v>
@@ -4314,7 +4330,7 @@
         <v>11</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>5</v>
@@ -4328,10 +4344,10 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>15</v>
@@ -4348,7 +4364,7 @@
         <v>41</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>15</v>
@@ -4362,10 +4378,10 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>15</v>
@@ -4379,10 +4395,10 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>30</v>
@@ -4396,10 +4412,10 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>15</v>
@@ -4416,7 +4432,7 @@
         <v>26</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>15</v>
@@ -4430,10 +4446,10 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>30</v>
@@ -4447,10 +4463,10 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>30</v>
@@ -4464,10 +4480,10 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>15</v>
@@ -4481,10 +4497,10 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>15</v>
@@ -4498,10 +4514,10 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>15</v>
@@ -4515,10 +4531,10 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>15</v>
@@ -4535,7 +4551,7 @@
         <v>27</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>15</v>
@@ -4584,7 +4600,7 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -4604,7 +4620,7 @@
       </c>
       <c r="B66" s="2"/>
       <c r="C66" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" s="2">
@@ -4656,7 +4672,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -4754,7 +4770,7 @@
         <v>3</v>
       </c>
       <c r="D9" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -4793,7 +4809,7 @@
       <c r="C13" s="2"/>
       <c r="D13" s="2">
         <f>AVERAGE(D2:D10)</f>
-        <v>15.4444444444444</v>
+        <v>15.6666666666667</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -5084,7 +5100,7 @@
         <v>5</v>
       </c>
       <c r="D39" s="6">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -5137,7 +5153,7 @@
       <c r="C44" s="6"/>
       <c r="D44" s="6">
         <f>AVERAGE(D35:D41)</f>
-        <v>13.2857142857143</v>
+        <v>13.5714285714286</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -5146,7 +5162,7 @@
       </c>
       <c r="D47">
         <f>AVERAGE(D2:D10,D16:D29,D35:D41)</f>
-        <v>14.4666666666667</v>
+        <v>14.6</v>
       </c>
     </row>
   </sheetData>
@@ -5261,7 +5277,7 @@
         <v>3</v>
       </c>
       <c r="D7" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -5275,7 +5291,7 @@
         <v>3</v>
       </c>
       <c r="D8" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -5294,7 +5310,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>5</v>
@@ -5303,7 +5319,7 @@
         <v>3</v>
       </c>
       <c r="D10" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -5317,7 +5333,7 @@
         <v>3</v>
       </c>
       <c r="D11" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -5328,10 +5344,10 @@
         <v>5</v>
       </c>
       <c r="C12" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D12" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -5384,7 +5400,7 @@
       <c r="C17" s="2"/>
       <c r="D17" s="2">
         <f>AVERAGE(D2:D14)</f>
-        <v>15.1538461538462</v>
+        <v>15.3076923076923</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -5605,7 +5621,7 @@
         <v>4</v>
       </c>
       <c r="D38" s="6">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -5658,7 +5674,7 @@
       <c r="C43" s="6"/>
       <c r="D43" s="6">
         <f>AVERAGE(D34:D40)</f>
-        <v>13</v>
+        <v>13.1428571428571</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -5667,7 +5683,7 @@
       </c>
       <c r="D46">
         <f>AVERAGE(D2:D14,D20:D28,D34:D40)</f>
-        <v>14.3793103448276</v>
+        <v>14.4827586206897</v>
       </c>
     </row>
   </sheetData>
@@ -5730,7 +5746,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
@@ -5739,12 +5755,12 @@
         <v>2</v>
       </c>
       <c r="D4" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -5753,12 +5769,12 @@
         <v>2</v>
       </c>
       <c r="D5" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>5</v>
@@ -5786,21 +5802,21 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" s="2">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>5</v>
@@ -5809,12 +5825,12 @@
         <v>3</v>
       </c>
       <c r="D9" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>5</v>
@@ -5828,7 +5844,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>5</v>
@@ -5842,7 +5858,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>5</v>
@@ -5856,7 +5872,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>5</v>
@@ -5870,7 +5886,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>5</v>
@@ -5879,7 +5895,7 @@
         <v>4</v>
       </c>
       <c r="D14" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -5904,7 +5920,7 @@
       <c r="C17" s="2"/>
       <c r="D17" s="2">
         <f>AVERAGE(D2:D14)</f>
-        <v>14.4615384615385</v>
+        <v>14.5384615384615</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -6089,7 +6105,7 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>30</v>
@@ -6112,12 +6128,12 @@
         <v>4</v>
       </c>
       <c r="D37" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>30</v>
@@ -6140,7 +6156,7 @@
         <v>4</v>
       </c>
       <c r="D39" s="6">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -6154,12 +6170,12 @@
         <v>5</v>
       </c>
       <c r="D40" s="6">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>30</v>
@@ -6193,7 +6209,7 @@
       <c r="C44" s="6"/>
       <c r="D44" s="6">
         <f>AVERAGE(D36:D41)</f>
-        <v>12.3333333333333</v>
+        <v>13</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -6204,7 +6220,7 @@
       <c r="C47" s="7"/>
       <c r="D47" s="7">
         <f>AVERAGE(D2:D14,D20:D30,D36:D41)</f>
-        <v>14</v>
+        <v>14.1666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -6267,7 +6283,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
@@ -6276,12 +6292,12 @@
         <v>1</v>
       </c>
       <c r="D4" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -6290,26 +6306,26 @@
         <v>2</v>
       </c>
       <c r="D5" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" s="2">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>5</v>
@@ -6318,12 +6334,12 @@
         <v>3</v>
       </c>
       <c r="D7" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>5</v>
@@ -6332,12 +6348,12 @@
         <v>3</v>
       </c>
       <c r="D8" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>5</v>
@@ -6351,7 +6367,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>5</v>
@@ -6365,7 +6381,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>5</v>
@@ -6374,12 +6390,12 @@
         <v>3</v>
       </c>
       <c r="D11" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>5</v>
@@ -6388,12 +6404,12 @@
         <v>4</v>
       </c>
       <c r="D12" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>5</v>
@@ -6455,7 +6471,7 @@
       <c r="C18" s="2"/>
       <c r="D18" s="2">
         <f>AVERAGE(D2:D15)</f>
-        <v>14.6428571428571</v>
+        <v>14.9285714285714</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -6525,7 +6541,7 @@
         <v>3</v>
       </c>
       <c r="D25" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -6539,7 +6555,7 @@
         <v>4</v>
       </c>
       <c r="D26" s="4">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -6606,7 +6622,7 @@
       <c r="C32" s="4"/>
       <c r="D32" s="4">
         <f>AVERAGE(D21:D29)</f>
-        <v>13.8888888888889</v>
+        <v>14.1111111111111</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -6634,12 +6650,12 @@
         <v>4</v>
       </c>
       <c r="D36" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>30</v>
@@ -6662,7 +6678,7 @@
         <v>4</v>
       </c>
       <c r="D38" s="6">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -6690,7 +6706,7 @@
         <v>6</v>
       </c>
       <c r="D40" s="6">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -6729,7 +6745,7 @@
       <c r="C44" s="6"/>
       <c r="D44" s="6">
         <f>AVERAGE(D35:D41)</f>
-        <v>12.7142857142857</v>
+        <v>13.1428571428571</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -6738,7 +6754,7 @@
       </c>
       <c r="D47">
         <f>AVERAGE(D2:D15,D21:D29,D35:D41)</f>
-        <v>13.9666666666667</v>
+        <v>14.2666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -6751,7 +6767,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="16.375" customWidth="1"/>
@@ -6778,48 +6794,48 @@
         <v>1</v>
       </c>
       <c r="C2" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="B3" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B4" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" s="2">
         <v>3</v>
       </c>
       <c r="C5" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C6" s="2">
         <v>16</v>
@@ -6833,113 +6849,119 @@
         <v>5</v>
       </c>
       <c r="C7" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
+      <c r="A8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="2">
+        <v>5</v>
+      </c>
+      <c r="C8" s="2">
+        <v>15</v>
+      </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="2">
-        <f>AVERAGE(C2:C7)</f>
+    <row r="10" spans="1:3">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="2">
+        <f>AVERAGE(C2:C8)</f>
         <v>16</v>
       </c>
-      <c r="D10" s="4"/>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="4">
-        <v>1</v>
-      </c>
-      <c r="C13" s="4">
-        <v>12</v>
-      </c>
+      <c r="D11" s="4"/>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14" s="4">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B15" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C15" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B16" s="4">
         <v>3</v>
       </c>
       <c r="C16" s="4">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B17" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C17" s="4">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B18" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C18" s="4">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B19" s="4">
         <v>6</v>
       </c>
       <c r="C19" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="4">
+        <v>6</v>
+      </c>
+      <c r="C20" s="4">
         <v>14</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="4"/>
@@ -6947,76 +6969,76 @@
       <c r="C21" s="4"/>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B22" s="4" t="s">
+      <c r="A22" s="4"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C22" s="4">
-        <f>AVERAGE(C13:C19)</f>
+      <c r="C23" s="4">
+        <f>AVERAGE(C14:C20)</f>
         <v>14.4285714285714</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="B25" s="6">
-        <v>1</v>
-      </c>
-      <c r="C25" s="6">
-        <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B26" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26" s="6">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B27" s="6">
         <v>2</v>
       </c>
       <c r="C27" s="6">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B28" s="6">
         <v>2</v>
       </c>
       <c r="C28" s="6">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B29" s="6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C29" s="6">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="6"/>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6"/>
+      <c r="A30" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B30" s="6">
+        <v>5</v>
+      </c>
+      <c r="C30" s="6">
+        <v>13</v>
+      </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="6"/>
@@ -7024,27 +7046,32 @@
       <c r="C31" s="6"/>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C32" s="6">
-        <f>AVERAGE(C25:C29)</f>
+      <c r="A32" s="6"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C33" s="6">
+        <f>AVERAGE(C26:C30)</f>
         <v>13.4</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="7" t="s">
+    <row r="36" spans="1:3">
+      <c r="A36" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B35" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C35" s="7">
-        <f>AVERAGE(C2:C7,C13:C19,C25:C29)</f>
-        <v>14.6666666666667</v>
+      <c r="B36" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C36" s="7">
+        <f>AVERAGE(C2:C8,C14:C20,C26:C30)</f>
+        <v>14.7368421052632</v>
       </c>
     </row>
   </sheetData>
@@ -7253,7 +7280,7 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B24" s="6">
         <v>4</v>
@@ -7264,18 +7291,18 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B25" s="6">
         <v>4</v>
       </c>
       <c r="C25" s="6">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B26" s="6">
         <v>7</v>
@@ -7303,7 +7330,7 @@
       </c>
       <c r="C29" s="6">
         <f>AVERAGE(C24:C26)</f>
-        <v>13</v>
+        <v>13.6666666666667</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -7311,11 +7338,11 @@
         <v>39</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C32" s="7">
         <f>AVERAGE(C2:C5,C11:C18,C24:C26)</f>
-        <v>14.1333333333333</v>
+        <v>14.2666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -7327,7 +7354,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="13.75" customWidth="1"/>
@@ -7359,51 +7386,51 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="B3" s="2">
         <v>2</v>
       </c>
       <c r="C3" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B4" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B5" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B6" s="2">
         <v>3</v>
       </c>
       <c r="C6" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="B7" s="2">
         <v>3</v>
@@ -7414,47 +7441,41 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B8" s="2">
         <v>3</v>
       </c>
       <c r="C8" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B9" s="2">
         <v>3</v>
       </c>
       <c r="C9" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="B10" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B11" s="2">
-        <v>4</v>
-      </c>
-      <c r="C11" s="2">
-        <v>15</v>
-      </c>
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2"/>
@@ -7462,39 +7483,45 @@
       <c r="C12" s="2"/>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14" s="2">
-        <f>AVERAGE(C2:C11)</f>
-        <v>14.6</v>
+      <c r="A13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="2">
+        <f>AVERAGE(C2:C10)</f>
+        <v>14.7777777777778</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" s="4">
+        <v>3</v>
+      </c>
+      <c r="C16" s="4">
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B17" s="4">
         <v>3</v>
       </c>
       <c r="C17" s="4">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B18" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C18" s="4">
         <v>14</v>
@@ -7502,25 +7529,19 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B19" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C19" s="4">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B20" s="4">
-        <v>5</v>
-      </c>
-      <c r="C20" s="4">
-        <v>13</v>
-      </c>
+      <c r="A20" s="4"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="4"/>
@@ -7528,28 +7549,34 @@
       <c r="C21" s="4"/>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B23" s="4" t="s">
+      <c r="A22" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C23" s="4">
-        <f>AVERAGE(C17:C20)</f>
+      <c r="C22" s="4">
+        <f>AVERAGE(C16:C19)</f>
         <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B25" s="6">
+        <v>3</v>
+      </c>
+      <c r="C25" s="6">
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="6" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B26" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C26" s="6">
         <v>12</v>
@@ -7557,25 +7584,19 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="6" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="B27" s="6">
         <v>4</v>
       </c>
       <c r="C27" s="6">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="B28" s="6">
-        <v>4</v>
-      </c>
-      <c r="C28" s="6">
-        <v>12</v>
-      </c>
+      <c r="A28" s="6"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="6"/>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="6"/>
@@ -7583,32 +7604,27 @@
       <c r="C29" s="6"/>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="6"/>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6"/>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B31" s="6" t="s">
+      <c r="A30" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B30" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="6">
-        <f>AVERAGE(C26:C28)</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="7" t="s">
+      <c r="C30" s="6">
+        <f>AVERAGE(C25:C27)</f>
+        <v>12.3333333333333</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B34" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="C34" s="7">
-        <f>AVERAGE(C2:C11,C17:C20,C26:C28)</f>
-        <v>14</v>
+      <c r="B33" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C33" s="7">
+        <f>AVERAGE(C2:C10,C16:C19,C25:C27)</f>
+        <v>14.125</v>
       </c>
     </row>
   </sheetData>
@@ -7641,7 +7657,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B2" s="2">
         <v>1</v>
@@ -7652,7 +7668,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B3" s="2">
         <v>1</v>
@@ -7663,7 +7679,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B4" s="2">
         <v>2</v>
@@ -7674,7 +7690,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B5" s="2">
         <v>2</v>
@@ -7685,7 +7701,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B6" s="2">
         <v>4</v>
@@ -7718,7 +7734,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B12" s="4">
         <v>2</v>
@@ -7729,7 +7745,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B13" s="4">
         <v>2</v>
@@ -7740,7 +7756,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B14" s="4">
         <v>4</v>
@@ -7751,7 +7767,7 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B15" s="4">
         <v>5</v>
@@ -7807,7 +7823,7 @@
         <v>12</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C25" s="6" t="e">
         <f>AVERAGE(C21,C22)</f>
@@ -7819,7 +7835,7 @@
         <v>39</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C28" s="7">
         <f>AVERAGE(C2:C6,C12:C15,C21:C22)</f>

--- a/src/utils/sxsyzlzq/zzz_cardList.xlsx
+++ b/src/utils/sxsyzlzq/zzz_cardList.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="13395" activeTab="3"/>
+    <workbookView windowWidth="28800" windowHeight="13395" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="伊萝莲" sheetId="1" r:id="rId1"/>
@@ -1857,7 +1857,7 @@
         <v>4</v>
       </c>
       <c r="D37" s="6">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -1938,7 +1938,7 @@
       <c r="C44" s="6"/>
       <c r="D44" s="6">
         <f>AVERAGE(D34:D41)</f>
-        <v>13.5</v>
+        <v>13.625</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1949,7 +1949,7 @@
       <c r="C47" s="7"/>
       <c r="D47" s="7">
         <f>AVERAGE(D2:D9,D15:D28,D34:D41)</f>
-        <v>14.7</v>
+        <v>14.7333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -5086,7 +5086,7 @@
         <v>4</v>
       </c>
       <c r="D38" s="6">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -5153,7 +5153,7 @@
       <c r="C44" s="6"/>
       <c r="D44" s="6">
         <f>AVERAGE(D35:D41)</f>
-        <v>13.5714285714286</v>
+        <v>13.7142857142857</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -5162,7 +5162,7 @@
       </c>
       <c r="D47">
         <f>AVERAGE(D2:D10,D16:D29,D35:D41)</f>
-        <v>14.6</v>
+        <v>14.6333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -5593,7 +5593,7 @@
         <v>4</v>
       </c>
       <c r="D36" s="6">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -5674,7 +5674,7 @@
       <c r="C43" s="6"/>
       <c r="D43" s="6">
         <f>AVERAGE(D34:D40)</f>
-        <v>13.1428571428571</v>
+        <v>13.2857142857143</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -5683,7 +5683,7 @@
       </c>
       <c r="D46">
         <f>AVERAGE(D2:D14,D20:D28,D34:D40)</f>
-        <v>14.4827586206897</v>
+        <v>14.5172413793103</v>
       </c>
     </row>
   </sheetData>
@@ -6692,7 +6692,7 @@
         <v>4</v>
       </c>
       <c r="D39" s="6">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -6745,7 +6745,7 @@
       <c r="C44" s="6"/>
       <c r="D44" s="6">
         <f>AVERAGE(D35:D41)</f>
-        <v>13.1428571428571</v>
+        <v>13.2857142857143</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -6754,7 +6754,7 @@
       </c>
       <c r="D47">
         <f>AVERAGE(D2:D15,D21:D29,D35:D41)</f>
-        <v>14.2666666666667</v>
+        <v>14.3</v>
       </c>
     </row>
   </sheetData>
@@ -7015,7 +7015,7 @@
         <v>2</v>
       </c>
       <c r="C28" s="6">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -7059,7 +7059,7 @@
       </c>
       <c r="C33" s="6">
         <f>AVERAGE(C26:C30)</f>
-        <v>13.4</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="C36" s="7">
         <f>AVERAGE(C2:C8,C14:C20,C26:C30)</f>
-        <v>14.7368421052632</v>
+        <v>14.7894736842105</v>
       </c>
     </row>
   </sheetData>

--- a/src/utils/sxsyzlzq/zzz_cardList.xlsx
+++ b/src/utils/sxsyzlzq/zzz_cardList.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="13395" activeTab="5"/>
+    <workbookView windowWidth="28800" windowHeight="13395" activeTab="13"/>
   </bookViews>
   <sheets>
     <sheet name="伊萝莲" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="尤瑞艾莉" sheetId="12" r:id="rId11"/>
     <sheet name="希拉" sheetId="10" r:id="rId12"/>
     <sheet name="圣母统计" sheetId="13" r:id="rId13"/>
+    <sheet name="洞察表" sheetId="14" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1217" uniqueCount="288">
   <si>
     <t>名称</t>
   </si>
@@ -432,6 +433,477 @@
   </si>
   <si>
     <t>总数：</t>
+  </si>
+  <si>
+    <t>种族</t>
+  </si>
+  <si>
+    <t>描述（18级数值）</t>
+  </si>
+  <si>
+    <t>(18/14)：【洞察1】、【协战7】。</t>
+  </si>
+  <si>
+    <t>(20/25)：【洞察1】、【回命】。</t>
+  </si>
+  <si>
+    <t>(法术)：【洞察1】、英雄生命+55、抓一张牌、获得《真理石残片》。</t>
+  </si>
+  <si>
+    <t>大型弩车</t>
+  </si>
+  <si>
+    <t>(0/50)：【洞察1】、【协战19】。</t>
+  </si>
+  <si>
+    <t>(法术)：【洞察1】、召唤3个10/10民兵-lv15，66%概率再召唤一个。</t>
+  </si>
+  <si>
+    <t>(25/12)：【先攻】、洞察时:自身+5/+3、死亡:【洞察1】。</t>
+  </si>
+  <si>
+    <t>精英射手</t>
+  </si>
+  <si>
+    <t>(27/20)：【洞察1】、【先攻】、【协战7】。</t>
+  </si>
+  <si>
+    <t>(法术)：【洞察1】、横排所有敌军受到130点伤害、50%概率获得《真理碎片》。</t>
+  </si>
+  <si>
+    <t>(16/28)：【洞察1】、命中英雄:召唤12/8警卫-lv13。</t>
+  </si>
+  <si>
+    <t>(0/75)：【守军】、【磐龙】、【护甲6】、回合结束:【洞察1】，若场上有冰封，自身生命+15。</t>
+  </si>
+  <si>
+    <t>(法术)：【洞察1】、目标友军+24/+24、并获得【护甲12】。</t>
+  </si>
+  <si>
+    <t>(法术)：【洞察1】、将横排敌军移回玩家手上、友军横排召唤18/8警卫-lv16。</t>
+  </si>
+  <si>
+    <t>(法术)：【洞察1】、在目标位置和随机位置，召唤2/50圣堂门卫-lv18、护甲友军攻击+10，获得【磐龙】1回合。</t>
+  </si>
+  <si>
+    <t>(30/70)：【回命】、【洞察3】、登场:消灭对面横排首位新进场敌军。</t>
+  </si>
+  <si>
+    <t>(25/50)：【洞察1】、【护甲7】、洞察时：全体友军+5/+5。</t>
+  </si>
+  <si>
+    <t>(15/24)：【洞察2】、攻击前:所有友军+5/+5，魔防+2。（皮肤：命中时：另一友军+1/+1。）</t>
+  </si>
+  <si>
+    <t>(30/30)：【回命】、【神佑】、【护甲11】。（皮肤：命中时：【洞察1】，50几率英雄生命额外+10。）</t>
+  </si>
+  <si>
+    <t>(0/17)：【魔防17】、同横排其他单位不会攻击（无视神佑和魔免）、回合结束:【洞察1】、另一友军+5/+10。（皮肤：登场：其他全体友军，攻击+3，本回合护甲+X（X等同露娜等级）。）</t>
+  </si>
+  <si>
+    <t>(16/60)：登场:英雄生命+60、英雄获得生命:回复效果加倍，自身+3/+10，其他友军+3/+4。（皮肤：【洞察1】、洞察时：自身魔防+2，其他友军攻击+1。）</t>
+  </si>
+  <si>
+    <t>方尖魔碑</t>
+  </si>
+  <si>
+    <t>(0/32)：【守军】、敌方法力上限-1、回合结束:70%几率【洞察1】。</t>
+  </si>
+  <si>
+    <t>(18/21)：洞察时：自身+4/+4、死亡：【洞察1】，英雄恢复生命（等同攻击力）。</t>
+  </si>
+  <si>
+    <t>全数否定</t>
+  </si>
+  <si>
+    <t>(法术)：【洞察1】、横排敌军攻击-25。</t>
+  </si>
+  <si>
+    <t>学仆-渗透型</t>
+  </si>
+  <si>
+    <t>(28/28)：【洞察1】、【穿透】、【护甲7】。</t>
+  </si>
+  <si>
+    <t>请示隐秘者</t>
+  </si>
+  <si>
+    <t>(法术)：【洞察1】、抽2张牌、随机友军生命+55、充能:多抽一张牌。</t>
+  </si>
+  <si>
+    <t>(法术)：【洞察1】、目标单位+18/+20，获得【隐形】。</t>
+  </si>
+  <si>
+    <t>(16/22)：【洞察1】、登场:沉默随机敌军、命中时:55%几率【洞察1】、回合结束:35%几率沉默随机敌军。</t>
+  </si>
+  <si>
+    <t>(法术)：【洞察1】、复制目标单位到手上，英雄生命+33。</t>
+  </si>
+  <si>
+    <t>学仆-猛禽型</t>
+  </si>
+  <si>
+    <t>(22/10)：【先攻】、命中时：【洞察1】、洞察时：全体先攻友军攻击+8。</t>
+  </si>
+  <si>
+    <t>(13/24)：【洞察1】、洞察时：自身+2/+7，射击英雄。</t>
+  </si>
+  <si>
+    <t>白首魔根</t>
+  </si>
+  <si>
+    <t>(13/55)：【洞察1】、【魔免】、回合结束:自身攻击加倍。</t>
+  </si>
+  <si>
+    <t>(0/45)：【洞察1】、【魔防5】、法力上限+2、回合开始:随机敌军-x/-x(x为你的法力)。</t>
+  </si>
+  <si>
+    <t>(30/30)：【磐龙】、【护甲9】、洞察时：自身+3/+6，护甲+3。</t>
+  </si>
+  <si>
+    <t>(14/30)：【洞察1】、【魔防14】、洞察时：抽一张牌。</t>
+  </si>
+  <si>
+    <t>(40/80)：【洞察1】、【磐龙】、【穿透】、【护甲12】、【魔防12】、洞察时：获得《渗透型》lv18、护甲友军死亡：自身+8/+20。</t>
+  </si>
+  <si>
+    <t>(22/21)：法力上限+3，你的法术卡使用后，移回手上、死亡:自身回手，75%概率获得沉默术-lv9。（皮肤：【洞察1】、洞察时：英雄生命+3。）</t>
+  </si>
+  <si>
+    <t>滑板少年·迪宁</t>
+  </si>
+  <si>
+    <t>(19/19)：【魔防15】、【先攻】、回合开始：全体先攻友军+4/+3、获得【连击】1回合。（皮肤：登场：【洞察1】、全体先攻友军获得【隐形】和【神佑】1回合。）</t>
+  </si>
+  <si>
+    <t>禅意</t>
+  </si>
+  <si>
+    <t>长耳庄巧姑</t>
+  </si>
+  <si>
+    <t>(10/12)：【洞察1】、【传承10】、法力上限+1。</t>
+  </si>
+  <si>
+    <t>飓风术</t>
+  </si>
+  <si>
+    <t>(法术)：【洞察1】、目标敌军吹回手上、英雄生命+30。</t>
+  </si>
+  <si>
+    <t>锁妖塔守卫</t>
+  </si>
+  <si>
+    <t>(26/24)：【洞察1】、【法力封锁1】。</t>
+  </si>
+  <si>
+    <t>(法术)：【洞察1】、目标友军加攻，等同其一半生命值、另一友军生命+18、75%几率抽一张牌。</t>
+  </si>
+  <si>
+    <t>明月曲</t>
+  </si>
+  <si>
+    <t>(法术)：【洞察1】、7个友军+6/+6、抽一张牌。</t>
+  </si>
+  <si>
+    <t>(23/23)：【洞察1】、登场:吹回随机敌军。</t>
+  </si>
+  <si>
+    <t>蟠桃隐士</t>
+  </si>
+  <si>
+    <t>(0/45)：【洞察1】、回合结束:获得手牌:仙桃-lv18。</t>
+  </si>
+  <si>
+    <t>(21/25)：【洞察1】、【神佑】、命中时:自身+4/+4。</t>
+  </si>
+  <si>
+    <t>墨轩隐士</t>
+  </si>
+  <si>
+    <t>(6/45)：【洞察1】、法力上限+1、回合结束:复制场上另一单位，到你手上。</t>
+  </si>
+  <si>
+    <t>蟠桃会</t>
+  </si>
+  <si>
+    <t>(法术)：【洞察1】、抓3张牌，英雄生命+40、随机一个友军+7/+7。</t>
+  </si>
+  <si>
+    <t>摇钱尊者</t>
+  </si>
+  <si>
+    <t>(15/99)：【洞察1】、【磐龙】、回合结束:若本回合受到过伤害，抽一张牌。</t>
+  </si>
+  <si>
+    <t>(13/21)：登场、命中:【洞察2】、洞察时:全体友军+1/+5，全体敌军-2/-2。（皮肤：登场时：本回合获得【穿透】。）</t>
+  </si>
+  <si>
+    <t>海港</t>
+  </si>
+  <si>
+    <t>狡诈学徒</t>
+  </si>
+  <si>
+    <t>(19/15)：【洞察1】、登场:吹回对面首位新进场敌军、洞察时自身攻击+4。</t>
+  </si>
+  <si>
+    <t>黑夜射手</t>
+  </si>
+  <si>
+    <t>(20/20)：命中英雄:【洞察1】，随机敌军受到8点伤害。</t>
+  </si>
+  <si>
+    <t>亡命之徒</t>
+  </si>
+  <si>
+    <t>(25/9)：【洞察1】、【暴露1】、对英雄伤害+8。</t>
+  </si>
+  <si>
+    <t>黑夜突袭</t>
+  </si>
+  <si>
+    <t>(法术)：【洞察1】、对随机单位造成50点伤害。</t>
+  </si>
+  <si>
+    <t>传记学者</t>
+  </si>
+  <si>
+    <t>(16/24)：回合开始:每使用过一个法术或传记，随机友军+1/+9、初次使用传记:抽一张牌、【洞察1】。</t>
+  </si>
+  <si>
+    <t>热血矿工</t>
+  </si>
+  <si>
+    <t>(18/40)：【洞察1】、回合结束、死亡时:向敌方英雄投掷铁镐。</t>
+  </si>
+  <si>
+    <t>不法交易</t>
+  </si>
+  <si>
+    <t>(法术)：【洞察1】、英雄生命-2，抽两张牌、敌方英雄生命-40。</t>
+  </si>
+  <si>
+    <t>走私狂徒</t>
+  </si>
+  <si>
+    <t>(16/10)：【洞察1】、登场:召唤30/55珍奇兽-lv18。</t>
+  </si>
+  <si>
+    <t>异域驯兽使</t>
+  </si>
+  <si>
+    <t>(24/24)：【洞察1】、唤醒其他迟缓友军、登场:本回合隐形。</t>
+  </si>
+  <si>
+    <t>红海猎魔人</t>
+  </si>
+  <si>
+    <t>(22/11)：【洞察1】、【先攻】、攻击前:本回合你每使用过一个法术或传记，随机敌军生命-6，自身攻击+6。</t>
+  </si>
+  <si>
+    <t>海神赐福</t>
+  </si>
+  <si>
+    <t>(法术)：【洞察1】、随机友军+15/+15获得【回命】、抽一张牌、无友军则再抽一张牌并且【洞察1】。</t>
+  </si>
+  <si>
+    <t>无情夺命客</t>
+  </si>
+  <si>
+    <t>(19/17)：【洞察1】、【二连击】、敌方英雄受伤时:攻击+1。</t>
+  </si>
+  <si>
+    <t>红海领航员</t>
+  </si>
+  <si>
+    <t>(25/20)：【洞察1】、【先攻】、攻击前：全体先攻友军+5/+4。</t>
+  </si>
+  <si>
+    <t>樱花·艾希尔</t>
+  </si>
+  <si>
+    <t>(28/15)：【洞察2】、【连击】、【魔防100】、回合开始：若生命高于对手，获得【隐形】1回合；若人数多于对手，攻击+2。（皮肤：登场：攻击力+X，持续1回合（X为艾希尔等级）。）</t>
+  </si>
+  <si>
+    <t>炼狱</t>
+  </si>
+  <si>
+    <t>地狱刀吏</t>
+  </si>
+  <si>
+    <t>(27/7)：【洞察1】、回合开始时:若你无手牌，自身攻击+9。</t>
+  </si>
+  <si>
+    <t>嗜血妖蛾</t>
+  </si>
+  <si>
+    <t>(20/20)：【洞察1】、敌方玩家受到伤害时:自身攻击+1。</t>
+  </si>
+  <si>
+    <t>(31/11)：【洞察1】、死亡:投掷长枪攻击英雄。</t>
+  </si>
+  <si>
+    <t>炼狱双头犬</t>
+  </si>
+  <si>
+    <t>(18/40)：【洞察1】、【二连击】。</t>
+  </si>
+  <si>
+    <t>狱铠战魂</t>
+  </si>
+  <si>
+    <t>(20/8)：【洞察1】、【护甲23】。</t>
+  </si>
+  <si>
+    <t>地狱三头犬</t>
+  </si>
+  <si>
+    <t>(19/55)：【洞察2】、【三连击】。</t>
+  </si>
+  <si>
+    <t>蛮石</t>
+  </si>
+  <si>
+    <t>愚笨鲸头鹅</t>
+  </si>
+  <si>
+    <t>(12/20)：【洞察1】、【迟缓】、命中英雄:抓一张牌，并且【洞察1】。</t>
+  </si>
+  <si>
+    <t>旷野祭师(</t>
+  </si>
+  <si>
+    <t>(8/20)：【洞察1】、你得法力上限+1、洞察时:英雄生命+15。</t>
+  </si>
+  <si>
+    <t>痴蛮野人</t>
+  </si>
+  <si>
+    <t>(30/30)：【迟缓】、洞察时:自身+5/+5。</t>
+  </si>
+  <si>
+    <t>高原卫士</t>
+  </si>
+  <si>
+    <t>(22/30)：【洞察1】、【迟缓】、回合结束：若本回合受到过伤害，自身+5/+10，【洞察1】。</t>
+  </si>
+  <si>
+    <t>盘旋秃鹫</t>
+  </si>
+  <si>
+    <t>(20/15)：命中英雄:【洞察1】、洞察时:自身攻击+7。</t>
+  </si>
+  <si>
+    <t>寻路斥候</t>
+  </si>
+  <si>
+    <t>(25/12)：登场:射击随机敌方，12点伤害、洞察时:射击随机敌军，9点伤害。</t>
+  </si>
+  <si>
+    <t>厚皮河马</t>
+  </si>
+  <si>
+    <t>(20/54)：【洞察1】、【迟缓】、回合结束:若本回合受到过伤害，自身生命+13。</t>
+  </si>
+  <si>
+    <t>机敏雀鹰</t>
+  </si>
+  <si>
+    <t>(13/32)：【洞察1】、洞察时：自身+4/+4，魔防+4。</t>
+  </si>
+  <si>
+    <t>原野狂战士</t>
+  </si>
+  <si>
+    <t>(28/28)：【洞察1】、【践踏】、【魔防7】。</t>
+  </si>
+  <si>
+    <t>生命源力</t>
+  </si>
+  <si>
+    <t>(法术)：【洞察1】、目标单位+28/+28，魔防+13。</t>
+  </si>
+  <si>
+    <t>雪原野人</t>
+  </si>
+  <si>
+    <t>(38/38)：【迟缓】、【回命】、【洞察1】、场上有冰封则失去【迟缓】。</t>
+  </si>
+  <si>
+    <t>鼓舞图腾</t>
+  </si>
+  <si>
+    <t>(0/90)：【洞察1】、回合开始:其他全体友军+3/+2，魔防+3。</t>
+  </si>
+  <si>
+    <t>迷茫巨人</t>
+  </si>
+  <si>
+    <t>(40/66)：【洞察1】、【迟缓】、【魔防13】。</t>
+  </si>
+  <si>
+    <t>无畏猎户</t>
+  </si>
+  <si>
+    <t>(18/30)：【洞察1】、命中英雄时:再攻击一次。</t>
+  </si>
+  <si>
+    <t>诱敌草人</t>
+  </si>
+  <si>
+    <t>(0/59)：回合结束：若本回合受到过伤害，抽一张牌，英雄生命+15，【洞察1】。</t>
+  </si>
+  <si>
+    <t>象牙少女</t>
+  </si>
+  <si>
+    <t>(7/10)：【洞察1】、回合结束:召唤30/50长毛象-lv18。</t>
+  </si>
+  <si>
+    <t>冬神</t>
+  </si>
+  <si>
+    <t>寒铁军士</t>
+  </si>
+  <si>
+    <t>(28/8)：【洞察1】、登场:冰封相邻随机位置。</t>
+  </si>
+  <si>
+    <t>寒风草人</t>
+  </si>
+  <si>
+    <t>(0/25)：【洞察1】、【传承7】、登场：冰封相邻随机位置，横排敌军-8/-8。</t>
+  </si>
+  <si>
+    <t>严冬苦行僧</t>
+  </si>
+  <si>
+    <t>(17/33)：【洞察1】、登场:随机敌军攻击-x/-x(x为敌方冰封数量)、敌方法力上限-1。</t>
+  </si>
+  <si>
+    <t>神庙祭师</t>
+  </si>
+  <si>
+    <t>(17/23)：【洞察1】、攻击前:吸取生命，等同自身攻击。</t>
+  </si>
+  <si>
+    <t>冬夜使者</t>
+  </si>
+  <si>
+    <t>(26/26)：【洞察2】、双方英雄法力上限-1。</t>
+  </si>
+  <si>
+    <t>极夜阴魂</t>
+  </si>
+  <si>
+    <t>(39/13)：【洞察1】、【隐形】、【穿透】、【魔防6】。</t>
+  </si>
+  <si>
+    <t>冰河世纪</t>
+  </si>
+  <si>
+    <t>(法术)：【洞察1】、所有单位-29/-29、全场每有一处冰封，再-2/-2（无视神佑和魔免）。</t>
   </si>
 </sst>
 </file>
@@ -454,23 +926,10 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="6"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF00B0F0"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color rgb="FF7030A0"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -485,6 +944,19 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="6"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF7030A0"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1098,14 +1570,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
@@ -1446,360 +1918,360 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="2">
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1">
         <v>1</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="1">
         <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="2">
-        <v>2</v>
-      </c>
-      <c r="D3" s="2">
+      <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1">
+        <v>2</v>
+      </c>
+      <c r="D3" s="1">
         <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="2">
-        <v>2</v>
-      </c>
-      <c r="D4" s="2">
+      <c r="B4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2</v>
+      </c>
+      <c r="D4" s="1">
         <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="2">
-        <v>2</v>
-      </c>
-      <c r="D5" s="2">
+      <c r="B5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2</v>
+      </c>
+      <c r="D5" s="1">
         <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="2">
-        <v>3</v>
-      </c>
-      <c r="D6" s="2">
+      <c r="B6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="1">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1">
         <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="2">
-        <v>3</v>
-      </c>
-      <c r="D7" s="2">
+      <c r="B7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="1">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1">
         <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="2">
-        <v>5</v>
-      </c>
-      <c r="D8" s="2">
+      <c r="B8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="1">
+        <v>5</v>
+      </c>
+      <c r="D8" s="1">
         <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="2">
-        <v>5</v>
-      </c>
-      <c r="D9" s="2">
+      <c r="B9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="1">
+        <v>5</v>
+      </c>
+      <c r="D9" s="1">
         <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2">
+      <c r="C12" s="1"/>
+      <c r="D12" s="1">
         <f>AVERAGE(D2:D9)</f>
         <v>16.125</v>
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="4">
+      <c r="B15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="2">
         <v>1</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15" s="2">
         <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" s="4">
+      <c r="B16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="2">
         <v>1</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="2">
         <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" s="4">
-        <v>2</v>
-      </c>
-      <c r="D17" s="4">
+      <c r="B17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="2">
+        <v>2</v>
+      </c>
+      <c r="D17" s="2">
         <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18" s="4">
-        <v>2</v>
-      </c>
-      <c r="D18" s="4">
+      <c r="B18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="2">
+        <v>2</v>
+      </c>
+      <c r="D18" s="2">
         <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="4">
-        <v>2</v>
-      </c>
-      <c r="D19" s="4">
+      <c r="B19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="2">
+        <v>2</v>
+      </c>
+      <c r="D19" s="2">
         <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="4">
-        <v>3</v>
-      </c>
-      <c r="D20" s="4">
+      <c r="B20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="2">
+        <v>3</v>
+      </c>
+      <c r="D20" s="2">
         <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C21" s="4">
-        <v>3</v>
-      </c>
-      <c r="D21" s="4">
+      <c r="B21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="2">
+        <v>3</v>
+      </c>
+      <c r="D21" s="2">
         <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C22" s="4">
-        <v>3</v>
-      </c>
-      <c r="D22" s="4">
+      <c r="B22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="2">
+        <v>3</v>
+      </c>
+      <c r="D22" s="2">
         <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C23" s="4">
-        <v>3</v>
-      </c>
-      <c r="D23" s="4">
+      <c r="B23" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="2">
+        <v>3</v>
+      </c>
+      <c r="D23" s="2">
         <v>14</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C24" s="4">
+      <c r="B24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" s="2">
         <v>4</v>
       </c>
-      <c r="D24" s="4">
+      <c r="D24" s="2">
         <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C25" s="4">
+      <c r="B25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" s="2">
         <v>4</v>
       </c>
-      <c r="D25" s="4">
+      <c r="D25" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C26" s="4">
+      <c r="B26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="2">
         <v>6</v>
       </c>
-      <c r="D26" s="4">
+      <c r="D26" s="2">
         <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C27" s="4">
+      <c r="B27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" s="2">
         <v>6</v>
       </c>
-      <c r="D27" s="4">
+      <c r="D27" s="2">
         <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:6">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C28" s="4">
+      <c r="B28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C28" s="2">
         <v>7</v>
       </c>
-      <c r="D28" s="4">
-        <v>15</v>
-      </c>
-      <c r="F28" s="5"/>
+      <c r="D28" s="2">
+        <v>15</v>
+      </c>
+      <c r="F28" s="3"/>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="4"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="4"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4">
+      <c r="C31" s="2"/>
+      <c r="D31" s="2">
         <f>AVERAGE(D15:D28)</f>
         <v>14.5714285714286</v>
       </c>
@@ -1984,416 +2456,416 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="2">
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1">
         <v>1</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="1">
         <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="2">
+      <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1">
         <v>1</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="1">
         <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="2">
+      <c r="B4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="1">
         <v>1</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="1">
         <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="2">
+      <c r="B5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="1">
         <v>1</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="1">
         <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="2">
-        <v>2</v>
-      </c>
-      <c r="D6" s="2">
+      <c r="B6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2</v>
+      </c>
+      <c r="D6" s="1">
         <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="2">
-        <v>2</v>
-      </c>
-      <c r="D7" s="2">
+      <c r="B7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2</v>
+      </c>
+      <c r="D7" s="1">
         <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="2">
-        <v>2</v>
-      </c>
-      <c r="D8" s="2">
+      <c r="B8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2</v>
+      </c>
+      <c r="D8" s="1">
         <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="2">
-        <v>2</v>
-      </c>
-      <c r="D9" s="2">
+      <c r="B9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2</v>
+      </c>
+      <c r="D9" s="1">
         <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" s="2">
-        <v>2</v>
-      </c>
-      <c r="D10" s="2">
+      <c r="B10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2</v>
+      </c>
+      <c r="D10" s="1">
         <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="2">
-        <v>3</v>
-      </c>
-      <c r="D11" s="2">
+      <c r="B11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="1">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1">
         <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" s="2">
-        <v>3</v>
-      </c>
-      <c r="D12" s="2">
+      <c r="B12" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="1">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1">
         <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="2">
-        <v>3</v>
-      </c>
-      <c r="D13" s="2">
+      <c r="B13" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="1">
+        <v>3</v>
+      </c>
+      <c r="D13" s="1">
         <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" s="2">
-        <v>3</v>
-      </c>
-      <c r="D14" s="2">
+      <c r="B14" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="1">
+        <v>3</v>
+      </c>
+      <c r="D14" s="1">
         <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15" s="2">
+      <c r="B15" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="1">
         <v>4</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="1">
         <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C16" s="2">
+      <c r="B16" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="1">
         <v>4</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="1">
         <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2">
+      <c r="C19" s="1"/>
+      <c r="D19" s="1">
         <f>AVERAGE(D2:D16)</f>
         <v>14.4666666666667</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B22" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C22" s="4">
-        <v>2</v>
-      </c>
-      <c r="D22" s="4">
+      <c r="B22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="2">
+        <v>2</v>
+      </c>
+      <c r="D22" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B23" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C23" s="4">
-        <v>2</v>
-      </c>
-      <c r="D23" s="4">
+      <c r="B23" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="2">
+        <v>2</v>
+      </c>
+      <c r="D23" s="2">
         <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C24" s="4">
-        <v>3</v>
-      </c>
-      <c r="D24" s="4">
+      <c r="B24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" s="2">
+        <v>3</v>
+      </c>
+      <c r="D24" s="2">
         <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B25" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C25" s="4">
-        <v>3</v>
-      </c>
-      <c r="D25" s="4">
+      <c r="B25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" s="2">
+        <v>3</v>
+      </c>
+      <c r="D25" s="2">
         <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B26" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C26" s="4">
-        <v>3</v>
-      </c>
-      <c r="D26" s="4">
+      <c r="B26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="2">
+        <v>3</v>
+      </c>
+      <c r="D26" s="2">
         <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B27" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C27" s="4">
-        <v>3</v>
-      </c>
-      <c r="D27" s="4">
+      <c r="B27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" s="2">
+        <v>3</v>
+      </c>
+      <c r="D27" s="2">
         <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B28" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C28" s="4">
+      <c r="B28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C28" s="2">
         <v>4</v>
       </c>
-      <c r="D28" s="4">
+      <c r="D28" s="2">
         <v>14</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B29" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C29" s="4">
+      <c r="B29" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C29" s="2">
         <v>4</v>
       </c>
-      <c r="D29" s="4">
+      <c r="D29" s="2">
         <v>12</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B30" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C30" s="4">
-        <v>5</v>
-      </c>
-      <c r="D30" s="4">
+      <c r="B30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="2">
+        <v>5</v>
+      </c>
+      <c r="D30" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B31" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C31" s="4">
-        <v>5</v>
-      </c>
-      <c r="D31" s="4">
+      <c r="B31" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C31" s="2">
+        <v>5</v>
+      </c>
+      <c r="D31" s="2">
         <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:6">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B32" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C32" s="4">
+      <c r="B32" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" s="2">
         <v>6</v>
       </c>
-      <c r="D32" s="4">
+      <c r="D32" s="2">
         <v>11</v>
       </c>
-      <c r="F32" s="5"/>
+      <c r="F32" s="3"/>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="4"/>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="4"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4">
+      <c r="C35" s="2"/>
+      <c r="D35" s="2">
         <f>AVERAGE(D22:D32)</f>
         <v>12.7272727272727</v>
       </c>
@@ -2521,415 +2993,415 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="2">
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1">
         <v>1</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="1">
         <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="2">
+      <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1">
         <v>1</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="1">
         <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="2">
-        <v>2</v>
-      </c>
-      <c r="D4" s="2">
+      <c r="B4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2</v>
+      </c>
+      <c r="D4" s="1">
         <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="2">
-        <v>2</v>
-      </c>
-      <c r="D5" s="2">
+      <c r="B5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2</v>
+      </c>
+      <c r="D5" s="1">
         <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="2">
-        <v>2</v>
-      </c>
-      <c r="D6" s="2">
+      <c r="B6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2</v>
+      </c>
+      <c r="D6" s="1">
         <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="2">
-        <v>2</v>
-      </c>
-      <c r="D7" s="2">
+      <c r="B7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2</v>
+      </c>
+      <c r="D7" s="1">
         <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="2">
-        <v>2</v>
-      </c>
-      <c r="D8" s="2">
+      <c r="B8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2</v>
+      </c>
+      <c r="D8" s="1">
         <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="2">
-        <v>2</v>
-      </c>
-      <c r="D9" s="2">
+      <c r="B9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2</v>
+      </c>
+      <c r="D9" s="1">
         <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" s="2">
-        <v>3</v>
-      </c>
-      <c r="D10" s="2">
+      <c r="B10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="1">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1">
         <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="2">
+      <c r="B11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="1">
         <v>4</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="1">
         <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2">
+      <c r="C14" s="1"/>
+      <c r="D14" s="1">
         <f>AVERAGE(D2:D11)</f>
         <v>13.8</v>
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" s="4">
+      <c r="B17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="2">
         <v>1</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17" s="2">
         <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18" s="4">
-        <v>2</v>
-      </c>
-      <c r="D18" s="4">
+      <c r="B18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="2">
+        <v>2</v>
+      </c>
+      <c r="D18" s="2">
         <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="4">
-        <v>2</v>
-      </c>
-      <c r="D19" s="4">
+      <c r="B19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="2">
+        <v>2</v>
+      </c>
+      <c r="D19" s="2">
         <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="4">
-        <v>2</v>
-      </c>
-      <c r="D20" s="4">
+      <c r="B20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="2">
+        <v>2</v>
+      </c>
+      <c r="D20" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C21" s="4">
-        <v>3</v>
-      </c>
-      <c r="D21" s="4">
+      <c r="B21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="2">
+        <v>3</v>
+      </c>
+      <c r="D21" s="2">
         <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C22" s="4">
-        <v>3</v>
-      </c>
-      <c r="D22" s="4">
+      <c r="B22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="2">
+        <v>3</v>
+      </c>
+      <c r="D22" s="2">
         <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C23" s="4">
-        <v>3</v>
-      </c>
-      <c r="D23" s="4">
+      <c r="B23" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="2">
+        <v>3</v>
+      </c>
+      <c r="D23" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C24" s="4">
-        <v>3</v>
-      </c>
-      <c r="D24" s="4">
+      <c r="B24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" s="2">
+        <v>3</v>
+      </c>
+      <c r="D24" s="2">
         <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B25" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C25" s="4">
-        <v>3</v>
-      </c>
-      <c r="D25" s="4">
+      <c r="B25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" s="2">
+        <v>3</v>
+      </c>
+      <c r="D25" s="2">
         <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B26" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C26" s="4">
+      <c r="B26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="2">
         <v>4</v>
       </c>
-      <c r="D26" s="4">
+      <c r="D26" s="2">
         <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B27" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C27" s="4">
+      <c r="B27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" s="2">
         <v>4</v>
       </c>
-      <c r="D27" s="4">
+      <c r="D27" s="2">
         <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B28" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C28" s="4">
-        <v>5</v>
-      </c>
-      <c r="D28" s="4">
+      <c r="B28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C28" s="2">
+        <v>5</v>
+      </c>
+      <c r="D28" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B29" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C29" s="4">
-        <v>5</v>
-      </c>
-      <c r="D29" s="4">
+      <c r="B29" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C29" s="2">
+        <v>5</v>
+      </c>
+      <c r="D29" s="2">
         <v>12</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B30" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C30" s="4">
-        <v>5</v>
-      </c>
-      <c r="D30" s="4">
+      <c r="B30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="2">
+        <v>5</v>
+      </c>
+      <c r="D30" s="2">
         <v>12</v>
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B31" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C31" s="4">
+      <c r="B31" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C31" s="2">
         <v>6</v>
       </c>
-      <c r="D31" s="4">
+      <c r="D31" s="2">
         <v>11</v>
       </c>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B32" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C32" s="4">
+      <c r="B32" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" s="2">
         <v>7</v>
       </c>
-      <c r="D32" s="4">
+      <c r="D32" s="2">
         <v>14</v>
       </c>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="4"/>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="4"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4">
+      <c r="C35" s="2"/>
+      <c r="D35" s="2">
         <f>AVERAGE(D17:D32)</f>
         <v>13</v>
       </c>
@@ -3055,430 +3527,430 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="2">
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1">
         <v>1</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="1">
         <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="2">
+      <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1">
         <v>1</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="1">
         <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="2">
+      <c r="B4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="1">
         <v>1</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="1">
         <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="2">
+      <c r="B5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="1">
         <v>1</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="1">
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="2">
+      <c r="B6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="1">
         <v>1</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="1">
         <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="2">
-        <v>2</v>
-      </c>
-      <c r="D7" s="2">
+      <c r="B7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2</v>
+      </c>
+      <c r="D7" s="1">
         <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="2">
-        <v>2</v>
-      </c>
-      <c r="D8" s="2">
+      <c r="B8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2</v>
+      </c>
+      <c r="D8" s="1">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="2">
-        <v>2</v>
-      </c>
-      <c r="D9" s="2">
+      <c r="B9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2</v>
+      </c>
+      <c r="D9" s="1">
         <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" s="2">
-        <v>2</v>
-      </c>
-      <c r="D10" s="2">
+      <c r="B10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2</v>
+      </c>
+      <c r="D10" s="1">
         <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="2">
-        <v>2</v>
-      </c>
-      <c r="D11" s="2">
+      <c r="B11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2</v>
+      </c>
+      <c r="D11" s="1">
         <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" s="2">
-        <v>2</v>
-      </c>
-      <c r="D12" s="2">
+      <c r="B12" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="1">
+        <v>2</v>
+      </c>
+      <c r="D12" s="1">
         <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="2">
-        <v>3</v>
-      </c>
-      <c r="D13" s="2">
+      <c r="B13" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="1">
+        <v>3</v>
+      </c>
+      <c r="D13" s="1">
         <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" s="2">
-        <v>3</v>
-      </c>
-      <c r="D14" s="2">
+      <c r="B14" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="1">
+        <v>3</v>
+      </c>
+      <c r="D14" s="1">
         <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15" s="2">
-        <v>3</v>
-      </c>
-      <c r="D15" s="2">
+      <c r="B15" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="1">
+        <v>3</v>
+      </c>
+      <c r="D15" s="1">
         <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C16" s="2">
+      <c r="B16" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="1">
         <v>4</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="1">
         <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" s="2">
+      <c r="B17" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="1">
         <v>4</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="1">
         <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2">
+      <c r="C20" s="1"/>
+      <c r="D20" s="1">
         <f>AVERAGE(D2:D17)</f>
         <v>13.9375</v>
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B23" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C23" s="4">
-        <v>2</v>
-      </c>
-      <c r="D23" s="4">
+      <c r="B23" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="2">
+        <v>2</v>
+      </c>
+      <c r="D23" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C24" s="4">
-        <v>2</v>
-      </c>
-      <c r="D24" s="4">
+      <c r="B24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" s="2">
+        <v>2</v>
+      </c>
+      <c r="D24" s="2">
         <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B25" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C25" s="4">
-        <v>3</v>
-      </c>
-      <c r="D25" s="4">
+      <c r="B25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" s="2">
+        <v>3</v>
+      </c>
+      <c r="D25" s="2">
         <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B26" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C26" s="4">
-        <v>3</v>
-      </c>
-      <c r="D26" s="4">
+      <c r="B26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="2">
+        <v>3</v>
+      </c>
+      <c r="D26" s="2">
         <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B27" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C27" s="4">
-        <v>3</v>
-      </c>
-      <c r="D27" s="4">
+      <c r="B27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" s="2">
+        <v>3</v>
+      </c>
+      <c r="D27" s="2">
         <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B28" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C28" s="4">
-        <v>3</v>
-      </c>
-      <c r="D28" s="4">
+      <c r="B28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C28" s="2">
+        <v>3</v>
+      </c>
+      <c r="D28" s="2">
         <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B29" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C29" s="4">
+      <c r="B29" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C29" s="2">
         <v>4</v>
       </c>
-      <c r="D29" s="4">
+      <c r="D29" s="2">
         <v>14</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B30" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C30" s="4">
+      <c r="B30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="2">
         <v>4</v>
       </c>
-      <c r="D30" s="4">
+      <c r="D30" s="2">
         <v>12</v>
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B31" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C31" s="4">
-        <v>5</v>
-      </c>
-      <c r="D31" s="4">
+      <c r="B31" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C31" s="2">
+        <v>5</v>
+      </c>
+      <c r="D31" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B32" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C32" s="4">
-        <v>5</v>
-      </c>
-      <c r="D32" s="4">
+      <c r="B32" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" s="2">
+        <v>5</v>
+      </c>
+      <c r="D32" s="2">
         <v>12</v>
       </c>
     </row>
     <row r="33" spans="1:6">
-      <c r="A33" s="4" t="s">
+      <c r="A33" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B33" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C33" s="4">
+      <c r="B33" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C33" s="2">
         <v>6</v>
       </c>
-      <c r="D33" s="4">
+      <c r="D33" s="2">
         <v>11</v>
       </c>
-      <c r="F33" s="5"/>
+      <c r="F33" s="3"/>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="4"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="4"/>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4">
+      <c r="C36" s="2"/>
+      <c r="D36" s="2">
         <f>AVERAGE(D23:D33)</f>
         <v>12.7272727272727</v>
       </c>
@@ -3595,1035 +4067,1035 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="4">
         <v>1</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="4">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="2">
+      <c r="C3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="1">
         <v>1</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="2">
+      <c r="C4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="1">
         <v>1</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="2">
+      <c r="C5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="1">
         <v>1</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="1">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="4">
+      <c r="C6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="2">
         <v>1</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="4">
+      <c r="C7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="2">
         <v>1</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="4">
+      <c r="C8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="2">
         <v>1</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="2">
         <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9" s="2">
-        <v>2</v>
-      </c>
-      <c r="E9" s="2">
+      <c r="C9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="1">
+        <v>2</v>
+      </c>
+      <c r="E9" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D10" s="2">
-        <v>2</v>
-      </c>
-      <c r="E10" s="2">
+      <c r="C10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" s="1">
+        <v>2</v>
+      </c>
+      <c r="E10" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D11" s="2">
-        <v>2</v>
-      </c>
-      <c r="E11" s="2">
+      <c r="C11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="1">
+        <v>2</v>
+      </c>
+      <c r="E11" s="1">
         <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D12" s="2">
-        <v>2</v>
-      </c>
-      <c r="E12" s="2">
+      <c r="C12" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" s="1">
+        <v>2</v>
+      </c>
+      <c r="E12" s="1">
         <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D13" s="2">
-        <v>2</v>
-      </c>
-      <c r="E13" s="2">
+      <c r="C13" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" s="1">
+        <v>2</v>
+      </c>
+      <c r="E13" s="1">
         <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D14" s="4">
-        <v>2</v>
-      </c>
-      <c r="E14" s="4">
+      <c r="C14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="2">
+        <v>2</v>
+      </c>
+      <c r="E14" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D15" s="4">
-        <v>2</v>
-      </c>
-      <c r="E15" s="4">
+      <c r="C15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="2">
+        <v>2</v>
+      </c>
+      <c r="E15" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D16" s="4">
-        <v>2</v>
-      </c>
-      <c r="E16" s="4">
+      <c r="C16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="2">
+        <v>2</v>
+      </c>
+      <c r="E16" s="2">
         <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D17" s="4">
-        <v>2</v>
-      </c>
-      <c r="E17" s="4">
+      <c r="C17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="2">
+        <v>2</v>
+      </c>
+      <c r="E17" s="2">
         <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C18" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" s="4">
-        <v>2</v>
-      </c>
-      <c r="E18" s="4">
+      <c r="C18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="2">
+        <v>2</v>
+      </c>
+      <c r="E18" s="2">
         <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D19" s="5">
-        <v>3</v>
-      </c>
-      <c r="E19" s="5">
+      <c r="D19" s="3">
+        <v>3</v>
+      </c>
+      <c r="E19" s="3">
         <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D20" s="5">
-        <v>3</v>
-      </c>
-      <c r="E20" s="5">
+      <c r="D20" s="3">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3">
         <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="5">
-        <v>3</v>
-      </c>
-      <c r="E21" s="5">
+      <c r="D21" s="3">
+        <v>3</v>
+      </c>
+      <c r="E21" s="3">
         <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D22" s="2">
-        <v>3</v>
-      </c>
-      <c r="E22" s="2">
+      <c r="C22" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D22" s="1">
+        <v>3</v>
+      </c>
+      <c r="E22" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D23" s="2">
-        <v>3</v>
-      </c>
-      <c r="E23" s="2">
+      <c r="C23" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D23" s="1">
+        <v>3</v>
+      </c>
+      <c r="E23" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D24" s="2">
-        <v>3</v>
-      </c>
-      <c r="E24" s="2">
+      <c r="C24" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D24" s="1">
+        <v>3</v>
+      </c>
+      <c r="E24" s="1">
         <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C25" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D25" s="4">
-        <v>3</v>
-      </c>
-      <c r="E25" s="4">
+      <c r="C25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="2">
+        <v>3</v>
+      </c>
+      <c r="E25" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C26" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D26" s="4">
-        <v>3</v>
-      </c>
-      <c r="E26" s="4">
+      <c r="C26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" s="2">
+        <v>3</v>
+      </c>
+      <c r="E26" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C27" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D27" s="4">
-        <v>3</v>
-      </c>
-      <c r="E27" s="4">
+      <c r="C27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" s="2">
+        <v>3</v>
+      </c>
+      <c r="E27" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C28" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D28" s="4">
-        <v>3</v>
-      </c>
-      <c r="E28" s="4">
+      <c r="C28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" s="2">
+        <v>3</v>
+      </c>
+      <c r="E28" s="2">
         <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C29" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D29" s="4">
-        <v>3</v>
-      </c>
-      <c r="E29" s="4">
+      <c r="C29" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29" s="2">
+        <v>3</v>
+      </c>
+      <c r="E29" s="2">
         <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C30" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D30" s="4">
-        <v>3</v>
-      </c>
-      <c r="E30" s="4">
+      <c r="C30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" s="2">
+        <v>3</v>
+      </c>
+      <c r="E30" s="2">
         <v>11</v>
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C31" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D31" s="4">
-        <v>3</v>
-      </c>
-      <c r="E31" s="4">
+      <c r="C31" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" s="2">
+        <v>3</v>
+      </c>
+      <c r="E31" s="2">
         <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+      <c r="A32" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D32" s="5">
+      <c r="D32" s="3">
         <v>4</v>
       </c>
-      <c r="E32" s="5">
+      <c r="E32" s="3">
         <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+      <c r="A33" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C33" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D33" s="5">
+      <c r="D33" s="3">
         <v>4</v>
       </c>
-      <c r="E33" s="5">
+      <c r="E33" s="3">
         <v>12</v>
       </c>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
+      <c r="A34" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B34" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C34" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D34" s="5">
+      <c r="D34" s="3">
         <v>4</v>
       </c>
-      <c r="E34" s="5">
+      <c r="E34" s="3">
         <v>12</v>
       </c>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="2" t="s">
+      <c r="A35" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C35" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D35" s="2">
+      <c r="C35" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D35" s="1">
         <v>4</v>
       </c>
-      <c r="E35" s="2">
+      <c r="E35" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C36" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D36" s="4">
+      <c r="C36" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D36" s="2">
         <v>4</v>
       </c>
-      <c r="E36" s="4">
+      <c r="E36" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C37" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D37" s="4">
+      <c r="C37" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D37" s="2">
         <v>4</v>
       </c>
-      <c r="E37" s="4">
+      <c r="E37" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C38" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D38" s="4">
+      <c r="C38" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D38" s="2">
         <v>4</v>
       </c>
-      <c r="E38" s="4">
+      <c r="E38" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C39" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D39" s="4">
+      <c r="C39" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" s="2">
         <v>4</v>
       </c>
-      <c r="E39" s="4">
+      <c r="E39" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C40" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D40" s="4">
+      <c r="C40" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D40" s="2">
         <v>4</v>
       </c>
-      <c r="E40" s="4">
+      <c r="E40" s="2">
         <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:5">
-      <c r="A41" s="4" t="s">
+      <c r="A41" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C41" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D41" s="4">
+      <c r="C41" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D41" s="2">
         <v>4</v>
       </c>
-      <c r="E41" s="4">
+      <c r="E41" s="2">
         <v>9</v>
       </c>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="4" t="s">
+      <c r="A42" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C42" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D42" s="4">
+      <c r="C42" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D42" s="2">
         <v>4</v>
       </c>
-      <c r="E42" s="4">
+      <c r="E42" s="2">
         <v>12</v>
       </c>
     </row>
     <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
+      <c r="A43" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="B43" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="C43" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D43" s="5">
-        <v>5</v>
-      </c>
-      <c r="E43" s="5">
+      <c r="D43" s="3">
+        <v>5</v>
+      </c>
+      <c r="E43" s="3">
         <v>12</v>
       </c>
     </row>
     <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
+      <c r="A44" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B44" s="5" t="s">
+      <c r="B44" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C44" s="5" t="s">
+      <c r="C44" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D44" s="5">
-        <v>5</v>
-      </c>
-      <c r="E44" s="5">
+      <c r="D44" s="3">
+        <v>5</v>
+      </c>
+      <c r="E44" s="3">
         <v>12</v>
       </c>
     </row>
     <row r="45" spans="1:5">
-      <c r="A45" s="2" t="s">
+      <c r="A45" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C45" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D45" s="2">
-        <v>5</v>
-      </c>
-      <c r="E45" s="2">
+      <c r="C45" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D45" s="1">
+        <v>5</v>
+      </c>
+      <c r="E45" s="1">
         <v>15</v>
       </c>
     </row>
     <row r="46" spans="1:5">
-      <c r="A46" s="4" t="s">
+      <c r="A46" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C46" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D46" s="4">
-        <v>5</v>
-      </c>
-      <c r="E46" s="4">
+      <c r="C46" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D46" s="2">
+        <v>5</v>
+      </c>
+      <c r="E46" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:5">
-      <c r="A47" s="4" t="s">
+      <c r="A47" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="B47" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C47" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D47" s="4">
-        <v>5</v>
-      </c>
-      <c r="E47" s="4">
+      <c r="C47" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D47" s="2">
+        <v>5</v>
+      </c>
+      <c r="E47" s="2">
         <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:5">
-      <c r="A48" s="4" t="s">
+      <c r="A48" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B48" s="4" t="s">
+      <c r="B48" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C48" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D48" s="4">
-        <v>5</v>
-      </c>
-      <c r="E48" s="4">
+      <c r="C48" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D48" s="2">
+        <v>5</v>
+      </c>
+      <c r="E48" s="2">
         <v>11</v>
       </c>
     </row>
     <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
+      <c r="A49" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B49" s="5" t="s">
+      <c r="B49" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C49" s="5" t="s">
+      <c r="C49" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D49" s="5">
+      <c r="D49" s="3">
         <v>6</v>
       </c>
-      <c r="E49" s="5">
+      <c r="E49" s="3">
         <v>12</v>
       </c>
     </row>
     <row r="50" spans="1:5">
-      <c r="A50" s="4" t="s">
+      <c r="A50" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B50" s="4" t="s">
+      <c r="B50" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C50" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D50" s="4">
+      <c r="C50" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D50" s="2">
         <v>6</v>
       </c>
-      <c r="E50" s="4">
+      <c r="E50" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="51" spans="1:5">
-      <c r="A51" s="4" t="s">
+      <c r="A51" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B51" s="4" t="s">
+      <c r="B51" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C51" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D51" s="4">
+      <c r="C51" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D51" s="2">
         <v>6</v>
       </c>
-      <c r="E51" s="4">
+      <c r="E51" s="2">
         <v>10</v>
       </c>
     </row>
     <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
+      <c r="A52" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B52" s="5" t="s">
+      <c r="B52" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C52" s="5" t="s">
+      <c r="C52" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D52" s="5">
+      <c r="D52" s="3">
         <v>7</v>
       </c>
-      <c r="E52" s="5">
+      <c r="E52" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
+      <c r="A53" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B53" s="5" t="s">
+      <c r="B53" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C53" s="5" t="s">
+      <c r="C53" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D53" s="5">
+      <c r="D53" s="3">
         <v>7</v>
       </c>
-      <c r="E53" s="5">
+      <c r="E53" s="3">
         <v>8</v>
       </c>
     </row>
     <row r="54" spans="1:5">
-      <c r="A54" s="4" t="s">
+      <c r="A54" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B54" s="4" t="s">
+      <c r="B54" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C54" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D54" s="4">
+      <c r="C54" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D54" s="2">
         <v>7</v>
       </c>
-      <c r="E54" s="4">
+      <c r="E54" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:5">
-      <c r="A55" s="4" t="s">
+      <c r="A55" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B55" s="4" t="s">
+      <c r="B55" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C55" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D55" s="4">
+      <c r="C55" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D55" s="2">
         <v>7</v>
       </c>
-      <c r="E55" s="4">
+      <c r="E55" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="56" spans="1:5">
-      <c r="A56" s="4" t="s">
+      <c r="A56" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="B56" s="4" t="s">
+      <c r="B56" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C56" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D56" s="4">
+      <c r="C56" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D56" s="2">
         <v>7</v>
       </c>
-      <c r="E56" s="4">
+      <c r="E56" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="57" spans="1:5">
-      <c r="A57" s="4" t="s">
+      <c r="A57" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B57" s="4" t="s">
+      <c r="B57" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C57" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D57" s="4">
+      <c r="C57" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D57" s="2">
         <v>7</v>
       </c>
-      <c r="E57" s="4">
+      <c r="E57" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:5">
-      <c r="A58" s="4" t="s">
+      <c r="A58" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B58" s="4" t="s">
+      <c r="B58" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C58" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D58" s="4">
+      <c r="C58" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D58" s="2">
         <v>7</v>
       </c>
-      <c r="E58" s="4">
+      <c r="E58" s="2">
         <v>12</v>
       </c>
     </row>
     <row r="59" spans="1:5">
-      <c r="A59" s="2"/>
-      <c r="B59" s="2"/>
-      <c r="C59" s="2"/>
-      <c r="D59" s="2"/>
-      <c r="E59" s="2"/>
+      <c r="A59" s="1"/>
+      <c r="B59" s="1"/>
+      <c r="C59" s="1"/>
+      <c r="D59" s="1"/>
+      <c r="E59" s="1"/>
     </row>
     <row r="60" spans="1:5">
-      <c r="A60" s="2"/>
-      <c r="B60" s="2"/>
-      <c r="C60" s="2"/>
-      <c r="D60" s="2"/>
-      <c r="E60" s="2"/>
+      <c r="A60" s="1"/>
+      <c r="B60" s="1"/>
+      <c r="C60" s="1"/>
+      <c r="D60" s="1"/>
+      <c r="E60" s="1"/>
     </row>
     <row r="61" spans="1:5">
-      <c r="A61" s="2"/>
-      <c r="B61" s="2"/>
-      <c r="C61" s="2"/>
-      <c r="D61" s="2"/>
-      <c r="E61" s="2"/>
+      <c r="A61" s="1"/>
+      <c r="B61" s="1"/>
+      <c r="C61" s="1"/>
+      <c r="D61" s="1"/>
+      <c r="E61" s="1"/>
     </row>
     <row r="62" spans="1:5">
-      <c r="A62" s="2"/>
-      <c r="B62" s="2"/>
-      <c r="C62" s="2"/>
-      <c r="D62" s="2"/>
-      <c r="E62" s="2"/>
+      <c r="A62" s="1"/>
+      <c r="B62" s="1"/>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
     </row>
     <row r="63" spans="1:5">
-      <c r="A63" s="2"/>
-      <c r="B63" s="2"/>
-      <c r="C63" s="2"/>
-      <c r="D63" s="2"/>
-      <c r="E63" s="2"/>
+      <c r="A63" s="1"/>
+      <c r="B63" s="1"/>
+      <c r="C63" s="1"/>
+      <c r="D63" s="1"/>
+      <c r="E63" s="1"/>
     </row>
     <row r="64" spans="1:5">
-      <c r="A64" s="2" t="s">
+      <c r="A64" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B64" s="2"/>
-      <c r="C64" s="2"/>
-      <c r="D64" s="2"/>
-      <c r="E64" s="2"/>
+      <c r="B64" s="1"/>
+      <c r="C64" s="1"/>
+      <c r="D64" s="1"/>
+      <c r="E64" s="1"/>
     </row>
     <row r="65" spans="1:5">
-      <c r="A65" s="2"/>
-      <c r="B65" s="2"/>
-      <c r="C65" s="2"/>
-      <c r="D65" s="2"/>
-      <c r="E65" s="2"/>
+      <c r="A65" s="1"/>
+      <c r="B65" s="1"/>
+      <c r="C65" s="1"/>
+      <c r="D65" s="1"/>
+      <c r="E65" s="1"/>
     </row>
     <row r="66" spans="1:5">
-      <c r="A66" s="2" t="s">
+      <c r="A66" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B66" s="2"/>
-      <c r="C66" s="2" t="s">
+      <c r="B66" s="1"/>
+      <c r="C66" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="D66" s="2"/>
-      <c r="E66" s="2">
+      <c r="D66" s="1"/>
+      <c r="E66" s="1">
         <f>SUM(E2:E58)</f>
         <v>360</v>
       </c>
@@ -4632,6 +5104,1589 @@
   <sortState ref="A2:E58">
     <sortCondition ref="D2"/>
   </sortState>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E104"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="10.625" customWidth="1"/>
+    <col min="2" max="2" width="18.5" customWidth="1"/>
+    <col min="3" max="3" width="12.125" customWidth="1"/>
+    <col min="4" max="4" width="11.125" customWidth="1"/>
+    <col min="5" max="5" width="158.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B5" t="s">
+        <v>136</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>102</v>
+      </c>
+      <c r="B8" t="s">
+        <v>140</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8">
+        <v>4</v>
+      </c>
+      <c r="E8" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>102</v>
+      </c>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9">
+        <v>5</v>
+      </c>
+      <c r="E9" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>102</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10">
+        <v>2</v>
+      </c>
+      <c r="E10" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>102</v>
+      </c>
+      <c r="B11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11">
+        <v>3</v>
+      </c>
+      <c r="E11" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>102</v>
+      </c>
+      <c r="B12" t="s">
+        <v>113</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12">
+        <v>3</v>
+      </c>
+      <c r="E12" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>102</v>
+      </c>
+      <c r="B13" t="s">
+        <v>116</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13">
+        <v>4</v>
+      </c>
+      <c r="E13" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>102</v>
+      </c>
+      <c r="B14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14">
+        <v>4</v>
+      </c>
+      <c r="E14" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15">
+        <v>6</v>
+      </c>
+      <c r="E15" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>102</v>
+      </c>
+      <c r="B16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16">
+        <v>6</v>
+      </c>
+      <c r="E16" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
+        <v>102</v>
+      </c>
+      <c r="B17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17">
+        <v>3</v>
+      </c>
+      <c r="E17" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
+        <v>102</v>
+      </c>
+      <c r="B18" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18">
+        <v>4</v>
+      </c>
+      <c r="E18" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
+        <v>102</v>
+      </c>
+      <c r="B19" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19">
+        <v>4</v>
+      </c>
+      <c r="E19" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
+        <v>102</v>
+      </c>
+      <c r="B20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20">
+        <v>6</v>
+      </c>
+      <c r="E20" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
+        <v>100</v>
+      </c>
+      <c r="B23" t="s">
+        <v>154</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D23">
+        <v>2</v>
+      </c>
+      <c r="E23" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
+        <v>100</v>
+      </c>
+      <c r="B24" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D24">
+        <v>2</v>
+      </c>
+      <c r="E24" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" t="s">
+        <v>100</v>
+      </c>
+      <c r="B25" t="s">
+        <v>157</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D25">
+        <v>3</v>
+      </c>
+      <c r="E25" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" t="s">
+        <v>100</v>
+      </c>
+      <c r="B26" t="s">
+        <v>159</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D26">
+        <v>4</v>
+      </c>
+      <c r="E26" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" t="s">
+        <v>100</v>
+      </c>
+      <c r="B27" t="s">
+        <v>161</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D27">
+        <v>5</v>
+      </c>
+      <c r="E27" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" t="s">
+        <v>100</v>
+      </c>
+      <c r="B28" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28">
+        <v>1</v>
+      </c>
+      <c r="E28" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" t="s">
+        <v>100</v>
+      </c>
+      <c r="B29" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29">
+        <v>2</v>
+      </c>
+      <c r="E29" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" t="s">
+        <v>100</v>
+      </c>
+      <c r="B30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30">
+        <v>2</v>
+      </c>
+      <c r="E30" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B31" t="s">
+        <v>166</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31">
+        <v>3</v>
+      </c>
+      <c r="E31" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" t="s">
+        <v>100</v>
+      </c>
+      <c r="B32" t="s">
+        <v>21</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32">
+        <v>3</v>
+      </c>
+      <c r="E32" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" t="s">
+        <v>100</v>
+      </c>
+      <c r="B33" t="s">
+        <v>169</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33">
+        <v>4</v>
+      </c>
+      <c r="E33" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" t="s">
+        <v>100</v>
+      </c>
+      <c r="B34" t="s">
+        <v>23</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34">
+        <v>4</v>
+      </c>
+      <c r="E34" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" t="s">
+        <v>100</v>
+      </c>
+      <c r="B35" t="s">
+        <v>119</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D35">
+        <v>4</v>
+      </c>
+      <c r="E35" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" t="s">
+        <v>100</v>
+      </c>
+      <c r="B36" t="s">
+        <v>41</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D36">
+        <v>5</v>
+      </c>
+      <c r="E36" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" t="s">
+        <v>100</v>
+      </c>
+      <c r="B37" t="s">
+        <v>27</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D37">
+        <v>7</v>
+      </c>
+      <c r="E37" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" t="s">
+        <v>100</v>
+      </c>
+      <c r="B38" t="s">
+        <v>34</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D38">
+        <v>5</v>
+      </c>
+      <c r="E38" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" t="s">
+        <v>100</v>
+      </c>
+      <c r="B39" t="s">
+        <v>176</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D39">
+        <v>6</v>
+      </c>
+      <c r="E39" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" t="s">
+        <v>178</v>
+      </c>
+      <c r="B42" t="s">
+        <v>179</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D42">
+        <v>2</v>
+      </c>
+      <c r="E42" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" t="s">
+        <v>178</v>
+      </c>
+      <c r="B43" t="s">
+        <v>181</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D43">
+        <v>2</v>
+      </c>
+      <c r="E43" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" t="s">
+        <v>178</v>
+      </c>
+      <c r="B44" t="s">
+        <v>183</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D44">
+        <v>2</v>
+      </c>
+      <c r="E44" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" t="s">
+        <v>178</v>
+      </c>
+      <c r="B45" t="s">
+        <v>55</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D45">
+        <v>3</v>
+      </c>
+      <c r="E45" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" t="s">
+        <v>178</v>
+      </c>
+      <c r="B46" t="s">
+        <v>186</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D46">
+        <v>3</v>
+      </c>
+      <c r="E46" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" t="s">
+        <v>178</v>
+      </c>
+      <c r="B47" t="s">
+        <v>56</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D47">
+        <v>4</v>
+      </c>
+      <c r="E47" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" t="s">
+        <v>178</v>
+      </c>
+      <c r="B48" t="s">
+        <v>189</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D48">
+        <v>2</v>
+      </c>
+      <c r="E48" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" t="s">
+        <v>178</v>
+      </c>
+      <c r="B49" t="s">
+        <v>48</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D49">
+        <v>3</v>
+      </c>
+      <c r="E49" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" t="s">
+        <v>178</v>
+      </c>
+      <c r="B50" t="s">
+        <v>192</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D50">
+        <v>4</v>
+      </c>
+      <c r="E50" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" t="s">
+        <v>178</v>
+      </c>
+      <c r="B51" t="s">
+        <v>194</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D51">
+        <v>4</v>
+      </c>
+      <c r="E51" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" t="s">
+        <v>178</v>
+      </c>
+      <c r="B52" t="s">
+        <v>196</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D52">
+        <v>5</v>
+      </c>
+      <c r="E52" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" t="s">
+        <v>178</v>
+      </c>
+      <c r="B53" t="s">
+        <v>58</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D53">
+        <v>4</v>
+      </c>
+      <c r="E53" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" t="s">
+        <v>199</v>
+      </c>
+      <c r="B56" t="s">
+        <v>200</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D56">
+        <v>2</v>
+      </c>
+      <c r="E56" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" t="s">
+        <v>199</v>
+      </c>
+      <c r="B57" t="s">
+        <v>202</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D57">
+        <v>2</v>
+      </c>
+      <c r="E57" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" t="s">
+        <v>199</v>
+      </c>
+      <c r="B58" t="s">
+        <v>204</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D58">
+        <v>2</v>
+      </c>
+      <c r="E58" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" t="s">
+        <v>199</v>
+      </c>
+      <c r="B59" t="s">
+        <v>206</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D59">
+        <v>2</v>
+      </c>
+      <c r="E59" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" t="s">
+        <v>199</v>
+      </c>
+      <c r="B60" t="s">
+        <v>2